--- a/model_results/model_results.xlsx
+++ b/model_results/model_results.xlsx
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="B189">
-        <v>6.146645332423043</v>
+        <v>5.84166090482096</v>
       </c>
       <c r="C189">
-        <v>1.480598783889802</v>
+        <v>1.514488689807316</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="E189">
-        <v>3.833552711608355</v>
+        <v>3.51444532920237</v>
       </c>
       <c r="F189">
-        <v>9.855413942318528</v>
+        <v>9.709925444951672</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="B190">
-        <v>5.311508275787451</v>
+        <v>4.53605086162661</v>
       </c>
       <c r="C190">
-        <v>1.151739292663612</v>
+        <v>1.088038392145243</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -7774,10 +7774,10 @@
         </is>
       </c>
       <c r="E190">
-        <v>3.472518977346656</v>
+        <v>2.834684500418442</v>
       </c>
       <c r="F190">
-        <v>8.124396251770929</v>
+        <v>7.258570545055795</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="B191">
-        <v>2.054753364466226</v>
+        <v>1.720509140818544</v>
       </c>
       <c r="C191">
-        <v>0.2372053502968635</v>
+        <v>0.2256817413569948</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="E191">
-        <v>1.638683494805752</v>
+        <v>1.330465485359423</v>
       </c>
       <c r="F191">
-        <v>2.57646543836444</v>
+        <v>2.22489928240452</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="B192">
-        <v>2.449489740315184</v>
+        <v>2.056493871381721</v>
       </c>
       <c r="C192">
-        <v>0.4380705632667217</v>
+        <v>0.4188011668143977</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -7852,10 +7852,10 @@
         </is>
       </c>
       <c r="E192">
-        <v>1.725223693632731</v>
+        <v>1.37969090798642</v>
       </c>
       <c r="F192">
-        <v>3.47780986897728</v>
+        <v>3.065300364414813</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -7880,10 +7880,10 @@
         </is>
       </c>
       <c r="B193">
-        <v>0.5454545588891426</v>
+        <v>0.1363636226626829</v>
       </c>
       <c r="C193">
-        <v>0.2490485152163013</v>
+        <v>0.1089787883890302</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -7891,10 +7891,10 @@
         </is>
       </c>
       <c r="E193">
-        <v>0.2228996421585102</v>
+        <v>0.02847325391198408</v>
       </c>
       <c r="F193">
-        <v>1.334774129432535</v>
+        <v>0.6530703390336473</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="B194">
-        <v>3.197220996514368</v>
+        <v>2.193741096866725</v>
       </c>
       <c r="C194">
-        <v>0.554371922097976</v>
+        <v>0.458333944045822</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="E194">
-        <v>2.276047302774105</v>
+        <v>1.456617534562295</v>
       </c>
       <c r="F194">
-        <v>4.491216895225868</v>
+        <v>3.303887181014988</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="B195">
-        <v>3.491059997134517</v>
+        <v>3.316624790264727</v>
       </c>
       <c r="C195">
-        <v>0.5922801924195055</v>
+        <v>0.6362100051893401</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="E195">
-        <v>2.503488725578003</v>
+        <v>2.277272507390442</v>
       </c>
       <c r="F195">
-        <v>4.868206426924897</v>
+        <v>4.830339787487093</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="B196">
-        <v>9.52138123464665</v>
+        <v>9.182384248003226</v>
       </c>
       <c r="C196">
-        <v>1.288448241356991</v>
+        <v>1.288041080301433</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         </is>
       </c>
       <c r="E196">
-        <v>7.303214003326709</v>
+        <v>6.975170412599903</v>
       </c>
       <c r="F196">
-        <v>12.41326087037653</v>
+        <v>12.08804595306654</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -8041,10 +8041,10 @@
         </is>
       </c>
       <c r="B197">
-        <v>10.66772929059595</v>
+        <v>10.45187161037223</v>
       </c>
       <c r="C197">
-        <v>3.471788148254209</v>
+        <v>3.522748966564482</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="E197">
-        <v>5.637030529871992</v>
+        <v>5.398846915165278</v>
       </c>
       <c r="F197">
-        <v>20.1880134610559</v>
+        <v>20.23425036424852</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -8080,10 +8080,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>11.78805898922008</v>
+        <v>11.11555466559428</v>
       </c>
       <c r="C198">
-        <v>1.477189261086419</v>
+        <v>1.585382277873384</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="E198">
-        <v>9.220962225483291</v>
+        <v>8.404783004066294</v>
       </c>
       <c r="F198">
-        <v>15.06983016905802</v>
+        <v>14.70062409273834</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -8119,10 +8119,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>11.04988667994102</v>
+        <v>10.09950493520196</v>
       </c>
       <c r="C199">
-        <v>1.492987696269583</v>
+        <v>1.555710833083208</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="E199">
-        <v>8.47908706000378</v>
+        <v>7.467623693678135</v>
       </c>
       <c r="F199">
-        <v>14.40013468141976</v>
+        <v>13.658963563271</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>1.309307372292669</v>
+        <v>0.6998542078035632</v>
       </c>
       <c r="C200">
-        <v>0.3526333048347243</v>
+        <v>0.2680345004404795</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="E200">
-        <v>0.7723054405160464</v>
+        <v>0.3303764920214332</v>
       </c>
       <c r="F200">
-        <v>2.219699234534028</v>
+        <v>1.482538630952524</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -8197,10 +8197,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>6.546536811752951</v>
+        <v>6.220166894968601</v>
       </c>
       <c r="C201">
-        <v>0.9516375174007795</v>
+        <v>1.151231230646866</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="E201">
-        <v>4.923531000725105</v>
+        <v>4.32774118755468</v>
       </c>
       <c r="F201">
-        <v>8.704554560807026</v>
+        <v>8.940108598112532</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -8236,10 +8236,10 @@
         </is>
       </c>
       <c r="B202">
-        <v>39.65217391304443</v>
+        <v>38.86956521738531</v>
       </c>
       <c r="C202">
-        <v>2.006204894343777</v>
+        <v>2.041034547926021</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="E202">
-        <v>35.9087586899842</v>
+        <v>35.06818009052157</v>
       </c>
       <c r="F202">
-        <v>43.78583257652044</v>
+        <v>43.08301988550954</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="B203">
-        <v>4.490293745602023</v>
+        <v>3.914066374975572</v>
       </c>
       <c r="C203">
-        <v>1.792093416218886</v>
+        <v>1.553528110041802</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -8291,10 +8291,10 @@
         </is>
       </c>
       <c r="E203">
-        <v>2.053794372345809</v>
+        <v>1.797954288995814</v>
       </c>
       <c r="F203">
-        <v>9.817310921328074</v>
+        <v>8.520748097700986</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -8319,10 +8319,10 @@
         </is>
       </c>
       <c r="B204">
-        <v>0.3542638036322032</v>
+        <v>0.4059262331696555</v>
       </c>
       <c r="C204">
-        <v>0.2587852538640231</v>
+        <v>0.3145633672531774</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="E204">
-        <v>0.08463202985613621</v>
+        <v>0.08888484219326316</v>
       </c>
       <c r="F204">
-        <v>1.482923696587394</v>
+        <v>1.853815596781184</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -8358,10 +8358,10 @@
         </is>
       </c>
       <c r="B205">
-        <v>2.291287831922499</v>
+        <v>1.684024159284263</v>
       </c>
       <c r="C205">
-        <v>0.4357938127739558</v>
+        <v>0.3813254165666463</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -8369,10 +8369,10 @@
         </is>
       </c>
       <c r="E205">
-        <v>1.57828165309925</v>
+        <v>1.080450250726844</v>
       </c>
       <c r="F205">
-        <v>3.326402431661518</v>
+        <v>2.624773669259892</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="B206">
-        <v>1.999999999732259</v>
+        <v>1.540540538051047</v>
       </c>
       <c r="C206">
-        <v>0.5281112773290084</v>
+        <v>0.5530044594666824</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -8413,10 +8413,10 @@
         </is>
       </c>
       <c r="E206">
-        <v>1.191970283830061</v>
+        <v>0.7622881684734613</v>
       </c>
       <c r="F206">
-        <v>3.355788355793704</v>
+        <v>3.113343808196904</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -8441,10 +8441,10 @@
         </is>
       </c>
       <c r="B207">
-        <v>1.343749993694977</v>
+        <v>1.312500005668109</v>
       </c>
       <c r="C207">
-        <v>0.399188270436835</v>
+        <v>0.5125751472504119</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -8452,10 +8452,10 @@
         </is>
       </c>
       <c r="E207">
-        <v>0.7506746350630893</v>
+        <v>0.6104873142797276</v>
       </c>
       <c r="F207">
-        <v>2.405388381616884</v>
+        <v>2.821772417844965</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -8480,10 +8480,10 @@
         </is>
       </c>
       <c r="B208">
-        <v>2.327373342689325</v>
+        <v>2.14087210029766</v>
       </c>
       <c r="C208">
-        <v>0.974551601471259</v>
+        <v>0.9865461280081222</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -8491,10 +8491,10 @@
         </is>
       </c>
       <c r="E208">
-        <v>1.024326882962736</v>
+        <v>0.8676493050921001</v>
       </c>
       <c r="F208">
-        <v>5.288025498846477</v>
+        <v>5.282472218826244</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="B209">
-        <v>1.640118968993126E-05</v>
+        <v>1.5081003868597E-05</v>
       </c>
       <c r="C209">
-        <v>0.166666659846385</v>
+        <v>0.1666666542988409</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="B210">
-        <v>1.527525156346855</v>
+        <v>0.9428089864056949</v>
       </c>
       <c r="C210">
-        <v>0.3353384947933306</v>
+        <v>0.2547829739326646</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="E210">
-        <v>0.9933987209547183</v>
+        <v>0.5551323893692843</v>
       </c>
       <c r="F210">
-        <v>2.348838441255494</v>
+        <v>1.601219460203444</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -8599,10 +8599,10 @@
         </is>
       </c>
       <c r="B211">
-        <v>2.261335107135777</v>
+        <v>1.82574197112222</v>
       </c>
       <c r="C211">
-        <v>0.3641575667292329</v>
+        <v>0.3272056449330704</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -8610,10 +8610,10 @@
         </is>
       </c>
       <c r="E211">
-        <v>1.649264759626041</v>
+        <v>1.284957740972649</v>
       </c>
       <c r="F211">
-        <v>3.100555224331753</v>
+        <v>2.594119354146294</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="B212">
-        <v>8.714297567511311</v>
+        <v>8.642856676988989</v>
       </c>
       <c r="C212">
-        <v>0.8281161741376144</v>
+        <v>0.8594463322729402</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="E212">
-        <v>7.233409417715399</v>
+        <v>7.112360549112898</v>
       </c>
       <c r="F212">
-        <v>10.49836635945849</v>
+        <v>10.50269752540738</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -8677,10 +8677,10 @@
         </is>
       </c>
       <c r="B213">
-        <v>5.000007528658325</v>
+        <v>5.000000859024079</v>
       </c>
       <c r="C213">
-        <v>1.028773949394598</v>
+        <v>1.055306006798526</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         </is>
       </c>
       <c r="E213">
-        <v>3.340658848528288</v>
+        <v>3.306088610953972</v>
       </c>
       <c r="F213">
-        <v>7.483576270487363</v>
+        <v>7.56180838813869</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -8716,10 +8716,10 @@
         </is>
       </c>
       <c r="B214">
-        <v>9.776670054010829</v>
+        <v>9.560354684462073</v>
       </c>
       <c r="C214">
-        <v>0.6006335388838961</v>
+        <v>0.6002500473295731</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -8727,10 +8727,10 @@
         </is>
       </c>
       <c r="E214">
-        <v>8.667564054767579</v>
+        <v>8.45339247284196</v>
       </c>
       <c r="F214">
-        <v>11.02769783309726</v>
+        <v>10.81227234939772</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="B215">
-        <v>6.771148099562557</v>
+        <v>6.694638656154042</v>
       </c>
       <c r="C215">
-        <v>0.9980937052244889</v>
+        <v>1.005601169198564</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -8766,10 +8766,10 @@
         </is>
       </c>
       <c r="E215">
-        <v>5.07214753105696</v>
+        <v>4.987331328192739</v>
       </c>
       <c r="F215">
-        <v>9.039257297915285</v>
+        <v>8.986406514265571</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -8794,10 +8794,10 @@
         </is>
       </c>
       <c r="B216">
-        <v>11.77746981830113</v>
+        <v>11.67948694549936</v>
       </c>
       <c r="C216">
-        <v>0.9180272413728101</v>
+        <v>0.9146656678018618</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="E216">
-        <v>10.10887338912219</v>
+        <v>10.01758162540351</v>
       </c>
       <c r="F216">
-        <v>13.72148903064251</v>
+        <v>13.61710045508067</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="B217">
-        <v>15.27786932047462</v>
+        <v>15.22920508852685</v>
       </c>
       <c r="C217">
-        <v>1.931712960834543</v>
+        <v>1.933986222964385</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="E217">
-        <v>11.92444098900092</v>
+        <v>11.87357511957689</v>
       </c>
       <c r="F217">
-        <v>19.57435918285811</v>
+        <v>19.53318063790352</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -8872,10 +8872,10 @@
         </is>
       </c>
       <c r="B218">
-        <v>10.56673145066133</v>
+        <v>9.882979752791137</v>
       </c>
       <c r="C218">
-        <v>1.371731578550474</v>
+        <v>1.332290712494709</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="E218">
-        <v>8.192963662836863</v>
+        <v>7.588227374845535</v>
       </c>
       <c r="F218">
-        <v>13.62825689766747</v>
+        <v>12.87168715026383</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="B219">
-        <v>7.776549189349026</v>
+        <v>7.508436917704992</v>
       </c>
       <c r="C219">
-        <v>1.329357227898847</v>
+        <v>1.338471954666383</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="E219">
-        <v>5.562612661107145</v>
+        <v>5.294345873714186</v>
       </c>
       <c r="F219">
-        <v>10.8716390981515</v>
+        <v>10.64845899605061</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="B220">
-        <v>7.957691574235427</v>
+        <v>7.335700375461917</v>
       </c>
       <c r="C220">
-        <v>1.682407159766591</v>
+        <v>1.606007242384282</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -8961,10 +8961,10 @@
         </is>
       </c>
       <c r="E220">
-        <v>5.258076826602047</v>
+        <v>4.776257765403543</v>
       </c>
       <c r="F220">
-        <v>12.04334917098962</v>
+        <v>11.266665796042</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="B221">
-        <v>1.891101606507347</v>
+        <v>0.9748115362599685</v>
       </c>
       <c r="C221">
-        <v>0.2217342296980927</v>
+        <v>0.2184869289956672</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -9005,10 +9005,10 @@
         </is>
       </c>
       <c r="E221">
-        <v>1.502831631522509</v>
+        <v>0.6282590389987188</v>
       </c>
       <c r="F221">
-        <v>2.37968459747655</v>
+        <v>1.512525044987785</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="B222">
-        <v>0.2496740862832052</v>
+        <v>0.2431213935569062</v>
       </c>
       <c r="C222">
-        <v>0.1504922164314485</v>
+        <v>0.1757846786878113</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -9044,10 +9044,10 @@
         </is>
       </c>
       <c r="E222">
-        <v>0.07661393716016339</v>
+        <v>0.05893547154246252</v>
       </c>
       <c r="F222">
-        <v>0.8136528635910719</v>
+        <v>1.002927616562214</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -22823,10 +22823,10 @@
         </is>
       </c>
       <c r="C313">
-        <v>3.874999914773325</v>
+        <v>3.500000122208655</v>
       </c>
       <c r="D313">
-        <v>1.374201520175102</v>
+        <v>1.336774543579652</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -22834,10 +22834,10 @@
         </is>
       </c>
       <c r="F313">
-        <v>1.933783415790542</v>
+        <v>1.655632383585808</v>
       </c>
       <c r="G313">
-        <v>7.764894567241286</v>
+        <v>7.398986017010161</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -22867,10 +22867,10 @@
         </is>
       </c>
       <c r="C314">
-        <v>1.727272690547183</v>
+        <v>1.272727299690979</v>
       </c>
       <c r="D314">
-        <v>0.5999286736719442</v>
+        <v>0.4954577212507574</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -22878,10 +22878,10 @@
         </is>
       </c>
       <c r="F314">
-        <v>0.8744108017457726</v>
+        <v>0.593434296520559</v>
       </c>
       <c r="G314">
-        <v>3.4119786049687</v>
+        <v>2.729594141889259</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -22911,10 +22911,10 @@
         </is>
       </c>
       <c r="C315">
-        <v>9.749999915756916</v>
+        <v>9.750000267251211</v>
       </c>
       <c r="D315">
-        <v>3.179258971916416</v>
+        <v>3.419193110705273</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -22922,10 +22922,10 @@
         </is>
       </c>
       <c r="F315">
-        <v>5.145725869668735</v>
+        <v>4.903427618375068</v>
       </c>
       <c r="G315">
-        <v>18.47406969687246</v>
+        <v>19.38694982570196</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -22955,10 +22955,10 @@
         </is>
       </c>
       <c r="C316">
-        <v>16.33333307366845</v>
+        <v>16.16666620120379</v>
       </c>
       <c r="D316">
-        <v>4.241623438752752</v>
+        <v>4.53229121310076</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -22966,10 +22966,10 @@
         </is>
       </c>
       <c r="F316">
-        <v>9.81804997439348</v>
+        <v>9.33228279738263</v>
       </c>
       <c r="G316">
-        <v>27.17217471811373</v>
+        <v>28.00612687545722</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -22999,10 +22999,10 @@
         </is>
       </c>
       <c r="C317">
-        <v>2.617647055198426</v>
+        <v>2.294117638143245</v>
       </c>
       <c r="D317">
-        <v>0.3861580071798363</v>
+        <v>0.381173788597688</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -23010,10 +23010,10 @@
         </is>
       </c>
       <c r="F317">
-        <v>1.960383122738111</v>
+        <v>1.656480273107439</v>
       </c>
       <c r="G317">
-        <v>3.495273972782698</v>
+        <v>3.177203992756866</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -23043,10 +23043,10 @@
         </is>
       </c>
       <c r="C318">
-        <v>2.250000009660818</v>
+        <v>1.750000106439604</v>
       </c>
       <c r="D318">
-        <v>0.5817985089270231</v>
+        <v>0.5235785077005235</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -23054,10 +23054,10 @@
         </is>
       </c>
       <c r="F318">
-        <v>1.355443070126434</v>
+        <v>0.9735741692662817</v>
       </c>
       <c r="G318">
-        <v>3.734941108962589</v>
+        <v>3.14562615691276</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -23087,10 +23087,10 @@
         </is>
       </c>
       <c r="C319">
-        <v>1.61290322941006</v>
+        <v>1.290322542498726</v>
       </c>
       <c r="D319">
-        <v>0.2864672100720093</v>
+        <v>0.2619612900309782</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -23098,10 +23098,10 @@
         </is>
       </c>
       <c r="F319">
-        <v>1.138745533122301</v>
+        <v>0.8667370118661217</v>
       </c>
       <c r="G319">
-        <v>2.284493551696775</v>
+        <v>1.920919772533662</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -23131,10 +23131,10 @@
         </is>
       </c>
       <c r="C320">
-        <v>2.666666649843184</v>
+        <v>2.41666673474373</v>
       </c>
       <c r="D320">
-        <v>0.6590233085928521</v>
+        <v>0.6678793794301675</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -23142,10 +23142,10 @@
         </is>
       </c>
       <c r="F320">
-        <v>1.642888564694385</v>
+        <v>1.405967910622734</v>
       </c>
       <c r="G320">
-        <v>4.328419574037696</v>
+        <v>4.153919917155245</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -23175,10 +23175,10 @@
         </is>
       </c>
       <c r="C321">
-        <v>0.5454545588891426</v>
+        <v>0.1363636226626829</v>
       </c>
       <c r="D321">
-        <v>0.2490485152163013</v>
+        <v>0.1089787883890302</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -23186,10 +23186,10 @@
         </is>
       </c>
       <c r="F321">
-        <v>0.2228996421585102</v>
+        <v>0.02847325391198408</v>
       </c>
       <c r="G321">
-        <v>1.334774129432535</v>
+        <v>0.6530703390336473</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -23224,10 +23224,10 @@
         </is>
       </c>
       <c r="C322">
-        <v>2.666666650986831</v>
+        <v>1.750000000070083</v>
       </c>
       <c r="D322">
-        <v>0.6792669046027803</v>
+        <v>0.542104212838403</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -23235,10 +23235,10 @@
         </is>
       </c>
       <c r="F322">
-        <v>1.61862535601265</v>
+        <v>0.9535820810125942</v>
       </c>
       <c r="G322">
-        <v>4.393302626250065</v>
+        <v>3.21157461032958</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -23268,10 +23268,10 @@
         </is>
       </c>
       <c r="C323">
-        <v>3.74999997012075</v>
+        <v>3.666666666517465</v>
       </c>
       <c r="D323">
-        <v>0.8862789364677992</v>
+        <v>0.9774816886368136</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -23279,10 +23279,10 @@
         </is>
       </c>
       <c r="F323">
-        <v>2.359703281121692</v>
+        <v>2.174468336607303</v>
       </c>
       <c r="G323">
-        <v>5.959435615659684</v>
+        <v>6.182865124781211</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -23312,10 +23312,10 @@
         </is>
       </c>
       <c r="C324">
-        <v>3.833333310246887</v>
+        <v>2.749999999936739</v>
       </c>
       <c r="D324">
-        <v>0.9020477641334654</v>
+        <v>0.7711963499308017</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -23323,10 +23323,10 @@
         </is>
       </c>
       <c r="F324">
-        <v>2.416988319813739</v>
+        <v>1.587179180624273</v>
       </c>
       <c r="G324">
-        <v>6.079650508439678</v>
+        <v>4.76474243864361</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -23356,10 +23356,10 @@
         </is>
       </c>
       <c r="C325">
-        <v>3.250000000186776</v>
+        <v>2.999999999958041</v>
       </c>
       <c r="D325">
-        <v>0.7912658591486406</v>
+        <v>0.827687748279863</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -23367,10 +23367,10 @@
         </is>
       </c>
       <c r="F325">
-        <v>2.016714264465464</v>
+        <v>1.746940949725286</v>
       </c>
       <c r="G325">
-        <v>5.237479690269195</v>
+        <v>5.1518627467995</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -23400,10 +23400,10 @@
         </is>
       </c>
       <c r="C326">
-        <v>6.32473526458479</v>
+        <v>5.959210628669375</v>
       </c>
       <c r="D326">
-        <v>0.9472389729336865</v>
+        <v>0.928175337858707</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -23411,10 +23411,10 @@
         </is>
       </c>
       <c r="F326">
-        <v>4.715851648362715</v>
+        <v>4.391471369645444</v>
       </c>
       <c r="G326">
-        <v>8.482513689965359</v>
+        <v>8.086627084104892</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -23444,10 +23444,10 @@
         </is>
       </c>
       <c r="C327">
-        <v>9.446971637713842</v>
+        <v>9.201851044967395</v>
       </c>
       <c r="D327">
-        <v>3.301025651673998</v>
+        <v>3.336541534649199</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -23455,10 +23455,10 @@
         </is>
       </c>
       <c r="F327">
-        <v>4.762773489498986</v>
+        <v>4.520995892416614</v>
       </c>
       <c r="G327">
-        <v>18.73808891406209</v>
+        <v>18.72907312209624</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -23488,10 +23488,10 @@
         </is>
       </c>
       <c r="C328">
-        <v>14.33367513785304</v>
+        <v>14.14888409420169</v>
       </c>
       <c r="D328">
-        <v>2.073789024834618</v>
+        <v>2.126418996642482</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -23499,10 +23499,10 @@
         </is>
       </c>
       <c r="F328">
-        <v>10.79458969368425</v>
+        <v>10.53892027856271</v>
       </c>
       <c r="G328">
-        <v>19.03307571548686</v>
+        <v>18.99539192059013</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -23532,10 +23532,10 @@
         </is>
       </c>
       <c r="C329">
-        <v>12.04623582896439</v>
+        <v>11.87170055523237</v>
       </c>
       <c r="D329">
-        <v>4.224724166984597</v>
+        <v>4.322015380171029</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -23543,10 +23543,10 @@
         </is>
       </c>
       <c r="F329">
-        <v>6.057971966964755</v>
+        <v>5.815997452336045</v>
       </c>
       <c r="G329">
-        <v>23.95385756790341</v>
+        <v>24.23269185176413</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -23576,10 +23576,10 @@
         </is>
       </c>
       <c r="C330">
-        <v>11.49999980269374</v>
+        <v>10.66666666292704</v>
       </c>
       <c r="D330">
-        <v>2.043678984060334</v>
+        <v>2.159684146696155</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -23587,10 +23587,10 @@
         </is>
       </c>
       <c r="F330">
-        <v>8.117639656475342</v>
+        <v>7.172748709869228</v>
       </c>
       <c r="G330">
-        <v>16.29168096374687</v>
+        <v>15.86250715035484</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -23620,10 +23620,10 @@
         </is>
       </c>
       <c r="C331">
-        <v>10.09090894818513</v>
+        <v>9.272727269950456</v>
       </c>
       <c r="D331">
-        <v>1.902776580641593</v>
+        <v>1.988826079226043</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -23631,10 +23631,10 @@
         </is>
       </c>
       <c r="F331">
-        <v>6.973082282188653</v>
+        <v>6.090328534256707</v>
       </c>
       <c r="G331">
-        <v>14.60278816165098</v>
+        <v>14.11803493674364</v>
       </c>
       <c r="H331" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         </is>
       </c>
       <c r="C332">
-        <v>12.08333366238694</v>
+        <v>11.58333333441862</v>
       </c>
       <c r="D332">
-        <v>2.135417818086735</v>
+        <v>2.327529608797147</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -23675,10 +23675,10 @@
         </is>
       </c>
       <c r="F332">
-        <v>8.545920178738516</v>
+        <v>7.812589076203643</v>
       </c>
       <c r="G332">
-        <v>17.08498901731211</v>
+        <v>17.174026411415</v>
       </c>
       <c r="H332" t="inlineStr">
         <is>
@@ -23708,10 +23708,10 @@
         </is>
       </c>
       <c r="C333">
-        <v>12.09999973902231</v>
+        <v>10.99999999641032</v>
       </c>
       <c r="D333">
-        <v>2.342103128848036</v>
+        <v>2.432692188769625</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -23719,10 +23719,10 @@
         </is>
       </c>
       <c r="F333">
-        <v>8.279895931510101</v>
+        <v>7.13093042295735</v>
       </c>
       <c r="G333">
-        <v>17.68258863341021</v>
+        <v>16.96833270613313</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
@@ -23752,10 +23752,10 @@
         </is>
       </c>
       <c r="C334">
-        <v>1.714285764459021</v>
+        <v>1.142857136124939</v>
       </c>
       <c r="D334">
-        <v>0.5821341420942494</v>
+        <v>0.4970971323546269</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -23763,10 +23763,10 @@
         </is>
       </c>
       <c r="F334">
-        <v>0.881117236712434</v>
+        <v>0.4872516593826024</v>
       </c>
       <c r="G334">
-        <v>3.335283387704244</v>
+        <v>2.680591042515254</v>
       </c>
       <c r="H334" t="inlineStr">
         <is>
@@ -23796,10 +23796,10 @@
         </is>
       </c>
       <c r="C335">
-        <v>7.142857288553404</v>
+        <v>7.142857103034685</v>
       </c>
       <c r="D335">
-        <v>1.628509571261323</v>
+        <v>2.072538921879342</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -23807,10 +23807,10 @@
         </is>
       </c>
       <c r="F335">
-        <v>4.568834185604482</v>
+        <v>4.044745444166408</v>
       </c>
       <c r="G335">
-        <v>11.16705228773589</v>
+        <v>12.61399717204897</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
@@ -23840,10 +23840,10 @@
         </is>
       </c>
       <c r="C336">
-        <v>1.000000017897198</v>
+        <v>0.4285714256823854</v>
       </c>
       <c r="D336">
-        <v>0.418135371878614</v>
+        <v>0.2702119922651597</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="F336">
-        <v>0.4406386016144326</v>
+        <v>0.1245504182492486</v>
       </c>
       <c r="G336">
-        <v>2.26943357238914</v>
+        <v>1.474691691069777</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
@@ -23884,10 +23884,10 @@
         </is>
       </c>
       <c r="C337">
-        <v>6.000000069484247</v>
+        <v>5.416666698375564</v>
       </c>
       <c r="D337">
-        <v>1.08239598619534</v>
+        <v>1.244995737552025</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -23895,10 +23895,10 @@
         </is>
       </c>
       <c r="F337">
-        <v>4.213035011218682</v>
+        <v>3.452131917856428</v>
       </c>
       <c r="G337">
-        <v>8.544909011662222</v>
+        <v>8.499176398655539</v>
       </c>
       <c r="H337" t="inlineStr">
         <is>
@@ -23928,10 +23928,10 @@
         </is>
       </c>
       <c r="C338">
-        <v>39.65217391304443</v>
+        <v>38.86956521738531</v>
       </c>
       <c r="D338">
-        <v>2.006204894343777</v>
+        <v>2.041034547926021</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -23939,10 +23939,10 @@
         </is>
       </c>
       <c r="F338">
-        <v>35.9087586899842</v>
+        <v>35.06818009052157</v>
       </c>
       <c r="G338">
-        <v>43.78583257652044</v>
+        <v>43.08301988550954</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
@@ -23977,10 +23977,10 @@
         </is>
       </c>
       <c r="C339">
-        <v>4.490293745602023</v>
+        <v>3.914066374975572</v>
       </c>
       <c r="D339">
-        <v>1.792093416218886</v>
+        <v>1.553528110041802</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -23988,10 +23988,10 @@
         </is>
       </c>
       <c r="F339">
-        <v>2.053794372345809</v>
+        <v>1.797954288995814</v>
       </c>
       <c r="G339">
-        <v>9.817310921328074</v>
+        <v>8.520748097700986</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
@@ -24021,10 +24021,10 @@
         </is>
       </c>
       <c r="C340">
-        <v>0.3542638036322032</v>
+        <v>0.4059262331696555</v>
       </c>
       <c r="D340">
-        <v>0.2587852538640231</v>
+        <v>0.3145633672531774</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -24032,10 +24032,10 @@
         </is>
       </c>
       <c r="F340">
-        <v>0.08463202985613621</v>
+        <v>0.08888484219326316</v>
       </c>
       <c r="G340">
-        <v>1.482923696587394</v>
+        <v>1.853815596781184</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
@@ -24065,10 +24065,10 @@
         </is>
       </c>
       <c r="C341">
-        <v>2.62500009480758</v>
+        <v>2.062500019762727</v>
       </c>
       <c r="D341">
-        <v>0.5460528981946179</v>
+        <v>0.4978447662631032</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -24076,10 +24076,10 @@
         </is>
       </c>
       <c r="F341">
-        <v>1.746072432726234</v>
+        <v>1.285084091069771</v>
       </c>
       <c r="G341">
-        <v>3.946357189192381</v>
+        <v>3.310216320536715</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
@@ -24109,10 +24109,10 @@
         </is>
       </c>
       <c r="C342">
-        <v>1.999999900609888</v>
+        <v>1.374999923335429</v>
       </c>
       <c r="D342">
-        <v>0.6369480501381657</v>
+        <v>0.5268797054383634</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -24120,10 +24120,10 @@
         </is>
       </c>
       <c r="F342">
-        <v>1.071382082306633</v>
+        <v>0.6488357753231344</v>
       </c>
       <c r="G342">
-        <v>3.733494958052461</v>
+        <v>2.913872602402144</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -24153,10 +24153,10 @@
         </is>
       </c>
       <c r="C343">
-        <v>1.999999999732259</v>
+        <v>1.540540538051047</v>
       </c>
       <c r="D343">
-        <v>0.5281112773290084</v>
+        <v>0.5530044594666824</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -24164,10 +24164,10 @@
         </is>
       </c>
       <c r="F343">
-        <v>1.191970283830061</v>
+        <v>0.7622881684734613</v>
       </c>
       <c r="G343">
-        <v>3.355788355793704</v>
+        <v>3.113343808196904</v>
       </c>
       <c r="H343" t="inlineStr">
         <is>
@@ -24197,10 +24197,10 @@
         </is>
       </c>
       <c r="C344">
-        <v>1.343749993694977</v>
+        <v>1.312500005668109</v>
       </c>
       <c r="D344">
-        <v>0.399188270436835</v>
+        <v>0.5125751472504119</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -24208,10 +24208,10 @@
         </is>
       </c>
       <c r="F344">
-        <v>0.7506746350630893</v>
+        <v>0.6104873142797276</v>
       </c>
       <c r="G344">
-        <v>2.405388381616884</v>
+        <v>2.821772417844965</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
@@ -24241,10 +24241,10 @@
         </is>
       </c>
       <c r="C345">
-        <v>1.250000022721531</v>
+        <v>1.250000010198441</v>
       </c>
       <c r="D345">
-        <v>0.7724749106358192</v>
+        <v>0.8285474689054859</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -24252,10 +24252,10 @@
         </is>
       </c>
       <c r="F345">
-        <v>0.3722927352193606</v>
+        <v>0.3409583367585173</v>
       </c>
       <c r="G345">
-        <v>4.196966282146708</v>
+        <v>4.582671420651426</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
@@ -24285,10 +24285,10 @@
         </is>
       </c>
       <c r="C346">
-        <v>4.034985350721777E-10</v>
+        <v>3.411550172866216E-10</v>
       </c>
       <c r="D346">
-        <v>8.200594509854489E-06</v>
+        <v>7.540501388370758E-06</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -24331,10 +24331,10 @@
         </is>
       </c>
       <c r="C347">
-        <v>4.333333262240732</v>
+        <v>3.666666649950906</v>
       </c>
       <c r="D347">
-        <v>2.449216195183898</v>
+        <v>2.347949475408133</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -24342,10 +24342,10 @@
         </is>
       </c>
       <c r="F347">
-        <v>1.431264136181318</v>
+        <v>1.045212607381162</v>
       </c>
       <c r="G347">
-        <v>13.11971472417518</v>
+        <v>12.86287997955554</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
@@ -24375,10 +24375,10 @@
         </is>
       </c>
       <c r="C348">
-        <v>0.6666666663287618</v>
+        <v>0.6666666651821711</v>
       </c>
       <c r="D348">
-        <v>0.4062107578293595</v>
+        <v>0.4266507672891822</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -24386,10 +24386,10 @@
         </is>
       </c>
       <c r="F348">
-        <v>0.2019565320844785</v>
+        <v>0.1901779017457637</v>
       </c>
       <c r="G348">
-        <v>2.200693581963436</v>
+        <v>2.336993091128251</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
@@ -24419,10 +24419,10 @@
         </is>
       </c>
       <c r="C349">
-        <v>2.333333454438329</v>
+        <v>1.333334331788311</v>
       </c>
       <c r="D349">
-        <v>0.5932420439002026</v>
+        <v>0.4307940878062508</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -24430,10 +24430,10 @@
         </is>
       </c>
       <c r="F349">
-        <v>1.417626193543324</v>
+        <v>0.7078151003176719</v>
       </c>
       <c r="G349">
-        <v>3.840536408256426</v>
+        <v>2.511645258101307</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
@@ -24463,10 +24463,10 @@
         </is>
       </c>
       <c r="C350">
-        <v>2.272727157890901</v>
+        <v>1.818181309723375</v>
       </c>
       <c r="D350">
-        <v>0.5277785213889167</v>
+        <v>0.471427145882377</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -24474,10 +24474,10 @@
         </is>
       </c>
       <c r="F350">
-        <v>1.441713944859535</v>
+        <v>1.093788604918227</v>
       </c>
       <c r="G350">
-        <v>3.582741744735016</v>
+        <v>3.022323747169181</v>
       </c>
       <c r="H350" t="inlineStr">
         <is>
@@ -24507,10 +24507,10 @@
         </is>
       </c>
       <c r="C351">
-        <v>0.999999849500359</v>
+        <v>0.6666660894084439</v>
       </c>
       <c r="D351">
-        <v>0.357957196110153</v>
+        <v>0.2888473316640036</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -24518,10 +24518,10 @@
         </is>
       </c>
       <c r="F351">
-        <v>0.4957995988535963</v>
+        <v>0.2851721460188358</v>
       </c>
       <c r="G351">
-        <v>2.016943340238621</v>
+        <v>1.5585101173864</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
@@ -24551,10 +24551,10 @@
         </is>
       </c>
       <c r="C352">
-        <v>2.250000159064517</v>
+        <v>1.833334072510291</v>
       </c>
       <c r="D352">
-        <v>0.5021269564541941</v>
+        <v>0.4537178179006285</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -24562,10 +24562,10 @@
         </is>
       </c>
       <c r="F352">
-        <v>1.452854125791003</v>
+        <v>1.128714891185077</v>
       </c>
       <c r="G352">
-        <v>3.484521003121414</v>
+        <v>2.97782358297605</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
@@ -24595,10 +24595,10 @@
         </is>
       </c>
       <c r="C353">
-        <v>8.714297567511311</v>
+        <v>8.642856676988989</v>
       </c>
       <c r="D353">
-        <v>0.8281161741376144</v>
+        <v>0.8594463322729402</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -24606,10 +24606,10 @@
         </is>
       </c>
       <c r="F353">
-        <v>7.233409417715399</v>
+        <v>7.112360549112898</v>
       </c>
       <c r="G353">
-        <v>10.49836635945849</v>
+        <v>10.50269752540738</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
@@ -24639,10 +24639,10 @@
         </is>
       </c>
       <c r="C354">
-        <v>5.000007528658325</v>
+        <v>5.000000859024079</v>
       </c>
       <c r="D354">
-        <v>1.028773949394598</v>
+        <v>1.055306006798526</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -24650,10 +24650,10 @@
         </is>
       </c>
       <c r="F354">
-        <v>3.340658848528288</v>
+        <v>3.306088610953972</v>
       </c>
       <c r="G354">
-        <v>7.483576270487363</v>
+        <v>7.56180838813869</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
@@ -24683,10 +24683,10 @@
         </is>
       </c>
       <c r="C355">
-        <v>8.915256454112887</v>
+        <v>8.644067592618484</v>
       </c>
       <c r="D355">
-        <v>0.7889817427351148</v>
+        <v>0.7823399104680318</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -24694,10 +24694,10 @@
         </is>
       </c>
       <c r="F355">
-        <v>7.495563121841606</v>
+        <v>7.239012296408877</v>
       </c>
       <c r="G355">
-        <v>10.60384608209041</v>
+        <v>10.32183694215081</v>
       </c>
       <c r="H355" t="inlineStr">
         <is>
@@ -24727,10 +24727,10 @@
         </is>
       </c>
       <c r="C356">
-        <v>7.41666458092403</v>
+        <v>7.250000659395417</v>
       </c>
       <c r="D356">
-        <v>1.490646852198784</v>
+        <v>1.488066733687299</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -24738,10 +24738,10 @@
         </is>
       </c>
       <c r="F356">
-        <v>5.001829899502865</v>
+        <v>4.848734989614504</v>
       </c>
       <c r="G356">
-        <v>10.99735788923973</v>
+        <v>10.8404583203284</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
@@ -24771,10 +24771,10 @@
         </is>
       </c>
       <c r="C357">
-        <v>10.72131551537102</v>
+        <v>10.57376989633519</v>
       </c>
       <c r="D357">
-        <v>0.9138526867928837</v>
+        <v>0.92038318162524</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -24782,10 +24782,10 @@
         </is>
       </c>
       <c r="F357">
-        <v>9.071815679534149</v>
+        <v>8.915339207097444</v>
       </c>
       <c r="G357">
-        <v>12.67073874080718</v>
+        <v>12.54070173029842</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
@@ -24815,10 +24815,10 @@
         </is>
       </c>
       <c r="C358">
-        <v>6.181814761332707</v>
+        <v>6.18181829795991</v>
       </c>
       <c r="D358">
-        <v>1.333270237430694</v>
+        <v>1.356120890123903</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -24826,10 +24826,10 @@
         </is>
       </c>
       <c r="F358">
-        <v>4.050718690884</v>
+        <v>4.021481093751961</v>
       </c>
       <c r="G358">
-        <v>9.434087296516564</v>
+        <v>9.502687337848016</v>
       </c>
       <c r="H358" t="inlineStr">
         <is>
@@ -24859,10 +24859,10 @@
         </is>
       </c>
       <c r="C359">
-        <v>10.68362251494558</v>
+        <v>10.52538771450328</v>
       </c>
       <c r="D359">
-        <v>1.012478139219654</v>
+        <v>1.004890867751326</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -24870,10 +24870,10 @@
         </is>
       </c>
       <c r="F359">
-        <v>8.872599183772</v>
+        <v>8.729136706681336</v>
       </c>
       <c r="G359">
-        <v>12.86430139328438</v>
+        <v>12.69126492838885</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
@@ -24903,10 +24903,10 @@
         </is>
       </c>
       <c r="C360">
-        <v>15.24101147630097</v>
+        <v>15.18853778632259</v>
       </c>
       <c r="D360">
-        <v>2.334878700168977</v>
+        <v>2.342665616621305</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -24914,10 +24914,10 @@
         </is>
       </c>
       <c r="F360">
-        <v>11.28787484388258</v>
+        <v>11.2260623464668</v>
       </c>
       <c r="G360">
-        <v>20.57857958503372</v>
+        <v>20.54965249316963</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -24947,10 +24947,10 @@
         </is>
       </c>
       <c r="C361">
-        <v>12.98331115002903</v>
+        <v>12.96013211201004</v>
       </c>
       <c r="D361">
-        <v>1.212595446853224</v>
+        <v>1.218215634712093</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -24958,10 +24958,10 @@
         </is>
       </c>
       <c r="F361">
-        <v>10.81150727223319</v>
+        <v>10.77950701490351</v>
       </c>
       <c r="G361">
-        <v>15.59138463990042</v>
+        <v>15.58188367320778</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
@@ -24991,10 +24991,10 @@
         </is>
       </c>
       <c r="C362">
-        <v>15.31481629919681</v>
+        <v>15.2699812774121</v>
       </c>
       <c r="D362">
-        <v>2.279074865648225</v>
+        <v>2.287048887559786</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -25002,10 +25002,10 @@
         </is>
       </c>
       <c r="F362">
-        <v>11.44037361234781</v>
+        <v>11.38545768313767</v>
       </c>
       <c r="G362">
-        <v>20.50139324339872</v>
+        <v>20.47983793904515</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
@@ -25035,10 +25035,10 @@
         </is>
       </c>
       <c r="C363">
-        <v>10.54754445587415</v>
+        <v>9.957452502669202</v>
       </c>
       <c r="D363">
-        <v>1.645172865198713</v>
+        <v>1.658350884102276</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -25046,10 +25046,10 @@
         </is>
       </c>
       <c r="F363">
-        <v>7.769330933777494</v>
+        <v>7.184325446500462</v>
       </c>
       <c r="G363">
-        <v>14.31921165373126</v>
+        <v>13.80099789204431</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
@@ -25079,10 +25079,10 @@
         </is>
       </c>
       <c r="C364">
-        <v>8.040904325622103</v>
+        <v>7.710464740909225</v>
       </c>
       <c r="D364">
-        <v>1.631890204794774</v>
+        <v>1.666955331284069</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -25090,10 +25090,10 @@
         </is>
       </c>
       <c r="F364">
-        <v>5.402002000668656</v>
+        <v>5.047263595737117</v>
       </c>
       <c r="G364">
-        <v>11.96892233024074</v>
+        <v>11.77891057067368</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
@@ -25123,10 +25123,10 @@
         </is>
       </c>
       <c r="C365">
-        <v>10.58595334843192</v>
+        <v>9.809063991808866</v>
       </c>
       <c r="D365">
-        <v>1.654970916521992</v>
+        <v>1.640299675825842</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -25134,10 +25134,10 @@
         </is>
       </c>
       <c r="F365">
-        <v>7.792128466531453</v>
+        <v>7.06784824917588</v>
       </c>
       <c r="G365">
-        <v>14.38148880328455</v>
+        <v>13.61344117803044</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
@@ -25167,10 +25167,10 @@
         </is>
       </c>
       <c r="C366">
-        <v>7.520885070310326</v>
+        <v>7.311702581044061</v>
       </c>
       <c r="D366">
-        <v>1.569459313969127</v>
+        <v>1.639235274529689</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -25178,10 +25178,10 @@
         </is>
       </c>
       <c r="F366">
-        <v>4.996203265577893</v>
+        <v>4.711777467134647</v>
       </c>
       <c r="G366">
-        <v>11.32133927186693</v>
+        <v>11.34624778155268</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
@@ -25211,10 +25211,10 @@
         </is>
       </c>
       <c r="C367">
-        <v>9.046916914945088</v>
+        <v>8.968749999695408</v>
       </c>
       <c r="D367">
-        <v>1.723790462288128</v>
+        <v>1.724361507311495</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -25222,10 +25222,10 @@
         </is>
       </c>
       <c r="F367">
-        <v>6.227496824593741</v>
+        <v>6.152860906004676</v>
       </c>
       <c r="G367">
-        <v>13.14279364104837</v>
+        <v>13.07334551940467</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
@@ -25255,10 +25255,10 @@
         </is>
       </c>
       <c r="C368">
-        <v>6.999606140523713</v>
+        <v>6.00000000004233</v>
       </c>
       <c r="D368">
-        <v>2.615443066069598</v>
+        <v>2.360348158568955</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -25266,10 +25266,10 @@
         </is>
       </c>
       <c r="F368">
-        <v>3.365249391478545</v>
+        <v>2.775210422575629</v>
       </c>
       <c r="G368">
-        <v>14.55894658105301</v>
+        <v>12.97198933373021</v>
       </c>
       <c r="H368" t="inlineStr">
         <is>
@@ -25299,10 +25299,10 @@
         </is>
       </c>
       <c r="C369">
-        <v>1.891101606507347</v>
+        <v>0.9748115362599685</v>
       </c>
       <c r="D369">
-        <v>0.2217342296980927</v>
+        <v>0.2184869289956672</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -25310,10 +25310,10 @@
         </is>
       </c>
       <c r="F369">
-        <v>1.502831631522509</v>
+        <v>0.6282590389987188</v>
       </c>
       <c r="G369">
-        <v>2.37968459747655</v>
+        <v>1.512525044987785</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
@@ -25343,10 +25343,10 @@
         </is>
       </c>
       <c r="C370">
-        <v>0.2496740862832052</v>
+        <v>0.2431213935569062</v>
       </c>
       <c r="D370">
-        <v>0.1504922164314485</v>
+        <v>0.1757846786878113</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -25354,10 +25354,10 @@
         </is>
       </c>
       <c r="F370">
-        <v>0.07661393716016339</v>
+        <v>0.05893547154246252</v>
       </c>
       <c r="G370">
-        <v>0.8136528635910719</v>
+        <v>1.002927616562214</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
@@ -49264,10 +49264,10 @@
         </is>
       </c>
       <c r="B508">
-        <v>6.146644334570748</v>
+        <v>5.841640633177787</v>
       </c>
       <c r="C508">
-        <v>1.480598351601307</v>
+        <v>1.514485790844385</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -49275,10 +49275,10 @@
         </is>
       </c>
       <c r="E508">
-        <v>3.833552323875838</v>
+        <v>3.514430354655458</v>
       </c>
       <c r="F508">
-        <v>9.855411739238424</v>
+        <v>9.709899427083466</v>
       </c>
       <c r="G508" s="2">
         <v>42348</v>
@@ -49311,10 +49311,10 @@
         </is>
       </c>
       <c r="B509">
-        <v>5.311507404334815</v>
+        <v>4.536054247237937</v>
       </c>
       <c r="C509">
-        <v>1.151738972524592</v>
+        <v>1.088041666387846</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -49322,10 +49322,10 @@
         </is>
       </c>
       <c r="E509">
-        <v>3.472518575698014</v>
+        <v>2.83468360045413</v>
       </c>
       <c r="F509">
-        <v>8.124394525559197</v>
+        <v>7.258583684820764</v>
       </c>
       <c r="G509" s="2">
         <v>46074</v>
@@ -49358,10 +49358,10 @@
         </is>
       </c>
       <c r="B510">
-        <v>1.667878382930387</v>
+        <v>1.620885693846321</v>
       </c>
       <c r="C510">
-        <v>0.34099075163525</v>
+        <v>0.3594984754339631</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -49369,10 +49369,10 @@
         </is>
       </c>
       <c r="E510">
-        <v>1.117222796046408</v>
+        <v>1.049453557071585</v>
       </c>
       <c r="F510">
-        <v>2.489940511499309</v>
+        <v>2.503465174625597</v>
       </c>
       <c r="G510" s="2">
         <v>42514</v>
@@ -49405,10 +49405,10 @@
         </is>
       </c>
       <c r="B511">
-        <v>2.316606805185299</v>
+        <v>1.91485310163097</v>
       </c>
       <c r="C511">
-        <v>0.439370012295441</v>
+        <v>0.419401022504712</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -49416,10 +49416,10 @@
         </is>
       </c>
       <c r="E511">
-        <v>1.597395931175653</v>
+        <v>1.246524737237324</v>
       </c>
       <c r="F511">
-        <v>3.359634881429223</v>
+        <v>2.941507931043697</v>
       </c>
       <c r="G511" s="2">
         <v>42830</v>
@@ -49452,10 +49452,10 @@
         </is>
       </c>
       <c r="B512">
-        <v>1.966664271390885</v>
+        <v>1.443137143649405</v>
       </c>
       <c r="C512">
-        <v>0.3735568073530152</v>
+        <v>0.3277410256923361</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -49463,10 +49463,10 @@
         </is>
       </c>
       <c r="E512">
-        <v>1.355343216709592</v>
+        <v>0.9246918559294314</v>
       </c>
       <c r="F512">
-        <v>2.853718754541998</v>
+        <v>2.252258200422067</v>
       </c>
       <c r="G512" s="2">
         <v>43187</v>
@@ -49499,10 +49499,10 @@
         </is>
       </c>
       <c r="B513">
-        <v>2.449489832006496</v>
+        <v>2.056493923539612</v>
       </c>
       <c r="C513">
-        <v>0.414235215812309</v>
+        <v>0.39979320440421</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -49510,10 +49510,10 @@
         </is>
       </c>
       <c r="E513">
-        <v>1.758442842859649</v>
+        <v>1.404912854973765</v>
       </c>
       <c r="F513">
-        <v>3.412110016237876</v>
+        <v>3.010270169130401</v>
       </c>
       <c r="G513" s="2">
         <v>46105</v>
@@ -49546,28 +49546,11 @@
         </is>
       </c>
       <c r="B514">
-        <v>0.5454545588891426</v>
-      </c>
-      <c r="C514">
-        <v>0.2490485152163013</v>
+        <v>1</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
           <t>Inf</t>
-        </is>
-      </c>
-      <c r="E514">
-        <v>0.2228996421585102</v>
-      </c>
-      <c r="F514">
-        <v>1.334774129432535</v>
-      </c>
-      <c r="G514" s="2">
-        <v>45972</v>
-      </c>
-      <c r="H514" t="inlineStr">
-        <is>
-          <t>Bloom</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -49598,10 +49581,10 @@
         </is>
       </c>
       <c r="B515">
-        <v>3.197214647733623</v>
+        <v>2.193742584751924</v>
       </c>
       <c r="C515">
-        <v>0.5543722906535823</v>
+        <v>0.4583342087542386</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -49609,10 +49592,10 @@
         </is>
       </c>
       <c r="E515">
-        <v>2.276040733008299</v>
+        <v>1.456618582562524</v>
       </c>
       <c r="F515">
-        <v>4.491212022454242</v>
+        <v>3.303889285613642</v>
       </c>
       <c r="G515" s="2">
         <v>42747</v>
@@ -49645,10 +49628,10 @@
         </is>
       </c>
       <c r="B516">
-        <v>3.491064494206273</v>
+        <v>3.316623561962152</v>
       </c>
       <c r="C516">
-        <v>0.5922825466361527</v>
+        <v>0.6362095694179754</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -49656,10 +49639,10 @@
         </is>
       </c>
       <c r="E516">
-        <v>2.503489713948083</v>
+        <v>2.27727193336614</v>
       </c>
       <c r="F516">
-        <v>4.86821704711044</v>
+        <v>4.830337427249156</v>
       </c>
       <c r="G516" s="2">
         <v>46091</v>
@@ -49692,10 +49675,10 @@
         </is>
       </c>
       <c r="B517">
-        <v>7.288067083973704</v>
+        <v>6.977647488196478</v>
       </c>
       <c r="C517">
-        <v>1.18113618663098</v>
+        <v>1.192569915178652</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -49703,10 +49686,10 @@
         </is>
       </c>
       <c r="E517">
-        <v>5.304725283062315</v>
+        <v>4.991461287407142</v>
       </c>
       <c r="F517">
-        <v>10.01294487201761</v>
+        <v>9.754170505612755</v>
       </c>
       <c r="G517" s="2">
         <v>42348</v>
@@ -49739,10 +49722,10 @@
         </is>
       </c>
       <c r="B518">
-        <v>6.24500796267986</v>
+        <v>5.968658936138224</v>
       </c>
       <c r="C518">
-        <v>0.8278200912742812</v>
+        <v>0.8321615542753223</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -49750,10 +49733,10 @@
         </is>
       </c>
       <c r="E518">
-        <v>4.816152118596842</v>
+        <v>4.541513998558763</v>
       </c>
       <c r="F518">
-        <v>8.097776709199403</v>
+        <v>7.844276051389062</v>
       </c>
       <c r="G518" s="2">
         <v>42710</v>
@@ -49786,10 +49769,10 @@
         </is>
       </c>
       <c r="B519">
-        <v>9.656980728497652</v>
+        <v>9.561851377577019</v>
       </c>
       <c r="C519">
-        <v>1.424404697296012</v>
+        <v>1.480911475964895</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -49797,10 +49780,10 @@
         </is>
       </c>
       <c r="E519">
-        <v>7.232511512046687</v>
+        <v>7.058467062022224</v>
       </c>
       <c r="F519">
-        <v>12.89417605976056</v>
+        <v>12.95309604245394</v>
       </c>
       <c r="G519" s="2">
         <v>43074</v>
@@ -49833,10 +49816,10 @@
         </is>
       </c>
       <c r="B520">
-        <v>6.636039346107128</v>
+        <v>6.110092108142785</v>
       </c>
       <c r="C520">
-        <v>0.9977527615064415</v>
+        <v>0.9758409038629511</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -49844,10 +49827,10 @@
         </is>
       </c>
       <c r="E520">
-        <v>4.942283915284315</v>
+        <v>4.467891565212514</v>
       </c>
       <c r="F520">
-        <v>8.91025666633492</v>
+        <v>8.35589338395526</v>
       </c>
       <c r="G520" s="2">
         <v>43445</v>
@@ -49880,10 +49863,10 @@
         </is>
       </c>
       <c r="B521">
-        <v>12.33896612139807</v>
+        <v>12.09218832504808</v>
       </c>
       <c r="C521">
-        <v>1.444461871636415</v>
+        <v>1.493363592380725</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -49891,10 +49874,10 @@
         </is>
       </c>
       <c r="E521">
-        <v>9.809182344479941</v>
+        <v>9.492553135652965</v>
       </c>
       <c r="F521">
-        <v>15.52118001259168</v>
+        <v>15.40376086379115</v>
       </c>
       <c r="G521" s="2">
         <v>44169</v>
@@ -49927,10 +49910,10 @@
         </is>
       </c>
       <c r="B522">
-        <v>16.93812409586581</v>
+        <v>16.41088643255398</v>
       </c>
       <c r="C522">
-        <v>2.004220745480048</v>
+        <v>2.057152415188338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -49938,10 +49921,10 @@
         </is>
       </c>
       <c r="E522">
-        <v>13.43216514836046</v>
+        <v>12.83605139376689</v>
       </c>
       <c r="F522">
-        <v>21.35918109389604</v>
+        <v>20.98131156073145</v>
       </c>
       <c r="G522" s="2">
         <v>45708</v>
@@ -49974,10 +49957,10 @@
         </is>
       </c>
       <c r="B523">
-        <v>10.63018111011905</v>
+        <v>10.40833442981612</v>
       </c>
       <c r="C523">
-        <v>1.293107661990776</v>
+        <v>1.333611129042695</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -49985,10 +49968,10 @@
         </is>
       </c>
       <c r="E523">
-        <v>8.375221654289748</v>
+        <v>8.096876234178167</v>
       </c>
       <c r="F523">
-        <v>13.49226982859056</v>
+        <v>13.37965685403507</v>
       </c>
       <c r="G523" s="2">
         <v>46008</v>
@@ -50021,10 +50004,10 @@
         </is>
       </c>
       <c r="B524">
-        <v>11.78805941935919</v>
+        <v>11.11555518166033</v>
       </c>
       <c r="C524">
-        <v>1.477188946743597</v>
+        <v>1.585382741563989</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -50032,10 +50015,10 @@
         </is>
       </c>
       <c r="E524">
-        <v>9.220963126521358</v>
+        <v>8.404782816178006</v>
       </c>
       <c r="F524">
-        <v>15.0698297962683</v>
+        <v>14.70062578639259</v>
       </c>
       <c r="G524" s="2">
         <v>42323</v>
@@ -50068,10 +50051,10 @@
         </is>
       </c>
       <c r="B525">
-        <v>11.04989330155888</v>
+        <v>10.09950771114037</v>
       </c>
       <c r="C525">
-        <v>1.4929884511434</v>
+        <v>1.555711741982069</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -50079,10 +50062,10 @@
         </is>
       </c>
       <c r="E525">
-        <v>8.479092351324441</v>
+        <v>7.467625048720319</v>
       </c>
       <c r="F525">
-        <v>14.40014295359852</v>
+        <v>13.65896859334989</v>
       </c>
       <c r="G525" s="2">
         <v>45995</v>
@@ -50115,10 +50098,10 @@
         </is>
       </c>
       <c r="B526">
-        <v>1.309307550994017</v>
+        <v>0.6998541759809807</v>
       </c>
       <c r="C526">
-        <v>0.3526333322456525</v>
+        <v>0.268034479583021</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -50126,10 +50109,10 @@
         </is>
       </c>
       <c r="E526">
-        <v>0.7723055698769872</v>
+        <v>0.3303764850207173</v>
       </c>
       <c r="F526">
-        <v>2.219699468648145</v>
+        <v>1.482538527544729</v>
       </c>
       <c r="G526" s="2">
         <v>42747</v>
@@ -50162,10 +50145,10 @@
         </is>
       </c>
       <c r="B527">
-        <v>6.546536670717146</v>
+        <v>6.22016720828039</v>
       </c>
       <c r="C527">
-        <v>0.9516376060632737</v>
+        <v>1.151231228629233</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -50173,10 +50156,10 @@
         </is>
       </c>
       <c r="E527">
-        <v>4.92353073374086</v>
+        <v>4.327741487371739</v>
       </c>
       <c r="F527">
-        <v>8.704554657767275</v>
+        <v>8.940108879392334</v>
       </c>
       <c r="G527" s="2">
         <v>46069</v>
@@ -50209,10 +50192,10 @@
         </is>
       </c>
       <c r="B528">
-        <v>37.18182470428442</v>
+        <v>36.09090888220705</v>
       </c>
       <c r="C528">
-        <v>2.673307598532068</v>
+        <v>2.677841342548781</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -50220,10 +50203,10 @@
         </is>
       </c>
       <c r="E528">
-        <v>32.2946669285772</v>
+        <v>31.20621668059263</v>
       </c>
       <c r="F528">
-        <v>42.8085569483544</v>
+        <v>41.74019930951254</v>
       </c>
       <c r="G528" s="2">
         <v>45971</v>
@@ -50256,10 +50239,10 @@
         </is>
       </c>
       <c r="B529">
-        <v>41.91666115864358</v>
+        <v>41.41666602217857</v>
       </c>
       <c r="C529">
-        <v>2.807292845903284</v>
+        <v>2.854306290982213</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -50267,10 +50250,10 @@
         </is>
       </c>
       <c r="E529">
-        <v>36.76029538524285</v>
+        <v>36.18370251207052</v>
       </c>
       <c r="F529">
-        <v>47.79631023840677</v>
+        <v>47.40643177188574</v>
       </c>
       <c r="G529" s="2">
         <v>46120</v>
@@ -50303,10 +50286,10 @@
         </is>
       </c>
       <c r="B530">
-        <v>3.00000728627757</v>
+        <v>2.636361311716807</v>
       </c>
       <c r="C530">
-        <v>1.331831329441892</v>
+        <v>1.53738000747012</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -50314,10 +50297,10 @@
         </is>
       </c>
       <c r="E530">
-        <v>1.256717317463464</v>
+        <v>0.8406811305052414</v>
       </c>
       <c r="F530">
-        <v>7.161549851070758</v>
+        <v>8.26758293211606</v>
       </c>
       <c r="G530" s="2">
         <v>44117</v>
@@ -50350,10 +50333,10 @@
         </is>
       </c>
       <c r="B531">
-        <v>5.800000852004977</v>
+        <v>4.53333437055332</v>
       </c>
       <c r="C531">
-        <v>2.121570901154667</v>
+        <v>2.215286006292295</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -50361,10 +50344,10 @@
         </is>
       </c>
       <c r="E531">
-        <v>2.831840049204033</v>
+        <v>1.739660764299698</v>
       </c>
       <c r="F531">
-        <v>11.87920549845811</v>
+        <v>11.81329195724717</v>
       </c>
       <c r="G531" s="2">
         <v>44494</v>
@@ -50397,10 +50380,10 @@
         </is>
       </c>
       <c r="B532">
-        <v>3.812505311945262</v>
+        <v>3.249999640409015</v>
       </c>
       <c r="C532">
-        <v>1.380190298110802</v>
+        <v>1.556317815995099</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -50408,10 +50391,10 @@
         </is>
       </c>
       <c r="E532">
-        <v>1.875259392256468</v>
+        <v>1.271366960745994</v>
       </c>
       <c r="F532">
-        <v>7.751032637741321</v>
+        <v>8.307985018315264</v>
       </c>
       <c r="G532" s="2">
         <v>44897</v>
@@ -50444,10 +50427,10 @@
         </is>
       </c>
       <c r="B533">
-        <v>4.866664900461062</v>
+        <v>4.333333403973765</v>
       </c>
       <c r="C533">
-        <v>1.794771699035372</v>
+        <v>2.120559413809725</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -50455,10 +50438,10 @@
         </is>
       </c>
       <c r="E533">
-        <v>2.362206251222554</v>
+        <v>1.660650495534624</v>
       </c>
       <c r="F533">
-        <v>10.0264010566909</v>
+        <v>11.30748368816137</v>
       </c>
       <c r="G533" s="2">
         <v>45253</v>
@@ -50491,10 +50474,10 @@
         </is>
       </c>
       <c r="B534">
-        <v>1.210527577642391</v>
+        <v>1.210527099168062</v>
       </c>
       <c r="C534">
-        <v>0.4529964782998704</v>
+        <v>0.5682909688242261</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -50502,10 +50485,10 @@
         </is>
       </c>
       <c r="E534">
-        <v>0.5813572263512081</v>
+        <v>0.4823603566546594</v>
       </c>
       <c r="F534">
-        <v>2.520613746267421</v>
+        <v>3.037927635643909</v>
       </c>
       <c r="G534" s="2">
         <v>46101</v>
@@ -50538,10 +50521,10 @@
         </is>
       </c>
       <c r="B535">
-        <v>2.291287831922499</v>
+        <v>1.684024159284263</v>
       </c>
       <c r="C535">
-        <v>0.4357938127739558</v>
+        <v>0.3813254165666463</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -50549,10 +50532,10 @@
         </is>
       </c>
       <c r="E535">
-        <v>1.57828165309925</v>
+        <v>1.080450250726844</v>
       </c>
       <c r="F535">
-        <v>3.326402431661518</v>
+        <v>2.624773669259892</v>
       </c>
       <c r="G535" s="2">
         <v>46048</v>
@@ -50590,10 +50573,10 @@
         </is>
       </c>
       <c r="B536">
-        <v>2.400014526750949</v>
+        <v>1.299999974685588</v>
       </c>
       <c r="C536">
-        <v>1.164195237073768</v>
+        <v>0.884768922178836</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -50601,10 +50584,10 @@
         </is>
       </c>
       <c r="E536">
-        <v>0.9275009795287337</v>
+        <v>0.3424702223102319</v>
       </c>
       <c r="F536">
-        <v>6.210311208018663</v>
+        <v>4.934735413730712</v>
       </c>
       <c r="G536" s="2">
         <v>44481</v>
@@ -50637,10 +50620,10 @@
         </is>
       </c>
       <c r="B537">
-        <v>2.000001232811482</v>
+        <v>1.499999950246205</v>
       </c>
       <c r="C537">
-        <v>0.9871856419465741</v>
+        <v>1.009521539497202</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -50648,10 +50631,10 @@
         </is>
       </c>
       <c r="E537">
-        <v>0.7601224358728567</v>
+        <v>0.4010701718519992</v>
       </c>
       <c r="F537">
-        <v>5.262316624892411</v>
+        <v>5.609990492060081</v>
       </c>
       <c r="G537" s="2">
         <v>44896</v>
@@ -50684,10 +50667,10 @@
         </is>
       </c>
       <c r="B538">
-        <v>2.500000877058497</v>
+        <v>2.500000633842356</v>
       </c>
       <c r="C538">
-        <v>1.208391743526469</v>
+        <v>1.632256854185475</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -50695,10 +50678,10 @@
         </is>
       </c>
       <c r="E538">
-        <v>0.9694074178906734</v>
+        <v>0.6953259509171513</v>
       </c>
       <c r="F538">
-        <v>6.447242170781603</v>
+        <v>8.98859471729522</v>
       </c>
       <c r="G538" s="2">
         <v>45261</v>
@@ -50731,10 +50714,10 @@
         </is>
       </c>
       <c r="B539">
-        <v>0.7142826644799463</v>
+        <v>0.5714283777240314</v>
       </c>
       <c r="C539">
-        <v>0.4931235840731789</v>
+        <v>0.5116856249105285</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -50742,10 +50725,10 @@
         </is>
       </c>
       <c r="E539">
-        <v>0.1845954630565509</v>
+        <v>0.09879916109006662</v>
       </c>
       <c r="F539">
-        <v>2.763880088538641</v>
+        <v>3.304991532981226</v>
       </c>
       <c r="G539" s="2">
         <v>45645</v>
@@ -50778,10 +50761,10 @@
         </is>
       </c>
       <c r="B540">
-        <v>1.437498613210762</v>
+        <v>1.437500147437496</v>
       </c>
       <c r="C540">
-        <v>0.5830277447260189</v>
+        <v>0.7672862844015628</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -50789,10 +50772,10 @@
         </is>
       </c>
       <c r="E540">
-        <v>0.6491916625817346</v>
+        <v>0.5049715230375144</v>
       </c>
       <c r="F540">
-        <v>3.183038819021648</v>
+        <v>4.092125158767236</v>
       </c>
       <c r="G540" s="2">
         <v>45974</v>
@@ -50825,10 +50808,10 @@
         </is>
       </c>
       <c r="B541">
-        <v>1.249999080846627</v>
+        <v>1.187499826908258</v>
       </c>
       <c r="C541">
-        <v>0.5169330094441744</v>
+        <v>0.6439464818835698</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -50836,10 +50819,10 @@
         </is>
       </c>
       <c r="E541">
-        <v>0.5557738318371683</v>
+        <v>0.4102530445084847</v>
       </c>
       <c r="F541">
-        <v>2.811391275750449</v>
+        <v>3.437283056842687</v>
       </c>
       <c r="G541" s="2">
         <v>46087</v>
@@ -50872,10 +50855,10 @@
         </is>
       </c>
       <c r="B542">
-        <v>2.327374013146676</v>
+        <v>2.140872085122573</v>
       </c>
       <c r="C542">
-        <v>0.9745523745589232</v>
+        <v>0.9865461154304267</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -50883,10 +50866,10 @@
         </is>
       </c>
       <c r="E542">
-        <v>1.024326753338619</v>
+        <v>0.8676493033781347</v>
       </c>
       <c r="F542">
-        <v>5.288029214716641</v>
+        <v>5.282472154374092</v>
       </c>
       <c r="G542" s="2">
         <v>42677</v>
@@ -50919,10 +50902,10 @@
         </is>
       </c>
       <c r="B543">
-        <v>1.616406679483519E-05</v>
+        <v>1.664823695021448E-05</v>
       </c>
       <c r="C543">
-        <v>0.1666666292259635</v>
+        <v>0.1666666504674301</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -50968,10 +50951,10 @@
         </is>
       </c>
       <c r="B544">
-        <v>1.527527046302872</v>
+        <v>0.9428090251875854</v>
       </c>
       <c r="C544">
-        <v>0.3353387039552978</v>
+        <v>0.2547824642926494</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -50979,10 +50962,10 @@
         </is>
       </c>
       <c r="E544">
-        <v>0.9934002122973098</v>
+        <v>0.5551330124444689</v>
       </c>
       <c r="F544">
-        <v>2.348840727334616</v>
+        <v>1.601217794742629</v>
       </c>
       <c r="G544" s="2">
         <v>42769</v>
@@ -51015,10 +50998,10 @@
         </is>
       </c>
       <c r="B545">
-        <v>2.261333928028967</v>
+        <v>1.825741995477442</v>
       </c>
       <c r="C545">
-        <v>0.3641573201924368</v>
+        <v>0.3272045365871372</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -51026,10 +51009,10 @@
         </is>
       </c>
       <c r="E545">
-        <v>1.649263980655298</v>
+        <v>1.284959293013943</v>
       </c>
       <c r="F545">
-        <v>3.100553455380218</v>
+        <v>2.594116290043269</v>
       </c>
       <c r="G545" s="2">
         <v>45975</v>
@@ -51062,10 +51045,10 @@
         </is>
       </c>
       <c r="B546">
-        <v>8.666666402351137</v>
+        <v>8.333333470528286</v>
       </c>
       <c r="C546">
-        <v>1.747992022993099</v>
+        <v>1.782907251737716</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -51073,10 +51056,10 @@
         </is>
       </c>
       <c r="E546">
-        <v>5.836762938208994</v>
+        <v>5.479048636581616</v>
       </c>
       <c r="F546">
-        <v>12.86862381165848</v>
+        <v>12.67454467685716</v>
       </c>
       <c r="G546" s="2">
         <v>44481</v>
@@ -51109,10 +51092,10 @@
         </is>
       </c>
       <c r="B547">
-        <v>7.999989215115778</v>
+        <v>7.999998620194553</v>
       </c>
       <c r="C547">
-        <v>1.451363159733457</v>
+        <v>1.509025238120127</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -51120,10 +51103,10 @@
         </is>
       </c>
       <c r="E547">
-        <v>5.606139149776291</v>
+        <v>5.527507085596076</v>
       </c>
       <c r="F547">
-        <v>11.41602549136202</v>
+        <v>11.57845244375894</v>
       </c>
       <c r="G547" s="2">
         <v>44896</v>
@@ -51156,10 +51139,10 @@
         </is>
       </c>
       <c r="B548">
-        <v>9.000008941362793</v>
+        <v>8.999997899707967</v>
       </c>
       <c r="C548">
-        <v>1.78315778954563</v>
+        <v>1.862176838026494</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -51167,10 +51150,10 @@
         </is>
       </c>
       <c r="E548">
-        <v>6.10373544306906</v>
+        <v>5.999589004454471</v>
       </c>
       <c r="F548">
-        <v>13.27058842902306</v>
+        <v>13.50091850201878</v>
       </c>
       <c r="G548" s="2">
         <v>45261</v>
@@ -51203,10 +51186,10 @@
         </is>
       </c>
       <c r="B549">
-        <v>9.250000000109459</v>
+        <v>9.249998645193346</v>
       </c>
       <c r="C549">
-        <v>1.566788260927024</v>
+        <v>1.637997412289485</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -51214,10 +51197,10 @@
         </is>
       </c>
       <c r="E549">
-        <v>6.636866391656568</v>
+        <v>6.537477327179014</v>
       </c>
       <c r="F549">
-        <v>12.8920027845654</v>
+        <v>13.08799566774173</v>
       </c>
       <c r="G549" s="2">
         <v>45645</v>
@@ -51250,10 +51233,10 @@
         </is>
       </c>
       <c r="B550">
-        <v>4.999990058833998</v>
+        <v>4.999998108898272</v>
       </c>
       <c r="C550">
-        <v>1.016496887726451</v>
+        <v>1.04240646230561</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -51261,10 +51244,10 @@
         </is>
       </c>
       <c r="E550">
-        <v>3.356758156671277</v>
+        <v>3.322845702138276</v>
       </c>
       <c r="F550">
-        <v>7.447632335011564</v>
+        <v>7.523665956832911</v>
       </c>
       <c r="G550" s="2">
         <v>45974</v>
@@ -51297,10 +51280,10 @@
         </is>
       </c>
       <c r="B551">
-        <v>10.9300032944719</v>
+        <v>10.51506962472882</v>
       </c>
       <c r="C551">
-        <v>1.53389155559282</v>
+        <v>1.513229455464459</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -51308,10 +51291,10 @@
         </is>
       </c>
       <c r="E551">
-        <v>8.301653901119048</v>
+        <v>7.93076845022929</v>
       </c>
       <c r="F551">
-        <v>14.39050259624324</v>
+        <v>13.94148497800336</v>
       </c>
       <c r="G551" s="2">
         <v>42348</v>
@@ -51344,10 +51327,10 @@
         </is>
       </c>
       <c r="B552">
-        <v>9.205026032293802</v>
+        <v>9.155298087414804</v>
       </c>
       <c r="C552">
-        <v>1.413992400247579</v>
+        <v>1.436012906587902</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -51355,10 +51338,10 @@
         </is>
       </c>
       <c r="E552">
-        <v>6.811945736251038</v>
+        <v>6.732263684620547</v>
       </c>
       <c r="F552">
-        <v>12.43881080911828</v>
+        <v>12.45041593675271</v>
       </c>
       <c r="G552" s="2">
         <v>42710</v>
@@ -51391,10 +51374,10 @@
         </is>
       </c>
       <c r="B553">
-        <v>9.627450119003065</v>
+        <v>9.496335945626107</v>
       </c>
       <c r="C553">
-        <v>1.443633198674396</v>
+        <v>1.456170534354665</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -51402,10 +51385,10 @@
         </is>
       </c>
       <c r="E553">
-        <v>7.175858499610547</v>
+        <v>7.03125116842136</v>
       </c>
       <c r="F553">
-        <v>12.91661420008805</v>
+        <v>12.82565424446892</v>
       </c>
       <c r="G553" s="2">
         <v>43074</v>
@@ -51438,10 +51421,10 @@
         </is>
       </c>
       <c r="B554">
-        <v>10.57787831144453</v>
+        <v>10.15740606108283</v>
       </c>
       <c r="C554">
-        <v>1.740833488858592</v>
+        <v>1.715227333716739</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -51449,10 +51432,10 @@
         </is>
       </c>
       <c r="E554">
-        <v>7.661498997977183</v>
+        <v>7.295329647550602</v>
       </c>
       <c r="F554">
-        <v>14.60438872357363</v>
+        <v>14.14232157752629</v>
       </c>
       <c r="G554" s="2">
         <v>43445</v>
@@ -51485,10 +51468,10 @@
         </is>
       </c>
       <c r="B555">
-        <v>8.729086656997445</v>
+        <v>8.647139427216183</v>
       </c>
       <c r="C555">
-        <v>1.226318363003482</v>
+        <v>1.24070914771018</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -51496,10 +51479,10 @@
         </is>
       </c>
       <c r="E555">
-        <v>6.628061433603676</v>
+        <v>6.527401597379212</v>
       </c>
       <c r="F555">
-        <v>11.49611460736606</v>
+        <v>11.45525047880284</v>
       </c>
       <c r="G555" s="2">
         <v>44217</v>
@@ -51532,10 +51515,10 @@
         </is>
       </c>
       <c r="B556">
-        <v>9.787088384580269</v>
+        <v>9.528288007973908</v>
       </c>
       <c r="C556">
-        <v>1.460129973879366</v>
+        <v>1.455603968773669</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -51543,10 +51526,10 @@
         </is>
       </c>
       <c r="E556">
-        <v>7.305723837892322</v>
+        <v>7.062845848718006</v>
       </c>
       <c r="F556">
-        <v>13.11124005957776</v>
+        <v>12.85434714384692</v>
       </c>
       <c r="G556" s="2">
         <v>45715</v>
@@ -51579,10 +51562,10 @@
         </is>
       </c>
       <c r="B557">
-        <v>6.771211986593153</v>
+        <v>6.694584448093238</v>
       </c>
       <c r="C557">
-        <v>0.9865067113128851</v>
+        <v>0.9951428605648285</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -51590,10 +51573,10 @@
         </is>
       </c>
       <c r="E557">
-        <v>5.089249548307444</v>
+        <v>5.002572828270536</v>
       </c>
       <c r="F557">
-        <v>9.009051596346088</v>
+        <v>8.958882253423567</v>
       </c>
       <c r="G557" s="2">
         <v>46001</v>
@@ -51626,10 +51609,10 @@
         </is>
       </c>
       <c r="B558">
-        <v>16.64927379594092</v>
+        <v>16.50694797140142</v>
       </c>
       <c r="C558">
-        <v>1.850217166010201</v>
+        <v>1.860331607711381</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -51637,10 +51620,10 @@
         </is>
       </c>
       <c r="E558">
-        <v>13.39066416202023</v>
+        <v>13.23538083394954</v>
       </c>
       <c r="F558">
-        <v>20.70086401826274</v>
+        <v>20.5871923708933</v>
       </c>
       <c r="G558" s="2">
         <v>42389</v>
@@ -51673,10 +51656,10 @@
         </is>
       </c>
       <c r="B559">
-        <v>8.532320064776423</v>
+        <v>8.449885004831897</v>
       </c>
       <c r="C559">
-        <v>1.004975573048784</v>
+        <v>1.007589765539337</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -51684,10 +51667,10 @@
         </is>
       </c>
       <c r="E559">
-        <v>6.773431424387756</v>
+        <v>6.688842349937683</v>
       </c>
       <c r="F559">
-        <v>10.74794755073006</v>
+        <v>10.67457608648052</v>
       </c>
       <c r="G559" s="2">
         <v>42710</v>
@@ -51720,10 +51703,10 @@
         </is>
       </c>
       <c r="B560">
-        <v>11.4015467245399</v>
+        <v>11.4017598546549</v>
       </c>
       <c r="C560">
-        <v>2.564960975364607</v>
+        <v>2.595786568450541</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -51731,10 +51714,10 @@
         </is>
       </c>
       <c r="E560">
-        <v>7.336219535867155</v>
+        <v>7.297644843599143</v>
       </c>
       <c r="F560">
-        <v>17.71965343680255</v>
+        <v>17.81398390430644</v>
       </c>
       <c r="G560" s="2">
         <v>43074</v>
@@ -51767,10 +51750,10 @@
         </is>
       </c>
       <c r="B561">
-        <v>11.19707523922406</v>
+        <v>11.19703867552847</v>
       </c>
       <c r="C561">
-        <v>1.47600586094523</v>
+        <v>1.493190548737774</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -51778,10 +51761,10 @@
         </is>
       </c>
       <c r="E561">
-        <v>8.647660799578501</v>
+        <v>8.621651770060973</v>
       </c>
       <c r="F561">
-        <v>14.49808183028588</v>
+        <v>14.54172337795473</v>
       </c>
       <c r="G561" s="2">
         <v>43117</v>
@@ -51814,10 +51797,10 @@
         </is>
       </c>
       <c r="B562">
-        <v>10.88883118617754</v>
+        <v>10.69090502717832</v>
       </c>
       <c r="C562">
-        <v>1.197636726997909</v>
+        <v>1.193617291888325</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -51825,10 +51808,10 @@
         </is>
       </c>
       <c r="E562">
-        <v>8.777273377017385</v>
+        <v>8.589731545944561</v>
       </c>
       <c r="F562">
-        <v>13.50836865939827</v>
+        <v>13.30605615423552</v>
       </c>
       <c r="G562" s="2">
         <v>43487</v>
@@ -51861,10 +51844,10 @@
         </is>
       </c>
       <c r="B563">
-        <v>12.37629211871688</v>
+        <v>12.29919866294905</v>
       </c>
       <c r="C563">
-        <v>1.303843842000352</v>
+        <v>1.312596025081808</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -51872,10 +51855,10 @@
         </is>
       </c>
       <c r="E563">
-        <v>10.06737782917133</v>
+        <v>9.977800586207707</v>
       </c>
       <c r="F563">
-        <v>15.21474699836726</v>
+        <v>15.16068460616345</v>
       </c>
       <c r="G563" s="2">
         <v>44217</v>
@@ -51908,10 +51891,10 @@
         </is>
       </c>
       <c r="B564">
-        <v>14.3788868023819</v>
+        <v>14.28275178045445</v>
       </c>
       <c r="C564">
-        <v>1.587273396050374</v>
+        <v>1.598104638708481</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -51919,10 +51902,10 @@
         </is>
       </c>
       <c r="E564">
-        <v>11.58142054230137</v>
+        <v>11.47018700531636</v>
       </c>
       <c r="F564">
-        <v>17.85207478828223</v>
+        <v>17.78497580968153</v>
       </c>
       <c r="G564" s="2">
         <v>45749</v>
@@ -51955,10 +51938,10 @@
         </is>
       </c>
       <c r="B565">
-        <v>16.06229096798873</v>
+        <v>16.06227283289428</v>
       </c>
       <c r="C565">
-        <v>1.74575151736187</v>
+        <v>1.768572474307948</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -51966,10 +51949,10 @@
         </is>
       </c>
       <c r="E565">
-        <v>12.98056253702989</v>
+        <v>12.94444840694199</v>
       </c>
       <c r="F565">
-        <v>19.87565565085019</v>
+        <v>19.9310623711067</v>
       </c>
       <c r="G565" s="2">
         <v>46049</v>
@@ -52002,10 +51985,10 @@
         </is>
       </c>
       <c r="B566">
-        <v>12.51739110746126</v>
+        <v>12.18773369866303</v>
       </c>
       <c r="C566">
-        <v>2.186339954811822</v>
+        <v>2.421852769576932</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -52013,10 +51996,10 @@
         </is>
       </c>
       <c r="E566">
-        <v>8.888723473303456</v>
+        <v>8.256171919153473</v>
       </c>
       <c r="F566">
-        <v>17.62739954817371</v>
+        <v>17.99149220293329</v>
       </c>
       <c r="G566" s="2">
         <v>42479</v>
@@ -52049,10 +52032,10 @@
         </is>
       </c>
       <c r="B567">
-        <v>10.40890327990179</v>
+        <v>9.017155540252848</v>
       </c>
       <c r="C567">
-        <v>1.877260688514581</v>
+        <v>1.858625626610616</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -52060,10 +52043,10 @@
         </is>
       </c>
       <c r="E567">
-        <v>7.309531627395246</v>
+        <v>6.020312009721096</v>
       </c>
       <c r="F567">
-        <v>14.82246373820797</v>
+        <v>13.50579403622628</v>
       </c>
       <c r="G567" s="2">
         <v>42888</v>
@@ -52096,10 +52079,10 @@
         </is>
       </c>
       <c r="B568">
-        <v>10.79320757458193</v>
+        <v>10.26470407268068</v>
       </c>
       <c r="C568">
-        <v>2.154891184464767</v>
+        <v>2.329403099974382</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -52107,10 +52090,10 @@
         </is>
       </c>
       <c r="E568">
-        <v>7.298035792471263</v>
+        <v>6.579311729739121</v>
       </c>
       <c r="F568">
-        <v>15.96228534096647</v>
+        <v>16.01446382658103</v>
       </c>
       <c r="G568" s="2">
         <v>43277</v>
@@ -52143,10 +52126,10 @@
         </is>
       </c>
       <c r="B569">
-        <v>10.18067779726596</v>
+        <v>9.416335854445807</v>
       </c>
       <c r="C569">
-        <v>1.934014063559674</v>
+        <v>2.035254143364439</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -52154,10 +52137,10 @@
         </is>
       </c>
       <c r="E569">
-        <v>7.015759824750921</v>
+        <v>6.164567008164698</v>
       </c>
       <c r="F569">
-        <v>14.77333931046075</v>
+        <v>14.38339153525066</v>
       </c>
       <c r="G569" s="2">
         <v>43622</v>
@@ -52190,10 +52173,10 @@
         </is>
       </c>
       <c r="B570">
-        <v>8.073008346643466</v>
+        <v>7.64329133865619</v>
       </c>
       <c r="C570">
-        <v>1.488604202509867</v>
+        <v>1.595869962284396</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -52201,10 +52184,10 @@
         </is>
       </c>
       <c r="E570">
-        <v>5.62444933371918</v>
+        <v>5.076390451537753</v>
       </c>
       <c r="F570">
-        <v>11.58752793349086</v>
+        <v>11.50815782302167</v>
       </c>
       <c r="G570" s="2">
         <v>44336</v>
@@ -52237,10 +52220,10 @@
         </is>
       </c>
       <c r="B571">
-        <v>6.513751132838636</v>
+        <v>5.916187288436221</v>
       </c>
       <c r="C571">
-        <v>1.449261534724875</v>
+        <v>1.490969313167762</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -52248,10 +52231,10 @@
         </is>
       </c>
       <c r="E571">
-        <v>4.211580468341829</v>
+        <v>3.610157584660402</v>
       </c>
       <c r="F571">
-        <v>10.0743543046351</v>
+        <v>9.695220003851107</v>
       </c>
       <c r="G571" s="2">
         <v>45756</v>
@@ -52284,10 +52267,10 @@
         </is>
       </c>
       <c r="B572">
-        <v>4.684494440530874</v>
+        <v>4.624809401341193</v>
       </c>
       <c r="C572">
-        <v>0.8612382616618126</v>
+        <v>0.9472529530280671</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -52295,10 +52278,10 @@
         </is>
       </c>
       <c r="E572">
-        <v>3.267160139412173</v>
+        <v>3.095642730065456</v>
       </c>
       <c r="F572">
-        <v>6.716685814890272</v>
+        <v>6.909344476674034</v>
       </c>
       <c r="G572" s="2">
         <v>45993</v>
@@ -52331,10 +52314,10 @@
         </is>
       </c>
       <c r="B573">
-        <v>12.86229008989483</v>
+        <v>12.48840741744468</v>
       </c>
       <c r="C573">
-        <v>2.188100614167149</v>
+        <v>2.417575594469811</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -52342,10 +52325,10 @@
         </is>
       </c>
       <c r="E573">
-        <v>9.215396440607513</v>
+        <v>8.545288192678207</v>
       </c>
       <c r="F573">
-        <v>17.95240252796987</v>
+        <v>18.25103101352599</v>
       </c>
       <c r="G573" s="2">
         <v>46082</v>
@@ -52378,10 +52361,10 @@
         </is>
       </c>
       <c r="B574">
-        <v>6.434768217696709</v>
+        <v>6.434766361103216</v>
       </c>
       <c r="C574">
-        <v>1.842750818526786</v>
+        <v>1.937856949593842</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -52389,10 +52372,10 @@
         </is>
       </c>
       <c r="E574">
-        <v>3.670885602287872</v>
+        <v>3.566069955977166</v>
       </c>
       <c r="F574">
-        <v>11.27963290102893</v>
+        <v>11.61116260565323</v>
       </c>
       <c r="G574" s="2">
         <v>45960</v>
@@ -52425,10 +52408,10 @@
         </is>
       </c>
       <c r="B575">
-        <v>9.440601321463015</v>
+        <v>8.065168565802331</v>
       </c>
       <c r="C575">
-        <v>2.654720298741903</v>
+        <v>2.42741771465415</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -52436,10 +52419,10 @@
         </is>
       </c>
       <c r="E575">
-        <v>5.44051098186223</v>
+        <v>4.471185454472951</v>
       </c>
       <c r="F575">
-        <v>16.38172473283065</v>
+        <v>14.54803086499876</v>
       </c>
       <c r="G575" s="2">
         <v>46045</v>
@@ -52472,10 +52455,10 @@
         </is>
       </c>
       <c r="B576">
-        <v>1.900043901321572</v>
+        <v>0.6999999966394507</v>
       </c>
       <c r="C576">
-        <v>0.5212742362942293</v>
+        <v>0.317292296408984</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -52483,10 +52466,10 @@
         </is>
       </c>
       <c r="E576">
-        <v>1.109782188278961</v>
+        <v>0.2879187208200017</v>
       </c>
       <c r="F576">
-        <v>3.25304088052441</v>
+        <v>1.701869173007213</v>
       </c>
       <c r="G576" s="2">
         <v>42837</v>
@@ -52519,10 +52502,10 @@
         </is>
       </c>
       <c r="B577">
-        <v>1.583327347797814</v>
+        <v>0.750000002177774</v>
       </c>
       <c r="C577">
-        <v>0.4233594307284868</v>
+        <v>0.3030579737364072</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -52530,10 +52513,10 @@
         </is>
       </c>
       <c r="E577">
-        <v>0.9375002886750947</v>
+        <v>0.33971134103954</v>
       </c>
       <c r="F577">
-        <v>2.674053032908744</v>
+        <v>1.655817558358142</v>
       </c>
       <c r="G577" s="2">
         <v>43062</v>
@@ -52566,10 +52549,10 @@
         </is>
       </c>
       <c r="B578">
-        <v>1.166676455148638</v>
+        <v>0.7500000021776985</v>
       </c>
       <c r="C578">
-        <v>0.3505695777800265</v>
+        <v>0.3030579737363987</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -52577,10 +52560,10 @@
         </is>
       </c>
       <c r="E578">
-        <v>0.6474057491001398</v>
+        <v>0.3397113410394863</v>
       </c>
       <c r="F578">
-        <v>2.102443410318949</v>
+        <v>1.65581755835807</v>
       </c>
       <c r="G578" s="2">
         <v>43214</v>
@@ -52613,10 +52596,10 @@
         </is>
       </c>
       <c r="B579">
-        <v>1.909091584209143</v>
+        <v>0.5454545485824026</v>
       </c>
       <c r="C579">
-        <v>0.4985523316883527</v>
+        <v>0.2579120563052243</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -52624,10 +52607,10 @@
         </is>
       </c>
       <c r="E579">
-        <v>1.144296507597266</v>
+        <v>0.2159123475565095</v>
       </c>
       <c r="F579">
-        <v>3.185040461716499</v>
+        <v>1.37796966193128</v>
       </c>
       <c r="G579" s="2">
         <v>43433</v>
@@ -52660,10 +52643,10 @@
         </is>
       </c>
       <c r="B580">
-        <v>1.999995759709102</v>
+        <v>1.111111122038386</v>
       </c>
       <c r="C580">
-        <v>0.5681782814311667</v>
+        <v>0.4575248396644329</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -52671,10 +52654,10 @@
         </is>
       </c>
       <c r="E580">
-        <v>1.146070799097848</v>
+        <v>0.4957425925659746</v>
       </c>
       <c r="F580">
-        <v>3.490170975478175</v>
+        <v>2.490340640547447</v>
       </c>
       <c r="G580" s="2">
         <v>43760</v>
@@ -52707,10 +52690,10 @@
         </is>
       </c>
       <c r="B581">
-        <v>2.833330479440562</v>
+        <v>2.333333332581703</v>
       </c>
       <c r="C581">
-        <v>0.6225291794587059</v>
+        <v>0.6917128592750829</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -52718,10 +52701,10 @@
         </is>
       </c>
       <c r="E581">
-        <v>1.84193496827903</v>
+        <v>1.305087038620103</v>
       </c>
       <c r="F581">
-        <v>4.358330638148121</v>
+        <v>4.171709839899543</v>
       </c>
       <c r="G581" s="2">
         <v>44132</v>
@@ -88219,10 +88202,10 @@
         </is>
       </c>
       <c r="B682">
-        <v>3.874998627166589</v>
+        <v>3.499968815620033</v>
       </c>
       <c r="C682">
-        <v>1.374200844661628</v>
+        <v>1.336762534288071</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -88230,10 +88213,10 @@
         </is>
       </c>
       <c r="E682">
-        <v>1.933782987315086</v>
+        <v>1.655617622774718</v>
       </c>
       <c r="F682">
-        <v>7.764891127411883</v>
+        <v>7.398919618760029</v>
       </c>
       <c r="G682" t="inlineStr">
         <is>
@@ -88271,10 +88254,10 @@
         </is>
       </c>
       <c r="B683">
-        <v>1.72727249482274</v>
+        <v>1.272726673683926</v>
       </c>
       <c r="C683">
-        <v>0.5999285653428873</v>
+        <v>0.4954582483098817</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -88282,10 +88265,10 @@
         </is>
       </c>
       <c r="E683">
-        <v>0.8744107426969017</v>
+        <v>0.5934333002602072</v>
       </c>
       <c r="F683">
-        <v>3.411978062128334</v>
+        <v>2.729596039177935</v>
       </c>
       <c r="G683" t="inlineStr">
         <is>
@@ -88323,10 +88306,10 @@
         </is>
       </c>
       <c r="B684">
-        <v>9.749999989893267</v>
+        <v>9.750019810147496</v>
       </c>
       <c r="C684">
-        <v>3.179258710740428</v>
+        <v>3.419211775292132</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -88334,10 +88317,10 @@
         </is>
       </c>
       <c r="E684">
-        <v>5.145726203962799</v>
+        <v>4.903425804599806</v>
       </c>
       <c r="F684">
-        <v>18.47406877764108</v>
+        <v>19.3870347154212</v>
       </c>
       <c r="G684" t="inlineStr">
         <is>
@@ -88375,10 +88358,10 @@
         </is>
       </c>
       <c r="B685">
-        <v>16.33332956488652</v>
+        <v>16.16669828591585</v>
       </c>
       <c r="C685">
-        <v>4.241621722594191</v>
+        <v>4.532316689713127</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -88386,10 +88369,10 @@
         </is>
       </c>
       <c r="E685">
-        <v>9.818048813604278</v>
+        <v>9.332282671048652</v>
       </c>
       <c r="F685">
-        <v>27.1721662562462</v>
+        <v>28.00623841781528</v>
       </c>
       <c r="G685" t="inlineStr">
         <is>
@@ -88427,10 +88410,10 @@
         </is>
       </c>
       <c r="B686">
-        <v>1.54545461929365</v>
+        <v>1.545455143673207</v>
       </c>
       <c r="C686">
-        <v>0.447842530481612</v>
+        <v>0.4800847432484988</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -88438,10 +88421,10 @@
         </is>
       </c>
       <c r="E686">
-        <v>0.8757793348668917</v>
+        <v>0.8406914814436539</v>
       </c>
       <c r="F686">
-        <v>2.727205227626311</v>
+        <v>2.841032238133903</v>
       </c>
       <c r="G686" t="inlineStr">
         <is>
@@ -88479,10 +88462,10 @@
         </is>
       </c>
       <c r="B687">
-        <v>3.833333431257338</v>
+        <v>3.33333249707218</v>
       </c>
       <c r="C687">
-        <v>0.8112962506493386</v>
+        <v>0.8133323755717657</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -88490,10 +88473,10 @@
         </is>
       </c>
       <c r="E687">
-        <v>2.531781246248079</v>
+        <v>2.06626325347086</v>
       </c>
       <c r="F687">
-        <v>5.803994802857193</v>
+        <v>5.377391054781275</v>
       </c>
       <c r="G687" t="inlineStr">
         <is>
@@ -88531,10 +88514,10 @@
         </is>
       </c>
       <c r="B688">
-        <v>2.363636266835618</v>
+        <v>1.909090360113869</v>
       </c>
       <c r="C688">
-        <v>0.5961366182560177</v>
+        <v>0.55755431217139</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -88542,10 +88525,10 @@
         </is>
       </c>
       <c r="E688">
-        <v>1.441775674200719</v>
+        <v>1.077038132746088</v>
       </c>
       <c r="F688">
-        <v>3.874927633938457</v>
+        <v>3.383934043065979</v>
       </c>
       <c r="G688" t="inlineStr">
         <is>
@@ -88583,10 +88566,10 @@
         </is>
       </c>
       <c r="B689">
-        <v>2.249999987142852</v>
+        <v>1.749999548964225</v>
       </c>
       <c r="C689">
-        <v>0.5515504631151854</v>
+        <v>0.5015968388198196</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -88594,10 +88577,10 @@
         </is>
       </c>
       <c r="E689">
-        <v>1.391632195455889</v>
+        <v>0.9978395859884358</v>
       </c>
       <c r="F689">
-        <v>3.637814617018397</v>
+        <v>3.069129010692989</v>
       </c>
       <c r="G689" t="inlineStr">
         <is>
@@ -88635,10 +88618,10 @@
         </is>
       </c>
       <c r="B690">
-        <v>1.799999990629237</v>
+        <v>1.6999978571175</v>
       </c>
       <c r="C690">
-        <v>0.5192607014555374</v>
+        <v>0.5383027145644053</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -88646,10 +88629,10 @@
         </is>
       </c>
       <c r="E690">
-        <v>1.022632145436371</v>
+        <v>0.9139368950355062</v>
       </c>
       <c r="F690">
-        <v>3.168294660718594</v>
+        <v>3.162135952605146</v>
       </c>
       <c r="G690" t="inlineStr">
         <is>
@@ -88687,10 +88670,10 @@
         </is>
       </c>
       <c r="B691">
-        <v>1.400000074627102</v>
+        <v>1.099998996213653</v>
       </c>
       <c r="C691">
-        <v>0.4407058502627884</v>
+        <v>0.4001823068299645</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -88698,10 +88681,10 @@
         </is>
       </c>
       <c r="E691">
-        <v>0.7554025218715603</v>
+        <v>0.5391667475535841</v>
       </c>
       <c r="F691">
-        <v>2.594643454591413</v>
+        <v>2.244199586048825</v>
       </c>
       <c r="G691" t="inlineStr">
         <is>
@@ -88739,10 +88722,10 @@
         </is>
       </c>
       <c r="B692">
-        <v>1.636363602401279</v>
+        <v>1.09090950271015</v>
       </c>
       <c r="C692">
-        <v>0.4648676468269207</v>
+        <v>0.3794873168799948</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -88750,10 +88733,10 @@
         </is>
       </c>
       <c r="E692">
-        <v>0.9377035237391991</v>
+        <v>0.5516796902801259</v>
       </c>
       <c r="F692">
-        <v>2.855578305375365</v>
+        <v>2.15720020887305</v>
       </c>
       <c r="G692" t="inlineStr">
         <is>
@@ -88791,10 +88774,10 @@
         </is>
       </c>
       <c r="B693">
-        <v>2.666666876172864</v>
+        <v>2.416667627176518</v>
       </c>
       <c r="C693">
-        <v>0.6214158657787909</v>
+        <v>0.6348924469086498</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -88802,10 +88785,10 @@
         </is>
       </c>
       <c r="E693">
-        <v>1.68893321995495</v>
+        <v>1.444090305264116</v>
       </c>
       <c r="F693">
-        <v>4.210416459608286</v>
+        <v>4.044263990245974</v>
       </c>
       <c r="G693" t="inlineStr">
         <is>
@@ -88843,33 +88826,16 @@
         </is>
       </c>
       <c r="B694">
-        <v>0.5454545588891426</v>
-      </c>
-      <c r="C694">
-        <v>0.2490485152163013</v>
+        <v>1</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
           <t>Inf</t>
         </is>
       </c>
-      <c r="E694">
-        <v>0.2228996421585102</v>
-      </c>
-      <c r="F694">
-        <v>1.334774129432535</v>
-      </c>
       <c r="G694" t="inlineStr">
         <is>
           <t>Fished</t>
-        </is>
-      </c>
-      <c r="H694" s="2">
-        <v>45972</v>
-      </c>
-      <c r="I694" t="inlineStr">
-        <is>
-          <t>Bloom</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
@@ -88900,10 +88866,10 @@
         </is>
       </c>
       <c r="B695">
-        <v>2.666639251966428</v>
+        <v>1.749998272118229</v>
       </c>
       <c r="C695">
-        <v>0.6792613350636907</v>
+        <v>0.5421035684374294</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -88911,10 +88877,10 @@
         </is>
       </c>
       <c r="E695">
-        <v>1.618607048182954</v>
+        <v>0.9535812559911198</v>
       </c>
       <c r="F695">
-        <v>4.393262038560149</v>
+        <v>3.211571046699882</v>
       </c>
       <c r="G695" t="inlineStr">
         <is>
@@ -88952,10 +88918,10 @@
         </is>
       </c>
       <c r="B696">
-        <v>3.750012066835287</v>
+        <v>3.666666191006504</v>
       </c>
       <c r="C696">
-        <v>0.8862844184747986</v>
+        <v>0.9774812782775562</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -88963,10 +88929,10 @@
         </is>
       </c>
       <c r="E696">
-        <v>2.359707657975684</v>
+        <v>2.174468384242714</v>
       </c>
       <c r="F696">
-        <v>5.959463009699302</v>
+        <v>6.182863385687872</v>
       </c>
       <c r="G696" t="inlineStr">
         <is>
@@ -89004,10 +88970,10 @@
         </is>
       </c>
       <c r="B697">
-        <v>3.833357472760673</v>
+        <v>2.750006445622891</v>
       </c>
       <c r="C697">
-        <v>0.9020564539027155</v>
+        <v>0.7711981789068322</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -89015,10 +88981,10 @@
         </is>
       </c>
       <c r="E697">
-        <v>2.416999842502706</v>
+        <v>1.587182876606194</v>
       </c>
       <c r="F697">
-        <v>6.079698167772487</v>
+        <v>4.764753679259755</v>
       </c>
       <c r="G697" t="inlineStr">
         <is>
@@ -89056,10 +89022,10 @@
         </is>
       </c>
       <c r="B698">
-        <v>3.249997889471595</v>
+        <v>2.999998166929671</v>
       </c>
       <c r="C698">
-        <v>0.7912672716533349</v>
+        <v>0.8276869680945046</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -89067,10 +89033,10 @@
         </is>
       </c>
       <c r="E698">
-        <v>2.016710611808841</v>
+        <v>1.746940195573217</v>
       </c>
       <c r="F698">
-        <v>5.237482373386258</v>
+        <v>5.151858675178206</v>
       </c>
       <c r="G698" t="inlineStr">
         <is>
@@ -89108,10 +89074,10 @@
         </is>
       </c>
       <c r="B699">
-        <v>3.714348942672417</v>
+        <v>3.428624545515361</v>
       </c>
       <c r="C699">
-        <v>1.0071510203415</v>
+        <v>0.9802889685734061</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -89119,10 +89085,10 @@
         </is>
       </c>
       <c r="E699">
-        <v>2.183122908125781</v>
+        <v>1.95771822799827</v>
       </c>
       <c r="F699">
-        <v>6.319565433801412</v>
+        <v>6.004677336089453</v>
       </c>
       <c r="G699" t="inlineStr">
         <is>
@@ -89160,10 +89126,10 @@
         </is>
       </c>
       <c r="B700">
-        <v>4.000021681756897</v>
+        <v>3.74998281832963</v>
       </c>
       <c r="C700">
-        <v>0.8127620885866613</v>
+        <v>0.8007951682781655</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -89171,10 +89137,10 @@
         </is>
       </c>
       <c r="E700">
-        <v>2.686007350767821</v>
+        <v>2.46750641018754</v>
       </c>
       <c r="F700">
-        <v>5.956861380126701</v>
+        <v>5.699021116909132</v>
       </c>
       <c r="G700" t="inlineStr">
         <is>
@@ -89212,10 +89178,10 @@
         </is>
       </c>
       <c r="B701">
-        <v>5.100026897636749</v>
+        <v>5.00010848870364</v>
       </c>
       <c r="C701">
-        <v>1.071624757474003</v>
+        <v>1.096107371163305</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -89223,10 +89189,10 @@
         </is>
       </c>
       <c r="E701">
-        <v>3.378444682756531</v>
+        <v>3.253732303104936</v>
       </c>
       <c r="F701">
-        <v>7.698890110403137</v>
+        <v>7.683817404077293</v>
       </c>
       <c r="G701" t="inlineStr">
         <is>
@@ -89264,10 +89230,10 @@
         </is>
       </c>
       <c r="B702">
-        <v>4.555518083589063</v>
+        <v>3.999988557616297</v>
       </c>
       <c r="C702">
-        <v>1.035419914302739</v>
+        <v>0.9711892636793696</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -89275,10 +89241,10 @@
         </is>
       </c>
       <c r="E702">
-        <v>2.917889791077031</v>
+        <v>2.485356585653379</v>
       </c>
       <c r="F702">
-        <v>7.112244291531951</v>
+        <v>6.437671179025227</v>
       </c>
       <c r="G702" t="inlineStr">
         <is>
@@ -89316,10 +89282,10 @@
         </is>
       </c>
       <c r="B703">
-        <v>9.666662963503461</v>
+        <v>9.333317693249185</v>
       </c>
       <c r="C703">
-        <v>1.648252277368252</v>
+        <v>1.677620018232546</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -89327,10 +89293,10 @@
         </is>
       </c>
       <c r="E703">
-        <v>6.920526239132145</v>
+        <v>6.562005188350772</v>
       </c>
       <c r="F703">
-        <v>13.50249527580545</v>
+        <v>13.27503052234127</v>
       </c>
       <c r="G703" t="inlineStr">
         <is>
@@ -89368,10 +89334,10 @@
         </is>
       </c>
       <c r="B704">
-        <v>12.58339902349283</v>
+        <v>11.91672645846292</v>
       </c>
       <c r="C704">
-        <v>2.070540677581051</v>
+        <v>2.076826466427103</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -89379,10 +89345,10 @@
         </is>
       </c>
       <c r="E704">
-        <v>9.114579828560366</v>
+        <v>8.468588656411397</v>
       </c>
       <c r="F704">
-        <v>17.37237853666922</v>
+        <v>16.76883542788662</v>
       </c>
       <c r="G704" t="inlineStr">
         <is>
@@ -89420,10 +89386,10 @@
         </is>
       </c>
       <c r="B705">
-        <v>9.416656118847893</v>
+        <v>9.166663679319951</v>
       </c>
       <c r="C705">
-        <v>1.611931076220594</v>
+        <v>1.651799507948602</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -89431,10 +89397,10 @@
         </is>
       </c>
       <c r="E705">
-        <v>6.732697874333915</v>
+        <v>6.439140042001321</v>
       </c>
       <c r="F705">
-        <v>13.17056165533169</v>
+        <v>13.0495256294577</v>
       </c>
       <c r="G705" t="inlineStr">
         <is>
@@ -89472,10 +89438,10 @@
         </is>
       </c>
       <c r="B706">
-        <v>14.30019705749156</v>
+        <v>14.20031963931948</v>
       </c>
       <c r="C706">
-        <v>2.539498240015555</v>
+        <v>2.660372835585603</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -89483,10 +89449,10 @@
         </is>
       </c>
       <c r="E706">
-        <v>10.09674830702394</v>
+        <v>9.83623578485444</v>
       </c>
       <c r="F706">
-        <v>20.25361330843814</v>
+        <v>20.50063482306272</v>
       </c>
       <c r="G706" t="inlineStr">
         <is>
@@ -89524,10 +89490,10 @@
         </is>
       </c>
       <c r="B707">
-        <v>9.7499782643191</v>
+        <v>9.500014059214067</v>
       </c>
       <c r="C707">
-        <v>1.660349709358064</v>
+        <v>1.703439628933879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -89535,10 +89501,10 @@
         </is>
       </c>
       <c r="E707">
-        <v>6.983132372950932</v>
+        <v>6.684916799794426</v>
       </c>
       <c r="F707">
-        <v>13.61309954869487</v>
+        <v>13.50058195608961</v>
       </c>
       <c r="G707" t="inlineStr">
         <is>
@@ -89576,10 +89542,10 @@
         </is>
       </c>
       <c r="B708">
-        <v>18.2856441078357</v>
+        <v>18.28540360142785</v>
       </c>
       <c r="C708">
-        <v>3.786232593747115</v>
+        <v>4.001607217492696</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -89587,10 +89553,10 @@
         </is>
       </c>
       <c r="E708">
-        <v>12.18597098349819</v>
+        <v>11.907654688821</v>
       </c>
       <c r="F708">
-        <v>27.43850128079342</v>
+        <v>28.07907968485237</v>
       </c>
       <c r="G708" t="inlineStr">
         <is>
@@ -89628,10 +89594,10 @@
         </is>
       </c>
       <c r="B709">
-        <v>9.666742046688869</v>
+        <v>9.333333091391804</v>
       </c>
       <c r="C709">
-        <v>1.903256530880975</v>
+        <v>1.93715264891464</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -89639,10 +89605,10 @@
         </is>
       </c>
       <c r="E709">
-        <v>6.571878880580382</v>
+        <v>6.213955215118015</v>
       </c>
       <c r="F709">
-        <v>14.21905416932608</v>
+        <v>14.01862478553684</v>
       </c>
       <c r="G709" t="inlineStr">
         <is>
@@ -89680,10 +89646,10 @@
         </is>
       </c>
       <c r="B710">
-        <v>15.75001482102256</v>
+        <v>15.6665639480151</v>
       </c>
       <c r="C710">
-        <v>2.527061557034445</v>
+        <v>2.6540313389652</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -89691,10 +89657,10 @@
         </is>
       </c>
       <c r="E710">
-        <v>11.50024810278743</v>
+        <v>11.24019754682781</v>
       </c>
       <c r="F710">
-        <v>21.57022741120729</v>
+        <v>21.83602422597229</v>
       </c>
       <c r="G710" t="inlineStr">
         <is>
@@ -89732,10 +89698,10 @@
         </is>
       </c>
       <c r="B711">
-        <v>22.79988478083833</v>
+        <v>22.59993081496998</v>
       </c>
       <c r="C711">
-        <v>3.877923894151356</v>
+        <v>4.073037737024262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -89743,10 +89709,10 @@
         </is>
       </c>
       <c r="E711">
-        <v>16.33638021989728</v>
+        <v>15.8745207186344</v>
       </c>
       <c r="F711">
-        <v>31.82068114369413</v>
+        <v>32.17463266414556</v>
       </c>
       <c r="G711" t="inlineStr">
         <is>
@@ -89784,10 +89750,10 @@
         </is>
       </c>
       <c r="B712">
-        <v>12.00009313367145</v>
+        <v>11.81819573541206</v>
       </c>
       <c r="C712">
-        <v>2.074586930799437</v>
+        <v>2.153299699209426</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -89795,10 +89761,10 @@
         </is>
       </c>
       <c r="E712">
-        <v>8.551220902946241</v>
+        <v>8.269142905858498</v>
       </c>
       <c r="F712">
-        <v>16.83996201842639</v>
+        <v>16.89047486911358</v>
       </c>
       <c r="G712" t="inlineStr">
         <is>
@@ -89836,10 +89802,10 @@
         </is>
       </c>
       <c r="B713">
-        <v>11.49999495648388</v>
+        <v>10.66667169532228</v>
       </c>
       <c r="C713">
-        <v>2.04367736625955</v>
+        <v>2.159685987363477</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -89847,10 +89813,10 @@
         </is>
       </c>
       <c r="E713">
-        <v>8.117637282347944</v>
+        <v>7.17275101083049</v>
       </c>
       <c r="F713">
-        <v>16.29167199755725</v>
+        <v>15.86251702923895</v>
       </c>
       <c r="G713" t="inlineStr">
         <is>
@@ -89888,10 +89854,10 @@
         </is>
       </c>
       <c r="B714">
-        <v>10.09091303962031</v>
+        <v>9.272731029898418</v>
       </c>
       <c r="C714">
-        <v>1.902777070516539</v>
+        <v>1.988827570953444</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -89899,10 +89865,10 @@
         </is>
       </c>
       <c r="E714">
-        <v>6.973085490900045</v>
+        <v>6.090330121615305</v>
       </c>
       <c r="F714">
-        <v>14.60279328369974</v>
+        <v>14.11804270636746</v>
       </c>
       <c r="G714" t="inlineStr">
         <is>
@@ -89940,10 +89906,10 @@
         </is>
       </c>
       <c r="B715">
-        <v>12.08333963624879</v>
+        <v>11.58332894512159</v>
       </c>
       <c r="C715">
-        <v>2.13541861535023</v>
+        <v>2.327528997190422</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -89951,10 +89917,10 @@
         </is>
       </c>
       <c r="E715">
-        <v>8.545924762019794</v>
+        <v>7.812585758352959</v>
       </c>
       <c r="F715">
-        <v>17.08499674767003</v>
+        <v>17.17402068930094</v>
       </c>
       <c r="G715" t="inlineStr">
         <is>
@@ -89992,10 +89958,10 @@
         </is>
       </c>
       <c r="B716">
-        <v>12.10000933477769</v>
+        <v>11.00000158297498</v>
       </c>
       <c r="C716">
-        <v>2.342104899445597</v>
+        <v>2.432693225012201</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -90003,10 +89969,10 @@
         </is>
       </c>
       <c r="E716">
-        <v>8.279902614164937</v>
+        <v>7.130930580660277</v>
       </c>
       <c r="F716">
-        <v>17.68260240781508</v>
+        <v>16.96833722566518</v>
       </c>
       <c r="G716" t="inlineStr">
         <is>
@@ -90044,10 +90010,10 @@
         </is>
       </c>
       <c r="B717">
-        <v>1.714284894535437</v>
+        <v>1.142856896921749</v>
       </c>
       <c r="C717">
-        <v>0.5821339463213046</v>
+        <v>0.4970970330433414</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -90055,10 +90021,10 @@
         </is>
       </c>
       <c r="E717">
-        <v>0.8811166892140451</v>
+        <v>0.487251553444865</v>
       </c>
       <c r="F717">
-        <v>3.335282075128726</v>
+        <v>2.680590503216126</v>
       </c>
       <c r="G717" t="inlineStr">
         <is>
@@ -90096,10 +90062,10 @@
         </is>
       </c>
       <c r="B718">
-        <v>7.142856205285217</v>
+        <v>7.142856667544796</v>
       </c>
       <c r="C718">
-        <v>1.628509505944091</v>
+        <v>2.072538650134741</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -90107,10 +90073,10 @@
         </is>
       </c>
       <c r="E718">
-        <v>4.568833264967375</v>
+        <v>4.044745358920495</v>
       </c>
       <c r="F718">
-        <v>11.16705115080313</v>
+        <v>12.61399589978293</v>
       </c>
       <c r="G718" t="inlineStr">
         <is>
@@ -90148,10 +90114,10 @@
         </is>
       </c>
       <c r="B719">
-        <v>1.000000798323849</v>
+        <v>0.4285714764090481</v>
       </c>
       <c r="C719">
-        <v>0.4181356107739144</v>
+        <v>0.2702120103262265</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -90159,10 +90125,10 @@
         </is>
       </c>
       <c r="E719">
-        <v>0.4406390210070776</v>
+        <v>0.1245504409211839</v>
       </c>
       <c r="F719">
-        <v>2.26943495463211</v>
+        <v>1.474691771726931</v>
       </c>
       <c r="G719" t="inlineStr">
         <is>
@@ -90200,10 +90166,10 @@
         </is>
       </c>
       <c r="B720">
-        <v>6.000000720906718</v>
+        <v>5.416667574300592</v>
       </c>
       <c r="C720">
-        <v>1.082396240866165</v>
+        <v>1.244995916771296</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -90211,10 +90177,10 @@
         </is>
       </c>
       <c r="E720">
-        <v>4.213035279872902</v>
+        <v>3.45213250371358</v>
       </c>
       <c r="F720">
-        <v>8.544910322224307</v>
+        <v>8.49917770506117</v>
       </c>
       <c r="G720" t="inlineStr">
         <is>
@@ -90252,10 +90218,10 @@
         </is>
       </c>
       <c r="B721">
-        <v>37.18182470428442</v>
+        <v>36.09090888220705</v>
       </c>
       <c r="C721">
-        <v>2.673307598532068</v>
+        <v>2.677841342548781</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -90263,10 +90229,10 @@
         </is>
       </c>
       <c r="E721">
-        <v>32.2946669285772</v>
+        <v>31.20621668059263</v>
       </c>
       <c r="F721">
-        <v>42.8085569483544</v>
+        <v>41.74019930951254</v>
       </c>
       <c r="G721" t="inlineStr">
         <is>
@@ -90304,10 +90270,10 @@
         </is>
       </c>
       <c r="B722">
-        <v>41.91666115864358</v>
+        <v>41.41666602217857</v>
       </c>
       <c r="C722">
-        <v>2.807292845903284</v>
+        <v>2.854306290982213</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -90315,10 +90281,10 @@
         </is>
       </c>
       <c r="E722">
-        <v>36.76029538524285</v>
+        <v>36.18370251207052</v>
       </c>
       <c r="F722">
-        <v>47.79631023840677</v>
+        <v>47.40643177188574</v>
       </c>
       <c r="G722" t="inlineStr">
         <is>
@@ -90356,10 +90322,10 @@
         </is>
       </c>
       <c r="B723">
-        <v>3.00000728627757</v>
+        <v>2.636361311716807</v>
       </c>
       <c r="C723">
-        <v>1.331831329441892</v>
+        <v>1.53738000747012</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -90367,10 +90333,10 @@
         </is>
       </c>
       <c r="E723">
-        <v>1.256717317463464</v>
+        <v>0.8406811305052414</v>
       </c>
       <c r="F723">
-        <v>7.161549851070758</v>
+        <v>8.26758293211606</v>
       </c>
       <c r="G723" t="inlineStr">
         <is>
@@ -90408,10 +90374,10 @@
         </is>
       </c>
       <c r="B724">
-        <v>5.800000852004977</v>
+        <v>4.53333437055332</v>
       </c>
       <c r="C724">
-        <v>2.121570901154667</v>
+        <v>2.215286006292295</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -90419,10 +90385,10 @@
         </is>
       </c>
       <c r="E724">
-        <v>2.831840049204033</v>
+        <v>1.739660764299698</v>
       </c>
       <c r="F724">
-        <v>11.87920549845811</v>
+        <v>11.81329195724717</v>
       </c>
       <c r="G724" t="inlineStr">
         <is>
@@ -90460,10 +90426,10 @@
         </is>
       </c>
       <c r="B725">
-        <v>3.812505311945262</v>
+        <v>3.249999640409015</v>
       </c>
       <c r="C725">
-        <v>1.380190298110802</v>
+        <v>1.556317815995099</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -90471,10 +90437,10 @@
         </is>
       </c>
       <c r="E725">
-        <v>1.875259392256468</v>
+        <v>1.271366960745994</v>
       </c>
       <c r="F725">
-        <v>7.751032637741321</v>
+        <v>8.307985018315264</v>
       </c>
       <c r="G725" t="inlineStr">
         <is>
@@ -90512,10 +90478,10 @@
         </is>
       </c>
       <c r="B726">
-        <v>4.866664900461062</v>
+        <v>4.333333403973765</v>
       </c>
       <c r="C726">
-        <v>1.794771699035372</v>
+        <v>2.120559413809725</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -90523,10 +90489,10 @@
         </is>
       </c>
       <c r="E726">
-        <v>2.362206251222554</v>
+        <v>1.660650495534624</v>
       </c>
       <c r="F726">
-        <v>10.0264010566909</v>
+        <v>11.30748368816137</v>
       </c>
       <c r="G726" t="inlineStr">
         <is>
@@ -90564,10 +90530,10 @@
         </is>
       </c>
       <c r="B727">
-        <v>1.210527577642391</v>
+        <v>1.210527099168062</v>
       </c>
       <c r="C727">
-        <v>0.4529964782998704</v>
+        <v>0.5682909688242261</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -90575,10 +90541,10 @@
         </is>
       </c>
       <c r="E727">
-        <v>0.5813572263512081</v>
+        <v>0.4823603566546594</v>
       </c>
       <c r="F727">
-        <v>2.520613746267421</v>
+        <v>3.037927635643909</v>
       </c>
       <c r="G727" t="inlineStr">
         <is>
@@ -90616,10 +90582,10 @@
         </is>
       </c>
       <c r="B728">
-        <v>2.62500009480758</v>
+        <v>2.062500019762727</v>
       </c>
       <c r="C728">
-        <v>0.5460528981946179</v>
+        <v>0.4978447662631032</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -90627,10 +90593,10 @@
         </is>
       </c>
       <c r="E728">
-        <v>1.746072432726234</v>
+        <v>1.285084091069771</v>
       </c>
       <c r="F728">
-        <v>3.946357189192381</v>
+        <v>3.310216320536715</v>
       </c>
       <c r="G728" t="inlineStr">
         <is>
@@ -90668,10 +90634,10 @@
         </is>
       </c>
       <c r="B729">
-        <v>1.999999900609888</v>
+        <v>1.374999923335429</v>
       </c>
       <c r="C729">
-        <v>0.6369480501381657</v>
+        <v>0.5268797054383634</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -90679,10 +90645,10 @@
         </is>
       </c>
       <c r="E729">
-        <v>1.071382082306633</v>
+        <v>0.6488357753231344</v>
       </c>
       <c r="F729">
-        <v>3.733494958052461</v>
+        <v>2.913872602402144</v>
       </c>
       <c r="G729" t="inlineStr">
         <is>
@@ -90720,10 +90686,10 @@
         </is>
       </c>
       <c r="B730">
-        <v>2.400014526750949</v>
+        <v>1.299999974685588</v>
       </c>
       <c r="C730">
-        <v>1.164195237073768</v>
+        <v>0.884768922178836</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -90731,10 +90697,10 @@
         </is>
       </c>
       <c r="E730">
-        <v>0.9275009795287337</v>
+        <v>0.3424702223102319</v>
       </c>
       <c r="F730">
-        <v>6.210311208018663</v>
+        <v>4.934735413730712</v>
       </c>
       <c r="G730" t="inlineStr">
         <is>
@@ -90772,10 +90738,10 @@
         </is>
       </c>
       <c r="B731">
-        <v>2.000001232811482</v>
+        <v>1.499999950246205</v>
       </c>
       <c r="C731">
-        <v>0.9871856419465741</v>
+        <v>1.009521539497202</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -90783,10 +90749,10 @@
         </is>
       </c>
       <c r="E731">
-        <v>0.7601224358728567</v>
+        <v>0.4010701718519992</v>
       </c>
       <c r="F731">
-        <v>5.262316624892411</v>
+        <v>5.609990492060081</v>
       </c>
       <c r="G731" t="inlineStr">
         <is>
@@ -90824,10 +90790,10 @@
         </is>
       </c>
       <c r="B732">
-        <v>2.500000877058497</v>
+        <v>2.500000633842356</v>
       </c>
       <c r="C732">
-        <v>1.208391743526469</v>
+        <v>1.632256854185475</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -90835,10 +90801,10 @@
         </is>
       </c>
       <c r="E732">
-        <v>0.9694074178906734</v>
+        <v>0.6953259509171513</v>
       </c>
       <c r="F732">
-        <v>6.447242170781603</v>
+        <v>8.98859471729522</v>
       </c>
       <c r="G732" t="inlineStr">
         <is>
@@ -90876,10 +90842,10 @@
         </is>
       </c>
       <c r="B733">
-        <v>0.7142826644799463</v>
+        <v>0.5714283777240314</v>
       </c>
       <c r="C733">
-        <v>0.4931235840731789</v>
+        <v>0.5116856249105285</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -90887,10 +90853,10 @@
         </is>
       </c>
       <c r="E733">
-        <v>0.1845954630565509</v>
+        <v>0.09879916109006662</v>
       </c>
       <c r="F733">
-        <v>2.763880088538641</v>
+        <v>3.304991532981226</v>
       </c>
       <c r="G733" t="inlineStr">
         <is>
@@ -90928,10 +90894,10 @@
         </is>
       </c>
       <c r="B734">
-        <v>1.437498613210762</v>
+        <v>1.437500147437496</v>
       </c>
       <c r="C734">
-        <v>0.5830277447260189</v>
+        <v>0.7672862844015628</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -90939,10 +90905,10 @@
         </is>
       </c>
       <c r="E734">
-        <v>0.6491916625817346</v>
+        <v>0.5049715230375144</v>
       </c>
       <c r="F734">
-        <v>3.183038819021648</v>
+        <v>4.092125158767236</v>
       </c>
       <c r="G734" t="inlineStr">
         <is>
@@ -90980,10 +90946,10 @@
         </is>
       </c>
       <c r="B735">
-        <v>1.249999080846627</v>
+        <v>1.187499826908258</v>
       </c>
       <c r="C735">
-        <v>0.5169330094441744</v>
+        <v>0.6439464818835698</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -90991,10 +90957,10 @@
         </is>
       </c>
       <c r="E735">
-        <v>0.5557738318371683</v>
+        <v>0.4102530445084847</v>
       </c>
       <c r="F735">
-        <v>2.811391275750449</v>
+        <v>3.437283056842687</v>
       </c>
       <c r="G735" t="inlineStr">
         <is>
@@ -91032,10 +90998,10 @@
         </is>
       </c>
       <c r="B736">
-        <v>1.249999696506304</v>
+        <v>1.249999992006448</v>
       </c>
       <c r="C736">
-        <v>0.7724749588379989</v>
+        <v>0.828547452617472</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -91043,10 +91009,10 @@
         </is>
       </c>
       <c r="E736">
-        <v>0.3722924922439869</v>
+        <v>0.3409583340575845</v>
       </c>
       <c r="F736">
-        <v>4.196966830697859</v>
+        <v>4.582671323564803</v>
       </c>
       <c r="G736" t="inlineStr">
         <is>
@@ -91084,10 +91050,10 @@
         </is>
       </c>
       <c r="B737">
-        <v>3.919156701509131E-10</v>
+        <v>4.157456889792702E-10</v>
       </c>
       <c r="C737">
-        <v>8.082033375071185E-06</v>
+        <v>8.324117634829842E-06</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -91138,10 +91104,10 @@
         </is>
       </c>
       <c r="B738">
-        <v>4.333336889768712</v>
+        <v>3.666666651333411</v>
       </c>
       <c r="C738">
-        <v>2.449220015210677</v>
+        <v>2.347949461603431</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -91149,10 +91115,10 @@
         </is>
       </c>
       <c r="E738">
-        <v>1.43126418866921</v>
+        <v>1.045212615982603</v>
       </c>
       <c r="F738">
-        <v>13.11973620865201</v>
+        <v>12.86287988340197</v>
       </c>
       <c r="G738" t="inlineStr">
         <is>
@@ -91190,10 +91156,10 @@
         </is>
       </c>
       <c r="B739">
-        <v>0.6666665184560862</v>
+        <v>0.6666666688257734</v>
       </c>
       <c r="C739">
-        <v>0.4062107672586078</v>
+        <v>0.4266507746369725</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -91201,10 +91167,10 @@
         </is>
       </c>
       <c r="E739">
-        <v>0.2019564281933663</v>
+        <v>0.1901778999806689</v>
       </c>
       <c r="F739">
-        <v>2.200693737783969</v>
+        <v>2.336993138363764</v>
       </c>
       <c r="G739" t="inlineStr">
         <is>
@@ -91242,10 +91208,10 @@
         </is>
       </c>
       <c r="B740">
-        <v>2.33333600774572</v>
+        <v>1.333333228532975</v>
       </c>
       <c r="C740">
-        <v>0.5932423724109908</v>
+        <v>0.4307926913486987</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -91253,10 +91219,10 @@
         </is>
       </c>
       <c r="E740">
-        <v>1.417628126651103</v>
+        <v>0.7078155967313278</v>
       </c>
       <c r="F740">
-        <v>3.840539576415081</v>
+        <v>2.511639340133068</v>
       </c>
       <c r="G740" t="inlineStr">
         <is>
@@ -91294,10 +91260,10 @@
         </is>
       </c>
       <c r="B741">
-        <v>2.272727176738618</v>
+        <v>1.818181917717993</v>
       </c>
       <c r="C741">
-        <v>0.5277783787981438</v>
+        <v>0.471425671187728</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -91305,10 +91271,10 @@
         </is>
       </c>
       <c r="E741">
-        <v>1.441714139542202</v>
+        <v>1.093790895341951</v>
       </c>
       <c r="F741">
-        <v>3.582741320360817</v>
+        <v>3.022319439661445</v>
       </c>
       <c r="G741" t="inlineStr">
         <is>
@@ -91346,10 +91312,10 @@
         </is>
       </c>
       <c r="B742">
-        <v>1.000001229759043</v>
+        <v>0.6666666958815552</v>
       </c>
       <c r="C742">
-        <v>0.3579574579479923</v>
+        <v>0.2888470651164315</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -91357,10 +91323,10 @@
         </is>
       </c>
       <c r="E742">
-        <v>0.49580050886044</v>
+        <v>0.2851728492164312</v>
       </c>
       <c r="F742">
-        <v>2.016945206083043</v>
+        <v>1.558509109891875</v>
       </c>
       <c r="G742" t="inlineStr">
         <is>
@@ -91398,10 +91364,10 @@
         </is>
       </c>
       <c r="B743">
-        <v>2.24999779401284</v>
+        <v>1.833333508361822</v>
       </c>
       <c r="C743">
-        <v>0.5021264193852972</v>
+        <v>0.4537161684691005</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -91409,10 +91375,10 @@
         </is>
       </c>
       <c r="E743">
-        <v>1.452852610373663</v>
+        <v>1.128716365719004</v>
       </c>
       <c r="F743">
-        <v>3.484517312296813</v>
+        <v>2.977817860150546</v>
       </c>
       <c r="G743" t="inlineStr">
         <is>
@@ -91450,10 +91416,10 @@
         </is>
       </c>
       <c r="B744">
-        <v>8.666666402351137</v>
+        <v>8.333333470528286</v>
       </c>
       <c r="C744">
-        <v>1.747992022993099</v>
+        <v>1.782907251737716</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -91461,10 +91427,10 @@
         </is>
       </c>
       <c r="E744">
-        <v>5.836762938208994</v>
+        <v>5.479048636581616</v>
       </c>
       <c r="F744">
-        <v>12.86862381165848</v>
+        <v>12.67454467685716</v>
       </c>
       <c r="G744" t="inlineStr">
         <is>
@@ -91502,10 +91468,10 @@
         </is>
       </c>
       <c r="B745">
-        <v>7.999989215115778</v>
+        <v>7.999998620194553</v>
       </c>
       <c r="C745">
-        <v>1.451363159733457</v>
+        <v>1.509025238120127</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -91513,10 +91479,10 @@
         </is>
       </c>
       <c r="E745">
-        <v>5.606139149776291</v>
+        <v>5.527507085596076</v>
       </c>
       <c r="F745">
-        <v>11.41602549136202</v>
+        <v>11.57845244375894</v>
       </c>
       <c r="G745" t="inlineStr">
         <is>
@@ -91554,10 +91520,10 @@
         </is>
       </c>
       <c r="B746">
-        <v>9.000008941362793</v>
+        <v>8.999997899707967</v>
       </c>
       <c r="C746">
-        <v>1.78315778954563</v>
+        <v>1.862176838026494</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -91565,10 +91531,10 @@
         </is>
       </c>
       <c r="E746">
-        <v>6.10373544306906</v>
+        <v>5.999589004454471</v>
       </c>
       <c r="F746">
-        <v>13.27058842902306</v>
+        <v>13.50091850201878</v>
       </c>
       <c r="G746" t="inlineStr">
         <is>
@@ -91606,10 +91572,10 @@
         </is>
       </c>
       <c r="B747">
-        <v>9.250000000109459</v>
+        <v>9.249998645193346</v>
       </c>
       <c r="C747">
-        <v>1.566788260927024</v>
+        <v>1.637997412289485</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -91617,10 +91583,10 @@
         </is>
       </c>
       <c r="E747">
-        <v>6.636866391656568</v>
+        <v>6.537477327179014</v>
       </c>
       <c r="F747">
-        <v>12.8920027845654</v>
+        <v>13.08799566774173</v>
       </c>
       <c r="G747" t="inlineStr">
         <is>
@@ -91658,10 +91624,10 @@
         </is>
       </c>
       <c r="B748">
-        <v>4.999990058833998</v>
+        <v>4.999998108898272</v>
       </c>
       <c r="C748">
-        <v>1.016496887726451</v>
+        <v>1.04240646230561</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -91669,10 +91635,10 @@
         </is>
       </c>
       <c r="E748">
-        <v>3.356758156671277</v>
+        <v>3.322845702138276</v>
       </c>
       <c r="F748">
-        <v>7.447632335011564</v>
+        <v>7.523665956832911</v>
       </c>
       <c r="G748" t="inlineStr">
         <is>
@@ -91710,10 +91676,10 @@
         </is>
       </c>
       <c r="B749">
-        <v>11.19990379887212</v>
+        <v>10.70000033871686</v>
       </c>
       <c r="C749">
-        <v>2.316167016255101</v>
+        <v>2.270701724638784</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -91721,10 +91687,10 @@
         </is>
       </c>
       <c r="E749">
-        <v>7.467646785978205</v>
+        <v>7.059045224162161</v>
       </c>
       <c r="F749">
-        <v>16.79750645672226</v>
+        <v>16.21890831024245</v>
       </c>
       <c r="G749" t="inlineStr">
         <is>
@@ -91762,10 +91728,10 @@
         </is>
       </c>
       <c r="B750">
-        <v>8.199895399563117</v>
+        <v>8.199788189448627</v>
       </c>
       <c r="C750">
-        <v>1.759326178637576</v>
+        <v>1.794311013738455</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -91773,10 +91739,10 @@
         </is>
       </c>
       <c r="E750">
-        <v>5.384916981809727</v>
+        <v>5.339975312659042</v>
       </c>
       <c r="F750">
-        <v>12.48641061522537</v>
+        <v>12.59116801390993</v>
       </c>
       <c r="G750" t="inlineStr">
         <is>
@@ -91814,10 +91780,10 @@
         </is>
       </c>
       <c r="B751">
-        <v>8.222331182812388</v>
+        <v>7.999973522977585</v>
       </c>
       <c r="C751">
-        <v>1.858912257721848</v>
+        <v>1.851155791736299</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -91825,10 +91791,10 @@
         </is>
       </c>
       <c r="E751">
-        <v>5.279034878253396</v>
+        <v>5.083052138537242</v>
       </c>
       <c r="F751">
-        <v>12.80664584322979</v>
+        <v>12.59077708118092</v>
       </c>
       <c r="G751" t="inlineStr">
         <is>
@@ -91866,10 +91832,10 @@
         </is>
       </c>
       <c r="B752">
-        <v>9.625054413812377</v>
+        <v>8.875066187011347</v>
       </c>
       <c r="C752">
-        <v>2.263132044394887</v>
+        <v>2.150195323374418</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -91877,10 +91843,10 @@
         </is>
       </c>
       <c r="E752">
-        <v>6.071007838350603</v>
+        <v>5.52011129567124</v>
       </c>
       <c r="F752">
-        <v>15.25968586033293</v>
+        <v>14.26906009768308</v>
       </c>
       <c r="G752" t="inlineStr">
         <is>
@@ -91918,10 +91884,10 @@
         </is>
       </c>
       <c r="B753">
-        <v>8.545438414271235</v>
+        <v>8.545522789250178</v>
       </c>
       <c r="C753">
-        <v>1.738757885982863</v>
+        <v>1.773755644855349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -91929,10 +91895,10 @@
         </is>
       </c>
       <c r="E753">
-        <v>5.735068695377905</v>
+        <v>5.689296519960497</v>
       </c>
       <c r="F753">
-        <v>12.73298046995592</v>
+        <v>12.83567475968034</v>
       </c>
       <c r="G753" t="inlineStr">
         <is>
@@ -91970,10 +91936,10 @@
         </is>
       </c>
       <c r="B754">
-        <v>7.908897951933557</v>
+        <v>7.636433806264698</v>
       </c>
       <c r="C754">
-        <v>1.625781638334448</v>
+        <v>1.60818858925469</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -91981,10 +91947,10 @@
         </is>
       </c>
       <c r="E754">
-        <v>5.286155169434993</v>
+        <v>5.053968053174418</v>
       </c>
       <c r="F754">
-        <v>11.83292294856802</v>
+        <v>11.53848236947885</v>
       </c>
       <c r="G754" t="inlineStr">
         <is>
@@ -92022,10 +91988,10 @@
         </is>
       </c>
       <c r="B755">
-        <v>7.416798514290022</v>
+        <v>7.249961519755068</v>
       </c>
       <c r="C755">
-        <v>1.472852225323446</v>
+        <v>1.472213029688527</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -92033,10 +91999,10 @@
         </is>
       </c>
       <c r="E755">
-        <v>5.025532443540291</v>
+        <v>4.869523968409902</v>
       </c>
       <c r="F755">
-        <v>10.94588500215175</v>
+        <v>10.79406167397772</v>
       </c>
       <c r="G755" t="inlineStr">
         <is>
@@ -92074,10 +92040,10 @@
         </is>
       </c>
       <c r="B756">
-        <v>10.66660697828469</v>
+        <v>10.33333511334765</v>
       </c>
       <c r="C756">
-        <v>2.024168190941358</v>
+        <v>2.00918233285433</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -92085,10 +92051,10 @@
         </is>
       </c>
       <c r="E756">
-        <v>7.353540268705851</v>
+        <v>7.058874620131298</v>
       </c>
       <c r="F756">
-        <v>15.47234396925593</v>
+        <v>15.12674757817944</v>
       </c>
       <c r="G756" t="inlineStr">
         <is>
@@ -92126,10 +92092,10 @@
         </is>
       </c>
       <c r="B757">
-        <v>10.33336404019508</v>
+        <v>10.22215222306339</v>
       </c>
       <c r="C757">
-        <v>2.27220124980129</v>
+        <v>2.297696081246998</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -92137,10 +92103,10 @@
         </is>
       </c>
       <c r="E757">
-        <v>6.715389402789933</v>
+        <v>6.579797579629747</v>
       </c>
       <c r="F757">
-        <v>15.90055408295985</v>
+        <v>15.88079189471961</v>
       </c>
       <c r="G757" t="inlineStr">
         <is>
@@ -92178,10 +92144,10 @@
         </is>
       </c>
       <c r="B758">
-        <v>11.27269064370003</v>
+        <v>11.27258685709068</v>
       </c>
       <c r="C758">
-        <v>2.22123662894086</v>
+        <v>2.268821235087921</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -92189,10 +92155,10 @@
         </is>
       </c>
       <c r="E758">
-        <v>7.661289586869488</v>
+        <v>7.598068176643337</v>
       </c>
       <c r="F758">
-        <v>16.586444476182</v>
+        <v>16.72414770392213</v>
       </c>
       <c r="G758" t="inlineStr">
         <is>
@@ -92230,10 +92196,10 @@
         </is>
       </c>
       <c r="B759">
-        <v>11.62502618282961</v>
+        <v>11.62502855930422</v>
       </c>
       <c r="C759">
-        <v>2.677578288369793</v>
+        <v>2.735332210886747</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -92241,10 +92207,10 @@
         </is>
       </c>
       <c r="E759">
-        <v>7.401806250160083</v>
+        <v>7.330085075484345</v>
       </c>
       <c r="F759">
-        <v>18.25787236035141</v>
+        <v>18.43652394385192</v>
       </c>
       <c r="G759" t="inlineStr">
         <is>
@@ -92282,10 +92248,10 @@
         </is>
       </c>
       <c r="B760">
-        <v>8.916681645978368</v>
+        <v>8.749964410343294</v>
       </c>
       <c r="C760">
-        <v>1.727741170127651</v>
+        <v>1.733838996434784</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -92293,10 +92259,10 @@
         </is>
       </c>
       <c r="E760">
-        <v>6.099161885861717</v>
+        <v>5.933861934068323</v>
       </c>
       <c r="F760">
-        <v>13.03576016895547</v>
+        <v>12.9025376783215</v>
       </c>
       <c r="G760" t="inlineStr">
         <is>
@@ -92334,10 +92300,10 @@
         </is>
       </c>
       <c r="B761">
-        <v>12.11130800140974</v>
+        <v>11.88883118300842</v>
       </c>
       <c r="C761">
-        <v>2.619335324558253</v>
+        <v>2.631721045472243</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -92345,10 +92311,10 @@
         </is>
       </c>
       <c r="E761">
-        <v>7.926840006760417</v>
+        <v>7.704004281326037</v>
       </c>
       <c r="F761">
-        <v>18.50469813695144</v>
+        <v>18.34686245446176</v>
       </c>
       <c r="G761" t="inlineStr">
         <is>
@@ -92386,10 +92352,10 @@
         </is>
       </c>
       <c r="B762">
-        <v>6.181819781007189</v>
+        <v>6.181751559719444</v>
       </c>
       <c r="C762">
-        <v>1.318170753001523</v>
+        <v>1.34231798293856</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -92397,10 +92363,10 @@
         </is>
       </c>
       <c r="E762">
-        <v>4.070162035118644</v>
+        <v>4.039056513732262</v>
       </c>
       <c r="F762">
-        <v>9.389035491737571</v>
+        <v>9.461133365223047</v>
       </c>
       <c r="G762" t="inlineStr">
         <is>
@@ -92438,10 +92404,10 @@
         </is>
       </c>
       <c r="B763">
-        <v>13.1999627953168</v>
+        <v>13.0999696823611</v>
       </c>
       <c r="C763">
-        <v>2.132774309586094</v>
+        <v>2.145176612059378</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -92449,10 +92415,10 @@
         </is>
       </c>
       <c r="E763">
-        <v>9.617018288587571</v>
+        <v>9.503473360280525</v>
       </c>
       <c r="F763">
-        <v>18.11777960373806</v>
+        <v>18.05752477783707</v>
       </c>
       <c r="G763" t="inlineStr">
         <is>
@@ -92490,10 +92456,10 @@
         </is>
       </c>
       <c r="B764">
-        <v>8.666623144055796</v>
+        <v>8.500011370601054</v>
       </c>
       <c r="C764">
-        <v>1.371887126491536</v>
+        <v>1.365009219608794</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -92501,10 +92467,10 @@
         </is>
       </c>
       <c r="E764">
-        <v>6.354897785267302</v>
+        <v>6.204771785476758</v>
       </c>
       <c r="F764">
-        <v>11.81928636133433</v>
+        <v>11.64429503587225</v>
       </c>
       <c r="G764" t="inlineStr">
         <is>
@@ -92542,10 +92508,10 @@
         </is>
       </c>
       <c r="B765">
-        <v>12.99970739129217</v>
+        <v>13.00009852175251</v>
       </c>
       <c r="C765">
-        <v>4.707131107712903</v>
+        <v>4.765410445514743</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -92553,10 +92519,10 @@
         </is>
       </c>
       <c r="E765">
-        <v>6.393190114755166</v>
+        <v>6.337588389971046</v>
       </c>
       <c r="F765">
-        <v>26.43318737998893</v>
+        <v>26.66669893594084</v>
       </c>
       <c r="G765" t="inlineStr">
         <is>
@@ -92594,10 +92560,10 @@
         </is>
       </c>
       <c r="B766">
-        <v>8.499926327452179</v>
+        <v>8.499946063112375</v>
       </c>
       <c r="C766">
-        <v>1.6540812226322</v>
+        <v>1.671773657124505</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -92605,10 +92571,10 @@
         </is>
       </c>
       <c r="E766">
-        <v>5.804593162239062</v>
+        <v>5.780979418715633</v>
       </c>
       <c r="F766">
-        <v>12.4468236709712</v>
+        <v>12.49772362826908</v>
       </c>
       <c r="G766" t="inlineStr">
         <is>
@@ -92646,10 +92612,10 @@
         </is>
       </c>
       <c r="B767">
-        <v>9.249971160099737</v>
+        <v>8.916661894737677</v>
       </c>
       <c r="C767">
-        <v>1.446403505907513</v>
+        <v>1.419142740626451</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -92657,10 +92623,10 @@
         </is>
       </c>
       <c r="E767">
-        <v>6.808310065427206</v>
+        <v>6.527219652787112</v>
       </c>
       <c r="F767">
-        <v>12.56728404559055</v>
+        <v>12.18081565726344</v>
       </c>
       <c r="G767" t="inlineStr">
         <is>
@@ -92698,10 +92664,10 @@
         </is>
       </c>
       <c r="B768">
-        <v>13.41664068909577</v>
+        <v>13.24999691399546</v>
       </c>
       <c r="C768">
-        <v>1.974264931782616</v>
+        <v>1.977503147739451</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -92709,10 +92675,10 @@
         </is>
       </c>
       <c r="E768">
-        <v>10.05516230670477</v>
+        <v>9.889577316011477</v>
       </c>
       <c r="F768">
-        <v>17.90187387231653</v>
+        <v>17.75226712031961</v>
       </c>
       <c r="G768" t="inlineStr">
         <is>
@@ -92750,10 +92716,10 @@
         </is>
       </c>
       <c r="B769">
-        <v>13.29999873817527</v>
+        <v>13.19993867955467</v>
       </c>
       <c r="C769">
-        <v>2.146593134376079</v>
+        <v>2.159213817061537</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -92761,10 +92727,10 @@
         </is>
       </c>
       <c r="E769">
-        <v>9.693249179199167</v>
+        <v>9.579314647936297</v>
       </c>
       <c r="F769">
-        <v>18.24877945106928</v>
+        <v>18.18902369821835</v>
       </c>
       <c r="G769" t="inlineStr">
         <is>
@@ -92802,10 +92768,10 @@
         </is>
       </c>
       <c r="B770">
-        <v>17.19994593473616</v>
+        <v>17.19986143718738</v>
       </c>
       <c r="C770">
-        <v>2.683656245490048</v>
+        <v>2.719306305757923</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -92813,10 +92779,10 @@
         </is>
       </c>
       <c r="E770">
-        <v>12.66825056484624</v>
+        <v>12.61681043188647</v>
       </c>
       <c r="F770">
-        <v>23.35272251235566</v>
+        <v>23.44770376439842</v>
       </c>
       <c r="G770" t="inlineStr">
         <is>
@@ -92854,10 +92820,10 @@
         </is>
       </c>
       <c r="B771">
-        <v>20.99993175969797</v>
+        <v>20.79999709445453</v>
       </c>
       <c r="C771">
-        <v>3.204975975192694</v>
+        <v>3.221623786372506</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -92865,10 +92831,10 @@
         </is>
       </c>
       <c r="E771">
-        <v>15.57072613784589</v>
+        <v>15.35409625339178</v>
       </c>
       <c r="F771">
-        <v>28.32219448263834</v>
+        <v>28.17748905499696</v>
       </c>
       <c r="G771" t="inlineStr">
         <is>
@@ -92906,10 +92872,10 @@
         </is>
       </c>
       <c r="B772">
-        <v>8.400098224845305</v>
+        <v>8.400054244849091</v>
       </c>
       <c r="C772">
-        <v>1.46545864821522</v>
+        <v>1.481049530843521</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -92917,10 +92883,10 @@
         </is>
       </c>
       <c r="E772">
-        <v>5.967411981842333</v>
+        <v>5.945701499159556</v>
       </c>
       <c r="F772">
-        <v>11.82449785631602</v>
+        <v>11.86755025061067</v>
       </c>
       <c r="G772" t="inlineStr">
         <is>
@@ -92958,10 +92924,10 @@
         </is>
       </c>
       <c r="B773">
-        <v>9.999861058329937</v>
+        <v>9.999934044014845</v>
       </c>
       <c r="C773">
-        <v>2.670655647757925</v>
+        <v>2.700993849149331</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -92969,10 +92935,10 @@
         </is>
       </c>
       <c r="E773">
-        <v>5.92467028523232</v>
+        <v>5.889610927674572</v>
       </c>
       <c r="F773">
-        <v>16.87810736660807</v>
+        <v>16.97882629474985</v>
       </c>
       <c r="G773" t="inlineStr">
         <is>
@@ -93010,10 +92976,10 @@
         </is>
       </c>
       <c r="B774">
-        <v>14.75006830446553</v>
+        <v>14.74993772553105</v>
       </c>
       <c r="C774">
-        <v>2.623596857415418</v>
+        <v>2.657114605144969</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -93021,10 +92987,10 @@
         </is>
       </c>
       <c r="E774">
-        <v>10.40856085057981</v>
+        <v>10.36218235257243</v>
       </c>
       <c r="F774">
-        <v>20.90245886147452</v>
+        <v>20.99564121770492</v>
       </c>
       <c r="G774" t="inlineStr">
         <is>
@@ -93062,10 +93028,10 @@
         </is>
       </c>
       <c r="B775">
-        <v>12.81805559702891</v>
+        <v>12.81818820197726</v>
       </c>
       <c r="C775">
-        <v>1.983199153311435</v>
+        <v>2.007604471816352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -93073,10 +93039,10 @@
         </is>
       </c>
       <c r="E775">
-        <v>9.46509417431816</v>
+        <v>9.429966304199814</v>
       </c>
       <c r="F775">
-        <v>17.35878653318948</v>
+        <v>17.42381080493703</v>
       </c>
       <c r="G775" t="inlineStr">
         <is>
@@ -93114,10 +93080,10 @@
         </is>
       </c>
       <c r="B776">
-        <v>11.41661390189148</v>
+        <v>11.41662814961917</v>
       </c>
       <c r="C776">
-        <v>1.721651503695165</v>
+        <v>1.742080605041153</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -93125,10 +93091,10 @@
         </is>
       </c>
       <c r="E776">
-        <v>8.49521105974023</v>
+        <v>8.465482600015301</v>
       </c>
       <c r="F776">
-        <v>15.34265270966055</v>
+        <v>15.39657033923161</v>
       </c>
       <c r="G776" t="inlineStr">
         <is>
@@ -93166,10 +93132,10 @@
         </is>
       </c>
       <c r="B777">
-        <v>15.54529363091339</v>
+        <v>15.45438985546538</v>
       </c>
       <c r="C777">
-        <v>2.341812890455656</v>
+        <v>2.360039745827458</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -93177,10 +93143,10 @@
         </is>
       </c>
       <c r="E777">
-        <v>11.57097896572502</v>
+        <v>11.4568409251851</v>
       </c>
       <c r="F777">
-        <v>20.8846766368808</v>
+        <v>20.84677332646588</v>
       </c>
       <c r="G777" t="inlineStr">
         <is>
@@ -93218,10 +93184,10 @@
         </is>
       </c>
       <c r="B778">
-        <v>14.99988384377965</v>
+        <v>14.99992366220611</v>
       </c>
       <c r="C778">
-        <v>2.270213800834195</v>
+        <v>2.299378861953832</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -93229,10 +93195,10 @@
         </is>
       </c>
       <c r="E778">
-        <v>11.14960800862112</v>
+        <v>11.1072376064302</v>
       </c>
       <c r="F778">
-        <v>20.17976911411679</v>
+        <v>20.2568557407789</v>
       </c>
       <c r="G778" t="inlineStr">
         <is>
@@ -93270,10 +93236,10 @@
         </is>
       </c>
       <c r="B779">
-        <v>13.16670679079194</v>
+        <v>12.91664919959471</v>
       </c>
       <c r="C779">
-        <v>3.090693215328839</v>
+        <v>3.450471179991642</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -93281,10 +93247,10 @@
         </is>
       </c>
       <c r="E779">
-        <v>8.311319221909418</v>
+        <v>7.651830135025358</v>
       </c>
       <c r="F779">
-        <v>20.85856205085801</v>
+        <v>21.80391143050875</v>
       </c>
       <c r="G779" t="inlineStr">
         <is>
@@ -93322,10 +93288,10 @@
         </is>
       </c>
       <c r="B780">
-        <v>10.72725659389793</v>
+        <v>9.454500570241796</v>
       </c>
       <c r="C780">
-        <v>2.664158703018341</v>
+        <v>2.681225895893869</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -93333,10 +93299,10 @@
         </is>
       </c>
       <c r="E780">
-        <v>6.593093465490337</v>
+        <v>5.423057120693779</v>
       </c>
       <c r="F780">
-        <v>17.4537240574017</v>
+        <v>16.48287654791786</v>
       </c>
       <c r="G780" t="inlineStr">
         <is>
@@ -93374,10 +93340,10 @@
         </is>
       </c>
       <c r="B781">
-        <v>9.285731333534295</v>
+        <v>8.714396993231288</v>
       </c>
       <c r="C781">
-        <v>2.921584326669321</v>
+        <v>3.113698606127596</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -93385,10 +93351,10 @@
         </is>
       </c>
       <c r="E781">
-        <v>5.011886496087889</v>
+        <v>4.326121144442607</v>
       </c>
       <c r="F781">
-        <v>17.20406207640273</v>
+        <v>17.55399639078368</v>
       </c>
       <c r="G781" t="inlineStr">
         <is>
@@ -93426,10 +93392,10 @@
         </is>
       </c>
       <c r="B782">
-        <v>8.799997958079397</v>
+        <v>8.400054559623877</v>
       </c>
       <c r="C782">
-        <v>2.326421049173709</v>
+        <v>2.517155837112051</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -93437,10 +93403,10 @@
         </is>
       </c>
       <c r="E782">
-        <v>5.241477765993696</v>
+        <v>4.668867076637337</v>
       </c>
       <c r="F782">
-        <v>14.7744524577832</v>
+        <v>15.11307035442055</v>
       </c>
       <c r="G782" t="inlineStr">
         <is>
@@ -93478,10 +93444,10 @@
         </is>
       </c>
       <c r="B783">
-        <v>9.727345615754746</v>
+        <v>9.272869236099524</v>
       </c>
       <c r="C783">
-        <v>2.432836146491962</v>
+        <v>2.632817173911404</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -93489,10 +93455,10 @@
         </is>
       </c>
       <c r="E783">
-        <v>5.958082019441083</v>
+        <v>5.315389639906843</v>
       </c>
       <c r="F783">
-        <v>15.88115981277132</v>
+        <v>16.17682045813446</v>
       </c>
       <c r="G783" t="inlineStr">
         <is>
@@ -93530,10 +93496,10 @@
         </is>
       </c>
       <c r="B784">
-        <v>6.750036168579359</v>
+        <v>6.12509287020301</v>
       </c>
       <c r="C784">
-        <v>2.04377974079391</v>
+        <v>2.102010037852904</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -93541,10 +93507,10 @@
         </is>
       </c>
       <c r="E784">
-        <v>3.728883531576167</v>
+        <v>3.12605949854091</v>
       </c>
       <c r="F784">
-        <v>12.21893574612947</v>
+        <v>12.00129514045484</v>
       </c>
       <c r="G784" t="inlineStr">
         <is>
@@ -93582,10 +93548,10 @@
         </is>
       </c>
       <c r="B785">
-        <v>6.5833887316261</v>
+        <v>6.41672329534324</v>
       </c>
       <c r="C785">
-        <v>1.631698396944586</v>
+        <v>1.790901711282565</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -93593,10 +93559,10 @@
         </is>
       </c>
       <c r="E785">
-        <v>4.050218809263457</v>
+        <v>3.713160529463212</v>
       </c>
       <c r="F785">
-        <v>10.70090511963801</v>
+        <v>11.08875781757621</v>
       </c>
       <c r="G785" t="inlineStr">
         <is>
@@ -93634,10 +93600,10 @@
         </is>
       </c>
       <c r="B786">
-        <v>11.09087961823437</v>
+        <v>10.81821788847213</v>
       </c>
       <c r="C786">
-        <v>2.748253656597242</v>
+        <v>3.044770218026615</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -93645,10 +93611,10 @@
         </is>
       </c>
       <c r="E786">
-        <v>6.824067883453679</v>
+        <v>6.231411103186729</v>
       </c>
       <c r="F786">
-        <v>18.0255549632534</v>
+        <v>18.78127383099591</v>
       </c>
       <c r="G786" t="inlineStr">
         <is>
@@ -93686,10 +93652,10 @@
         </is>
       </c>
       <c r="B787">
-        <v>11.90009640426771</v>
+        <v>11.49995253522773</v>
       </c>
       <c r="C787">
-        <v>3.078644169978103</v>
+        <v>3.383917805483516</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -93697,10 +93663,10 @@
         </is>
       </c>
       <c r="E787">
-        <v>7.167014084047607</v>
+        <v>6.459899948032415</v>
       </c>
       <c r="F787">
-        <v>19.75889718789125</v>
+        <v>20.47228430415113</v>
       </c>
       <c r="G787" t="inlineStr">
         <is>
@@ -93738,10 +93704,10 @@
         </is>
       </c>
       <c r="B788">
-        <v>10.09999775263894</v>
+        <v>8.600041158496976</v>
       </c>
       <c r="C788">
-        <v>2.642009267192842</v>
+        <v>2.573106260112341</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -93749,10 +93715,10 @@
         </is>
       </c>
       <c r="E788">
-        <v>6.048666046084906</v>
+        <v>4.784357311952022</v>
       </c>
       <c r="F788">
-        <v>16.86486802645341</v>
+        <v>15.45885959292325</v>
       </c>
       <c r="G788" t="inlineStr">
         <is>
@@ -93790,10 +93756,10 @@
         </is>
       </c>
       <c r="B789">
-        <v>12.54541247896233</v>
+        <v>12.09081360208247</v>
       </c>
       <c r="C789">
-        <v>3.084526288379363</v>
+        <v>3.383871500350025</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -93801,10 +93767,10 @@
         </is>
       </c>
       <c r="E789">
-        <v>7.748202995773886</v>
+        <v>6.986001249631376</v>
       </c>
       <c r="F789">
-        <v>20.31275824254318</v>
+        <v>20.92581554691478</v>
       </c>
       <c r="G789" t="inlineStr">
         <is>
@@ -93842,10 +93808,10 @@
         </is>
       </c>
       <c r="B790">
-        <v>11.77798005243684</v>
+        <v>10.55557202567644</v>
       </c>
       <c r="C790">
-        <v>3.213977180192234</v>
+        <v>3.288726439648071</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -93853,10 +93819,10 @@
         </is>
       </c>
       <c r="E790">
-        <v>6.899137396034853</v>
+        <v>5.73163870029139</v>
       </c>
       <c r="F790">
-        <v>20.1069794892514</v>
+        <v>19.4394843456512</v>
       </c>
       <c r="G790" t="inlineStr">
         <is>
@@ -93894,10 +93860,10 @@
         </is>
       </c>
       <c r="B791">
-        <v>6.700025509468671</v>
+        <v>6.300089109436212</v>
       </c>
       <c r="C791">
-        <v>1.81583478833614</v>
+        <v>1.929149610768327</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -93905,10 +93871,10 @@
         </is>
       </c>
       <c r="E791">
-        <v>3.938987405129734</v>
+        <v>3.457007796008833</v>
       </c>
       <c r="F791">
-        <v>11.39641669558789</v>
+        <v>11.48135183052256</v>
       </c>
       <c r="G791" t="inlineStr">
         <is>
@@ -93946,10 +93912,10 @@
         </is>
       </c>
       <c r="B792">
-        <v>6.285737255462201</v>
+        <v>5.714406748365637</v>
       </c>
       <c r="C792">
-        <v>2.049726679263457</v>
+        <v>2.109491822390349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -93957,10 +93923,10 @@
         </is>
       </c>
       <c r="E792">
-        <v>3.317313181887925</v>
+        <v>2.771707097951223</v>
       </c>
       <c r="F792">
-        <v>11.91038972757452</v>
+        <v>11.78134749876857</v>
       </c>
       <c r="G792" t="inlineStr">
         <is>
@@ -93998,10 +93964,10 @@
         </is>
       </c>
       <c r="B793">
-        <v>3.333311924593636</v>
+        <v>3.3332997254621</v>
       </c>
       <c r="C793">
-        <v>0.9053569523840287</v>
+        <v>0.9994811296166722</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -94009,10 +93975,10 @@
         </is>
       </c>
       <c r="E793">
-        <v>1.957411342549166</v>
+        <v>1.852012140276977</v>
       </c>
       <c r="F793">
-        <v>5.676358435814595</v>
+        <v>5.999359733194852</v>
       </c>
       <c r="G793" t="inlineStr">
         <is>
@@ -94050,10 +94016,10 @@
         </is>
       </c>
       <c r="B794">
-        <v>14.91662627774009</v>
+        <v>14.41645208406075</v>
       </c>
       <c r="C794">
-        <v>3.47778114704353</v>
+        <v>3.83294124327799</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -94061,10 +94027,10 @@
         </is>
       </c>
       <c r="E794">
-        <v>9.445276947759979</v>
+        <v>8.561446128661172</v>
       </c>
       <c r="F794">
-        <v>23.55735472240812</v>
+        <v>24.27558236876045</v>
       </c>
       <c r="G794" t="inlineStr">
         <is>
@@ -94102,10 +94068,10 @@
         </is>
       </c>
       <c r="B795">
-        <v>6.625000354546485</v>
+        <v>6.624995732664535</v>
       </c>
       <c r="C795">
-        <v>1.691066487124621</v>
+        <v>1.778934494654207</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -94113,10 +94079,10 @@
         </is>
       </c>
       <c r="E795">
-        <v>4.017095867061967</v>
+        <v>3.914012127891755</v>
       </c>
       <c r="F795">
-        <v>10.92596023351613</v>
+        <v>11.21370272336497</v>
       </c>
       <c r="G795" t="inlineStr">
         <is>
@@ -94154,10 +94120,10 @@
         </is>
       </c>
       <c r="B796">
-        <v>11.49999851785112</v>
+        <v>11.31249872146588</v>
       </c>
       <c r="C796">
-        <v>2.843921493540355</v>
+        <v>2.954125492387209</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -94165,10 +94131,10 @@
         </is>
       </c>
       <c r="E796">
-        <v>7.082681713229856</v>
+        <v>6.780743384197573</v>
       </c>
       <c r="F796">
-        <v>18.67230115163105</v>
+        <v>18.87294947946351</v>
       </c>
       <c r="G796" t="inlineStr">
         <is>
@@ -94206,10 +94172,10 @@
         </is>
       </c>
       <c r="B797">
-        <v>6.24999846031165</v>
+        <v>6.249999214011899</v>
       </c>
       <c r="C797">
-        <v>3.204519824066272</v>
+        <v>3.369631822244456</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -94217,10 +94183,10 @@
         </is>
       </c>
       <c r="E797">
-        <v>2.287963267489697</v>
+        <v>2.172511959434877</v>
       </c>
       <c r="F797">
-        <v>17.07303666494458</v>
+        <v>17.98033378159652</v>
       </c>
       <c r="G797" t="inlineStr">
         <is>
@@ -94258,10 +94224,10 @@
         </is>
       </c>
       <c r="B798">
-        <v>7.749996938909435</v>
+        <v>5.750006748851786</v>
       </c>
       <c r="C798">
-        <v>3.914655408002425</v>
+        <v>3.118559626872249</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -94269,10 +94235,10 @@
         </is>
       </c>
       <c r="E798">
-        <v>2.879686024004904</v>
+        <v>1.986153284841419</v>
       </c>
       <c r="F798">
-        <v>20.85729209796774</v>
+        <v>16.64653874611744</v>
       </c>
       <c r="G798" t="inlineStr">
         <is>
@@ -94310,10 +94276,10 @@
         </is>
       </c>
       <c r="B799">
-        <v>1.900043901321572</v>
+        <v>0.6999999966394507</v>
       </c>
       <c r="C799">
-        <v>0.5212742362942293</v>
+        <v>0.317292296408984</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -94321,10 +94287,10 @@
         </is>
       </c>
       <c r="E799">
-        <v>1.109782188278961</v>
+        <v>0.2879187208200017</v>
       </c>
       <c r="F799">
-        <v>3.25304088052441</v>
+        <v>1.701869173007213</v>
       </c>
       <c r="G799" t="inlineStr">
         <is>
@@ -94362,10 +94328,10 @@
         </is>
       </c>
       <c r="B800">
-        <v>1.583327347797814</v>
+        <v>0.750000002177774</v>
       </c>
       <c r="C800">
-        <v>0.4233594307284868</v>
+        <v>0.3030579737364072</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -94373,10 +94339,10 @@
         </is>
       </c>
       <c r="E800">
-        <v>0.9375002886750947</v>
+        <v>0.33971134103954</v>
       </c>
       <c r="F800">
-        <v>2.674053032908744</v>
+        <v>1.655817558358142</v>
       </c>
       <c r="G800" t="inlineStr">
         <is>
@@ -94414,10 +94380,10 @@
         </is>
       </c>
       <c r="B801">
-        <v>1.166676455148638</v>
+        <v>0.7500000021776985</v>
       </c>
       <c r="C801">
-        <v>0.3505695777800265</v>
+        <v>0.3030579737363987</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -94425,10 +94391,10 @@
         </is>
       </c>
       <c r="E801">
-        <v>0.6474057491001398</v>
+        <v>0.3397113410394863</v>
       </c>
       <c r="F801">
-        <v>2.102443410318949</v>
+        <v>1.65581755835807</v>
       </c>
       <c r="G801" t="inlineStr">
         <is>
@@ -94466,10 +94432,10 @@
         </is>
       </c>
       <c r="B802">
-        <v>1.909091584209143</v>
+        <v>0.5454545485824026</v>
       </c>
       <c r="C802">
-        <v>0.4985523316883527</v>
+        <v>0.2579120563052243</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -94477,10 +94443,10 @@
         </is>
       </c>
       <c r="E802">
-        <v>1.144296507597266</v>
+        <v>0.2159123475565095</v>
       </c>
       <c r="F802">
-        <v>3.185040461716499</v>
+        <v>1.37796966193128</v>
       </c>
       <c r="G802" t="inlineStr">
         <is>
@@ -94518,10 +94484,10 @@
         </is>
       </c>
       <c r="B803">
-        <v>1.999995759709102</v>
+        <v>1.111111122038386</v>
       </c>
       <c r="C803">
-        <v>0.5681782814311667</v>
+        <v>0.4575248396644329</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -94529,10 +94495,10 @@
         </is>
       </c>
       <c r="E803">
-        <v>1.146070799097848</v>
+        <v>0.4957425925659746</v>
       </c>
       <c r="F803">
-        <v>3.490170975478175</v>
+        <v>2.490340640547447</v>
       </c>
       <c r="G803" t="inlineStr">
         <is>
@@ -94570,10 +94536,10 @@
         </is>
       </c>
       <c r="B804">
-        <v>2.833330479440562</v>
+        <v>2.333333332581703</v>
       </c>
       <c r="C804">
-        <v>0.6225291794587059</v>
+        <v>0.6917128592750829</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -94581,10 +94547,10 @@
         </is>
       </c>
       <c r="E804">
-        <v>1.84193496827903</v>
+        <v>1.305087038620103</v>
       </c>
       <c r="F804">
-        <v>4.358330638148121</v>
+        <v>4.171709839899543</v>
       </c>
       <c r="G804" t="inlineStr">
         <is>

--- a/model_results/model_results.xlsx
+++ b/model_results/model_results.xlsx
@@ -4690,10 +4690,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>5.11341236596837</v>
+        <v>5.372782420915257</v>
       </c>
       <c r="C111">
-        <v>0.5503698080899182</v>
+        <v>0.6143774001983098</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="E111">
-        <v>4.140890936223253</v>
+        <v>4.294023330659163</v>
       </c>
       <c r="F111">
-        <v>6.314338249218872</v>
+        <v>6.722551024906695</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>2.175513274765717</v>
+        <v>2.36570486967903</v>
       </c>
       <c r="C112">
-        <v>0.603966630263888</v>
+        <v>0.6940045959826109</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="E112">
-        <v>1.262556775304442</v>
+        <v>1.331225321581196</v>
       </c>
       <c r="F112">
-        <v>3.748629844816772</v>
+        <v>4.204066313714363</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.2256677161120489</v>
+        <v>0.3842899857596687</v>
       </c>
       <c r="C113">
-        <v>0.05726536029444562</v>
+        <v>0.08181856088970837</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="E113">
-        <v>0.1372362458627031</v>
+        <v>0.2531810053059483</v>
       </c>
       <c r="F113">
-        <v>0.3710821275756607</v>
+        <v>0.5832933358357935</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.1863381984833258</v>
+        <v>0.1848864229639864</v>
       </c>
       <c r="C114">
-        <v>0.1020620299412114</v>
+        <v>0.1049990636638958</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="E114">
-        <v>0.06369096080254927</v>
+        <v>0.06074326906893279</v>
       </c>
       <c r="F114">
-        <v>0.545162512489866</v>
+        <v>0.5627453036422266</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.2206161122069034</v>
+        <v>0.2399137870809855</v>
       </c>
       <c r="C115">
-        <v>0.1090221862273569</v>
+        <v>0.1061067056493954</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="E115">
-        <v>0.083752488093434</v>
+        <v>0.1008310234528371</v>
       </c>
       <c r="F115">
-        <v>0.5811346035593743</v>
+        <v>0.5708424179435508</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>0.1170263629334564</v>
+        <v>0.1488716504952723</v>
       </c>
       <c r="C116">
-        <v>0.09116142502613932</v>
+        <v>0.10150597323412</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="E116">
-        <v>0.02542219614816965</v>
+        <v>0.03912303973523568</v>
       </c>
       <c r="F116">
-        <v>0.5387091477704254</v>
+        <v>0.5664889147462098</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>2.788865465193983</v>
+        <v>2.832106567901934</v>
       </c>
       <c r="C117">
-        <v>0.342844494861494</v>
+        <v>0.3475291634723073</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -4935,10 +4935,10 @@
         </is>
       </c>
       <c r="E117">
-        <v>2.191727371830895</v>
+        <v>2.226682208638481</v>
       </c>
       <c r="F117">
-        <v>3.548694369069437</v>
+        <v>3.602142946504098</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4963,10 +4963,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>1.922094209201065</v>
+        <v>1.972026128024048</v>
       </c>
       <c r="C118">
-        <v>0.286667302744764</v>
+        <v>0.2909511866477635</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="E118">
-        <v>1.434906948604671</v>
+        <v>1.476818273095419</v>
       </c>
       <c r="F118">
-        <v>2.574693887040419</v>
+        <v>2.633287467020833</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>6.468559569842236</v>
+        <v>6.632734663091421</v>
       </c>
       <c r="C119">
-        <v>0.581609415234535</v>
+        <v>0.6026234499350813</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="E119">
-        <v>5.423420249489408</v>
+        <v>5.550804017538977</v>
       </c>
       <c r="F119">
-        <v>7.715106147737096</v>
+        <v>7.92554897848464</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>6.353416897821763</v>
+        <v>6.397196640816609</v>
       </c>
       <c r="C120">
-        <v>1.458909960920171</v>
+        <v>1.48758205563251</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="E120">
-        <v>4.050879404942385</v>
+        <v>4.055591720473982</v>
       </c>
       <c r="F120">
-        <v>9.96472672780078</v>
+        <v>10.09079011939901</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>7.187952896778759</v>
+        <v>7.187952980373725</v>
       </c>
       <c r="C121">
-        <v>0.768632926095373</v>
+        <v>0.7782473502807675</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="E121">
-        <v>5.828855195456653</v>
+        <v>5.813594373231877</v>
       </c>
       <c r="F121">
-        <v>8.863947570113279</v>
+        <v>8.887215848074572</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>5.490788663947885</v>
+        <v>5.538744116557741</v>
       </c>
       <c r="C122">
-        <v>0.6594633753409842</v>
+        <v>0.6706975481086651</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -5130,10 +5130,10 @@
         </is>
       </c>
       <c r="E122">
-        <v>4.339127142756201</v>
+        <v>4.368553038260232</v>
       </c>
       <c r="F122">
-        <v>6.948116328526893</v>
+        <v>7.022390736709544</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.001006951816228127</v>
+        <v>1.042524334656674E-05</v>
       </c>
       <c r="C123">
-        <v>0.1082531268951095</v>
+        <v>0.1082531768786623</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -5171,8 +5171,10 @@
       <c r="E123">
         <v>2.220446049250313E-16</v>
       </c>
-      <c r="F123">
-        <v>3.25149501172394E+88</v>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -5197,10 +5199,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>0.3535536095215912</v>
+        <v>0.5590169944354789</v>
       </c>
       <c r="C124">
-        <v>0.1350278973218884</v>
+        <v>0.2176533141940155</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -5208,10 +5210,10 @@
         </is>
       </c>
       <c r="E124">
-        <v>0.1672505309697025</v>
+        <v>0.2606211266273666</v>
       </c>
       <c r="F124">
-        <v>0.7473827083298742</v>
+        <v>1.199058587888331</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -5236,10 +5238,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>3.050820105595005</v>
+        <v>3.050830052910358</v>
       </c>
       <c r="C125">
-        <v>2.079536970872567</v>
+        <v>2.079534405327655</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -5247,10 +5249,10 @@
         </is>
       </c>
       <c r="E125">
-        <v>0.8020663363739069</v>
+        <v>0.8020737673230141</v>
       </c>
       <c r="F125">
-        <v>11.60440588839743</v>
+        <v>11.60437405004002</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -5275,10 +5277,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>15.91361996479092</v>
+        <v>16.00037016915394</v>
       </c>
       <c r="C126">
-        <v>16.31026789881376</v>
+        <v>16.39898528751336</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -5286,10 +5288,10 @@
         </is>
       </c>
       <c r="E126">
-        <v>2.134770484430267</v>
+        <v>2.146459086518233</v>
       </c>
       <c r="F126">
-        <v>118.6278816532253</v>
+        <v>119.2717099328585</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -5314,10 +5316,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>1.42622947799121</v>
+        <v>1.491803275231747</v>
       </c>
       <c r="C127">
-        <v>0.3280204577316385</v>
+        <v>0.3334113839750386</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -5325,10 +5327,10 @@
         </is>
       </c>
       <c r="E127">
-        <v>0.9086997479775287</v>
+        <v>0.9626575131552125</v>
       </c>
       <c r="F127">
-        <v>2.238506754754136</v>
+        <v>2.31180558150731</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -5353,10 +5355,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>0.4324324338673615</v>
+        <v>0.4594594587707326</v>
       </c>
       <c r="C128">
-        <v>0.1563690224345009</v>
+        <v>0.1611759600083705</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -5364,10 +5366,10 @@
         </is>
       </c>
       <c r="E128">
-        <v>0.2128731659603444</v>
+        <v>0.2310203168486974</v>
       </c>
       <c r="F128">
-        <v>0.8784470744202927</v>
+        <v>0.9137854069871812</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -5392,10 +5394,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>1.155664962046459</v>
+        <v>1.186488143572073</v>
       </c>
       <c r="C129">
-        <v>0.1462544790805521</v>
+        <v>0.1485221337008149</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -5403,10 +5405,10 @@
         </is>
       </c>
       <c r="E129">
-        <v>0.9017967187642013</v>
+        <v>0.9283500234539535</v>
       </c>
       <c r="F129">
-        <v>1.481000625431485</v>
+        <v>1.516404458740157</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -5431,10 +5433,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>0.4419417394823106</v>
+        <v>0.4841229426301021</v>
       </c>
       <c r="C130">
-        <v>0.1397542395719922</v>
+        <v>0.1465754958636674</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -5442,10 +5444,10 @@
         </is>
       </c>
       <c r="E130">
-        <v>0.2377888444580178</v>
+        <v>0.2674493865272609</v>
       </c>
       <c r="F130">
-        <v>0.8213694866208636</v>
+        <v>0.8763341229684951</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5548,10 +5550,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>0.808198233576678</v>
+        <v>0.8361614224921071</v>
       </c>
       <c r="C133">
-        <v>0.1994902796242849</v>
+        <v>0.2134169385783109</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -5559,10 +5561,10 @@
         </is>
       </c>
       <c r="E133">
-        <v>0.4982106031789511</v>
+        <v>0.5070309101715065</v>
       </c>
       <c r="F133">
-        <v>1.311060785516535</v>
+        <v>1.37894142238296</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -5587,10 +5589,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>0.2312642625334121</v>
+        <v>0.2311420100988467</v>
       </c>
       <c r="C134">
-        <v>0.1587680209432326</v>
+        <v>0.1617431426766729</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -5598,10 +5600,10 @@
         </is>
       </c>
       <c r="E134">
-        <v>0.06021987892378233</v>
+        <v>0.05864689236327118</v>
       </c>
       <c r="F134">
-        <v>0.8881312961923133</v>
+        <v>0.9109882327881852</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -5626,10 +5628,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>7.333333083719854</v>
+        <v>7.499999925586994</v>
       </c>
       <c r="C135">
-        <v>1.147489998505174</v>
+        <v>1.14398781297197</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -5637,10 +5639,10 @@
         </is>
       </c>
       <c r="E135">
-        <v>5.396458873769295</v>
+        <v>5.561936576239034</v>
       </c>
       <c r="F135">
-        <v>9.965381998587842</v>
+        <v>10.11338373114657</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5730,10 +5732,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>4.695456901528026</v>
+        <v>4.84059440167619</v>
       </c>
       <c r="C138">
-        <v>1.247436711286089</v>
+        <v>1.307304578701699</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -5741,10 +5743,10 @@
         </is>
       </c>
       <c r="E138">
-        <v>2.789588279837912</v>
+        <v>2.851108668032045</v>
       </c>
       <c r="F138">
-        <v>7.903429933892688</v>
+        <v>8.218330793302304</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -5769,10 +5771,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>4.257187406907024</v>
+        <v>4.256962556498384</v>
       </c>
       <c r="C139">
-        <v>2.967491349490299</v>
+        <v>3.020499931084274</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -5780,10 +5782,10 @@
         </is>
       </c>
       <c r="E139">
-        <v>1.085897818479966</v>
+        <v>1.059583883966395</v>
       </c>
       <c r="F139">
-        <v>16.69000923392326</v>
+        <v>17.10268576338973</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -5808,10 +5810,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>6.65230654386764</v>
+        <v>6.690249003840572</v>
       </c>
       <c r="C140">
-        <v>0.4449794081450604</v>
+        <v>0.4558734385177328</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -5819,10 +5821,10 @@
         </is>
       </c>
       <c r="E140">
-        <v>5.834915014499146</v>
+        <v>5.853847781891339</v>
       </c>
       <c r="F140">
-        <v>7.584203410610053</v>
+        <v>7.646155725444625</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5847,10 +5849,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>6.195845742260315</v>
+        <v>6.322075192367533</v>
       </c>
       <c r="C141">
-        <v>1.017045279806355</v>
+        <v>1.055000701849459</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -5858,10 +5860,10 @@
         </is>
       </c>
       <c r="E141">
-        <v>4.49134325615355</v>
+        <v>4.558424922853431</v>
       </c>
       <c r="F141">
-        <v>8.547221237051861</v>
+        <v>8.76808007466971</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -5886,10 +5888,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>10.71921170446308</v>
+        <v>10.75119523115531</v>
       </c>
       <c r="C142">
-        <v>0.5471586800418972</v>
+        <v>0.5448426537664807</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -5897,10 +5899,10 @@
         </is>
       </c>
       <c r="E142">
-        <v>9.698700358554575</v>
+        <v>9.734643794074209</v>
       </c>
       <c r="F142">
-        <v>11.84710273719833</v>
+        <v>11.87390122777568</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5925,10 +5927,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>10.45075952600698</v>
+        <v>10.57803903430081</v>
       </c>
       <c r="C143">
-        <v>0.8776450028650916</v>
+        <v>0.8803041517391799</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -5936,10 +5938,10 @@
         </is>
       </c>
       <c r="E143">
-        <v>8.864714350397765</v>
+        <v>8.986036814797828</v>
       </c>
       <c r="F143">
-        <v>12.32057462353821</v>
+        <v>12.45208673382328</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -5964,10 +5966,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>7.138920353666716</v>
+        <v>7.189062467013026</v>
       </c>
       <c r="C144">
-        <v>0.4809601855058446</v>
+        <v>0.491692274861217</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -5975,10 +5977,10 @@
         </is>
       </c>
       <c r="E144">
-        <v>6.25584187383873</v>
+        <v>6.287163582920567</v>
       </c>
       <c r="F144">
-        <v>8.14665473389341</v>
+        <v>8.220339501745137</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -6003,10 +6005,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>5.74759954897481</v>
+        <v>5.783963268558245</v>
       </c>
       <c r="C145">
-        <v>0.5412448493233708</v>
+        <v>0.5510635336956891</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -6014,10 +6016,10 @@
         </is>
       </c>
       <c r="E145">
-        <v>4.778920767645072</v>
+        <v>4.798746674343685</v>
       </c>
       <c r="F145">
-        <v>6.912627804803336</v>
+        <v>6.971451789879373</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -6042,10 +6044,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>5.061133893981285</v>
+        <v>5.207514082798908</v>
       </c>
       <c r="C146">
-        <v>1.180324669525075</v>
+        <v>1.207668087613156</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -6053,10 +6055,10 @@
         </is>
       </c>
       <c r="E146">
-        <v>3.204321982696482</v>
+        <v>3.305440669140983</v>
       </c>
       <c r="F146">
-        <v>7.993914603816037</v>
+        <v>8.204111232647362</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -6081,10 +6083,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>5.699179027243114</v>
+        <v>6.174313937914175</v>
       </c>
       <c r="C147">
-        <v>1.385965896548159</v>
+        <v>1.490711488174999</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -6092,10 +6094,10 @@
         </is>
       </c>
       <c r="E147">
-        <v>3.538434841612591</v>
+        <v>3.84659672074599</v>
       </c>
       <c r="F147">
-        <v>9.179381008402343</v>
+        <v>9.910618495127308</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -6120,10 +6122,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>0.3472222109942356</v>
+        <v>0.4027777743480607</v>
       </c>
       <c r="C148">
-        <v>0.06944443746849148</v>
+        <v>0.0747939533498156</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -6131,10 +6133,10 @@
         </is>
       </c>
       <c r="E148">
-        <v>0.234621172683786</v>
+        <v>0.2798989974303398</v>
       </c>
       <c r="F148">
-        <v>0.5138635291462645</v>
+        <v>0.5796017027504805</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -6159,10 +6161,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>0.7500005073497509</v>
+        <v>0.7499999915248144</v>
       </c>
       <c r="C149">
-        <v>0.250000063747706</v>
+        <v>0.25000000187967</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -6170,10 +6172,10 @@
         </is>
       </c>
       <c r="E149">
-        <v>0.3902364471571022</v>
+        <v>0.3902360665128861</v>
       </c>
       <c r="F149">
-        <v>1.441435737545117</v>
+        <v>1.441435160808355</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -17129,10 +17131,10 @@
         </is>
       </c>
       <c r="C183">
-        <v>3.534806352886996</v>
+        <v>3.708193060096156</v>
       </c>
       <c r="D183">
-        <v>0.5805514072704197</v>
+        <v>0.6255214777497877</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -17140,10 +17142,10 @@
         </is>
       </c>
       <c r="F183">
-        <v>2.561919826784721</v>
+        <v>2.664257963010976</v>
       </c>
       <c r="G183">
-        <v>4.87714557722583</v>
+        <v>5.161172815039698</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -17173,10 +17175,10 @@
         </is>
       </c>
       <c r="C184">
-        <v>0.9131454209346132</v>
+        <v>1.079288373686324</v>
       </c>
       <c r="D184">
-        <v>0.364063598379691</v>
+        <v>0.4282383833450648</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -17184,10 +17186,10 @@
         </is>
       </c>
       <c r="F184">
-        <v>0.4179967103087771</v>
+        <v>0.4959056515610347</v>
       </c>
       <c r="G184">
-        <v>1.994835220492268</v>
+        <v>2.348961722673779</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -17217,10 +17219,10 @@
         </is>
       </c>
       <c r="C185">
-        <v>7.397006628972225</v>
+        <v>7.784597639516507</v>
       </c>
       <c r="D185">
-        <v>0.8423631806996601</v>
+        <v>0.9359390898534958</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -17228,10 +17230,10 @@
         </is>
       </c>
       <c r="F185">
-        <v>5.917279577910366</v>
+        <v>6.150303477765689</v>
       </c>
       <c r="G185">
-        <v>9.246767259961276</v>
+        <v>9.853165884942802</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -17261,10 +17263,10 @@
         </is>
       </c>
       <c r="C186">
-        <v>5.183027697645058</v>
+        <v>5.185416304734156</v>
       </c>
       <c r="D186">
-        <v>1.501474824837731</v>
+        <v>1.609842877759787</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -17272,10 +17274,10 @@
         </is>
       </c>
       <c r="F186">
-        <v>2.9376386582453</v>
+        <v>2.821779810945657</v>
       </c>
       <c r="G186">
-        <v>9.144683618305187</v>
+        <v>9.528929985643259</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -17305,10 +17307,10 @@
         </is>
       </c>
       <c r="C187">
-        <v>0.3055559387377709</v>
+        <v>0.3575168250040291</v>
       </c>
       <c r="D187">
-        <v>0.09212851670295327</v>
+        <v>0.1058314962792494</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -17316,10 +17318,10 @@
         </is>
       </c>
       <c r="F187">
-        <v>0.1692169990766681</v>
+        <v>0.2001360454156855</v>
       </c>
       <c r="G187">
-        <v>0.5517438094716437</v>
+        <v>0.6386569690406401</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -17349,10 +17351,10 @@
         </is>
       </c>
       <c r="C188">
-        <v>0.08333252337007355</v>
+        <v>0.08266849575885236</v>
       </c>
       <c r="D188">
-        <v>0.08333292144578311</v>
+        <v>0.08372013928589324</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -17360,10 +17362,10 @@
         </is>
       </c>
       <c r="F188">
-        <v>0.01173840051034999</v>
+        <v>0.0113582173763588</v>
       </c>
       <c r="G188">
-        <v>0.5915890708534702</v>
+        <v>0.6016859833353752</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -17393,10 +17395,10 @@
         </is>
       </c>
       <c r="C189">
-        <v>0.1666664320307422</v>
+        <v>0.4130680930988411</v>
       </c>
       <c r="D189">
-        <v>0.06804132826069791</v>
+        <v>0.1145471622812885</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -17404,10 +17406,10 @@
         </is>
       </c>
       <c r="F189">
-        <v>0.07487663992477796</v>
+        <v>0.2398703101091418</v>
       </c>
       <c r="G189">
-        <v>0.3709795150231612</v>
+        <v>0.7113229205343413</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -17437,10 +17439,10 @@
         </is>
       </c>
       <c r="C190">
-        <v>0.4166671403890393</v>
+        <v>0.4134947549563661</v>
       </c>
       <c r="D190">
-        <v>0.1863390890812629</v>
+        <v>0.1963562203514383</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -17448,10 +17450,10 @@
         </is>
       </c>
       <c r="F190">
-        <v>0.1734285513312286</v>
+        <v>0.1630271731554816</v>
       </c>
       <c r="G190">
-        <v>1.001054927503842</v>
+        <v>1.048769411056161</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -17481,10 +17483,10 @@
         </is>
       </c>
       <c r="C191">
-        <v>0.2206161122069034</v>
+        <v>0.2399137870809855</v>
       </c>
       <c r="D191">
-        <v>0.1090221862273569</v>
+        <v>0.1061067056493954</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -17492,10 +17494,10 @@
         </is>
       </c>
       <c r="F191">
-        <v>0.083752488093434</v>
+        <v>0.1008310234528371</v>
       </c>
       <c r="G191">
-        <v>0.5811346035593743</v>
+        <v>0.5708424179435508</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -17525,10 +17527,10 @@
         </is>
       </c>
       <c r="C192">
-        <v>0.1170263629334564</v>
+        <v>0.1488716504952723</v>
       </c>
       <c r="D192">
-        <v>0.09116142502613932</v>
+        <v>0.10150597323412</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -17536,10 +17538,10 @@
         </is>
       </c>
       <c r="F192">
-        <v>0.02542219614816965</v>
+        <v>0.03912303973523568</v>
       </c>
       <c r="G192">
-        <v>0.5387091477704254</v>
+        <v>0.5664889147462098</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -17569,10 +17571,10 @@
         </is>
       </c>
       <c r="C193">
-        <v>2.666666614472926</v>
+        <v>2.749999465376205</v>
       </c>
       <c r="D193">
-        <v>0.4737705001329935</v>
+        <v>0.484043038173523</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -17580,10 +17582,10 @@
         </is>
       </c>
       <c r="F193">
-        <v>1.882525652969056</v>
+        <v>1.947635971880981</v>
       </c>
       <c r="G193">
-        <v>3.777431038737288</v>
+        <v>3.882910959107894</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -17613,10 +17615,10 @@
         </is>
       </c>
       <c r="C194">
-        <v>1.583333807828417</v>
+        <v>1.66666539216155</v>
       </c>
       <c r="D194">
-        <v>0.3643251953358441</v>
+        <v>0.3751978812873778</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -17624,10 +17626,10 @@
         </is>
       </c>
       <c r="F194">
-        <v>1.008581420657841</v>
+        <v>1.072079179095076</v>
       </c>
       <c r="G194">
-        <v>2.485615831964557</v>
+        <v>2.59101527535838</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -17657,10 +17659,10 @@
         </is>
       </c>
       <c r="C195">
-        <v>2.916664025693721</v>
+        <v>2.916665153189768</v>
       </c>
       <c r="D195">
-        <v>0.4957121707355948</v>
+        <v>0.4988258795171759</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -17668,10 +17670,10 @@
         </is>
       </c>
       <c r="F195">
-        <v>2.090342121330058</v>
+        <v>2.085973989455612</v>
       </c>
       <c r="G195">
-        <v>4.069634798997904</v>
+        <v>4.078159966918665</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -17701,10 +17703,10 @@
         </is>
       </c>
       <c r="C196">
-        <v>2.33333371066667</v>
+        <v>2.333334014073394</v>
       </c>
       <c r="D196">
-        <v>0.4428957170308087</v>
+        <v>0.4451274806384051</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -17712,10 +17714,10 @@
         </is>
       </c>
       <c r="F196">
-        <v>1.608452467023211</v>
+        <v>1.60544029828606</v>
       </c>
       <c r="G196">
-        <v>3.384897171011596</v>
+        <v>3.391248884835056</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -17745,10 +17747,10 @@
         </is>
       </c>
       <c r="C197">
-        <v>5.652665199437532</v>
+        <v>5.830427086914773</v>
       </c>
       <c r="D197">
-        <v>0.5508148311604431</v>
+        <v>0.5723740551561706</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -17756,10 +17758,10 @@
         </is>
       </c>
       <c r="F197">
-        <v>4.669918527363976</v>
+        <v>4.809919002084793</v>
       </c>
       <c r="G197">
-        <v>6.842222978773982</v>
+        <v>7.067453734895603</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -17789,10 +17791,10 @@
         </is>
       </c>
       <c r="C198">
-        <v>6.068876246346494</v>
+        <v>6.152378938462419</v>
       </c>
       <c r="D198">
-        <v>1.498223781347279</v>
+        <v>1.535115789777987</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -17800,10 +17802,10 @@
         </is>
       </c>
       <c r="F198">
-        <v>3.740865676720218</v>
+        <v>3.772722286966257</v>
       </c>
       <c r="G198">
-        <v>9.845651268013533</v>
+        <v>10.03301163544522</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -17833,10 +17835,10 @@
         </is>
       </c>
       <c r="C199">
-        <v>7.402218499118093</v>
+        <v>7.545445377356375</v>
       </c>
       <c r="D199">
-        <v>0.7132994882752993</v>
+        <v>0.7345732304632828</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -17844,10 +17846,10 @@
         </is>
       </c>
       <c r="F199">
-        <v>6.128266212858454</v>
+        <v>6.234730534531737</v>
       </c>
       <c r="G199">
-        <v>8.941001713293501</v>
+        <v>9.13170916166062</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -17877,10 +17879,10 @@
         </is>
       </c>
       <c r="C200">
-        <v>6.651298302849343</v>
+        <v>6.651756218303245</v>
       </c>
       <c r="D200">
-        <v>1.625768483535167</v>
+        <v>1.646141627463636</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -17888,10 +17890,10 @@
         </is>
       </c>
       <c r="F200">
-        <v>4.119536001572789</v>
+        <v>4.095297397403568</v>
       </c>
       <c r="G200">
-        <v>10.73901747589931</v>
+        <v>10.80406536916901</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -17921,10 +17923,10 @@
         </is>
       </c>
       <c r="C201">
-        <v>7.749999921505244</v>
+        <v>7.750000225824689</v>
       </c>
       <c r="D201">
-        <v>1.149403336974842</v>
+        <v>1.164348037846134</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -17932,10 +17934,10 @@
         </is>
       </c>
       <c r="F201">
-        <v>5.795086249273578</v>
+        <v>5.773225389130515</v>
       </c>
       <c r="G201">
-        <v>10.36438392799766</v>
+        <v>10.40363045817765</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -17965,10 +17967,10 @@
         </is>
       </c>
       <c r="C202">
-        <v>5.818181981779771</v>
+        <v>5.818181806241961</v>
       </c>
       <c r="D202">
-        <v>0.9716592044772669</v>
+        <v>0.9825382997815564</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -17976,10 +17978,10 @@
         </is>
       </c>
       <c r="F202">
-        <v>4.194047122449351</v>
+        <v>4.178704624893864</v>
       </c>
       <c r="G202">
-        <v>8.071259235956662</v>
+        <v>8.100893116211767</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -18009,10 +18011,10 @@
         </is>
       </c>
       <c r="C203">
-        <v>6.666666757368843</v>
+        <v>6.666666650653625</v>
       </c>
       <c r="D203">
-        <v>1.027255267924408</v>
+        <v>1.039634643733724</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -18020,10 +18022,10 @@
         </is>
       </c>
       <c r="F203">
-        <v>4.928883557041765</v>
+        <v>4.910977536513347</v>
       </c>
       <c r="G203">
-        <v>9.017142551543994</v>
+        <v>9.050019858671863</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -18053,10 +18055,10 @@
         </is>
       </c>
       <c r="C204">
-        <v>5.1818180054444</v>
+        <v>5.272727358878822</v>
       </c>
       <c r="D204">
-        <v>0.8946580927449179</v>
+        <v>0.9153115982975009</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -18064,10 +18066,10 @@
         </is>
       </c>
       <c r="F204">
-        <v>3.694191303364496</v>
+        <v>3.752080915527091</v>
       </c>
       <c r="G204">
-        <v>7.268502261128962</v>
+        <v>7.409662645072159</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -18097,10 +18099,10 @@
         </is>
       </c>
       <c r="C205">
-        <v>0.3749970206409827</v>
+        <v>0.3749999997200773</v>
       </c>
       <c r="D205">
-        <v>0.2165263719708745</v>
+        <v>0.259037271073038</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -18108,10 +18110,10 @@
         </is>
       </c>
       <c r="F205">
-        <v>0.1209308281925399</v>
+        <v>0.09683896384262111</v>
       </c>
       <c r="G205">
-        <v>1.162836371762222</v>
+        <v>1.452153081879276</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -18141,10 +18143,10 @@
         </is>
       </c>
       <c r="C206">
-        <v>0.5000014885822631</v>
+        <v>0.625000000326168</v>
       </c>
       <c r="D206">
-        <v>0.2500325280139248</v>
+        <v>0.3664783936805166</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -18152,10 +18154,10 @@
         </is>
       </c>
       <c r="F206">
-        <v>0.1876361084466096</v>
+        <v>0.1980454453833687</v>
       </c>
       <c r="G206">
-        <v>1.332374086492073</v>
+        <v>1.972400827757252</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -18185,10 +18187,10 @@
         </is>
       </c>
       <c r="C207">
-        <v>2.703893376197959E-06</v>
+        <v>2.898285304433692E-10</v>
       </c>
       <c r="D207">
-        <v>0.0005813661638691779</v>
+        <v>6.019017131824634E-06</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -18198,8 +18200,10 @@
       <c r="F207">
         <v>2.220446049250313E-16</v>
       </c>
-      <c r="G207">
-        <v>2.815000150489916E+177</v>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -18229,10 +18233,10 @@
         </is>
       </c>
       <c r="C208">
-        <v>0.249999565321654</v>
+        <v>0.4999999998473475</v>
       </c>
       <c r="D208">
-        <v>0.1443467186391438</v>
+        <v>0.25619798603372</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -18240,10 +18244,10 @@
         </is>
       </c>
       <c r="F208">
-        <v>0.0806242709213347</v>
+        <v>0.1831545710249747</v>
       </c>
       <c r="G208">
-        <v>0.7751981127618151</v>
+        <v>1.364967297557962</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -18273,10 +18277,10 @@
         </is>
       </c>
       <c r="C209">
-        <v>3.050820105595005</v>
+        <v>3.050830052910358</v>
       </c>
       <c r="D209">
-        <v>2.079536970872567</v>
+        <v>2.079534405327655</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -18284,10 +18288,10 @@
         </is>
       </c>
       <c r="F209">
-        <v>0.8020663363739069</v>
+        <v>0.8020737673230141</v>
       </c>
       <c r="G209">
-        <v>11.60440588839743</v>
+        <v>11.60437405004002</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -18317,10 +18321,10 @@
         </is>
       </c>
       <c r="C210">
-        <v>15.91361996479092</v>
+        <v>16.00037016915394</v>
       </c>
       <c r="D210">
-        <v>16.31026789881376</v>
+        <v>16.39898528751336</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -18328,10 +18332,10 @@
         </is>
       </c>
       <c r="F210">
-        <v>2.134770484430267</v>
+        <v>2.146459086518233</v>
       </c>
       <c r="G210">
-        <v>118.6278816532253</v>
+        <v>119.2717099328585</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -18361,10 +18365,10 @@
         </is>
       </c>
       <c r="C211">
-        <v>1.42622947799121</v>
+        <v>1.491803275231747</v>
       </c>
       <c r="D211">
-        <v>0.3280204577316385</v>
+        <v>0.3334113839750386</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -18372,10 +18376,10 @@
         </is>
       </c>
       <c r="F211">
-        <v>0.9086997479775287</v>
+        <v>0.9626575131552125</v>
       </c>
       <c r="G211">
-        <v>2.238506754754136</v>
+        <v>2.31180558150731</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -18405,10 +18409,10 @@
         </is>
       </c>
       <c r="C212">
-        <v>0.4324324338673615</v>
+        <v>0.4594594587707326</v>
       </c>
       <c r="D212">
-        <v>0.1563690224345009</v>
+        <v>0.1611759600083705</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -18416,10 +18420,10 @@
         </is>
       </c>
       <c r="F212">
-        <v>0.2128731659603444</v>
+        <v>0.2310203168486974</v>
       </c>
       <c r="G212">
-        <v>0.8784470744202927</v>
+        <v>0.9137854069871812</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -18449,10 +18453,10 @@
         </is>
       </c>
       <c r="C213">
-        <v>0.7941176553652785</v>
+        <v>0.7941177063056886</v>
       </c>
       <c r="D213">
-        <v>0.1528280049948259</v>
+        <v>0.1528280181416982</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -18460,10 +18464,10 @@
         </is>
       </c>
       <c r="F213">
-        <v>0.54459173750099</v>
+        <v>0.5445917679411419</v>
       </c>
       <c r="G213">
-        <v>1.157973592211727</v>
+        <v>1.157973676047861</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -18493,10 +18497,10 @@
         </is>
       </c>
       <c r="C214">
-        <v>0.3125000062516433</v>
+        <v>0.3750000007464183</v>
       </c>
       <c r="D214">
-        <v>0.139754239964321</v>
+        <v>0.153093109079641</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -18504,10 +18508,10 @@
         </is>
       </c>
       <c r="F214">
-        <v>0.1300712035676332</v>
+        <v>0.168472761293514</v>
       </c>
       <c r="G214">
-        <v>0.7507907302210723</v>
+        <v>0.8347046696457728</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -18537,10 +18541,10 @@
         </is>
       </c>
       <c r="C215">
-        <v>1.681818173262388</v>
+        <v>1.772727271610793</v>
       </c>
       <c r="D215">
-        <v>0.2764891994148184</v>
+        <v>0.2838635453423144</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -18548,10 +18552,10 @@
         </is>
       </c>
       <c r="F215">
-        <v>1.218547244411598</v>
+        <v>1.29521120901666</v>
       </c>
       <c r="G215">
-        <v>2.321216826748021</v>
+        <v>2.426293069142381</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -18581,10 +18585,10 @@
         </is>
       </c>
       <c r="C216">
-        <v>0.6249999910059951</v>
+        <v>0.6250000616381806</v>
       </c>
       <c r="D216">
-        <v>0.2795084783593259</v>
+        <v>0.2795085109827953</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -18592,10 +18596,10 @@
         </is>
       </c>
       <c r="F216">
-        <v>0.2601423916248076</v>
+        <v>0.2601424201788943</v>
       </c>
       <c r="G216">
-        <v>1.501581446675081</v>
+        <v>1.501581621248488</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -18713,10 +18717,10 @@
         </is>
       </c>
       <c r="C219">
-        <v>0.5161236220072331</v>
+        <v>0.547180409314869</v>
       </c>
       <c r="D219">
-        <v>0.1642859860697628</v>
+        <v>0.17726937283557</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -18724,10 +18728,10 @@
         </is>
       </c>
       <c r="F219">
-        <v>0.2765731122510478</v>
+        <v>0.2899798424104788</v>
       </c>
       <c r="G219">
-        <v>0.9631579549644235</v>
+        <v>1.032507631734502</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -18757,10 +18761,10 @@
         </is>
       </c>
       <c r="C220">
-        <v>0.3275206363873051</v>
+        <v>0.3275120717836588</v>
       </c>
       <c r="D220">
-        <v>0.2610387905155789</v>
+        <v>0.2671949624068088</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -18768,10 +18772,10 @@
         </is>
       </c>
       <c r="F220">
-        <v>0.06867812847251761</v>
+        <v>0.06618956196724667</v>
       </c>
       <c r="G220">
-        <v>1.561920361625326</v>
+        <v>1.620560009403042</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -18801,10 +18805,10 @@
         </is>
       </c>
       <c r="C221">
-        <v>1.265558011501571</v>
+        <v>1.277761251247021</v>
       </c>
       <c r="D221">
-        <v>0.4081729717789695</v>
+        <v>0.4354593422846215</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -18812,10 +18816,10 @@
         </is>
       </c>
       <c r="F221">
-        <v>0.6725878798144128</v>
+        <v>0.6551810913559635</v>
       </c>
       <c r="G221">
-        <v>2.381305296369229</v>
+        <v>2.49194281814417</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -18845,10 +18849,10 @@
         </is>
       </c>
       <c r="C222">
-        <v>0.1632970664537828</v>
+        <v>0.1631287315352052</v>
       </c>
       <c r="D222">
-        <v>0.174053442414499</v>
+        <v>0.1762121719795941</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -18856,10 +18860,10 @@
         </is>
       </c>
       <c r="F222">
-        <v>0.02021660396319044</v>
+        <v>0.0196363090548669</v>
       </c>
       <c r="G222">
-        <v>1.319011440346923</v>
+        <v>1.355192718648388</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -18889,10 +18893,10 @@
         </is>
       </c>
       <c r="C223">
-        <v>7.333333083719854</v>
+        <v>7.499999925586994</v>
       </c>
       <c r="D223">
-        <v>1.147489998505174</v>
+        <v>1.14398781297197</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -18900,10 +18904,10 @@
         </is>
       </c>
       <c r="F223">
-        <v>5.396458873769295</v>
+        <v>5.561936576239034</v>
       </c>
       <c r="G223">
-        <v>9.965381998587842</v>
+        <v>10.11338373114657</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -19078,10 +19082,10 @@
         </is>
       </c>
       <c r="C228">
-        <v>4.695456901528026</v>
+        <v>4.84059440167619</v>
       </c>
       <c r="D228">
-        <v>1.247436711286089</v>
+        <v>1.307304578701699</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -19089,10 +19093,10 @@
         </is>
       </c>
       <c r="F228">
-        <v>2.789588279837912</v>
+        <v>2.851108668032045</v>
       </c>
       <c r="G228">
-        <v>7.903429933892688</v>
+        <v>8.218330793302304</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -19122,10 +19126,10 @@
         </is>
       </c>
       <c r="C229">
-        <v>4.257187406907024</v>
+        <v>4.256962556498384</v>
       </c>
       <c r="D229">
-        <v>2.967491349490299</v>
+        <v>3.020499931084274</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -19133,10 +19137,10 @@
         </is>
       </c>
       <c r="F229">
-        <v>1.085897818479966</v>
+        <v>1.059583883966395</v>
       </c>
       <c r="G229">
-        <v>16.69000923392326</v>
+        <v>17.10268576338973</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -19166,10 +19170,10 @@
         </is>
       </c>
       <c r="C230">
-        <v>6.030436552829274</v>
+        <v>6.057562951334629</v>
       </c>
       <c r="D230">
-        <v>0.4694802049693432</v>
+        <v>0.4796203101831957</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -19177,10 +19181,10 @@
         </is>
       </c>
       <c r="F230">
-        <v>5.177036171370845</v>
+        <v>5.18683294180842</v>
       </c>
       <c r="G230">
-        <v>7.024514377319851</v>
+        <v>7.074465154566612</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -19210,10 +19214,10 @@
         </is>
       </c>
       <c r="C231">
-        <v>6.072223693534967</v>
+        <v>6.239352107301236</v>
       </c>
       <c r="D231">
-        <v>1.143122643635365</v>
+        <v>1.189729884955871</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -19221,10 +19225,10 @@
         </is>
       </c>
       <c r="F231">
-        <v>4.198608224256492</v>
+        <v>4.293693007099409</v>
       </c>
       <c r="G231">
-        <v>8.781934063604348</v>
+        <v>9.066673992415465</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -19254,10 +19258,10 @@
         </is>
       </c>
       <c r="C232">
-        <v>7.338304941260374</v>
+        <v>7.389016357399666</v>
       </c>
       <c r="D232">
-        <v>0.5470320106694112</v>
+        <v>0.5607965489243963</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -19265,10 +19269,10 @@
         </is>
       </c>
       <c r="F232">
-        <v>6.340786929303538</v>
+        <v>6.367718599099616</v>
       </c>
       <c r="G232">
-        <v>8.49275019194523</v>
+        <v>8.57411675472591</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -19298,10 +19302,10 @@
         </is>
       </c>
       <c r="C233">
-        <v>6.321984564362658</v>
+        <v>6.40589504336164</v>
       </c>
       <c r="D233">
-        <v>1.181020945881316</v>
+        <v>1.215651109214772</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -19309,10 +19313,10 @@
         </is>
       </c>
       <c r="F233">
-        <v>4.383681458913405</v>
+        <v>4.41617948883379</v>
       </c>
       <c r="G233">
-        <v>9.117334187403879</v>
+        <v>9.292079592852268</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -19342,10 +19346,10 @@
         </is>
       </c>
       <c r="C234">
-        <v>9.801853292870899</v>
+        <v>9.832910139498683</v>
       </c>
       <c r="D234">
-        <v>0.6211441019785353</v>
+        <v>0.6204244330719119</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -19353,10 +19357,10 @@
         </is>
       </c>
       <c r="F234">
-        <v>8.657001624453031</v>
+        <v>8.689084887469251</v>
       </c>
       <c r="G234">
-        <v>11.09810672826741</v>
+        <v>11.12730777332945</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -19386,10 +19390,10 @@
         </is>
       </c>
       <c r="C235">
-        <v>9.241586501322956</v>
+        <v>9.323892685876583</v>
       </c>
       <c r="D235">
-        <v>0.956377559030914</v>
+        <v>0.9591450050817852</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -19397,10 +19401,10 @@
         </is>
       </c>
       <c r="F235">
-        <v>7.544992940264626</v>
+        <v>7.621395754639051</v>
       </c>
       <c r="G235">
-        <v>11.31968203782563</v>
+        <v>11.40669998206386</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -19430,10 +19434,10 @@
         </is>
       </c>
       <c r="C236">
-        <v>11.72242596700246</v>
+        <v>11.75523799755885</v>
       </c>
       <c r="D236">
-        <v>0.7286142518078047</v>
+        <v>0.7275475836181486</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -19441,10 +19445,10 @@
         </is>
       </c>
       <c r="F236">
-        <v>10.37792596510613</v>
+        <v>10.41236565986975</v>
       </c>
       <c r="G236">
-        <v>13.24111108653956</v>
+        <v>13.27129923143518</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -19474,10 +19478,10 @@
         </is>
       </c>
       <c r="C237">
-        <v>11.81814125256424</v>
+        <v>12.00087920152545</v>
       </c>
       <c r="D237">
-        <v>1.198452784108369</v>
+        <v>1.208482063807185</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -19485,10 +19489,10 @@
         </is>
       </c>
       <c r="F237">
-        <v>9.687921761282418</v>
+        <v>9.851390351074739</v>
       </c>
       <c r="G237">
-        <v>14.41676203700806</v>
+        <v>14.61936807669936</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -19518,10 +19522,10 @@
         </is>
       </c>
       <c r="C238">
-        <v>6.869772501333349</v>
+        <v>6.920760564884747</v>
       </c>
       <c r="D238">
-        <v>0.594980833496851</v>
+        <v>0.6023971171921341</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -19529,10 +19533,10 @@
         </is>
       </c>
       <c r="F238">
-        <v>5.797236912662856</v>
+        <v>5.835304260802356</v>
       </c>
       <c r="G238">
-        <v>8.140735824853197</v>
+        <v>8.208128429258284</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -19562,10 +19566,10 @@
         </is>
       </c>
       <c r="C239">
-        <v>6.077280430230815</v>
+        <v>6.131081414282935</v>
       </c>
       <c r="D239">
-        <v>0.7271868000036531</v>
+        <v>0.7356781695438597</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -19573,10 +19577,10 @@
         </is>
       </c>
       <c r="F239">
-        <v>4.806814717457351</v>
+        <v>4.846185812024649</v>
       </c>
       <c r="G239">
-        <v>7.683536728289575</v>
+        <v>7.756648375985639</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -19606,10 +19610,10 @@
         </is>
       </c>
       <c r="C240">
-        <v>7.418613033561928</v>
+        <v>7.467765814186362</v>
       </c>
       <c r="D240">
-        <v>0.6390829668220823</v>
+        <v>0.6466360463886708</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -19617,10 +19621,10 @@
         </is>
       </c>
       <c r="F240">
-        <v>6.266069536245724</v>
+        <v>6.302094299196281</v>
       </c>
       <c r="G240">
-        <v>8.783148514931623</v>
+        <v>8.849046619731261</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -19650,10 +19654,10 @@
         </is>
       </c>
       <c r="C241">
-        <v>5.435803227220957</v>
+        <v>5.456497611350612</v>
       </c>
       <c r="D241">
-        <v>0.6678307873310642</v>
+        <v>0.672606700176798</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -19661,10 +19665,10 @@
         </is>
       </c>
       <c r="F241">
-        <v>4.272548331512843</v>
+        <v>4.285374823124839</v>
       </c>
       <c r="G241">
-        <v>6.915768864948872</v>
+        <v>6.947669086496517</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -19694,10 +19698,10 @@
         </is>
       </c>
       <c r="C242">
-        <v>5.496217388308366</v>
+        <v>5.602165210503236</v>
       </c>
       <c r="D242">
-        <v>1.353252322708944</v>
+        <v>1.376156980687179</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -19705,10 +19709,10 @@
         </is>
       </c>
       <c r="F242">
-        <v>3.392228779673654</v>
+        <v>3.461469566077165</v>
       </c>
       <c r="G242">
-        <v>8.905179320614511</v>
+        <v>9.066743025373498</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -19738,10 +19742,10 @@
         </is>
       </c>
       <c r="C243">
-        <v>7.619473420161848</v>
+        <v>7.619044478924322</v>
       </c>
       <c r="D243">
-        <v>1.698888829444048</v>
+        <v>1.707479742052046</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -19749,10 +19753,10 @@
         </is>
       </c>
       <c r="F243">
-        <v>4.921929184880841</v>
+        <v>4.910666578709651</v>
       </c>
       <c r="G243">
-        <v>11.79545113710497</v>
+        <v>11.8211729184596</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -19782,10 +19786,10 @@
         </is>
       </c>
       <c r="C244">
-        <v>4.660491840678452</v>
+        <v>4.840664618691771</v>
       </c>
       <c r="D244">
-        <v>1.710822138901965</v>
+        <v>1.756381752971814</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -19793,10 +19797,10 @@
         </is>
       </c>
       <c r="F244">
-        <v>2.269675541612157</v>
+        <v>2.377146266203791</v>
       </c>
       <c r="G244">
-        <v>9.569730914755562</v>
+        <v>9.857211684358989</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -19826,10 +19830,10 @@
         </is>
       </c>
       <c r="C245">
-        <v>4.262845972875358</v>
+        <v>5.003534591427329</v>
       </c>
       <c r="D245">
-        <v>1.576504544413084</v>
+        <v>1.801735767300979</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -19837,10 +19841,10 @@
         </is>
       </c>
       <c r="F245">
-        <v>2.064926143462594</v>
+        <v>2.470390064274333</v>
       </c>
       <c r="G245">
-        <v>8.800244912386061</v>
+        <v>10.13417223848976</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -19870,10 +19874,10 @@
         </is>
       </c>
       <c r="C246">
-        <v>0.3472222109942356</v>
+        <v>0.4027777743480607</v>
       </c>
       <c r="D246">
-        <v>0.06944443746849148</v>
+        <v>0.0747939533498156</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -19881,10 +19885,10 @@
         </is>
       </c>
       <c r="F246">
-        <v>0.234621172683786</v>
+        <v>0.2798989974303398</v>
       </c>
       <c r="G246">
-        <v>0.5138635291462645</v>
+        <v>0.5796017027504805</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -19914,10 +19918,10 @@
         </is>
       </c>
       <c r="C247">
-        <v>0.7500005073497509</v>
+        <v>0.7499999915248144</v>
       </c>
       <c r="D247">
-        <v>0.250000063747706</v>
+        <v>0.25000000187967</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -19925,10 +19929,10 @@
         </is>
       </c>
       <c r="F247">
-        <v>0.3902364471571022</v>
+        <v>0.3902360665128861</v>
       </c>
       <c r="G247">
-        <v>1.441435737545117</v>
+        <v>1.441435160808355</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -39433,10 +39437,10 @@
         </is>
       </c>
       <c r="B299">
-        <v>5.833353543143454</v>
+        <v>6.000000819505097</v>
       </c>
       <c r="C299">
-        <v>1.472154470526223</v>
+        <v>1.485744244993134</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -39444,10 +39448,10 @@
         </is>
       </c>
       <c r="E299">
-        <v>3.557147492655998</v>
+        <v>3.692949533628961</v>
       </c>
       <c r="F299">
-        <v>9.566095763405288</v>
+        <v>9.748308095259999</v>
       </c>
       <c r="G299" s="2">
         <v>41885</v>
@@ -39480,10 +39484,10 @@
         </is>
       </c>
       <c r="B300">
-        <v>3.87500250184243</v>
+        <v>3.937494687740474</v>
       </c>
       <c r="C300">
-        <v>0.8936233984748413</v>
+        <v>0.8930786357767486</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -39491,10 +39495,10 @@
         </is>
       </c>
       <c r="E300">
-        <v>2.46589401575865</v>
+        <v>2.524385142985673</v>
       </c>
       <c r="F300">
-        <v>6.089330803889163</v>
+        <v>6.141639859933386</v>
       </c>
       <c r="G300" s="2">
         <v>42348</v>
@@ -39527,10 +39531,10 @@
         </is>
       </c>
       <c r="B301">
-        <v>6.600010129167218</v>
+        <v>7.099977669938008</v>
       </c>
       <c r="C301">
-        <v>1.800682935417391</v>
+        <v>1.891832685027754</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -39538,10 +39542,10 @@
         </is>
       </c>
       <c r="E301">
-        <v>3.866437594481288</v>
+        <v>4.211619233504152</v>
       </c>
       <c r="F301">
-        <v>11.26621926273552</v>
+        <v>11.96919287304054</v>
       </c>
       <c r="G301" s="2">
         <v>42412</v>
@@ -39574,10 +39578,10 @@
         </is>
       </c>
       <c r="B302">
-        <v>6.58333716030362</v>
+        <v>6.916659942866033</v>
       </c>
       <c r="C302">
-        <v>1.640060501790921</v>
+        <v>1.686827348508602</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -39585,10 +39589,10 @@
         </is>
       </c>
       <c r="E302">
-        <v>4.04010118030086</v>
+        <v>4.288509107495185</v>
       </c>
       <c r="F302">
-        <v>10.72753533440146</v>
+        <v>11.1554350395655</v>
       </c>
       <c r="G302" s="2">
         <v>42693</v>
@@ -39621,10 +39625,10 @@
         </is>
       </c>
       <c r="B303">
-        <v>8.333338699408676</v>
+        <v>8.916672186963137</v>
       </c>
       <c r="C303">
-        <v>2.031079783011102</v>
+        <v>2.124612497611873</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -39632,10 +39636,10 @@
         </is>
       </c>
       <c r="E303">
-        <v>5.16840071291345</v>
+        <v>5.589635329491247</v>
       </c>
       <c r="F303">
-        <v>13.43636798624232</v>
+        <v>14.22401251657297</v>
       </c>
       <c r="G303" s="2">
         <v>43806</v>
@@ -39668,10 +39672,10 @@
         </is>
       </c>
       <c r="B304">
-        <v>7.583320265641435</v>
+        <v>8.250001472664776</v>
       </c>
       <c r="C304">
-        <v>1.863599198634214</v>
+        <v>1.978792913095172</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -39679,10 +39683,10 @@
         </is>
       </c>
       <c r="E304">
-        <v>4.684646401923724</v>
+        <v>5.155730815964307</v>
       </c>
       <c r="F304">
-        <v>12.2755788414838</v>
+        <v>13.20133395797562</v>
       </c>
       <c r="G304" s="2">
         <v>44161</v>
@@ -39715,10 +39719,10 @@
         </is>
       </c>
       <c r="B305">
-        <v>7.999994734814892</v>
+        <v>8.499998985491588</v>
       </c>
       <c r="C305">
-        <v>2.396408629495268</v>
+        <v>2.490499786555067</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -39726,10 +39730,10 @@
         </is>
       </c>
       <c r="E305">
-        <v>4.447451214803934</v>
+        <v>4.786486224202359</v>
       </c>
       <c r="F305">
-        <v>14.39024570838096</v>
+        <v>15.09457655764968</v>
       </c>
       <c r="G305" s="2">
         <v>44522</v>
@@ -39762,10 +39766,10 @@
         </is>
       </c>
       <c r="B306">
-        <v>4.105257641679016</v>
+        <v>4.105274212158974</v>
       </c>
       <c r="C306">
-        <v>0.8613513341797308</v>
+        <v>0.849063248110054</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -39773,10 +39777,10 @@
         </is>
       </c>
       <c r="E306">
-        <v>2.721097960068091</v>
+        <v>2.737124198796343</v>
       </c>
       <c r="F306">
-        <v>6.193507382638376</v>
+        <v>6.157293251226507</v>
       </c>
       <c r="G306" s="2">
         <v>45694</v>
@@ -39809,10 +39813,10 @@
         </is>
       </c>
       <c r="B307">
-        <v>3.041675772406805</v>
+        <v>3.125004142808105</v>
       </c>
       <c r="C307">
-        <v>0.5960494723982518</v>
+        <v>0.6014941122758047</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -39820,10 +39824,10 @@
         </is>
       </c>
       <c r="E307">
-        <v>2.071622941845326</v>
+        <v>2.142955463527774</v>
       </c>
       <c r="F307">
-        <v>4.465963046443854</v>
+        <v>4.557094656783681</v>
       </c>
       <c r="G307" s="2">
         <v>46074</v>
@@ -39856,10 +39860,10 @@
         </is>
       </c>
       <c r="B308">
-        <v>0.2357022066287501</v>
+        <v>0.5270483835949014</v>
       </c>
       <c r="C308">
-        <v>0.1250001052100181</v>
+        <v>0.155902424532717</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -39867,10 +39871,10 @@
         </is>
       </c>
       <c r="E308">
-        <v>0.0833576337499923</v>
+        <v>0.2951634828364395</v>
       </c>
       <c r="F308">
-        <v>0.666472015943796</v>
+        <v>0.941105573022141</v>
       </c>
       <c r="G308" s="2">
         <v>42514</v>
@@ -39903,10 +39907,10 @@
         </is>
       </c>
       <c r="B309">
-        <v>0.1666668706427614</v>
+        <v>0.3118032931623324</v>
       </c>
       <c r="C309">
-        <v>0.08333337805723673</v>
+        <v>0.1250002033479704</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -39914,10 +39918,10 @@
         </is>
       </c>
       <c r="E309">
-        <v>0.06255309491546185</v>
+        <v>0.1421146142725065</v>
       </c>
       <c r="F309">
-        <v>0.444068288026223</v>
+        <v>0.6841048271112525</v>
       </c>
       <c r="G309" s="2">
         <v>42830</v>
@@ -39950,10 +39954,10 @@
         </is>
       </c>
       <c r="B310">
-        <v>0.1443365529530182</v>
+        <v>0.1666650309787779</v>
       </c>
       <c r="C310">
-        <v>0.08333326875093745</v>
+        <v>0.09316918200721944</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -39961,10 +39965,10 @@
         </is>
       </c>
       <c r="E310">
-        <v>0.04655130028640651</v>
+        <v>0.05571925594789347</v>
       </c>
       <c r="F310">
-        <v>0.4475286488279451</v>
+        <v>0.4985212397152827</v>
       </c>
       <c r="G310" s="2">
         <v>43187</v>
@@ -39997,10 +40001,10 @@
         </is>
       </c>
       <c r="B311">
-        <v>0.1863389686201035</v>
+        <v>0.186340494494809</v>
       </c>
       <c r="C311">
-        <v>0.102062048457545</v>
+        <v>0.1020620118595351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -40008,10 +40012,10 @@
         </is>
       </c>
       <c r="E311">
-        <v>0.06369149422201079</v>
+        <v>0.0636926001867531</v>
       </c>
       <c r="F311">
-        <v>0.5451624530172267</v>
+        <v>0.5451619149910547</v>
       </c>
       <c r="G311" s="2">
         <v>46105</v>
@@ -40044,10 +40048,10 @@
         </is>
       </c>
       <c r="B312">
-        <v>0.1458333312193889</v>
+        <v>0.1874999531583771</v>
       </c>
       <c r="C312">
-        <v>0.05511981401391951</v>
+        <v>0.06249998698638666</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -40055,10 +40059,10 @@
         </is>
       </c>
       <c r="E312">
-        <v>0.06952370017216954</v>
+        <v>0.09755899190600231</v>
       </c>
       <c r="F312">
-        <v>0.3059008718160451</v>
+        <v>0.3603587096130155</v>
       </c>
       <c r="G312" s="2">
         <v>44480</v>
@@ -40091,10 +40095,10 @@
         </is>
       </c>
       <c r="B313">
-        <v>0.7391304271327237</v>
+        <v>0.7391308854805023</v>
       </c>
       <c r="C313">
-        <v>0.1792654465488175</v>
+        <v>0.179265501718282</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -40102,10 +40106,10 @@
         </is>
       </c>
       <c r="E313">
-        <v>0.4594882373791083</v>
+        <v>0.4594885905434212</v>
       </c>
       <c r="F313">
-        <v>1.188961422450206</v>
+        <v>1.188961983201986</v>
       </c>
       <c r="G313" s="2">
         <v>45376</v>
@@ -40138,10 +40142,10 @@
         </is>
       </c>
       <c r="B314">
-        <v>0.4166666645797895</v>
+        <v>0.4166664480171317</v>
       </c>
       <c r="C314">
-        <v>0.1317615580426315</v>
+        <v>0.1317615236296038</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -40149,10 +40153,10 @@
         </is>
       </c>
       <c r="E314">
-        <v>0.2241894724726094</v>
+        <v>0.2241893200208225</v>
       </c>
       <c r="F314">
-        <v>0.7743945666015069</v>
+        <v>0.7743942882162642</v>
       </c>
       <c r="G314" s="2">
         <v>45610</v>
@@ -40185,10 +40189,10 @@
         </is>
       </c>
       <c r="B315">
-        <v>0.2727272642561515</v>
+        <v>0.2727268964920495</v>
       </c>
       <c r="C315">
-        <v>0.1113404319452871</v>
+        <v>0.1113403567809682</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -40196,10 +40200,10 @@
         </is>
       </c>
       <c r="E315">
-        <v>0.1225256469921766</v>
+        <v>0.1225254157523621</v>
       </c>
       <c r="F315">
-        <v>0.6070578894669615</v>
+        <v>0.6070573979566455</v>
       </c>
       <c r="G315" s="2">
         <v>45972</v>
@@ -40232,10 +40236,10 @@
         </is>
       </c>
       <c r="B316">
-        <v>2.788866488911453</v>
+        <v>2.832107572935201</v>
       </c>
       <c r="C316">
-        <v>0.3428439479050111</v>
+        <v>0.3475275128567057</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -40243,10 +40247,10 @@
         </is>
       </c>
       <c r="E316">
-        <v>2.19172921268171</v>
+        <v>2.226685732435847</v>
       </c>
       <c r="F316">
-        <v>3.548693993751504</v>
+        <v>3.602139802594709</v>
       </c>
       <c r="G316" s="2">
         <v>42747</v>
@@ -40279,10 +40283,10 @@
         </is>
       </c>
       <c r="B317">
-        <v>1.922094182997613</v>
+        <v>1.972026939071845</v>
       </c>
       <c r="C317">
-        <v>0.2866669548533204</v>
+        <v>0.2909502414610615</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -40290,10 +40294,10 @@
         </is>
       </c>
       <c r="E317">
-        <v>1.43490743235192</v>
+        <v>1.476820443444886</v>
       </c>
       <c r="F317">
-        <v>2.574692948839068</v>
+        <v>2.633285763131569</v>
       </c>
       <c r="G317" s="2">
         <v>46091</v>
@@ -40326,10 +40330,10 @@
         </is>
       </c>
       <c r="B318">
-        <v>5.526318898858108</v>
+        <v>5.631579992862449</v>
       </c>
       <c r="C318">
-        <v>0.5853388776363322</v>
+        <v>0.5931219868903032</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -40337,10 +40341,10 @@
         </is>
       </c>
       <c r="E318">
-        <v>4.490327668771329</v>
+        <v>4.581219587773228</v>
       </c>
       <c r="F318">
-        <v>6.801330064234018</v>
+        <v>6.922762074241465</v>
       </c>
       <c r="G318" s="2">
         <v>42348</v>
@@ -40373,10 +40377,10 @@
         </is>
       </c>
       <c r="B319">
-        <v>4.291668748397404</v>
+        <v>4.291667878423757</v>
       </c>
       <c r="C319">
-        <v>0.4511466986750166</v>
+        <v>0.4519822421296537</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -40384,10 +40388,10 @@
         </is>
       </c>
       <c r="E319">
-        <v>3.492581926135752</v>
+        <v>3.49124861078885</v>
       </c>
       <c r="F319">
-        <v>5.273582992611249</v>
+        <v>5.27559484643307</v>
       </c>
       <c r="G319" s="2">
         <v>42710</v>
@@ -40420,10 +40424,10 @@
         </is>
       </c>
       <c r="B320">
-        <v>6.583328816523499</v>
+        <v>6.624998771418097</v>
       </c>
       <c r="C320">
-        <v>0.5765927231052831</v>
+        <v>0.5802863782090038</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -40431,10 +40435,10 @@
         </is>
       </c>
       <c r="E320">
-        <v>5.544905020563816</v>
+        <v>5.579929442750418</v>
       </c>
       <c r="F320">
-        <v>7.816223748781507</v>
+        <v>7.865799948118531</v>
       </c>
       <c r="G320" s="2">
         <v>43074</v>
@@ -40467,10 +40471,10 @@
         </is>
       </c>
       <c r="B321">
-        <v>6.608699651745802</v>
+        <v>6.956521471453435</v>
       </c>
       <c r="C321">
-        <v>0.5903267648645755</v>
+        <v>0.6101504694991475</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -40478,10 +40482,10 @@
         </is>
       </c>
       <c r="E321">
-        <v>5.547302328496434</v>
+        <v>5.857792454204294</v>
       </c>
       <c r="F321">
-        <v>7.873180241615376</v>
+        <v>8.261335880560189</v>
       </c>
       <c r="G321" s="2">
         <v>43445</v>
@@ -40514,10 +40518,10 @@
         </is>
       </c>
       <c r="B322">
-        <v>6.791669393126003</v>
+        <v>7.041667221006793</v>
       </c>
       <c r="C322">
-        <v>0.5872640690686417</v>
+        <v>0.6016374599379709</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -40525,10 +40529,10 @@
         </is>
       </c>
       <c r="E322">
-        <v>5.732902969777424</v>
+        <v>5.955924036564094</v>
       </c>
       <c r="F322">
-        <v>8.045971367158057</v>
+        <v>8.325337419851749</v>
       </c>
       <c r="G322" s="2">
         <v>44169</v>
@@ -40561,10 +40565,10 @@
         </is>
       </c>
       <c r="B323">
-        <v>6.750002088937262</v>
+        <v>7.249997948228454</v>
       </c>
       <c r="C323">
-        <v>1.433288191406224</v>
+        <v>1.499530144933809</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -40572,10 +40576,10 @@
         </is>
       </c>
       <c r="E323">
-        <v>4.452056693191706</v>
+        <v>4.833729397864677</v>
       </c>
       <c r="F323">
-        <v>10.23404043132105</v>
+        <v>10.87410277301342</v>
       </c>
       <c r="G323" s="2">
         <v>45694</v>
@@ -40608,10 +40612,10 @@
         </is>
       </c>
       <c r="B324">
-        <v>9.869560291482289</v>
+        <v>9.913042303656157</v>
       </c>
       <c r="C324">
-        <v>0.7519948047400089</v>
+        <v>0.7568305841598822</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -40619,10 +40623,10 @@
         </is>
       </c>
       <c r="E324">
-        <v>8.50044990323893</v>
+        <v>8.53532995442907</v>
       </c>
       <c r="F324">
-        <v>11.45918409684274</v>
+        <v>11.51313519673415</v>
       </c>
       <c r="G324" s="2">
         <v>45708</v>
@@ -40655,10 +40659,10 @@
         </is>
       </c>
       <c r="B325">
-        <v>6.37500342283135</v>
+        <v>6.416665673709891</v>
       </c>
       <c r="C325">
-        <v>0.5658239654490451</v>
+        <v>0.5694688158430001</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -40666,10 +40670,10 @@
         </is>
       </c>
       <c r="E325">
-        <v>5.357110720523104</v>
+        <v>5.392207999398535</v>
       </c>
       <c r="F325">
-        <v>7.5863036553299</v>
+        <v>7.635758556190607</v>
       </c>
       <c r="G325" s="2">
         <v>46008</v>
@@ -40702,10 +40706,10 @@
         </is>
       </c>
       <c r="B326">
-        <v>7.187952927348838</v>
+        <v>7.187952100766494</v>
       </c>
       <c r="C326">
-        <v>0.7686329220567735</v>
+        <v>0.7782472859516002</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -40713,10 +40717,10 @@
         </is>
       </c>
       <c r="E326">
-        <v>5.828855231860998</v>
+        <v>5.81359361281431</v>
       </c>
       <c r="F326">
-        <v>8.863947590149179</v>
+        <v>8.887214835421233</v>
       </c>
       <c r="G326" s="2">
         <v>42323</v>
@@ -40749,10 +40753,10 @@
         </is>
       </c>
       <c r="B327">
-        <v>5.490788697192046</v>
+        <v>5.538745611898268</v>
       </c>
       <c r="C327">
-        <v>0.6594633735921108</v>
+        <v>0.6706977403477014</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -40760,10 +40764,10 @@
         </is>
       </c>
       <c r="E327">
-        <v>4.339127177920621</v>
+        <v>4.36855420041448</v>
       </c>
       <c r="F327">
-        <v>6.948116356354342</v>
+        <v>7.022392660347827</v>
       </c>
       <c r="G327" s="2">
         <v>45995</v>
@@ -40796,10 +40800,10 @@
         </is>
       </c>
       <c r="B328">
-        <v>0.0001602398564810358</v>
+        <v>1.22455141447295E-05</v>
       </c>
       <c r="C328">
-        <v>0.1082531743722539</v>
+        <v>0.1082532481374174</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -40845,10 +40849,10 @@
         </is>
       </c>
       <c r="B329">
-        <v>0.3535533933762104</v>
+        <v>0.5590164757336562</v>
       </c>
       <c r="C329">
-        <v>0.1350156997097538</v>
+        <v>0.2176529532702002</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -40856,10 +40860,10 @@
         </is>
       </c>
       <c r="E329">
-        <v>0.1672616618453571</v>
+        <v>0.2606210300598171</v>
       </c>
       <c r="F329">
-        <v>0.7473320579787313</v>
+        <v>1.199056807004229</v>
       </c>
       <c r="G329" s="2">
         <v>46069</v>
@@ -40892,10 +40896,10 @@
         </is>
       </c>
       <c r="B330">
-        <v>7.166668949894281</v>
+        <v>7.166708483647556</v>
       </c>
       <c r="C330">
-        <v>2.97545490995247</v>
+        <v>2.975519924372275</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -40903,10 +40907,10 @@
         </is>
       </c>
       <c r="E330">
-        <v>3.176258264556973</v>
+        <v>3.176233568882223</v>
       </c>
       <c r="F330">
-        <v>16.17032985337</v>
+        <v>16.17063398384175</v>
       </c>
       <c r="G330" s="2">
         <v>42388</v>
@@ -40939,10 +40943,10 @@
         </is>
       </c>
       <c r="B331">
-        <v>6.000001026286184</v>
+        <v>6.000056853513934</v>
       </c>
       <c r="C331">
-        <v>1.317876448518867</v>
+        <v>1.317911306051661</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -40950,10 +40954,10 @@
         </is>
       </c>
       <c r="E331">
-        <v>3.901110741307669</v>
+        <v>3.901118245359604</v>
       </c>
       <c r="F331">
-        <v>9.228144162697594</v>
+        <v>9.228298139443091</v>
       </c>
       <c r="G331" s="2">
         <v>43512</v>
@@ -40986,10 +40990,10 @@
         </is>
       </c>
       <c r="B332">
-        <v>5.041667229010918</v>
+        <v>5.041714308109698</v>
       </c>
       <c r="C332">
-        <v>1.075944630936614</v>
+        <v>1.075972457167668</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -40997,10 +41001,10 @@
         </is>
       </c>
       <c r="E332">
-        <v>3.318324441090738</v>
+        <v>3.318332492544584</v>
       </c>
       <c r="F332">
-        <v>7.660013027456581</v>
+        <v>7.660137500297987</v>
       </c>
       <c r="G332" s="2">
         <v>43931</v>
@@ -41033,10 +41037,10 @@
         </is>
       </c>
       <c r="B333">
-        <v>10.0833327385998</v>
+        <v>10.08334169272473</v>
       </c>
       <c r="C333">
-        <v>2.90189117969914</v>
+        <v>2.901938030108442</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -41044,10 +41048,10 @@
         </is>
       </c>
       <c r="E333">
-        <v>5.736355516934944</v>
+        <v>5.736311245567516</v>
       </c>
       <c r="F333">
-        <v>17.72442429991592</v>
+        <v>17.72459257171667</v>
       </c>
       <c r="G333" s="2">
         <v>44636</v>
@@ -41080,10 +41084,10 @@
         </is>
       </c>
       <c r="B334">
-        <v>15.50000033889721</v>
+        <v>15.58335866566931</v>
       </c>
       <c r="C334">
-        <v>4.382293747381443</v>
+        <v>4.405140226520501</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -41091,10 +41095,10 @@
         </is>
       </c>
       <c r="E334">
-        <v>8.905794461112979</v>
+        <v>8.954501757763582</v>
       </c>
       <c r="F334">
-        <v>26.97681959255423</v>
+        <v>27.11943934706884</v>
       </c>
       <c r="G334" s="2">
         <v>45971</v>
@@ -41127,10 +41131,10 @@
         </is>
       </c>
       <c r="B335">
-        <v>15.16666627119107</v>
+        <v>15.25035684249721</v>
       </c>
       <c r="C335">
-        <v>4.291218728027172</v>
+        <v>4.314198853514867</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -41138,10 +41142,10 @@
         </is>
       </c>
       <c r="E335">
-        <v>8.710704657510368</v>
+        <v>8.75955781117616</v>
       </c>
       <c r="F335">
-        <v>26.40748077520397</v>
+        <v>26.55081327584427</v>
       </c>
       <c r="G335" s="2">
         <v>46120</v>
@@ -41174,10 +41178,10 @@
         </is>
       </c>
       <c r="B336">
-        <v>1.357145949100642</v>
+        <v>1.428570510554043</v>
       </c>
       <c r="C336">
-        <v>0.6243377018886158</v>
+        <v>0.6450567699517034</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -41185,10 +41189,10 @@
         </is>
       </c>
       <c r="E336">
-        <v>0.5508611320788935</v>
+        <v>0.5895900032739662</v>
       </c>
       <c r="F336">
-        <v>3.343574305577429</v>
+        <v>3.461411645876109</v>
       </c>
       <c r="G336" s="2">
         <v>44117</v>
@@ -41221,10 +41225,10 @@
         </is>
       </c>
       <c r="B337">
-        <v>1.399999409567985</v>
+        <v>1.466667944421783</v>
       </c>
       <c r="C337">
-        <v>0.6198398351391733</v>
+        <v>0.6377625811176141</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -41232,10 +41236,10 @@
         </is>
       </c>
       <c r="E337">
-        <v>0.5878471142362661</v>
+        <v>0.6254566880485304</v>
       </c>
       <c r="F337">
-        <v>3.334197445771502</v>
+        <v>3.439270696594597</v>
       </c>
       <c r="G337" s="2">
         <v>44494</v>
@@ -41268,10 +41272,10 @@
         </is>
       </c>
       <c r="B338">
-        <v>0.9999998850398218</v>
+        <v>1.06249910013649</v>
       </c>
       <c r="C338">
-        <v>0.4490290651431539</v>
+        <v>0.4673497159585276</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -41279,10 +41283,10 @@
         </is>
       </c>
       <c r="E338">
-        <v>0.4147493107212729</v>
+        <v>0.4486627066398312</v>
       </c>
       <c r="F338">
-        <v>2.411094471358131</v>
+        <v>2.516153718782541</v>
       </c>
       <c r="G338" s="2">
         <v>44897</v>
@@ -41315,10 +41319,10 @@
         </is>
       </c>
       <c r="B339">
-        <v>1.937498472289012</v>
+        <v>1.999997491366146</v>
       </c>
       <c r="C339">
-        <v>0.8020989195822872</v>
+        <v>0.8146210287566168</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -41326,10 +41330,10 @@
         </is>
       </c>
       <c r="E339">
-        <v>0.8607065538193635</v>
+        <v>0.9001723681726183</v>
       </c>
       <c r="F339">
-        <v>4.361417156014924</v>
+        <v>4.443582259241081</v>
       </c>
       <c r="G339" s="2">
         <v>45253</v>
@@ -41362,10 +41366,10 @@
         </is>
       </c>
       <c r="B340">
-        <v>0.1111108400395863</v>
+        <v>0.1666665230583166</v>
       </c>
       <c r="C340">
-        <v>0.08774728340632286</v>
+        <v>0.1121784013721027</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -41373,10 +41377,10 @@
         </is>
       </c>
       <c r="E340">
-        <v>0.02363410625047743</v>
+        <v>0.04455837165605232</v>
       </c>
       <c r="F340">
-        <v>0.5223645287645746</v>
+        <v>0.6234009205445313</v>
       </c>
       <c r="G340" s="2">
         <v>45951</v>
@@ -41409,10 +41413,10 @@
         </is>
       </c>
       <c r="B341">
-        <v>0.7368423581037838</v>
+        <v>0.7368426016663441</v>
       </c>
       <c r="C341">
-        <v>0.3199867237307444</v>
+        <v>0.3167738622691902</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -41420,10 +41424,10 @@
         </is>
       </c>
       <c r="E341">
-        <v>0.3145758488455025</v>
+        <v>0.3172759438163327</v>
       </c>
       <c r="F341">
-        <v>1.725932434700659</v>
+        <v>1.711245463805874</v>
       </c>
       <c r="G341" s="2">
         <v>46101</v>
@@ -41456,10 +41460,10 @@
         </is>
       </c>
       <c r="B342">
-        <v>1.260869575599951</v>
+        <v>1.347826086967049</v>
       </c>
       <c r="C342">
-        <v>0.234251500461256</v>
+        <v>0.242076696143823</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -41467,10 +41471,10 @@
         </is>
       </c>
       <c r="E342">
-        <v>0.8760504466521489</v>
+        <v>0.947880430720853</v>
       </c>
       <c r="F342">
-        <v>1.814726643595738</v>
+        <v>1.91652354224401</v>
       </c>
       <c r="G342" s="2">
         <v>42011</v>
@@ -41503,10 +41507,10 @@
         </is>
       </c>
       <c r="B343">
-        <v>1.285714184040422</v>
+        <v>1.285714285729357</v>
       </c>
       <c r="C343">
-        <v>0.2475651035195406</v>
+        <v>0.2474358138010048</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -41514,10 +41518,10 @@
         </is>
       </c>
       <c r="E343">
-        <v>0.881546090081927</v>
+        <v>0.8817199483872623</v>
       </c>
       <c r="F343">
-        <v>1.875183818113354</v>
+        <v>1.874814364302559</v>
       </c>
       <c r="G343" s="2">
         <v>42379</v>
@@ -41550,10 +41554,10 @@
         </is>
       </c>
       <c r="B344">
-        <v>1.333333318962954</v>
+        <v>1.333333333346369</v>
       </c>
       <c r="C344">
-        <v>0.4714044789878267</v>
+        <v>0.4714044909268846</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -41561,10 +41565,10 @@
         </is>
       </c>
       <c r="E344">
-        <v>0.6667968871086455</v>
+        <v>0.6667968875838914</v>
       </c>
       <c r="F344">
-        <v>2.666145829152771</v>
+        <v>2.666145884774954</v>
       </c>
       <c r="G344" s="2">
         <v>42440</v>
@@ -41597,10 +41601,10 @@
         </is>
       </c>
       <c r="B345">
-        <v>0.4166666962822476</v>
+        <v>0.4583333333378959</v>
       </c>
       <c r="C345">
-        <v>0.1319909416999481</v>
+        <v>0.1381926890317851</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -41608,10 +41612,10 @@
         </is>
       </c>
       <c r="E345">
-        <v>0.2239477299066336</v>
+        <v>0.253825085575388</v>
       </c>
       <c r="F345">
-        <v>0.7752306123537988</v>
+        <v>0.8276149852266458</v>
       </c>
       <c r="G345" s="2">
         <v>46048</v>
@@ -42067,10 +42071,10 @@
         </is>
       </c>
       <c r="B355">
-        <v>1.118032966860657</v>
+        <v>1.118034069877615</v>
       </c>
       <c r="C355">
-        <v>0.2935468770766615</v>
+        <v>0.3065841706870792</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -42078,10 +42082,10 @@
         </is>
       </c>
       <c r="E355">
-        <v>0.6682917043237376</v>
+        <v>0.6531921177020154</v>
       </c>
       <c r="F355">
-        <v>1.870437275967908</v>
+        <v>1.913679218611376</v>
       </c>
       <c r="G355" s="2">
         <v>41885</v>
@@ -42114,10 +42118,10 @@
         </is>
       </c>
       <c r="B356">
-        <v>2.377767660314467E-05</v>
+        <v>2.657813713935213E-05</v>
       </c>
       <c r="C356">
-        <v>0.1628346464959031</v>
+        <v>0.1628346882182792</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -42163,10 +42167,10 @@
         </is>
       </c>
       <c r="B357">
-        <v>0.8164960889296407</v>
+        <v>0.8728710234788485</v>
       </c>
       <c r="C357">
-        <v>0.357296821706945</v>
+        <v>0.3893334957842375</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42174,10 +42178,10 @@
         </is>
       </c>
       <c r="E357">
-        <v>0.3463141682910363</v>
+        <v>0.3641514039573894</v>
       </c>
       <c r="F357">
-        <v>1.925032020859006</v>
+        <v>2.09227210261742</v>
       </c>
       <c r="G357" s="2">
         <v>42677</v>
@@ -42210,10 +42214,10 @@
         </is>
       </c>
       <c r="B358">
-        <v>0.2357014899312558</v>
+        <v>0.2357019766135715</v>
       </c>
       <c r="C358">
-        <v>0.1484258279297697</v>
+        <v>0.1499795950437264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42221,10 +42225,10 @@
         </is>
       </c>
       <c r="E358">
-        <v>0.06860315750334023</v>
+        <v>0.06772280171334999</v>
       </c>
       <c r="F358">
-        <v>0.8098051806596355</v>
+        <v>0.8203355498299345</v>
       </c>
       <c r="G358" s="2">
         <v>45943</v>
@@ -42257,10 +42261,10 @@
         </is>
       </c>
       <c r="B359">
-        <v>7.333333083719854</v>
+        <v>7.499999925586994</v>
       </c>
       <c r="C359">
-        <v>1.147489998505174</v>
+        <v>1.14398781297197</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42268,10 +42272,10 @@
         </is>
       </c>
       <c r="E359">
-        <v>5.396458873769295</v>
+        <v>5.561936576239034</v>
       </c>
       <c r="F359">
-        <v>9.965381998587842</v>
+        <v>10.11338373114657</v>
       </c>
       <c r="G359" s="2">
         <v>42769</v>
@@ -42403,10 +42407,10 @@
         </is>
       </c>
       <c r="B362">
-        <v>0.7272727209324156</v>
+        <v>0.7272727141114353</v>
       </c>
       <c r="C362">
-        <v>0.2571297168204916</v>
+        <v>0.2571297149529692</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42414,10 +42418,10 @@
         </is>
       </c>
       <c r="E362">
-        <v>0.3637073932477403</v>
+        <v>0.3637073893033126</v>
       </c>
       <c r="F362">
-        <v>1.454261366230079</v>
+        <v>1.454261354723034</v>
       </c>
       <c r="G362" s="2">
         <v>42122</v>
@@ -42450,10 +42454,10 @@
         </is>
       </c>
       <c r="B363">
-        <v>6.916666554034431</v>
+        <v>7.083333392101308</v>
       </c>
       <c r="C363">
-        <v>0.7592027500258481</v>
+        <v>0.7682953133303558</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -42461,10 +42465,10 @@
         </is>
       </c>
       <c r="E363">
-        <v>5.577830801271071</v>
+        <v>5.726798740681464</v>
       </c>
       <c r="F363">
-        <v>8.576860418354162</v>
+        <v>8.761196999510236</v>
       </c>
       <c r="G363" s="2">
         <v>42286</v>
@@ -42497,10 +42501,10 @@
         </is>
       </c>
       <c r="B364">
-        <v>5.74999992353852</v>
+        <v>6.249999938620112</v>
       </c>
       <c r="C364">
-        <v>1.198957800792891</v>
+        <v>1.249999893608732</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -42508,10 +42512,10 @@
         </is>
       </c>
       <c r="E364">
-        <v>3.821026567826744</v>
+        <v>4.223181215274619</v>
       </c>
       <c r="F364">
-        <v>8.652779176957596</v>
+        <v>9.249543706878633</v>
       </c>
       <c r="G364" s="2">
         <v>44481</v>
@@ -42544,10 +42548,10 @@
         </is>
       </c>
       <c r="B365">
-        <v>9.499999862201479</v>
+        <v>9.750000243968081</v>
       </c>
       <c r="C365">
-        <v>1.541103420282436</v>
+        <v>1.56124939665557</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -42555,10 +42559,10 @@
         </is>
       </c>
       <c r="E365">
-        <v>6.912584929595971</v>
+        <v>7.123662036786921</v>
       </c>
       <c r="F365">
-        <v>13.05589707772358</v>
+        <v>13.34461183959464</v>
       </c>
       <c r="G365" s="2">
         <v>44896</v>
@@ -42591,10 +42595,10 @@
         </is>
       </c>
       <c r="B366">
-        <v>6.249999915993759</v>
+        <v>6.749999890772609</v>
       </c>
       <c r="C366">
-        <v>1.249999918992642</v>
+        <v>1.299037991306498</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -42602,10 +42606,10 @@
         </is>
       </c>
       <c r="E366">
-        <v>4.223181160375107</v>
+        <v>4.629029667665272</v>
       </c>
       <c r="F366">
-        <v>9.249543760147962</v>
+        <v>9.842775224296727</v>
       </c>
       <c r="G366" s="2">
         <v>45261</v>
@@ -42638,10 +42642,10 @@
         </is>
       </c>
       <c r="B367">
-        <v>7.249999906572736</v>
+        <v>7.250000386528751</v>
       </c>
       <c r="C367">
-        <v>1.346291120347752</v>
+        <v>1.346291130371531</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -42649,10 +42653,10 @@
         </is>
       </c>
       <c r="E367">
-        <v>5.038181978118046</v>
+        <v>5.038182419388239</v>
       </c>
       <c r="F367">
-        <v>10.43283050782909</v>
+        <v>10.43283097539161</v>
       </c>
       <c r="G367" s="2">
         <v>45645</v>
@@ -42685,10 +42689,10 @@
         </is>
       </c>
       <c r="B368">
-        <v>3.499999953775438</v>
+        <v>3.499999808285787</v>
       </c>
       <c r="C368">
-        <v>0.9354142757902669</v>
+        <v>0.9354142447631232</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -42696,10 +42700,10 @@
         </is>
       </c>
       <c r="E368">
-        <v>2.072883388758375</v>
+        <v>2.072883293471891</v>
       </c>
       <c r="F368">
-        <v>5.909642454014564</v>
+        <v>5.909642234359904</v>
       </c>
       <c r="G368" s="2">
         <v>45692</v>
@@ -42732,10 +42736,10 @@
         </is>
       </c>
       <c r="B369">
-        <v>4.333333261161916</v>
+        <v>4.333333083772111</v>
       </c>
       <c r="C369">
-        <v>0.8498365225787105</v>
+        <v>0.8498364921520839</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -42743,10 +42747,10 @@
         </is>
       </c>
       <c r="E369">
-        <v>2.950446493366765</v>
+        <v>2.950446366765439</v>
       </c>
       <c r="F369">
-        <v>6.364384914116771</v>
+        <v>6.364384666141176</v>
       </c>
       <c r="G369" s="2">
         <v>45974</v>
@@ -42779,10 +42783,10 @@
         </is>
       </c>
       <c r="B370">
-        <v>5.477225681964649</v>
+        <v>5.47720076319367</v>
       </c>
       <c r="C370">
-        <v>0.4994500148183854</v>
+        <v>0.5063223709179533</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -42790,10 +42794,10 @@
         </is>
       </c>
       <c r="E370">
-        <v>4.580811223702099</v>
+        <v>4.569535396178167</v>
       </c>
       <c r="F370">
-        <v>6.549058606900603</v>
+        <v>6.565159386974059</v>
       </c>
       <c r="G370" s="2">
         <v>42348</v>
@@ -42826,10 +42830,10 @@
         </is>
       </c>
       <c r="B371">
-        <v>5.748154756745699</v>
+        <v>5.748163237352045</v>
       </c>
       <c r="C371">
-        <v>0.5097390079941028</v>
+        <v>0.517153619568975</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -42837,10 +42841,10 @@
         </is>
       </c>
       <c r="E371">
-        <v>4.831088446048543</v>
+        <v>4.818898373087258</v>
       </c>
       <c r="F371">
-        <v>6.839304118831319</v>
+        <v>6.856625320794505</v>
       </c>
       <c r="G371" s="2">
         <v>42710</v>
@@ -42873,10 +42877,10 @@
         </is>
       </c>
       <c r="B372">
-        <v>6.175203116654576</v>
+        <v>6.175211404993275</v>
       </c>
       <c r="C372">
-        <v>0.5614019362450735</v>
+        <v>0.5699455565237388</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -42884,10 +42888,10 @@
         </is>
       </c>
       <c r="E372">
-        <v>5.167334246507592</v>
+        <v>5.153349227620903</v>
       </c>
       <c r="F372">
-        <v>7.379652972461217</v>
+        <v>7.399699537530398</v>
       </c>
       <c r="G372" s="2">
         <v>43074</v>
@@ -42920,10 +42924,10 @@
         </is>
       </c>
       <c r="B373">
-        <v>5.942261650262304</v>
+        <v>6.03020765796356</v>
       </c>
       <c r="C373">
-        <v>0.5310838782986893</v>
+        <v>0.5433363867039476</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -42931,10 +42935,10 @@
         </is>
       </c>
       <c r="E373">
-        <v>4.987425913897603</v>
+        <v>5.054019778136324</v>
       </c>
       <c r="F373">
-        <v>7.079899356857503</v>
+        <v>7.194946991594762</v>
       </c>
       <c r="G373" s="2">
         <v>43445</v>
@@ -42967,10 +42971,10 @@
         </is>
       </c>
       <c r="B374">
-        <v>7.943423148100039</v>
+        <v>7.976969501524413</v>
       </c>
       <c r="C374">
-        <v>0.6114762534215935</v>
+        <v>0.6249793267024574</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -42978,10 +42982,10 @@
         </is>
       </c>
       <c r="E374">
-        <v>6.830981512525656</v>
+        <v>6.841447883499771</v>
       </c>
       <c r="F374">
-        <v>9.23702855791246</v>
+        <v>9.300961362538274</v>
       </c>
       <c r="G374" s="2">
         <v>44217</v>
@@ -43014,10 +43018,10 @@
         </is>
       </c>
       <c r="B375">
-        <v>8.716112078516058</v>
+        <v>8.843331800082924</v>
       </c>
       <c r="C375">
-        <v>0.6520678808409747</v>
+        <v>0.6715801187735475</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -43025,10 +43029,10 @@
         </is>
       </c>
       <c r="E375">
-        <v>7.527363718075702</v>
+        <v>7.620333705736005</v>
       </c>
       <c r="F375">
-        <v>10.09259185693696</v>
+        <v>10.26261058193442</v>
       </c>
       <c r="G375" s="2">
         <v>45715</v>
@@ -43061,10 +43065,10 @@
         </is>
       </c>
       <c r="B376">
-        <v>6.207076882920052</v>
+        <v>6.332779651851649</v>
       </c>
       <c r="C376">
-        <v>0.5294063971161286</v>
+        <v>0.543694317303686</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -43072,10 +43076,10 @@
         </is>
       </c>
       <c r="E376">
-        <v>5.251549767503353</v>
+        <v>5.35199056980143</v>
       </c>
       <c r="F376">
-        <v>7.336463546226101</v>
+        <v>7.49330507889782</v>
       </c>
       <c r="G376" s="2">
         <v>46001</v>
@@ -43108,10 +43112,10 @@
         </is>
       </c>
       <c r="B377">
-        <v>12.78991293020447</v>
+        <v>12.78993127184115</v>
       </c>
       <c r="C377">
-        <v>0.9660556014805886</v>
+        <v>0.9688711369634341</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -43119,10 +43123,10 @@
         </is>
       </c>
       <c r="E377">
-        <v>11.02996431422716</v>
+        <v>11.02522450013422</v>
       </c>
       <c r="F377">
-        <v>14.83068014564772</v>
+        <v>14.83709850411017</v>
       </c>
       <c r="G377" s="2">
         <v>42389</v>
@@ -43155,10 +43159,10 @@
         </is>
       </c>
       <c r="B378">
-        <v>8.647125712465712</v>
+        <v>8.68817323617516</v>
       </c>
       <c r="C378">
-        <v>0.7266439207981238</v>
+        <v>0.7305680265832444</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -43166,10 +43170,10 @@
         </is>
       </c>
       <c r="E378">
-        <v>7.334031196486782</v>
+        <v>7.368056351025147</v>
       </c>
       <c r="F378">
-        <v>10.19531838411105</v>
+        <v>10.24481227960315</v>
       </c>
       <c r="G378" s="2">
         <v>42710</v>
@@ -43202,10 +43206,10 @@
         </is>
       </c>
       <c r="B379">
-        <v>13.3696588740714</v>
+        <v>13.36979264354332</v>
       </c>
       <c r="C379">
-        <v>1.645751056091855</v>
+        <v>1.650688735070082</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -43213,10 +43217,10 @@
         </is>
       </c>
       <c r="E379">
-        <v>10.5036647403496</v>
+        <v>10.496194808978</v>
       </c>
       <c r="F379">
-        <v>17.01765839139748</v>
+        <v>17.03011030039657</v>
       </c>
       <c r="G379" s="2">
         <v>43074</v>
@@ -43249,10 +43253,10 @@
         </is>
       </c>
       <c r="B380">
-        <v>9.210187059826147</v>
+        <v>9.210197329775195</v>
       </c>
       <c r="C380">
-        <v>0.9120913699177536</v>
+        <v>0.9142006228588794</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -43260,10 +43264,10 @@
         </is>
       </c>
       <c r="E380">
-        <v>7.585310395938759</v>
+        <v>7.581916536973164</v>
       </c>
       <c r="F380">
-        <v>11.18313440705161</v>
+        <v>11.18816521386595</v>
       </c>
       <c r="G380" s="2">
         <v>43117</v>
@@ -43296,10 +43300,10 @@
         </is>
       </c>
       <c r="B381">
-        <v>10.69010268070889</v>
+        <v>10.73416665609699</v>
       </c>
       <c r="C381">
-        <v>0.8167612823157694</v>
+        <v>0.8210638812567539</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -43307,10 +43311,10 @@
         </is>
       </c>
       <c r="E381">
-        <v>9.203374570505138</v>
+        <v>9.239731158412818</v>
       </c>
       <c r="F381">
-        <v>12.41699927006524</v>
+        <v>12.47031237439781</v>
       </c>
       <c r="G381" s="2">
         <v>43487</v>
@@ -43343,10 +43347,10 @@
         </is>
       </c>
       <c r="B382">
-        <v>10.87486929587752</v>
+        <v>10.95830995101997</v>
       </c>
       <c r="C382">
-        <v>0.825676347532457</v>
+        <v>0.8320914863272355</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -43354,10 +43358,10 @@
         </is>
       </c>
       <c r="E382">
-        <v>9.371226187813541</v>
+        <v>9.442994761301458</v>
       </c>
       <c r="F382">
-        <v>12.61977673276205</v>
+        <v>12.71678741946829</v>
       </c>
       <c r="G382" s="2">
         <v>44217</v>
@@ -43390,10 +43394,10 @@
         </is>
       </c>
       <c r="B383">
-        <v>10.17350151336568</v>
+        <v>10.24690573318336</v>
       </c>
       <c r="C383">
-        <v>0.8111964565186847</v>
+        <v>0.8174201076414287</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -43401,10 +43405,10 @@
         </is>
       </c>
       <c r="E383">
-        <v>8.701595055322334</v>
+        <v>8.763757742947805</v>
       </c>
       <c r="F383">
-        <v>11.89438630324998</v>
+        <v>11.98105654954222</v>
       </c>
       <c r="G383" s="2">
         <v>45749</v>
@@ -43437,10 +43441,10 @@
         </is>
       </c>
       <c r="B384">
-        <v>10.66217311891511</v>
+        <v>10.83631264186583</v>
       </c>
       <c r="C384">
-        <v>0.832927933503775</v>
+        <v>0.8441741697225904</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -43448,10 +43452,10 @@
         </is>
       </c>
       <c r="E384">
-        <v>9.148501160168085</v>
+        <v>9.30188422764768</v>
       </c>
       <c r="F384">
-        <v>12.42629078003279</v>
+        <v>12.62385865040556</v>
       </c>
       <c r="G384" s="2">
         <v>46049</v>
@@ -43484,10 +43488,10 @@
         </is>
       </c>
       <c r="B385">
-        <v>6.62173006751294</v>
+        <v>6.702011557131824</v>
       </c>
       <c r="C385">
-        <v>0.771890235299056</v>
+        <v>0.7708027129989846</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -43495,10 +43499,10 @@
         </is>
       </c>
       <c r="E385">
-        <v>5.269234552653142</v>
+        <v>5.349435170411367</v>
       </c>
       <c r="F385">
-        <v>8.321381151068159</v>
+        <v>8.396579728710769</v>
       </c>
       <c r="G385" s="2">
         <v>42479</v>
@@ -43531,10 +43535,10 @@
         </is>
       </c>
       <c r="B386">
-        <v>7.567879104377732</v>
+        <v>7.609800370144247</v>
       </c>
       <c r="C386">
-        <v>0.8753364631993946</v>
+        <v>0.8691955460889181</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -43542,10 +43546,10 @@
         </is>
       </c>
       <c r="E386">
-        <v>6.032817879082811</v>
+        <v>6.083430624762966</v>
       </c>
       <c r="F386">
-        <v>9.493539385144587</v>
+        <v>9.519145568575276</v>
       </c>
       <c r="G386" s="2">
         <v>42888</v>
@@ -43578,10 +43582,10 @@
         </is>
       </c>
       <c r="B387">
-        <v>7.408543655976254</v>
+        <v>7.408535659168805</v>
       </c>
       <c r="C387">
-        <v>0.8648820039070519</v>
+        <v>0.8552618532011079</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -43589,10 +43593,10 @@
         </is>
       </c>
       <c r="E387">
-        <v>5.893354775907403</v>
+        <v>5.908364968433842</v>
       </c>
       <c r="F387">
-        <v>9.313289491222779</v>
+        <v>9.289609038441773</v>
       </c>
       <c r="G387" s="2">
         <v>43277</v>
@@ -43625,10 +43629,10 @@
         </is>
       </c>
       <c r="B388">
-        <v>7.500019489740797</v>
+        <v>7.611684570691535</v>
       </c>
       <c r="C388">
-        <v>0.8511541386517361</v>
+        <v>0.8516285116134108</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -43636,10 +43640,10 @@
         </is>
       </c>
       <c r="E388">
-        <v>6.004296739868478</v>
+        <v>6.112862635903282</v>
       </c>
       <c r="F388">
-        <v>9.368339837868167</v>
+        <v>9.478004897969097</v>
       </c>
       <c r="G388" s="2">
         <v>43622</v>
@@ -43672,10 +43676,10 @@
         </is>
       </c>
       <c r="B389">
-        <v>6.393087917436808</v>
+        <v>6.393061150058232</v>
       </c>
       <c r="C389">
-        <v>0.7693666162253245</v>
+        <v>0.7613137911042761</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -43683,10 +43687,10 @@
         </is>
       </c>
       <c r="E389">
-        <v>5.049799076487489</v>
+        <v>5.062255273394135</v>
       </c>
       <c r="F389">
-        <v>8.093702838669318</v>
+        <v>8.073719846407625</v>
       </c>
       <c r="G389" s="2">
         <v>44336</v>
@@ -43719,10 +43723,10 @@
         </is>
       </c>
       <c r="B390">
-        <v>4.922884911437642</v>
+        <v>4.97493498764779</v>
       </c>
       <c r="C390">
-        <v>0.7600107044399834</v>
+        <v>0.759241839159398</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -43730,10 +43734,10 @@
         </is>
       </c>
       <c r="E390">
-        <v>3.637545785447702</v>
+        <v>3.688778957151022</v>
       </c>
       <c r="F390">
-        <v>6.66240297186462</v>
+        <v>6.709531370358234</v>
       </c>
       <c r="G390" s="2">
         <v>45756</v>
@@ -43766,10 +43770,10 @@
         </is>
       </c>
       <c r="B391">
-        <v>4.532291928861699</v>
+        <v>4.532288668220328</v>
       </c>
       <c r="C391">
-        <v>0.5822744696770389</v>
+        <v>0.5771654138946964</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -43777,10 +43781,10 @@
         </is>
       </c>
       <c r="E391">
-        <v>3.523400090906907</v>
+        <v>3.531190059868698</v>
       </c>
       <c r="F391">
-        <v>5.830070272586491</v>
+        <v>5.817200497229029</v>
       </c>
       <c r="G391" s="2">
         <v>45993</v>
@@ -43813,10 +43817,10 @@
         </is>
       </c>
       <c r="B392">
-        <v>7.708198939699812</v>
+        <v>7.791567877100104</v>
       </c>
       <c r="C392">
-        <v>0.8686157952449778</v>
+        <v>0.8659602245385689</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -43824,10 +43828,10 @@
         </is>
       </c>
       <c r="E392">
-        <v>6.180638568764754</v>
+        <v>6.26645221341739</v>
       </c>
       <c r="F392">
-        <v>9.613299699203104</v>
+        <v>9.687862911245441</v>
       </c>
       <c r="G392" s="2">
         <v>46082</v>
@@ -43860,10 +43864,10 @@
         </is>
       </c>
       <c r="B393">
-        <v>3.2105242817957</v>
+        <v>3.315789464945865</v>
       </c>
       <c r="C393">
-        <v>0.7060281542776641</v>
+        <v>0.705863056434012</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -43871,10 +43875,10 @@
         </is>
       </c>
       <c r="E393">
-        <v>2.086352857814489</v>
+        <v>2.184659355140892</v>
       </c>
       <c r="F393">
-        <v>4.940423248825296</v>
+        <v>5.032573957113298</v>
       </c>
       <c r="G393" s="2">
         <v>43067</v>
@@ -43907,10 +43911,10 @@
         </is>
       </c>
       <c r="B394">
-        <v>4.79998893472282</v>
+        <v>4.800000531086908</v>
       </c>
       <c r="C394">
-        <v>1.93875527202479</v>
+        <v>1.88093967233135</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -43918,10 +43922,10 @@
         </is>
       </c>
       <c r="E394">
-        <v>2.174867910423411</v>
+        <v>2.226831805859571</v>
       </c>
       <c r="F394">
-        <v>10.59369797266264</v>
+        <v>10.34654033493159</v>
       </c>
       <c r="G394" s="2">
         <v>43431</v>
@@ -43954,10 +43958,10 @@
         </is>
       </c>
       <c r="B395">
-        <v>9.999979486079235</v>
+        <v>10.24999902907889</v>
       </c>
       <c r="C395">
-        <v>2.973577566218318</v>
+        <v>2.937407603228272</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -43965,10 +43969,10 @@
         </is>
       </c>
       <c r="E395">
-        <v>5.583251721895336</v>
+        <v>5.845068006406024</v>
       </c>
       <c r="F395">
-        <v>17.91063607786948</v>
+        <v>17.97455221752302</v>
       </c>
       <c r="G395" s="2">
         <v>44523</v>
@@ -44001,10 +44005,10 @@
         </is>
       </c>
       <c r="B396">
-        <v>7.050006683266504</v>
+        <v>7.300000740271065</v>
       </c>
       <c r="C396">
-        <v>1.364519151450524</v>
+        <v>1.362221605193042</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -44012,10 +44016,10 @@
         </is>
       </c>
       <c r="E396">
-        <v>4.824370288819969</v>
+        <v>5.063885310757354</v>
       </c>
       <c r="F396">
-        <v>10.30240036700407</v>
+        <v>10.52354220873696</v>
       </c>
       <c r="G396" s="2">
         <v>45960</v>
@@ -44048,10 +44052,10 @@
         </is>
       </c>
       <c r="B397">
-        <v>6.749996432132501</v>
+        <v>6.800000387446299</v>
       </c>
       <c r="C397">
-        <v>1.311936916634182</v>
+        <v>1.278061933215564</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -44059,10 +44063,10 @@
         </is>
       </c>
       <c r="E397">
-        <v>4.611721278354135</v>
+        <v>4.704628926607757</v>
       </c>
       <c r="F397">
-        <v>9.879706314355181</v>
+        <v>9.828619002819185</v>
       </c>
       <c r="G397" s="2">
         <v>46045</v>
@@ -44095,10 +44099,10 @@
         </is>
       </c>
       <c r="B398">
-        <v>0.2500061962037443</v>
+        <v>0.2500062056657638</v>
       </c>
       <c r="C398">
-        <v>0.1443393560674443</v>
+        <v>0.1443393588762009</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -44106,10 +44110,10 @@
         </is>
       </c>
       <c r="E398">
-        <v>0.08063348342775867</v>
+        <v>0.08063348815725045</v>
       </c>
       <c r="F398">
-        <v>0.7751506630153588</v>
+        <v>0.775150676223995</v>
       </c>
       <c r="G398" s="2">
         <v>42837</v>
@@ -44142,10 +44146,10 @@
         </is>
       </c>
       <c r="B399">
-        <v>0.4166659376146522</v>
+        <v>0.4999945479345276</v>
       </c>
       <c r="C399">
-        <v>0.1863388351482951</v>
+        <v>0.2041230327671473</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -44153,10 +44157,10 @@
         </is>
       </c>
       <c r="E399">
-        <v>0.1734278190476007</v>
+        <v>0.2246269180454594</v>
       </c>
       <c r="F399">
-        <v>1.00105337495276</v>
+        <v>1.112932279619575</v>
       </c>
       <c r="G399" s="2">
         <v>43062</v>
@@ -44189,10 +44193,10 @@
         </is>
       </c>
       <c r="B400">
-        <v>0.4166671795613961</v>
+        <v>0.4166640483236801</v>
       </c>
       <c r="C400">
-        <v>0.1863391128477562</v>
+        <v>0.1863384129967167</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -44200,10 +44204,10 @@
         </is>
       </c>
       <c r="E400">
-        <v>0.1734285625387172</v>
+        <v>0.1734266877846302</v>
       </c>
       <c r="F400">
-        <v>1.001055051038036</v>
+        <v>1.001050826624067</v>
       </c>
       <c r="G400" s="2">
         <v>43214</v>
@@ -44236,10 +44240,10 @@
         </is>
       </c>
       <c r="B401">
-        <v>0.2499994850786755</v>
+        <v>0.416662449755704</v>
       </c>
       <c r="C401">
-        <v>0.1443374721118492</v>
+        <v>0.1863380555576488</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -44247,10 +44251,10 @@
         </is>
       </c>
       <c r="E401">
-        <v>0.08063006054742948</v>
+        <v>0.1734257308025408</v>
       </c>
       <c r="F401">
-        <v>0.7751419522107185</v>
+        <v>1.001048669266332</v>
       </c>
       <c r="G401" s="2">
         <v>43433</v>
@@ -44283,10 +44287,10 @@
         </is>
       </c>
       <c r="B402">
-        <v>0.166667166374438</v>
+        <v>0.1666651087470506</v>
       </c>
       <c r="C402">
-        <v>0.1178513068952221</v>
+        <v>0.1178505794780054</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -44294,10 +44298,10 @@
         </is>
       </c>
       <c r="E402">
-        <v>0.04168315377618675</v>
+        <v>0.04168228253941109</v>
       </c>
       <c r="F402">
-        <v>0.6664069733407244</v>
+        <v>0.6664044476787582</v>
       </c>
       <c r="G402" s="2">
         <v>43760</v>
@@ -44330,10 +44334,10 @@
         </is>
       </c>
       <c r="B403">
-        <v>0.5833354354574221</v>
+        <v>0.6666611824824404</v>
       </c>
       <c r="C403">
-        <v>0.220479673216261</v>
+        <v>0.2357012916112486</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -44341,10 +44345,10 @@
         </is>
       </c>
       <c r="E403">
-        <v>0.2780961624654896</v>
+        <v>0.3333947355916473</v>
       </c>
       <c r="F403">
-        <v>1.223606349845001</v>
+        <v>1.333065836928051</v>
       </c>
       <c r="G403" s="2">
         <v>44132</v>
@@ -44377,10 +44381,10 @@
         </is>
       </c>
       <c r="B404">
-        <v>0.7500017594110894</v>
+        <v>0.7499932503292445</v>
       </c>
       <c r="C404">
-        <v>0.2500002932945256</v>
+        <v>0.249998875903895</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -44388,10 +44392,10 @@
         </is>
       </c>
       <c r="E404">
-        <v>0.390237290148407</v>
+        <v>0.3902314156859952</v>
       </c>
       <c r="F404">
-        <v>1.441437436452601</v>
+        <v>1.4414264278303</v>
       </c>
       <c r="G404" s="2">
         <v>45954</v>
@@ -73860,10 +73864,10 @@
         </is>
       </c>
       <c r="B399">
-        <v>5.833353543143454</v>
+        <v>6.000000819505097</v>
       </c>
       <c r="C399">
-        <v>1.472154470526223</v>
+        <v>1.485744244993134</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -73871,10 +73875,10 @@
         </is>
       </c>
       <c r="E399">
-        <v>3.557147492655998</v>
+        <v>3.692949533628961</v>
       </c>
       <c r="F399">
-        <v>9.566095763405288</v>
+        <v>9.748308095259999</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -73912,10 +73916,10 @@
         </is>
       </c>
       <c r="B400">
-        <v>3.87500250184243</v>
+        <v>3.937494687740474</v>
       </c>
       <c r="C400">
-        <v>0.8936233984748413</v>
+        <v>0.8930786357767486</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -73923,10 +73927,10 @@
         </is>
       </c>
       <c r="E400">
-        <v>2.46589401575865</v>
+        <v>2.524385142985673</v>
       </c>
       <c r="F400">
-        <v>6.089330803889163</v>
+        <v>6.141639859933386</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -73964,10 +73968,10 @@
         </is>
       </c>
       <c r="B401">
-        <v>6.600010129167218</v>
+        <v>7.099977669938008</v>
       </c>
       <c r="C401">
-        <v>1.800682935417391</v>
+        <v>1.891832685027754</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -73975,10 +73979,10 @@
         </is>
       </c>
       <c r="E401">
-        <v>3.866437594481288</v>
+        <v>4.211619233504152</v>
       </c>
       <c r="F401">
-        <v>11.26621926273552</v>
+        <v>11.96919287304054</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
@@ -74016,10 +74020,10 @@
         </is>
       </c>
       <c r="B402">
-        <v>6.58333716030362</v>
+        <v>6.916659942866033</v>
       </c>
       <c r="C402">
-        <v>1.640060501790921</v>
+        <v>1.686827348508602</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -74027,10 +74031,10 @@
         </is>
       </c>
       <c r="E402">
-        <v>4.04010118030086</v>
+        <v>4.288509107495185</v>
       </c>
       <c r="F402">
-        <v>10.72753533440146</v>
+        <v>11.1554350395655</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -74068,10 +74072,10 @@
         </is>
       </c>
       <c r="B403">
-        <v>8.333338699408676</v>
+        <v>8.916672186963137</v>
       </c>
       <c r="C403">
-        <v>2.031079783011102</v>
+        <v>2.124612497611873</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -74079,10 +74083,10 @@
         </is>
       </c>
       <c r="E403">
-        <v>5.16840071291345</v>
+        <v>5.589635329491247</v>
       </c>
       <c r="F403">
-        <v>13.43636798624232</v>
+        <v>14.22401251657297</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
@@ -74120,10 +74124,10 @@
         </is>
       </c>
       <c r="B404">
-        <v>7.583320265641435</v>
+        <v>8.250001472664776</v>
       </c>
       <c r="C404">
-        <v>1.863599198634214</v>
+        <v>1.978792913095172</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -74131,10 +74135,10 @@
         </is>
       </c>
       <c r="E404">
-        <v>4.684646401923724</v>
+        <v>5.155730815964307</v>
       </c>
       <c r="F404">
-        <v>12.2755788414838</v>
+        <v>13.20133395797562</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
@@ -74172,10 +74176,10 @@
         </is>
       </c>
       <c r="B405">
-        <v>7.999994734814892</v>
+        <v>8.499998985491588</v>
       </c>
       <c r="C405">
-        <v>2.396408629495268</v>
+        <v>2.490499786555067</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -74183,10 +74187,10 @@
         </is>
       </c>
       <c r="E405">
-        <v>4.447451214803934</v>
+        <v>4.786486224202359</v>
       </c>
       <c r="F405">
-        <v>14.39024570838096</v>
+        <v>15.09457655764968</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
@@ -74224,10 +74228,10 @@
         </is>
       </c>
       <c r="B406">
-        <v>4.105257641679016</v>
+        <v>4.105274212158974</v>
       </c>
       <c r="C406">
-        <v>0.8613513341797308</v>
+        <v>0.849063248110054</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -74235,10 +74239,10 @@
         </is>
       </c>
       <c r="E406">
-        <v>2.721097960068091</v>
+        <v>2.737124198796343</v>
       </c>
       <c r="F406">
-        <v>6.193507382638376</v>
+        <v>6.157293251226507</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
@@ -74276,10 +74280,10 @@
         </is>
       </c>
       <c r="B407">
-        <v>3.041675772406805</v>
+        <v>3.125004142808105</v>
       </c>
       <c r="C407">
-        <v>0.5960494723982518</v>
+        <v>0.6014941122758047</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -74287,10 +74291,10 @@
         </is>
       </c>
       <c r="E407">
-        <v>2.071622941845326</v>
+        <v>2.142955463527774</v>
       </c>
       <c r="F407">
-        <v>4.465963046443854</v>
+        <v>4.557094656783681</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
@@ -74328,10 +74332,10 @@
         </is>
       </c>
       <c r="B408">
-        <v>0.6666682835240696</v>
+        <v>0.8333300333559698</v>
       </c>
       <c r="C408">
-        <v>0.2357025342049645</v>
+        <v>0.2635225964939752</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -74339,10 +74343,10 @@
         </is>
       </c>
       <c r="E408">
-        <v>0.3333995296679963</v>
+        <v>0.4483766204705712</v>
       </c>
       <c r="F408">
-        <v>1.333075066721045</v>
+        <v>1.54878491158671</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
@@ -74380,10 +74384,10 @@
         </is>
       </c>
       <c r="B409">
-        <v>0.1666671700990353</v>
+        <v>0.166663413343412</v>
       </c>
       <c r="C409">
-        <v>0.1178512993204275</v>
+        <v>0.1178499703159813</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -74391,10 +74395,10 @@
         </is>
       </c>
       <c r="E409">
-        <v>0.04168315971172894</v>
+        <v>0.04168156948026405</v>
       </c>
       <c r="F409">
-        <v>0.6664069082316838</v>
+        <v>0.6664022898760825</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
@@ -74432,10 +74436,10 @@
         </is>
       </c>
       <c r="B410">
-        <v>0.08333180902755746</v>
+        <v>0.08333207486285388</v>
       </c>
       <c r="C410">
-        <v>0.08333256456966166</v>
+        <v>0.08333269721078344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -74443,10 +74447,10 @@
         </is>
       </c>
       <c r="E410">
-        <v>0.0117382011949475</v>
+        <v>0.0117382754140704</v>
       </c>
       <c r="F410">
-        <v>0.5915889735127654</v>
+        <v>0.5915890074128259</v>
       </c>
       <c r="G410" t="inlineStr">
         <is>
@@ -74484,10 +74488,10 @@
         </is>
       </c>
       <c r="B411">
-        <v>0.08333334037415366</v>
+        <v>0.08333513463103814</v>
       </c>
       <c r="C411">
-        <v>0.08333333024646888</v>
+        <v>0.08333422709226104</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -74495,10 +74499,10 @@
         </is>
       </c>
       <c r="E411">
-        <v>0.01173862829568892</v>
+        <v>0.01173912880752961</v>
       </c>
       <c r="F411">
-        <v>0.591589191086742</v>
+        <v>0.5915894422692436</v>
       </c>
       <c r="G411" t="inlineStr">
         <is>
@@ -74536,10 +74540,10 @@
         </is>
       </c>
       <c r="B412">
-        <v>0.0833330932079</v>
+        <v>0.333337318386724</v>
       </c>
       <c r="C412">
-        <v>0.08333320666326038</v>
+        <v>0.1666676495136101</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -74547,10 +74551,10 @@
         </is>
       </c>
       <c r="E412">
-        <v>0.01173855935930971</v>
+        <v>0.1251081908649644</v>
       </c>
       <c r="F412">
-        <v>0.59158915596308</v>
+        <v>0.8881414323158341</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
@@ -74588,10 +74592,10 @@
         </is>
       </c>
       <c r="B413">
-        <v>0.1666665711870257</v>
+        <v>0.5833391485061556</v>
       </c>
       <c r="C413">
-        <v>0.1178510875732948</v>
+        <v>0.2204803576109675</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -74599,10 +74603,10 @@
         </is>
       </c>
       <c r="E413">
-        <v>0.04168290613019146</v>
+        <v>0.2780986044290825</v>
       </c>
       <c r="F413">
-        <v>0.6664061729400416</v>
+        <v>1.223611182366297</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
@@ -74640,10 +74644,10 @@
         </is>
       </c>
       <c r="B414">
-        <v>0.2500010591570146</v>
+        <v>0.3333318244730155</v>
       </c>
       <c r="C414">
-        <v>0.1443378627730073</v>
+        <v>0.166666276037689</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -74651,10 +74655,10 @@
         </is>
       </c>
       <c r="E414">
-        <v>0.08063089574940353</v>
+        <v>0.1251051185535245</v>
       </c>
       <c r="F414">
-        <v>0.7751436840522939</v>
+        <v>0.8881339667886752</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
@@ -74692,10 +74696,10 @@
         </is>
       </c>
       <c r="B415">
-        <v>0.4166664995127594</v>
+        <v>0.4166643522243432</v>
       </c>
       <c r="C415">
-        <v>0.186338948989395</v>
+        <v>0.1863384657355833</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -74703,10 +74707,10 @@
         </is>
       </c>
       <c r="E415">
-        <v>0.173428165053573</v>
+        <v>0.1734268821254535</v>
       </c>
       <c r="F415">
-        <v>1.001054077707544</v>
+        <v>1.00105116511837</v>
       </c>
       <c r="G415" t="inlineStr">
         <is>
@@ -74744,10 +74748,10 @@
         </is>
       </c>
       <c r="B416">
-        <v>0.1458333312193889</v>
+        <v>0.1874999531583771</v>
       </c>
       <c r="C416">
-        <v>0.05511981401391951</v>
+        <v>0.06249998698638666</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -74755,10 +74759,10 @@
         </is>
       </c>
       <c r="E416">
-        <v>0.06952370017216954</v>
+        <v>0.09755899190600231</v>
       </c>
       <c r="F416">
-        <v>0.3059008718160451</v>
+        <v>0.3603587096130155</v>
       </c>
       <c r="G416" t="inlineStr">
         <is>
@@ -74796,10 +74800,10 @@
         </is>
       </c>
       <c r="B417">
-        <v>0.7391304271327237</v>
+        <v>0.7391308854805023</v>
       </c>
       <c r="C417">
-        <v>0.1792654465488175</v>
+        <v>0.179265501718282</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -74807,10 +74811,10 @@
         </is>
       </c>
       <c r="E417">
-        <v>0.4594882373791083</v>
+        <v>0.4594885905434212</v>
       </c>
       <c r="F417">
-        <v>1.188961422450206</v>
+        <v>1.188961983201986</v>
       </c>
       <c r="G417" t="inlineStr">
         <is>
@@ -74848,10 +74852,10 @@
         </is>
       </c>
       <c r="B418">
-        <v>0.4166666645797895</v>
+        <v>0.4166664480171317</v>
       </c>
       <c r="C418">
-        <v>0.1317615580426315</v>
+        <v>0.1317615236296038</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -74859,10 +74863,10 @@
         </is>
       </c>
       <c r="E418">
-        <v>0.2241894724726094</v>
+        <v>0.2241893200208225</v>
       </c>
       <c r="F418">
-        <v>0.7743945666015069</v>
+        <v>0.7743942882162642</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
@@ -74900,10 +74904,10 @@
         </is>
       </c>
       <c r="B419">
-        <v>0.2727272642561515</v>
+        <v>0.2727268964920495</v>
       </c>
       <c r="C419">
-        <v>0.1113404319452871</v>
+        <v>0.1113403567809682</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -74911,10 +74915,10 @@
         </is>
       </c>
       <c r="E419">
-        <v>0.1225256469921766</v>
+        <v>0.1225254157523621</v>
       </c>
       <c r="F419">
-        <v>0.6070578894669615</v>
+        <v>0.6070573979566455</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -74952,10 +74956,10 @@
         </is>
       </c>
       <c r="B420">
-        <v>2.666666433514629</v>
+        <v>2.75000021704615</v>
       </c>
       <c r="C420">
-        <v>0.4737696715944829</v>
+        <v>0.4840407864224479</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -74963,10 +74967,10 @@
         </is>
       </c>
       <c r="E420">
-        <v>1.882526627130511</v>
+        <v>1.94763981356842</v>
       </c>
       <c r="F420">
-        <v>3.777428571341336</v>
+        <v>3.882905422793773</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
@@ -75004,10 +75008,10 @@
         </is>
       </c>
       <c r="B421">
-        <v>1.58333360197019</v>
+        <v>1.666667013824293</v>
       </c>
       <c r="C421">
-        <v>0.3643247990531154</v>
+        <v>0.3751969689679469</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -75015,10 +75019,10 @@
         </is>
       </c>
       <c r="E421">
-        <v>1.008581725144601</v>
+        <v>1.072081832683406</v>
       </c>
       <c r="F421">
-        <v>2.485614435229305</v>
+        <v>2.591013904243898</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
@@ -75056,10 +75060,10 @@
         </is>
       </c>
       <c r="B422">
-        <v>2.916666364875001</v>
+        <v>2.916666426045708</v>
       </c>
       <c r="C422">
-        <v>0.4957114452901927</v>
+        <v>0.4988234601439038</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -75067,10 +75071,10 @@
         </is>
       </c>
       <c r="E422">
-        <v>2.090345375271905</v>
+        <v>2.085978596298907</v>
       </c>
       <c r="F422">
-        <v>4.069634991723126</v>
+        <v>4.07815451985743</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
@@ -75108,10 +75112,10 @@
         </is>
       </c>
       <c r="B423">
-        <v>2.333333950417114</v>
+        <v>2.333333663034296</v>
       </c>
       <c r="C423">
-        <v>0.4428950750395124</v>
+        <v>0.4451256290319035</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -75119,10 +75123,10 @@
         </is>
       </c>
       <c r="E423">
-        <v>1.608453561154855</v>
+        <v>1.605442463422597</v>
       </c>
       <c r="F423">
-        <v>3.384895564072157</v>
+        <v>3.39124329092566</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
@@ -75160,10 +75164,10 @@
         </is>
       </c>
       <c r="B424">
-        <v>5.526318898858108</v>
+        <v>5.631579992862449</v>
       </c>
       <c r="C424">
-        <v>0.5853388776363322</v>
+        <v>0.5931219868903032</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -75171,10 +75175,10 @@
         </is>
       </c>
       <c r="E424">
-        <v>4.490327668771329</v>
+        <v>4.581219587773228</v>
       </c>
       <c r="F424">
-        <v>6.801330064234018</v>
+        <v>6.922762074241465</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
@@ -75212,10 +75216,10 @@
         </is>
       </c>
       <c r="B425">
-        <v>4.291668748397404</v>
+        <v>4.291667878423757</v>
       </c>
       <c r="C425">
-        <v>0.4511466986750166</v>
+        <v>0.4519822421296537</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -75223,10 +75227,10 @@
         </is>
       </c>
       <c r="E425">
-        <v>3.492581926135752</v>
+        <v>3.49124861078885</v>
       </c>
       <c r="F425">
-        <v>5.273582992611249</v>
+        <v>5.27559484643307</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
@@ -75264,10 +75268,10 @@
         </is>
       </c>
       <c r="B426">
-        <v>6.583328816523499</v>
+        <v>6.624998771418097</v>
       </c>
       <c r="C426">
-        <v>0.5765927231052831</v>
+        <v>0.5802863782090038</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -75275,10 +75279,10 @@
         </is>
       </c>
       <c r="E426">
-        <v>5.544905020563816</v>
+        <v>5.579929442750418</v>
       </c>
       <c r="F426">
-        <v>7.816223748781507</v>
+        <v>7.865799948118531</v>
       </c>
       <c r="G426" t="inlineStr">
         <is>
@@ -75316,10 +75320,10 @@
         </is>
       </c>
       <c r="B427">
-        <v>6.608699651745802</v>
+        <v>6.956521471453435</v>
       </c>
       <c r="C427">
-        <v>0.5903267648645755</v>
+        <v>0.6101504694991475</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -75327,10 +75331,10 @@
         </is>
       </c>
       <c r="E427">
-        <v>5.547302328496434</v>
+        <v>5.857792454204294</v>
       </c>
       <c r="F427">
-        <v>7.873180241615376</v>
+        <v>8.261335880560189</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
@@ -75368,10 +75372,10 @@
         </is>
       </c>
       <c r="B428">
-        <v>6.791669393126003</v>
+        <v>7.041667221006793</v>
       </c>
       <c r="C428">
-        <v>0.5872640690686417</v>
+        <v>0.6016374599379709</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -75379,10 +75383,10 @@
         </is>
       </c>
       <c r="E428">
-        <v>5.732902969777424</v>
+        <v>5.955924036564094</v>
       </c>
       <c r="F428">
-        <v>8.045971367158057</v>
+        <v>8.325337419851749</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
@@ -75420,10 +75424,10 @@
         </is>
       </c>
       <c r="B429">
-        <v>6.750002088937262</v>
+        <v>7.249997948228454</v>
       </c>
       <c r="C429">
-        <v>1.433288191406224</v>
+        <v>1.499530144933809</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -75431,10 +75435,10 @@
         </is>
       </c>
       <c r="E429">
-        <v>4.452056693191706</v>
+        <v>4.833729397864677</v>
       </c>
       <c r="F429">
-        <v>10.23404043132105</v>
+        <v>10.87410277301342</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
@@ -75472,10 +75476,10 @@
         </is>
       </c>
       <c r="B430">
-        <v>9.869560291482289</v>
+        <v>9.913042303656157</v>
       </c>
       <c r="C430">
-        <v>0.7519948047400089</v>
+        <v>0.7568305841598822</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -75483,10 +75487,10 @@
         </is>
       </c>
       <c r="E430">
-        <v>8.50044990323893</v>
+        <v>8.53532995442907</v>
       </c>
       <c r="F430">
-        <v>11.45918409684274</v>
+        <v>11.51313519673415</v>
       </c>
       <c r="G430" t="inlineStr">
         <is>
@@ -75524,10 +75528,10 @@
         </is>
       </c>
       <c r="B431">
-        <v>6.37500342283135</v>
+        <v>6.416665673709891</v>
       </c>
       <c r="C431">
-        <v>0.5658239654490451</v>
+        <v>0.5694688158430001</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -75535,10 +75539,10 @@
         </is>
       </c>
       <c r="E431">
-        <v>5.357110720523104</v>
+        <v>5.392207999398535</v>
       </c>
       <c r="F431">
-        <v>7.5863036553299</v>
+        <v>7.635758556190607</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -75576,10 +75580,10 @@
         </is>
       </c>
       <c r="B432">
-        <v>7.750000055689174</v>
+        <v>7.749999789195972</v>
       </c>
       <c r="C432">
-        <v>1.149403350937517</v>
+        <v>1.16434802103566</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -75587,10 +75591,10 @@
         </is>
       </c>
       <c r="E432">
-        <v>5.795086358312805</v>
+        <v>5.773224992639309</v>
       </c>
       <c r="F432">
-        <v>10.36438409188245</v>
+        <v>10.40363000040974</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -75628,10 +75632,10 @@
         </is>
       </c>
       <c r="B433">
-        <v>5.818181841198322</v>
+        <v>5.818182768393902</v>
       </c>
       <c r="C433">
-        <v>0.9716591782615353</v>
+        <v>0.9825384913501841</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -75639,10 +75643,10 @@
         </is>
       </c>
       <c r="E433">
-        <v>4.194047024979433</v>
+        <v>4.178705274981477</v>
       </c>
       <c r="F433">
-        <v>8.071259033490662</v>
+        <v>8.100894535230363</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -75680,10 +75684,10 @@
         </is>
       </c>
       <c r="B434">
-        <v>6.666666698647942</v>
+        <v>6.666665394615919</v>
       </c>
       <c r="C434">
-        <v>1.027255254013533</v>
+        <v>1.039634492318625</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -75691,10 +75695,10 @@
         </is>
       </c>
       <c r="E434">
-        <v>4.92888352067382</v>
+        <v>4.910976547068977</v>
       </c>
       <c r="F434">
-        <v>9.017142459228886</v>
+        <v>9.050018271884284</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
@@ -75732,10 +75736,10 @@
         </is>
       </c>
       <c r="B435">
-        <v>5.181818193396725</v>
+        <v>5.272729333972237</v>
       </c>
       <c r="C435">
-        <v>0.894658118744915</v>
+        <v>0.9153119489286586</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -75743,10 +75747,10 @@
         </is>
       </c>
       <c r="E435">
-        <v>3.694191446371693</v>
+        <v>3.752082310172994</v>
       </c>
       <c r="F435">
-        <v>7.268502507034295</v>
+        <v>7.409665442027438</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
@@ -75784,10 +75788,10 @@
         </is>
       </c>
       <c r="B436">
-        <v>0.3749999867649113</v>
+        <v>0.3750006518182728</v>
       </c>
       <c r="C436">
-        <v>0.2165067988721224</v>
+        <v>0.2590374599545601</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -75795,10 +75799,10 @@
         </is>
       </c>
       <c r="E436">
-        <v>0.1209452393190487</v>
+        <v>0.09683926462652141</v>
       </c>
       <c r="F436">
-        <v>1.162716208305814</v>
+        <v>1.452153621844174</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
@@ -75836,10 +75840,10 @@
         </is>
       </c>
       <c r="B437">
-        <v>0.5000000131819258</v>
+        <v>0.6249984796770409</v>
       </c>
       <c r="C437">
-        <v>0.2500007057493491</v>
+        <v>0.3664772369357475</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -75847,10 +75851,10 @@
         </is>
       </c>
       <c r="E437">
-        <v>0.187658419347166</v>
+        <v>0.1980451281669681</v>
       </c>
       <c r="F437">
-        <v>1.332207817009418</v>
+        <v>1.972394389168137</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
@@ -75888,10 +75892,10 @@
         </is>
       </c>
       <c r="B438">
-        <v>6.847150003010496E-08</v>
+        <v>3.998729493980668E-10</v>
       </c>
       <c r="C438">
-        <v>9.251451815246235E-05</v>
+        <v>7.069943339246969E-06</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -75942,10 +75946,10 @@
         </is>
       </c>
       <c r="B439">
-        <v>0.2499999973447039</v>
+        <v>0.5000002884857528</v>
       </c>
       <c r="C439">
-        <v>0.1443377633002312</v>
+        <v>0.2561978988031925</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -75953,10 +75957,10 @@
         </is>
       </c>
       <c r="E439">
-        <v>0.08063022865210809</v>
+        <v>0.1831548455665007</v>
       </c>
       <c r="F439">
-        <v>0.7751435127639054</v>
+        <v>1.364966827454559</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
@@ -75994,10 +75998,10 @@
         </is>
       </c>
       <c r="B440">
-        <v>7.166668949894281</v>
+        <v>7.166708483647556</v>
       </c>
       <c r="C440">
-        <v>2.97545490995247</v>
+        <v>2.975519924372275</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -76005,10 +76009,10 @@
         </is>
       </c>
       <c r="E440">
-        <v>3.176258264556973</v>
+        <v>3.176233568882223</v>
       </c>
       <c r="F440">
-        <v>16.17032985337</v>
+        <v>16.17063398384175</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
@@ -76046,10 +76050,10 @@
         </is>
       </c>
       <c r="B441">
-        <v>6.000001026286184</v>
+        <v>6.000056853513934</v>
       </c>
       <c r="C441">
-        <v>1.317876448518867</v>
+        <v>1.317911306051661</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -76057,10 +76061,10 @@
         </is>
       </c>
       <c r="E441">
-        <v>3.901110741307669</v>
+        <v>3.901118245359604</v>
       </c>
       <c r="F441">
-        <v>9.228144162697594</v>
+        <v>9.228298139443091</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
@@ -76098,10 +76102,10 @@
         </is>
       </c>
       <c r="B442">
-        <v>5.041667229010918</v>
+        <v>5.041714308109698</v>
       </c>
       <c r="C442">
-        <v>1.075944630936614</v>
+        <v>1.075972457167668</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -76109,10 +76113,10 @@
         </is>
       </c>
       <c r="E442">
-        <v>3.318324441090738</v>
+        <v>3.318332492544584</v>
       </c>
       <c r="F442">
-        <v>7.660013027456581</v>
+        <v>7.660137500297987</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -76150,10 +76154,10 @@
         </is>
       </c>
       <c r="B443">
-        <v>10.0833327385998</v>
+        <v>10.08334169272473</v>
       </c>
       <c r="C443">
-        <v>2.90189117969914</v>
+        <v>2.901938030108442</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -76161,10 +76165,10 @@
         </is>
       </c>
       <c r="E443">
-        <v>5.736355516934944</v>
+        <v>5.736311245567516</v>
       </c>
       <c r="F443">
-        <v>17.72442429991592</v>
+        <v>17.72459257171667</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
@@ -76202,10 +76206,10 @@
         </is>
       </c>
       <c r="B444">
-        <v>15.50000033889721</v>
+        <v>15.58335866566931</v>
       </c>
       <c r="C444">
-        <v>4.382293747381443</v>
+        <v>4.405140226520501</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -76213,10 +76217,10 @@
         </is>
       </c>
       <c r="E444">
-        <v>8.905794461112979</v>
+        <v>8.954501757763582</v>
       </c>
       <c r="F444">
-        <v>26.97681959255423</v>
+        <v>27.11943934706884</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
@@ -76254,10 +76258,10 @@
         </is>
       </c>
       <c r="B445">
-        <v>15.16666627119107</v>
+        <v>15.25035684249721</v>
       </c>
       <c r="C445">
-        <v>4.291218728027172</v>
+        <v>4.314198853514867</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -76265,10 +76269,10 @@
         </is>
       </c>
       <c r="E445">
-        <v>8.710704657510368</v>
+        <v>8.75955781117616</v>
       </c>
       <c r="F445">
-        <v>26.40748077520397</v>
+        <v>26.55081327584427</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
@@ -76306,10 +76310,10 @@
         </is>
       </c>
       <c r="B446">
-        <v>1.357145949100642</v>
+        <v>1.428570510554043</v>
       </c>
       <c r="C446">
-        <v>0.6243377018886158</v>
+        <v>0.6450567699517034</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -76317,10 +76321,10 @@
         </is>
       </c>
       <c r="E446">
-        <v>0.5508611320788935</v>
+        <v>0.5895900032739662</v>
       </c>
       <c r="F446">
-        <v>3.343574305577429</v>
+        <v>3.461411645876109</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
@@ -76358,10 +76362,10 @@
         </is>
       </c>
       <c r="B447">
-        <v>1.399999409567985</v>
+        <v>1.466667944421783</v>
       </c>
       <c r="C447">
-        <v>0.6198398351391733</v>
+        <v>0.6377625811176141</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -76369,10 +76373,10 @@
         </is>
       </c>
       <c r="E447">
-        <v>0.5878471142362661</v>
+        <v>0.6254566880485304</v>
       </c>
       <c r="F447">
-        <v>3.334197445771502</v>
+        <v>3.439270696594597</v>
       </c>
       <c r="G447" t="inlineStr">
         <is>
@@ -76410,10 +76414,10 @@
         </is>
       </c>
       <c r="B448">
-        <v>0.9999998850398218</v>
+        <v>1.06249910013649</v>
       </c>
       <c r="C448">
-        <v>0.4490290651431539</v>
+        <v>0.4673497159585276</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -76421,10 +76425,10 @@
         </is>
       </c>
       <c r="E448">
-        <v>0.4147493107212729</v>
+        <v>0.4486627066398312</v>
       </c>
       <c r="F448">
-        <v>2.411094471358131</v>
+        <v>2.516153718782541</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -76462,10 +76466,10 @@
         </is>
       </c>
       <c r="B449">
-        <v>1.937498472289012</v>
+        <v>1.999997491366146</v>
       </c>
       <c r="C449">
-        <v>0.8020989195822872</v>
+        <v>0.8146210287566168</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -76473,10 +76477,10 @@
         </is>
       </c>
       <c r="E449">
-        <v>0.8607065538193635</v>
+        <v>0.9001723681726183</v>
       </c>
       <c r="F449">
-        <v>4.361417156014924</v>
+        <v>4.443582259241081</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
@@ -76514,10 +76518,10 @@
         </is>
       </c>
       <c r="B450">
-        <v>0.1111108400395863</v>
+        <v>0.1666665230583166</v>
       </c>
       <c r="C450">
-        <v>0.08774728340632286</v>
+        <v>0.1121784013721027</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -76525,10 +76529,10 @@
         </is>
       </c>
       <c r="E450">
-        <v>0.02363410625047743</v>
+        <v>0.04455837165605232</v>
       </c>
       <c r="F450">
-        <v>0.5223645287645746</v>
+        <v>0.6234009205445313</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
@@ -76566,10 +76570,10 @@
         </is>
       </c>
       <c r="B451">
-        <v>0.7368423581037838</v>
+        <v>0.7368426016663441</v>
       </c>
       <c r="C451">
-        <v>0.3199867237307444</v>
+        <v>0.3167738622691902</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -76577,10 +76581,10 @@
         </is>
       </c>
       <c r="E451">
-        <v>0.3145758488455025</v>
+        <v>0.3172759438163327</v>
       </c>
       <c r="F451">
-        <v>1.725932434700659</v>
+        <v>1.711245463805874</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
@@ -76618,10 +76622,10 @@
         </is>
       </c>
       <c r="B452">
-        <v>1.260869575599951</v>
+        <v>1.347826086967049</v>
       </c>
       <c r="C452">
-        <v>0.234251500461256</v>
+        <v>0.242076696143823</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -76629,10 +76633,10 @@
         </is>
       </c>
       <c r="E452">
-        <v>0.8760504466521489</v>
+        <v>0.947880430720853</v>
       </c>
       <c r="F452">
-        <v>1.814726643595738</v>
+        <v>1.91652354224401</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
@@ -76670,10 +76674,10 @@
         </is>
       </c>
       <c r="B453">
-        <v>1.285714184040422</v>
+        <v>1.285714285729357</v>
       </c>
       <c r="C453">
-        <v>0.2475651035195406</v>
+        <v>0.2474358138010048</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -76681,10 +76685,10 @@
         </is>
       </c>
       <c r="E453">
-        <v>0.881546090081927</v>
+        <v>0.8817199483872623</v>
       </c>
       <c r="F453">
-        <v>1.875183818113354</v>
+        <v>1.874814364302559</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
@@ -76722,10 +76726,10 @@
         </is>
       </c>
       <c r="B454">
-        <v>1.333333318962954</v>
+        <v>1.333333333346369</v>
       </c>
       <c r="C454">
-        <v>0.4714044789878267</v>
+        <v>0.4714044909268846</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -76733,10 +76737,10 @@
         </is>
       </c>
       <c r="E454">
-        <v>0.6667968871086455</v>
+        <v>0.6667968875838914</v>
       </c>
       <c r="F454">
-        <v>2.666145829152771</v>
+        <v>2.666145884774954</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
@@ -76774,10 +76778,10 @@
         </is>
       </c>
       <c r="B455">
-        <v>0.4166666962822476</v>
+        <v>0.4583333333378959</v>
       </c>
       <c r="C455">
-        <v>0.1319909416999481</v>
+        <v>0.1381926890317851</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -76785,10 +76789,10 @@
         </is>
       </c>
       <c r="E455">
-        <v>0.2239477299066336</v>
+        <v>0.253825085575388</v>
       </c>
       <c r="F455">
-        <v>0.7752306123537988</v>
+        <v>0.8276149852266458</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -77294,10 +77298,10 @@
         </is>
       </c>
       <c r="B465">
-        <v>0.7499965582972477</v>
+        <v>0.7499990733360188</v>
       </c>
       <c r="C465">
-        <v>0.2731631722219118</v>
+        <v>0.2816253198202218</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -77305,10 +77309,10 @@
         </is>
       </c>
       <c r="E465">
-        <v>0.3673121515761691</v>
+        <v>0.3592806182836401</v>
       </c>
       <c r="F465">
-        <v>1.531380965873308</v>
+        <v>1.565624699412015</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
@@ -77346,10 +77350,10 @@
         </is>
       </c>
       <c r="B466">
-        <v>4.846099897089051E-10</v>
+        <v>6.054836589949155E-10</v>
       </c>
       <c r="C466">
-        <v>6.637426998488767E-06</v>
+        <v>7.419161264028796E-06</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -77400,10 +77404,10 @@
         </is>
       </c>
       <c r="B467">
-        <v>1.000000292352731</v>
+        <v>1.142857821588668</v>
       </c>
       <c r="C467">
-        <v>0.4240165269585418</v>
+        <v>0.4797818150102137</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -77411,10 +77415,10 @@
         </is>
       </c>
       <c r="E467">
-        <v>0.4355888058986978</v>
+        <v>0.5019382283527943</v>
       </c>
       <c r="F467">
-        <v>2.29574445248281</v>
+        <v>2.60216083690754</v>
       </c>
       <c r="G467" t="inlineStr">
         <is>
@@ -77452,10 +77456,10 @@
         </is>
       </c>
       <c r="B468">
-        <v>0.3333360449172613</v>
+        <v>0.3333348334875795</v>
       </c>
       <c r="C468">
-        <v>0.2456495546435817</v>
+        <v>0.2493953647771849</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -77463,10 +77467,10 @@
         </is>
       </c>
       <c r="E468">
-        <v>0.0786313154084809</v>
+        <v>0.07691772096735132</v>
       </c>
       <c r="F468">
-        <v>1.413087371918723</v>
+        <v>1.444558026665341</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
@@ -77504,10 +77508,10 @@
         </is>
       </c>
       <c r="B469">
-        <v>1.666671268232445</v>
+        <v>1.666668967798939</v>
       </c>
       <c r="C469">
-        <v>0.630451567547282</v>
+        <v>0.6662077811804874</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -77515,10 +77519,10 @@
         </is>
       </c>
       <c r="E469">
-        <v>0.7940832390261322</v>
+        <v>0.7613836809088823</v>
       </c>
       <c r="F469">
-        <v>3.498113270541067</v>
+        <v>3.648338568155374</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
@@ -77556,10 +77560,10 @@
         </is>
       </c>
       <c r="B470">
-        <v>1.166665806834365</v>
+        <v>1.166666289509459</v>
       </c>
       <c r="C470">
-        <v>0.5030825903256522</v>
+        <v>0.5251768738487395</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -77567,10 +77571,10 @@
         </is>
       </c>
       <c r="E470">
-        <v>0.5010677780862072</v>
+        <v>0.4828105857174456</v>
       </c>
       <c r="F470">
-        <v>2.71641714826513</v>
+        <v>2.819139164182141</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
@@ -77608,10 +77612,10 @@
         </is>
       </c>
       <c r="B471">
-        <v>0.6666656683358709</v>
+        <v>0.6666654497493858</v>
       </c>
       <c r="C471">
-        <v>0.5104139367251309</v>
+        <v>0.5247463956561844</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -77619,10 +77623,10 @@
         </is>
       </c>
       <c r="E471">
-        <v>0.1486652339894916</v>
+        <v>0.1425309935536282</v>
       </c>
       <c r="F471">
-        <v>2.989556478074281</v>
+        <v>3.118218787426934</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
@@ -77660,10 +77664,10 @@
         </is>
       </c>
       <c r="B472">
-        <v>0.16666422129537</v>
+        <v>0.1666655152666925</v>
       </c>
       <c r="C472">
-        <v>0.1702181250832135</v>
+        <v>0.1715753111899066</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -77671,10 +77675,10 @@
         </is>
       </c>
       <c r="E472">
-        <v>0.02251593766447708</v>
+        <v>0.0221599449755625</v>
       </c>
       <c r="F472">
-        <v>1.233657823800747</v>
+        <v>1.253495620577777</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
@@ -77712,10 +77716,10 @@
         </is>
       </c>
       <c r="B473">
-        <v>7.333333083719854</v>
+        <v>7.499999925586994</v>
       </c>
       <c r="C473">
-        <v>1.147489998505174</v>
+        <v>1.14398781297197</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -77723,10 +77727,10 @@
         </is>
       </c>
       <c r="E473">
-        <v>5.396458873769295</v>
+        <v>5.561936576239034</v>
       </c>
       <c r="F473">
-        <v>9.965381998587842</v>
+        <v>10.11338373114657</v>
       </c>
       <c r="G473" t="inlineStr">
         <is>
@@ -77977,10 +77981,10 @@
         </is>
       </c>
       <c r="B478">
-        <v>0.7272727209324156</v>
+        <v>0.7272727141114353</v>
       </c>
       <c r="C478">
-        <v>0.2571297168204916</v>
+        <v>0.2571297149529692</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -77988,10 +77992,10 @@
         </is>
       </c>
       <c r="E478">
-        <v>0.3637073932477403</v>
+        <v>0.3637073893033126</v>
       </c>
       <c r="F478">
-        <v>1.454261366230079</v>
+        <v>1.454261354723034</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -78029,10 +78033,10 @@
         </is>
       </c>
       <c r="B479">
-        <v>6.916666554034431</v>
+        <v>7.083333392101308</v>
       </c>
       <c r="C479">
-        <v>0.7592027500258481</v>
+        <v>0.7682953133303558</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -78040,10 +78044,10 @@
         </is>
       </c>
       <c r="E479">
-        <v>5.577830801271071</v>
+        <v>5.726798740681464</v>
       </c>
       <c r="F479">
-        <v>8.576860418354162</v>
+        <v>8.761196999510236</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
@@ -78081,10 +78085,10 @@
         </is>
       </c>
       <c r="B480">
-        <v>5.74999992353852</v>
+        <v>6.249999938620112</v>
       </c>
       <c r="C480">
-        <v>1.198957800792891</v>
+        <v>1.249999893608732</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -78092,10 +78096,10 @@
         </is>
       </c>
       <c r="E480">
-        <v>3.821026567826744</v>
+        <v>4.223181215274619</v>
       </c>
       <c r="F480">
-        <v>8.652779176957596</v>
+        <v>9.249543706878633</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
@@ -78133,10 +78137,10 @@
         </is>
       </c>
       <c r="B481">
-        <v>9.499999862201479</v>
+        <v>9.750000243968081</v>
       </c>
       <c r="C481">
-        <v>1.541103420282436</v>
+        <v>1.56124939665557</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -78144,10 +78148,10 @@
         </is>
       </c>
       <c r="E481">
-        <v>6.912584929595971</v>
+        <v>7.123662036786921</v>
       </c>
       <c r="F481">
-        <v>13.05589707772358</v>
+        <v>13.34461183959464</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -78185,10 +78189,10 @@
         </is>
       </c>
       <c r="B482">
-        <v>6.249999915993759</v>
+        <v>6.749999890772609</v>
       </c>
       <c r="C482">
-        <v>1.249999918992642</v>
+        <v>1.299037991306498</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -78196,10 +78200,10 @@
         </is>
       </c>
       <c r="E482">
-        <v>4.223181160375107</v>
+        <v>4.629029667665272</v>
       </c>
       <c r="F482">
-        <v>9.249543760147962</v>
+        <v>9.842775224296727</v>
       </c>
       <c r="G482" t="inlineStr">
         <is>
@@ -78237,10 +78241,10 @@
         </is>
       </c>
       <c r="B483">
-        <v>7.249999906572736</v>
+        <v>7.250000386528751</v>
       </c>
       <c r="C483">
-        <v>1.346291120347752</v>
+        <v>1.346291130371531</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -78248,10 +78252,10 @@
         </is>
       </c>
       <c r="E483">
-        <v>5.038181978118046</v>
+        <v>5.038182419388239</v>
       </c>
       <c r="F483">
-        <v>10.43283050782909</v>
+        <v>10.43283097539161</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
@@ -78289,10 +78293,10 @@
         </is>
       </c>
       <c r="B484">
-        <v>3.499999953775438</v>
+        <v>3.499999808285787</v>
       </c>
       <c r="C484">
-        <v>0.9354142757902669</v>
+        <v>0.9354142447631232</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -78300,10 +78304,10 @@
         </is>
       </c>
       <c r="E484">
-        <v>2.072883388758375</v>
+        <v>2.072883293471891</v>
       </c>
       <c r="F484">
-        <v>5.909642454014564</v>
+        <v>5.909642234359904</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
@@ -78341,10 +78345,10 @@
         </is>
       </c>
       <c r="B485">
-        <v>4.333333261161916</v>
+        <v>4.333333083772111</v>
       </c>
       <c r="C485">
-        <v>0.8498365225787105</v>
+        <v>0.8498364921520839</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -78352,10 +78356,10 @@
         </is>
       </c>
       <c r="E485">
-        <v>2.950446493366765</v>
+        <v>2.950446366765439</v>
       </c>
       <c r="F485">
-        <v>6.364384914116771</v>
+        <v>6.364384666141176</v>
       </c>
       <c r="G485" t="inlineStr">
         <is>
@@ -78393,10 +78397,10 @@
         </is>
       </c>
       <c r="B486">
-        <v>6.666638890466644</v>
+        <v>6.666697567761439</v>
       </c>
       <c r="C486">
-        <v>0.7780519411602973</v>
+        <v>0.791109156828927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -78404,10 +78408,10 @@
         </is>
       </c>
       <c r="E486">
-        <v>5.303525552438643</v>
+        <v>5.283262897197562</v>
       </c>
       <c r="F486">
-        <v>8.380099927197721</v>
+        <v>8.41238782260324</v>
       </c>
       <c r="G486" t="inlineStr">
         <is>
@@ -78445,10 +78449,10 @@
         </is>
       </c>
       <c r="B487">
-        <v>5.08330211057131</v>
+        <v>5.083312340848775</v>
       </c>
       <c r="C487">
-        <v>0.6727325520396905</v>
+        <v>0.6815266344954757</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -78456,10 +78460,10 @@
         </is>
       </c>
       <c r="E487">
-        <v>3.9218999546399</v>
+        <v>3.908634319178503</v>
       </c>
       <c r="F487">
-        <v>6.588633225273413</v>
+        <v>6.611021201915964</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
@@ -78497,10 +78501,10 @@
         </is>
       </c>
       <c r="B488">
-        <v>5.199983415845836</v>
+        <v>5.20001082391588</v>
       </c>
       <c r="C488">
-        <v>0.7458986993704458</v>
+        <v>0.7558584914727857</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -78508,10 +78512,10 @@
         </is>
       </c>
       <c r="E488">
-        <v>3.925576710209738</v>
+        <v>3.910894135113889</v>
       </c>
       <c r="F488">
-        <v>6.888115943511147</v>
+        <v>6.914048714861179</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
@@ -78549,10 +78553,10 @@
         </is>
       </c>
       <c r="B489">
-        <v>5.363625001840747</v>
+        <v>5.454521619614615</v>
       </c>
       <c r="C489">
-        <v>0.7230327356274593</v>
+        <v>0.739729346660207</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -78560,10 +78564,10 @@
         </is>
       </c>
       <c r="E489">
-        <v>4.118261176779038</v>
+        <v>4.181371198180505</v>
       </c>
       <c r="F489">
-        <v>6.985587345111382</v>
+        <v>7.115322866285953</v>
       </c>
       <c r="G489" t="inlineStr">
         <is>
@@ -78601,10 +78605,10 @@
         </is>
       </c>
       <c r="B490">
-        <v>6.41670371920486</v>
+        <v>6.416675731662275</v>
       </c>
       <c r="C490">
-        <v>0.7621498829463683</v>
+        <v>0.7744963511464702</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -78612,10 +78616,10 @@
         </is>
       </c>
       <c r="E490">
-        <v>5.084049158140585</v>
+        <v>5.064885013113623</v>
       </c>
       <c r="F490">
-        <v>8.09867987883821</v>
+        <v>8.1292521624281</v>
       </c>
       <c r="G490" t="inlineStr">
         <is>
@@ -78653,10 +78657,10 @@
         </is>
       </c>
       <c r="B491">
-        <v>7.666705911142001</v>
+        <v>7.750020227332468</v>
       </c>
       <c r="C491">
-        <v>0.8395057040411925</v>
+        <v>0.8607161708992345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -78664,10 +78668,10 @@
         </is>
       </c>
       <c r="E491">
-        <v>6.185888380123298</v>
+        <v>6.234024586171452</v>
       </c>
       <c r="F491">
-        <v>9.502011015395677</v>
+        <v>9.63467703629145</v>
       </c>
       <c r="G491" t="inlineStr">
         <is>
@@ -78705,10 +78709,10 @@
         </is>
       </c>
       <c r="B492">
-        <v>6.083340747299261</v>
+        <v>6.250014913199734</v>
       </c>
       <c r="C492">
-        <v>0.7405549611768161</v>
+        <v>0.763293762391971</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -78716,10 +78720,10 @@
         </is>
       </c>
       <c r="E492">
-        <v>4.792048412248569</v>
+        <v>4.919563935501562</v>
       </c>
       <c r="F492">
-        <v>7.722591982410034</v>
+        <v>7.940274164002005</v>
       </c>
       <c r="G492" t="inlineStr">
         <is>
@@ -78757,10 +78761,10 @@
         </is>
       </c>
       <c r="B493">
-        <v>4.500018924689831</v>
+        <v>4.499938372096083</v>
       </c>
       <c r="C493">
-        <v>0.6306326422788676</v>
+        <v>0.6379823679180264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -78768,10 +78772,10 @@
         </is>
       </c>
       <c r="E493">
-        <v>3.419219312236546</v>
+        <v>3.408213444454389</v>
       </c>
       <c r="F493">
-        <v>5.922454359711949</v>
+        <v>5.941366549566093</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
@@ -78809,10 +78813,10 @@
         </is>
       </c>
       <c r="B494">
-        <v>6.499964469706621</v>
+        <v>6.499970567956194</v>
       </c>
       <c r="C494">
-        <v>0.7674735529006805</v>
+        <v>0.7800558304901251</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -78820,10 +78824,10 @@
         </is>
       </c>
       <c r="E494">
-        <v>5.157112881091956</v>
+        <v>5.137589861507484</v>
       </c>
       <c r="F494">
-        <v>8.192478831004886</v>
+        <v>8.223625965327599</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
@@ -78861,10 +78865,10 @@
         </is>
       </c>
       <c r="B495">
-        <v>7.333318297850305</v>
+        <v>7.333299331027684</v>
       </c>
       <c r="C495">
-        <v>0.8193791949170874</v>
+        <v>0.8343641636362314</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -78872,10 +78876,10 @@
         </is>
       </c>
       <c r="E495">
-        <v>5.891048394124995</v>
+        <v>5.867483321392623</v>
       </c>
       <c r="F495">
-        <v>9.128690457069951</v>
+        <v>9.165305827522534</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -78913,10 +78917,10 @@
         </is>
       </c>
       <c r="B496">
-        <v>6.583322567864055</v>
+        <v>6.666653271186702</v>
       </c>
       <c r="C496">
-        <v>0.7727772366660758</v>
+        <v>0.7911059381701678</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -78924,10 +78928,10 @@
         </is>
       </c>
       <c r="E496">
-        <v>5.230312386837149</v>
+        <v>5.283224627546272</v>
       </c>
       <c r="F496">
-        <v>8.286337952130738</v>
+        <v>8.412336966801643</v>
       </c>
       <c r="G496" t="inlineStr">
         <is>
@@ -78965,10 +78969,10 @@
         </is>
       </c>
       <c r="B497">
-        <v>9.833393292092106</v>
+        <v>9.91666792732978</v>
       </c>
       <c r="C497">
-        <v>0.9632362965000119</v>
+        <v>0.9909222355287129</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -78976,10 +78980,10 @@
         </is>
       </c>
       <c r="E497">
-        <v>8.11565208304641</v>
+        <v>8.152851381403432</v>
       </c>
       <c r="F497">
-        <v>11.91470785680415</v>
+        <v>12.06207474911714</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
@@ -79017,10 +79021,10 @@
         </is>
       </c>
       <c r="B498">
-        <v>9.909159245934509</v>
+        <v>10.09087912448915</v>
       </c>
       <c r="C498">
-        <v>1.010390327125628</v>
+        <v>1.045487346687896</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -79028,10 +79032,10 @@
         </is>
       </c>
       <c r="E498">
-        <v>8.114164219325886</v>
+        <v>8.23641892595605</v>
       </c>
       <c r="F498">
-        <v>12.10123856347672</v>
+        <v>12.36287789881104</v>
       </c>
       <c r="G498" t="inlineStr">
         <is>
@@ -79069,10 +79073,10 @@
         </is>
       </c>
       <c r="B499">
-        <v>6.333329831570782</v>
+        <v>6.416640388202651</v>
       </c>
       <c r="C499">
-        <v>0.7567912011051018</v>
+        <v>0.7744937550291923</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -79080,10 +79084,10 @@
         </is>
       </c>
       <c r="E499">
-        <v>5.010939139476781</v>
+        <v>5.064854532031047</v>
       </c>
       <c r="F499">
-        <v>8.00470044416716</v>
+        <v>8.129211532360168</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
@@ -79121,10 +79125,10 @@
         </is>
       </c>
       <c r="B500">
-        <v>10.83329706492363</v>
+        <v>10.83331167759836</v>
       </c>
       <c r="C500">
-        <v>1.164698803975384</v>
+        <v>1.167745562319539</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -79132,10 +79136,10 @@
         </is>
       </c>
       <c r="E500">
-        <v>8.774999638003253</v>
+        <v>8.770178339264287</v>
       </c>
       <c r="F500">
-        <v>13.37439659696536</v>
+        <v>13.38178510903966</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
@@ -79173,10 +79177,10 @@
         </is>
       </c>
       <c r="B501">
-        <v>7.833340439547683</v>
+        <v>7.83332587836929</v>
       </c>
       <c r="C501">
-        <v>0.9434083860464743</v>
+        <v>0.9453733498841275</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -79184,10 +79188,10 @@
         </is>
       </c>
       <c r="E501">
-        <v>6.186322270280541</v>
+        <v>6.183267302531961</v>
       </c>
       <c r="F501">
-        <v>9.9188531991998</v>
+        <v>9.923716914454522</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
@@ -79225,10 +79229,10 @@
         </is>
       </c>
       <c r="B502">
-        <v>12.99994347108062</v>
+        <v>13.00000817424844</v>
       </c>
       <c r="C502">
-        <v>2.282580500315195</v>
+        <v>2.289302482446259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -79236,10 +79240,10 @@
         </is>
       </c>
       <c r="E502">
-        <v>9.214763537053308</v>
+        <v>9.205491161008318</v>
       </c>
       <c r="F502">
-        <v>18.33997471250726</v>
+        <v>18.35863068842652</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
@@ -79277,10 +79281,10 @@
         </is>
       </c>
       <c r="B503">
-        <v>7.625005585191435</v>
+        <v>7.625018266764081</v>
       </c>
       <c r="C503">
-        <v>1.135918107493531</v>
+        <v>1.138240647070256</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -79288,10 +79292,10 @@
         </is>
       </c>
       <c r="E503">
-        <v>5.694221084481892</v>
+        <v>5.69083490860904</v>
       </c>
       <c r="F503">
-        <v>10.210476430683</v>
+        <v>10.2165858792584</v>
       </c>
       <c r="G503" t="inlineStr">
         <is>
@@ -79329,10 +79333,10 @@
         </is>
       </c>
       <c r="B504">
-        <v>10.08338831816771</v>
+        <v>10.16668768919187</v>
       </c>
       <c r="C504">
-        <v>1.110580628733624</v>
+        <v>1.11942281314111</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -79340,10 +79344,10 @@
         </is>
       </c>
       <c r="E504">
-        <v>8.125600608682566</v>
+        <v>8.19325157774999</v>
       </c>
       <c r="F504">
-        <v>12.51288672326783</v>
+        <v>12.61544791939007</v>
       </c>
       <c r="G504" t="inlineStr">
         <is>
@@ -79381,10 +79385,10 @@
         </is>
       </c>
       <c r="B505">
-        <v>10.8332653109702</v>
+        <v>10.91672243078845</v>
       </c>
       <c r="C505">
-        <v>1.164695955115511</v>
+        <v>1.173758024251443</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -79392,10 +79396,10 @@
         </is>
       </c>
       <c r="E505">
-        <v>8.774973020171961</v>
+        <v>8.842431409305249</v>
       </c>
       <c r="F505">
-        <v>13.37435876191108</v>
+        <v>13.47760848961374</v>
       </c>
       <c r="G505" t="inlineStr">
         <is>
@@ -79433,10 +79437,10 @@
         </is>
       </c>
       <c r="B506">
-        <v>8.250023001298693</v>
+        <v>8.249979602287066</v>
       </c>
       <c r="C506">
-        <v>0.9750149012943412</v>
+        <v>0.9771211797468708</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -79444,10 +79448,10 @@
         </is>
       </c>
       <c r="E506">
-        <v>6.544211947233303</v>
+        <v>6.540895711644874</v>
       </c>
       <c r="F506">
-        <v>10.40046992223906</v>
+        <v>10.40563348487278</v>
       </c>
       <c r="G506" t="inlineStr">
         <is>
@@ -79485,10 +79489,10 @@
         </is>
       </c>
       <c r="B507">
-        <v>10.2500105789344</v>
+        <v>10.41672222854324</v>
       </c>
       <c r="C507">
-        <v>1.122662819157061</v>
+        <v>1.13760921772483</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -79496,10 +79500,10 @@
         </is>
       </c>
       <c r="E507">
-        <v>8.269779675784118</v>
+        <v>8.409524613213247</v>
       </c>
       <c r="F507">
-        <v>12.70441547262931</v>
+        <v>12.90300070186327</v>
       </c>
       <c r="G507" t="inlineStr">
         <is>
@@ -79537,10 +79541,10 @@
         </is>
       </c>
       <c r="B508">
-        <v>15.09991573035154</v>
+        <v>15.09993867126371</v>
       </c>
       <c r="C508">
-        <v>1.602447998045445</v>
+        <v>1.607609126083832</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -79548,10 +79552,10 @@
         </is>
       </c>
       <c r="E508">
-        <v>12.26429201093488</v>
+        <v>12.25610126334349</v>
       </c>
       <c r="F508">
-        <v>18.59116326164003</v>
+        <v>18.60364425658508</v>
       </c>
       <c r="G508" t="inlineStr">
         <is>
@@ -79589,10 +79593,10 @@
         </is>
       </c>
       <c r="B509">
-        <v>9.545453011295802</v>
+        <v>9.636309704697798</v>
       </c>
       <c r="C509">
-        <v>1.118961251821666</v>
+        <v>1.128633602909912</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -79600,10 +79604,10 @@
         </is>
       </c>
       <c r="E509">
-        <v>7.586035006676825</v>
+        <v>7.65976528958821</v>
       </c>
       <c r="F509">
-        <v>12.01097452235073</v>
+        <v>12.12288643505486</v>
       </c>
       <c r="G509" t="inlineStr">
         <is>
@@ -79641,10 +79645,10 @@
         </is>
       </c>
       <c r="B510">
-        <v>13.74988889810748</v>
+        <v>13.7500956103575</v>
       </c>
       <c r="C510">
-        <v>2.372832773080767</v>
+        <v>2.380087430874737</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -79652,10 +79656,10 @@
         </is>
       </c>
       <c r="E510">
-        <v>9.804070925169775</v>
+        <v>9.794134891993112</v>
       </c>
       <c r="F510">
-        <v>19.28376958442143</v>
+        <v>19.30391314587027</v>
       </c>
       <c r="G510" t="inlineStr">
         <is>
@@ -79693,10 +79697,10 @@
         </is>
       </c>
       <c r="B511">
-        <v>11.12491587438743</v>
+        <v>11.12492218191072</v>
       </c>
       <c r="C511">
-        <v>1.452022901783089</v>
+        <v>1.455887637646276</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -79704,10 +79708,10 @@
         </is>
       </c>
       <c r="E511">
-        <v>8.613863704070697</v>
+        <v>8.608006817075792</v>
       </c>
       <c r="F511">
-        <v>14.3679720812984</v>
+        <v>14.37776435167981</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
@@ -79745,10 +79749,10 @@
         </is>
       </c>
       <c r="B512">
-        <v>11.33332285916221</v>
+        <v>11.33332087336137</v>
       </c>
       <c r="C512">
-        <v>1.20043607890838</v>
+        <v>1.203669613607139</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -79756,10 +79760,10 @@
         </is>
       </c>
       <c r="E512">
-        <v>9.208676218880367</v>
+        <v>9.203526204223564</v>
       </c>
       <c r="F512">
-        <v>13.94817278586277</v>
+        <v>13.95597287044445</v>
       </c>
       <c r="G512" t="inlineStr">
         <is>
@@ -79797,10 +79801,10 @@
         </is>
       </c>
       <c r="B513">
-        <v>10.91663305639364</v>
+        <v>11.00005589992365</v>
       </c>
       <c r="C513">
-        <v>1.170673284115594</v>
+        <v>1.179756049627445</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -79808,10 +79812,10 @@
         </is>
       </c>
       <c r="E513">
-        <v>8.847242289825758</v>
+        <v>8.914634102511807</v>
       </c>
       <c r="F513">
-        <v>13.47005918725589</v>
+        <v>13.57332543433852</v>
       </c>
       <c r="G513" t="inlineStr">
         <is>
@@ -79849,10 +79853,10 @@
         </is>
       </c>
       <c r="B514">
-        <v>12.54543569468364</v>
+        <v>12.72719232852868</v>
       </c>
       <c r="C514">
-        <v>1.343250161250176</v>
+        <v>1.360481724859678</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -79860,10 +79864,10 @@
         </is>
       </c>
       <c r="E514">
-        <v>10.17060754463571</v>
+        <v>10.32150077584478</v>
       </c>
       <c r="F514">
-        <v>15.47478418361091</v>
+        <v>15.69359224837164</v>
       </c>
       <c r="G514" t="inlineStr">
         <is>
@@ -79901,10 +79905,10 @@
         </is>
       </c>
       <c r="B515">
-        <v>11.0909091012406</v>
+        <v>11.27280435207332</v>
       </c>
       <c r="C515">
-        <v>1.235753335861124</v>
+        <v>1.252666708645054</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -79912,10 +79916,10 @@
         </is>
       </c>
       <c r="E515">
-        <v>8.915094360760405</v>
+        <v>9.066590183663752</v>
       </c>
       <c r="F515">
-        <v>13.79775240892566</v>
+        <v>14.01586653702401</v>
       </c>
       <c r="G515" t="inlineStr">
         <is>
@@ -79953,10 +79957,10 @@
         </is>
       </c>
       <c r="B516">
-        <v>6.8333310905287</v>
+        <v>7.00002025693452</v>
       </c>
       <c r="C516">
-        <v>1.118264585936246</v>
+        <v>1.126846192093256</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -79964,10 +79968,10 @@
         </is>
       </c>
       <c r="E516">
-        <v>4.958320353213246</v>
+        <v>5.105931074723226</v>
       </c>
       <c r="F516">
-        <v>9.417385418133742</v>
+        <v>9.596738162030467</v>
       </c>
       <c r="G516" t="inlineStr">
         <is>
@@ -80005,10 +80009,10 @@
         </is>
       </c>
       <c r="B517">
-        <v>7.500016547562712</v>
+        <v>7.583334765631118</v>
       </c>
       <c r="C517">
-        <v>1.202270168007266</v>
+        <v>1.198982994096259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -80016,10 +80020,10 @@
         </is>
       </c>
       <c r="E517">
-        <v>5.477881413794838</v>
+        <v>5.562612150679229</v>
       </c>
       <c r="F517">
-        <v>10.26861371479504</v>
+        <v>10.33812256002921</v>
       </c>
       <c r="G517" t="inlineStr">
         <is>
@@ -80057,10 +80061,10 @@
         </is>
       </c>
       <c r="B518">
-        <v>6.272719065050252</v>
+        <v>6.272722694520949</v>
       </c>
       <c r="C518">
-        <v>1.093765923339562</v>
+        <v>1.082391094172971</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -80068,10 +80072,10 @@
         </is>
       </c>
       <c r="E518">
-        <v>4.456900343943863</v>
+        <v>4.472772533337394</v>
       </c>
       <c r="F518">
-        <v>8.828333916532486</v>
+        <v>8.797015656192793</v>
       </c>
       <c r="G518" t="inlineStr">
         <is>
@@ -80109,10 +80113,10 @@
         </is>
       </c>
       <c r="B519">
-        <v>6.75004444647208</v>
+        <v>6.750007007970432</v>
       </c>
       <c r="C519">
-        <v>1.107735846212833</v>
+        <v>1.09580471414943</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -80120,10 +80124,10 @@
         </is>
       </c>
       <c r="E519">
-        <v>4.893478743141264</v>
+        <v>4.910425016892749</v>
       </c>
       <c r="F519">
-        <v>9.310983539718066</v>
+        <v>9.278747654410031</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
@@ -80161,10 +80165,10 @@
         </is>
       </c>
       <c r="B520">
-        <v>6.916701984623605</v>
+        <v>6.916663827625995</v>
       </c>
       <c r="C520">
-        <v>1.128799106050062</v>
+        <v>1.116504648708283</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -80172,10 +80176,10 @@
         </is>
       </c>
       <c r="E520">
-        <v>5.023238416187714</v>
+        <v>5.040732496031366</v>
       </c>
       <c r="F520">
-        <v>9.523889248403206</v>
+        <v>9.490731464535189</v>
       </c>
       <c r="G520" t="inlineStr">
         <is>
@@ -80213,10 +80217,10 @@
         </is>
       </c>
       <c r="B521">
-        <v>5.875028150008588</v>
+        <v>6.000017809876043</v>
       </c>
       <c r="C521">
-        <v>1.220468046842957</v>
+        <v>1.227393730837289</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -80224,10 +80228,10 @@
         </is>
       </c>
       <c r="E521">
-        <v>3.91005472429937</v>
+        <v>4.018153129073941</v>
       </c>
       <c r="F521">
-        <v>8.827486620299961</v>
+        <v>8.959393174527083</v>
       </c>
       <c r="G521" t="inlineStr">
         <is>
@@ -80265,10 +80269,10 @@
         </is>
       </c>
       <c r="B522">
-        <v>4.833289271694972</v>
+        <v>4.8333359373676</v>
       </c>
       <c r="C522">
-        <v>0.8622664467399629</v>
+        <v>0.8544264218076553</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -80276,10 +80280,10 @@
         </is>
       </c>
       <c r="E522">
-        <v>3.407117313889566</v>
+        <v>3.418011015222534</v>
       </c>
       <c r="F522">
-        <v>6.856436991074179</v>
+        <v>6.834716500153871</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>
@@ -80317,10 +80321,10 @@
         </is>
       </c>
       <c r="B523">
-        <v>7.666662780034629</v>
+        <v>7.750003066088806</v>
       </c>
       <c r="C523">
-        <v>1.223193960503604</v>
+        <v>1.219528835836174</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -80328,10 +80332,10 @@
         </is>
       </c>
       <c r="E523">
-        <v>5.607891559653208</v>
+        <v>5.693221472436303</v>
       </c>
       <c r="F523">
-        <v>10.48125085114932</v>
+        <v>10.54983506529271</v>
       </c>
       <c r="G523" t="inlineStr">
         <is>
@@ -80369,10 +80373,10 @@
         </is>
       </c>
       <c r="B524">
-        <v>6.4166814846392</v>
+        <v>6.416689847066067</v>
       </c>
       <c r="C524">
-        <v>1.065492556995268</v>
+        <v>1.054292099265705</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -80380,10 +80384,10 @@
         </is>
       </c>
       <c r="E524">
-        <v>4.634129024529401</v>
+        <v>4.650018283413514</v>
       </c>
       <c r="F524">
-        <v>8.884906108002195</v>
+        <v>8.854569183159329</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
@@ -80421,10 +80425,10 @@
         </is>
       </c>
       <c r="B525">
-        <v>7.63635570338696</v>
+        <v>7.636358338801108</v>
       </c>
       <c r="C525">
-        <v>1.27361163737032</v>
+        <v>1.259126725815029</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -80432,10 +80436,10 @@
         </is>
       </c>
       <c r="E525">
-        <v>5.507068785573022</v>
+        <v>5.527583207083674</v>
       </c>
       <c r="F525">
-        <v>10.58892320019985</v>
+        <v>10.5496319989986</v>
       </c>
       <c r="G525" t="inlineStr">
         <is>
@@ -80473,10 +80477,10 @@
         </is>
       </c>
       <c r="B526">
-        <v>8.750036233619571</v>
+        <v>8.750012281129139</v>
       </c>
       <c r="C526">
-        <v>1.358640026485308</v>
+        <v>1.342287898618169</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -80484,10 +80488,10 @@
         </is>
       </c>
       <c r="E526">
-        <v>6.454188680524636</v>
+        <v>6.477849328764199</v>
       </c>
       <c r="F526">
-        <v>11.86254971452614</v>
+        <v>11.81915648762348</v>
       </c>
       <c r="G526" t="inlineStr">
         <is>
@@ -80525,10 +80529,10 @@
         </is>
       </c>
       <c r="B527">
-        <v>8.333321771813084</v>
+        <v>8.583360274336087</v>
       </c>
       <c r="C527">
-        <v>1.306650860400796</v>
+        <v>1.321886483690464</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -80536,10 +80540,10 @@
         </is>
       </c>
       <c r="E527">
-        <v>6.128457501684687</v>
+        <v>6.346984602424437</v>
       </c>
       <c r="F527">
-        <v>11.33144053515653</v>
+        <v>11.607728427592</v>
       </c>
       <c r="G527" t="inlineStr">
         <is>
@@ -80577,10 +80581,10 @@
         </is>
       </c>
       <c r="B528">
-        <v>5.90911292852249</v>
+        <v>5.909096044994875</v>
       </c>
       <c r="C528">
-        <v>1.045367208489604</v>
+        <v>1.034803507873265</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -80588,10 +80592,10 @@
         </is>
       </c>
       <c r="E528">
-        <v>4.177709480493976</v>
+        <v>4.192357010383614</v>
       </c>
       <c r="F528">
-        <v>8.358076540521662</v>
+        <v>8.328826954023896</v>
       </c>
       <c r="G528" t="inlineStr">
         <is>
@@ -80629,10 +80633,10 @@
         </is>
       </c>
       <c r="B529">
-        <v>4.125051869108909</v>
+        <v>4.124984110977736</v>
       </c>
       <c r="C529">
-        <v>0.9422967979285272</v>
+        <v>0.9344393597365781</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -80640,10 +80644,10 @@
         </is>
       </c>
       <c r="E529">
-        <v>2.636253287295615</v>
+        <v>2.64605099685661</v>
       </c>
       <c r="F529">
-        <v>6.454635070477133</v>
+        <v>6.430523801707688</v>
       </c>
       <c r="G529" t="inlineStr">
         <is>
@@ -80681,10 +80685,10 @@
         </is>
       </c>
       <c r="B530">
-        <v>4.250039460439992</v>
+        <v>4.249992311369541</v>
       </c>
       <c r="C530">
-        <v>0.7858955857547106</v>
+        <v>0.7792319012621649</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -80692,10 +80696,10 @@
         </is>
       </c>
       <c r="E530">
-        <v>2.957965615942638</v>
+        <v>2.967024827425674</v>
       </c>
       <c r="F530">
-        <v>6.106506214251863</v>
+        <v>6.087726155757184</v>
       </c>
       <c r="G530" t="inlineStr">
         <is>
@@ -80733,10 +80737,10 @@
         </is>
       </c>
       <c r="B531">
-        <v>7.749960132421647</v>
+        <v>7.833355608476678</v>
       </c>
       <c r="C531">
-        <v>1.233641476493459</v>
+        <v>1.229794784725958</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -80744,10 +80748,10 @@
         </is>
       </c>
       <c r="E531">
-        <v>5.672896978721963</v>
+        <v>5.758558314249803</v>
       </c>
       <c r="F531">
-        <v>10.58751503498239</v>
+        <v>10.65569830855258</v>
       </c>
       <c r="G531" t="inlineStr">
         <is>
@@ -80785,10 +80789,10 @@
         </is>
       </c>
       <c r="B532">
-        <v>3.2105242817957</v>
+        <v>3.315789464945865</v>
       </c>
       <c r="C532">
-        <v>0.7060281542776641</v>
+        <v>0.705863056434012</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -80796,10 +80800,10 @@
         </is>
       </c>
       <c r="E532">
-        <v>2.086352857814489</v>
+        <v>2.184659355140892</v>
       </c>
       <c r="F532">
-        <v>4.940423248825296</v>
+        <v>5.032573957113298</v>
       </c>
       <c r="G532" t="inlineStr">
         <is>
@@ -80837,10 +80841,10 @@
         </is>
       </c>
       <c r="B533">
-        <v>4.79998893472282</v>
+        <v>4.800000531086908</v>
       </c>
       <c r="C533">
-        <v>1.93875527202479</v>
+        <v>1.88093967233135</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -80848,10 +80852,10 @@
         </is>
       </c>
       <c r="E533">
-        <v>2.174867910423411</v>
+        <v>2.226831805859571</v>
       </c>
       <c r="F533">
-        <v>10.59369797266264</v>
+        <v>10.34654033493159</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
@@ -80889,10 +80893,10 @@
         </is>
       </c>
       <c r="B534">
-        <v>9.999979486079235</v>
+        <v>10.24999902907889</v>
       </c>
       <c r="C534">
-        <v>2.973577566218318</v>
+        <v>2.937407603228272</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -80900,10 +80904,10 @@
         </is>
       </c>
       <c r="E534">
-        <v>5.583251721895336</v>
+        <v>5.845068006406024</v>
       </c>
       <c r="F534">
-        <v>17.91063607786948</v>
+        <v>17.97455221752302</v>
       </c>
       <c r="G534" t="inlineStr">
         <is>
@@ -80941,10 +80945,10 @@
         </is>
       </c>
       <c r="B535">
-        <v>7.050006683266504</v>
+        <v>7.300000740271065</v>
       </c>
       <c r="C535">
-        <v>1.364519151450524</v>
+        <v>1.362221605193042</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -80952,10 +80956,10 @@
         </is>
       </c>
       <c r="E535">
-        <v>4.824370288819969</v>
+        <v>5.063885310757354</v>
       </c>
       <c r="F535">
-        <v>10.30240036700407</v>
+        <v>10.52354220873696</v>
       </c>
       <c r="G535" t="inlineStr">
         <is>
@@ -80993,10 +80997,10 @@
         </is>
       </c>
       <c r="B536">
-        <v>6.749996432132501</v>
+        <v>6.800000387446299</v>
       </c>
       <c r="C536">
-        <v>1.311936916634182</v>
+        <v>1.278061933215564</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -81004,10 +81008,10 @@
         </is>
       </c>
       <c r="E536">
-        <v>4.611721278354135</v>
+        <v>4.704628926607757</v>
       </c>
       <c r="F536">
-        <v>9.879706314355181</v>
+        <v>9.828619002819185</v>
       </c>
       <c r="G536" t="inlineStr">
         <is>
@@ -81045,10 +81049,10 @@
         </is>
       </c>
       <c r="B537">
-        <v>0.2500061962037443</v>
+        <v>0.2500062056657638</v>
       </c>
       <c r="C537">
-        <v>0.1443393560674443</v>
+        <v>0.1443393588762009</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -81056,10 +81060,10 @@
         </is>
       </c>
       <c r="E537">
-        <v>0.08063348342775867</v>
+        <v>0.08063348815725045</v>
       </c>
       <c r="F537">
-        <v>0.7751506630153588</v>
+        <v>0.775150676223995</v>
       </c>
       <c r="G537" t="inlineStr">
         <is>
@@ -81097,10 +81101,10 @@
         </is>
       </c>
       <c r="B538">
-        <v>0.4166659376146522</v>
+        <v>0.4999945479345276</v>
       </c>
       <c r="C538">
-        <v>0.1863388351482951</v>
+        <v>0.2041230327671473</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -81108,10 +81112,10 @@
         </is>
       </c>
       <c r="E538">
-        <v>0.1734278190476007</v>
+        <v>0.2246269180454594</v>
       </c>
       <c r="F538">
-        <v>1.00105337495276</v>
+        <v>1.112932279619575</v>
       </c>
       <c r="G538" t="inlineStr">
         <is>
@@ -81149,10 +81153,10 @@
         </is>
       </c>
       <c r="B539">
-        <v>0.4166671795613961</v>
+        <v>0.4166640483236801</v>
       </c>
       <c r="C539">
-        <v>0.1863391128477562</v>
+        <v>0.1863384129967167</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -81160,10 +81164,10 @@
         </is>
       </c>
       <c r="E539">
-        <v>0.1734285625387172</v>
+        <v>0.1734266877846302</v>
       </c>
       <c r="F539">
-        <v>1.001055051038036</v>
+        <v>1.001050826624067</v>
       </c>
       <c r="G539" t="inlineStr">
         <is>
@@ -81201,10 +81205,10 @@
         </is>
       </c>
       <c r="B540">
-        <v>0.2499994850786755</v>
+        <v>0.416662449755704</v>
       </c>
       <c r="C540">
-        <v>0.1443374721118492</v>
+        <v>0.1863380555576488</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -81212,10 +81216,10 @@
         </is>
       </c>
       <c r="E540">
-        <v>0.08063006054742948</v>
+        <v>0.1734257308025408</v>
       </c>
       <c r="F540">
-        <v>0.7751419522107185</v>
+        <v>1.001048669266332</v>
       </c>
       <c r="G540" t="inlineStr">
         <is>
@@ -81253,10 +81257,10 @@
         </is>
       </c>
       <c r="B541">
-        <v>0.166667166374438</v>
+        <v>0.1666651087470506</v>
       </c>
       <c r="C541">
-        <v>0.1178513068952221</v>
+        <v>0.1178505794780054</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -81264,10 +81268,10 @@
         </is>
       </c>
       <c r="E541">
-        <v>0.04168315377618675</v>
+        <v>0.04168228253941109</v>
       </c>
       <c r="F541">
-        <v>0.6664069733407244</v>
+        <v>0.6664044476787582</v>
       </c>
       <c r="G541" t="inlineStr">
         <is>
@@ -81305,10 +81309,10 @@
         </is>
       </c>
       <c r="B542">
-        <v>0.5833354354574221</v>
+        <v>0.6666611824824404</v>
       </c>
       <c r="C542">
-        <v>0.220479673216261</v>
+        <v>0.2357012916112486</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -81316,10 +81320,10 @@
         </is>
       </c>
       <c r="E542">
-        <v>0.2780961624654896</v>
+        <v>0.3333947355916473</v>
       </c>
       <c r="F542">
-        <v>1.223606349845001</v>
+        <v>1.333065836928051</v>
       </c>
       <c r="G542" t="inlineStr">
         <is>
@@ -81357,10 +81361,10 @@
         </is>
       </c>
       <c r="B543">
-        <v>0.7500017594110894</v>
+        <v>0.7499932503292445</v>
       </c>
       <c r="C543">
-        <v>0.2500002932945256</v>
+        <v>0.249998875903895</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -81368,10 +81372,10 @@
         </is>
       </c>
       <c r="E543">
-        <v>0.390237290148407</v>
+        <v>0.3902314156859952</v>
       </c>
       <c r="F543">
-        <v>1.441437436452601</v>
+        <v>1.4414264278303</v>
       </c>
       <c r="G543" t="inlineStr">
         <is>

--- a/model_results/model_results.xlsx
+++ b/model_results/model_results.xlsx
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>54.39554894921703</v>
+        <v>53.8050957844205</v>
       </c>
       <c r="C6">
-        <v>26.40290950679339</v>
+        <v>26.58793991623825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="E6">
-        <v>21.00878475285498</v>
+        <v>20.42677307462774</v>
       </c>
       <c r="F6">
-        <v>140.839928643877</v>
+        <v>141.7251918251616</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>36.97318639561054</v>
+        <v>37.10402538438835</v>
       </c>
       <c r="C7">
-        <v>25.09747163264186</v>
+        <v>25.64527010365702</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="E7">
-        <v>9.774388544938466</v>
+        <v>9.574017177620778</v>
       </c>
       <c r="F7">
-        <v>139.8569850133952</v>
+        <v>143.7963473622531</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>65.16972616560392</v>
+        <v>90.02605602904687</v>
       </c>
       <c r="C16">
-        <v>6.680869051694412</v>
+        <v>16.30031517602278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="E16">
-        <v>53.30709804087025</v>
+        <v>63.13174678573355</v>
       </c>
       <c r="F16">
-        <v>79.67218934415783</v>
+        <v>128.3774198685181</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>113.2837345455801</v>
+        <v>114.1643162661077</v>
       </c>
       <c r="C17">
-        <v>17.34297694018339</v>
+        <v>32.85757371868844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="E17">
-        <v>83.91784701623297</v>
+        <v>64.9451160805832</v>
       </c>
       <c r="F17">
-        <v>152.9258074281984</v>
+        <v>200.6846995597953</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>43.90952843525387</v>
+        <v>44.46152625565278</v>
       </c>
       <c r="C22">
-        <v>14.81369812229629</v>
+        <v>15.07955361426927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="E22">
-        <v>22.66679211418147</v>
+        <v>22.87131782678436</v>
       </c>
       <c r="F22">
-        <v>85.06041250539754</v>
+        <v>86.43259351969039</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>56.22079263758614</v>
+        <v>55.87001406754705</v>
       </c>
       <c r="C23">
-        <v>26.59422633498228</v>
+        <v>27.3014564884895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="E23">
-        <v>22.24597842474823</v>
+        <v>21.44027738458317</v>
       </c>
       <c r="F23">
-        <v>142.0830976479844</v>
+        <v>145.588530218943</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>47.95717740569766</v>
+        <v>51.09039141395343</v>
       </c>
       <c r="C29">
-        <v>9.775897052735727</v>
+        <v>11.19940934960214</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="E29">
-        <v>32.16171951461919</v>
+        <v>33.24675488005372</v>
       </c>
       <c r="F29">
-        <v>71.51019595442148</v>
+        <v>78.51076305786955</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>28.88867698075944</v>
+        <v>28.71110335920381</v>
       </c>
       <c r="C30">
-        <v>13.98144042524336</v>
+        <v>12.49958015561968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="E30">
-        <v>11.18835195072431</v>
+        <v>12.23131983374387</v>
       </c>
       <c r="F30">
-        <v>74.59147346939093</v>
+        <v>67.39480835328355</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>6.594673063748478</v>
+        <v>6.545049038694915</v>
       </c>
       <c r="C45">
-        <v>0.6832713081755707</v>
+        <v>0.6732661075647761</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="E45">
-        <v>5.382705699093748</v>
+        <v>5.349987959668783</v>
       </c>
       <c r="F45">
-        <v>8.079526403431609</v>
+        <v>8.007058565711855</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>6.372641538497676</v>
+        <v>6.372430455808225</v>
       </c>
       <c r="C46">
-        <v>0.936541579069879</v>
+        <v>0.9487036926196882</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="E46">
-        <v>4.777761683086264</v>
+        <v>4.75971985209074</v>
       </c>
       <c r="F46">
-        <v>8.499913321744643</v>
+        <v>8.531567230007234</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>12.34205353363573</v>
+        <v>14.6875302541931</v>
       </c>
       <c r="C55">
-        <v>1.201469832151453</v>
+        <v>2.186339239028763</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="E55">
-        <v>10.19823372846994</v>
+        <v>10.97088362340551</v>
       </c>
       <c r="F55">
-        <v>14.93653602014316</v>
+        <v>19.66327894570031</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>21.01366087843392</v>
+        <v>21.07176065924943</v>
       </c>
       <c r="C56">
-        <v>2.999514037109731</v>
+        <v>4.943306492668542</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="E56">
-        <v>15.88547609805879</v>
+        <v>13.30497723731398</v>
       </c>
       <c r="F56">
-        <v>27.79733769312617</v>
+        <v>33.37240563143805</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>7.251172817222687</v>
+        <v>7.422014673448216</v>
       </c>
       <c r="C61">
-        <v>0.8122109911180107</v>
+        <v>0.8658004066776671</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="E61">
-        <v>5.821894546443334</v>
+        <v>5.90509080341915</v>
       </c>
       <c r="F61">
-        <v>9.031339679168642</v>
+        <v>9.328612149534552</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>4.4240851541318</v>
+        <v>4.421188814099455</v>
       </c>
       <c r="C62">
-        <v>0.8758185067377169</v>
+        <v>0.9459209006530866</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="E62">
-        <v>3.001335190766546</v>
+        <v>2.906852786276614</v>
       </c>
       <c r="F62">
-        <v>6.521274102014089</v>
+        <v>6.724423961956384</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>8.49675602835925</v>
+        <v>8.237373818308416</v>
       </c>
       <c r="C68">
-        <v>0.9486239869286902</v>
+        <v>1.066070985291034</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="E68">
-        <v>6.826850388935858</v>
+        <v>6.39186064393784</v>
       </c>
       <c r="F68">
-        <v>10.57513478286621</v>
+        <v>10.61573948532612</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>8.44294113934108</v>
+        <v>8.433995358585774</v>
       </c>
       <c r="C69">
-        <v>2.362031935298869</v>
+        <v>2.835391858903747</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="E69">
-        <v>4.879306696253529</v>
+        <v>4.363864383603863</v>
       </c>
       <c r="F69">
-        <v>14.60929995179671</v>
+        <v>16.30029520988513</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.2710968672491423</v>
+        <v>0.2597860392987643</v>
       </c>
       <c r="C84">
-        <v>0.07862912914724053</v>
+        <v>0.07329549183118837</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="E84">
-        <v>0.153547020984009</v>
+        <v>0.1494374949885568</v>
       </c>
       <c r="F84">
-        <v>0.4786384715334396</v>
+        <v>0.4516188271203762</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>0.1827599871041677</v>
+        <v>0.1807035838828483</v>
       </c>
       <c r="C85">
-        <v>0.08210069439319335</v>
+        <v>0.08453010028360566</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="E85">
-        <v>0.07577021607482355</v>
+        <v>0.07224187116924073</v>
       </c>
       <c r="F85">
-        <v>0.4408224579078887</v>
+        <v>0.4520063600181078</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.6603773781752778</v>
+        <v>0.8157894779587422</v>
       </c>
       <c r="C94">
-        <v>0.1116241406355907</v>
+        <v>0.1036053781392519</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="E94">
-        <v>0.4741468599948633</v>
+        <v>0.6360267536872662</v>
       </c>
       <c r="F94">
-        <v>0.9197536004148128</v>
+        <v>1.04635924273624</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>1.083333327275095</v>
+        <v>1.083333325258372</v>
       </c>
       <c r="C95">
-        <v>0.2124591327549221</v>
+        <v>0.2124591686765684</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -4072,10 +4072,10 @@
         </is>
       </c>
       <c r="E95">
-        <v>0.7376116318221362</v>
+        <v>0.7376115819842988</v>
       </c>
       <c r="F95">
-        <v>1.591096245439804</v>
+        <v>1.591096347020678</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.3998815393909391</v>
+        <v>0.3936181226209304</v>
       </c>
       <c r="C100">
-        <v>0.1322283752779291</v>
+        <v>0.1333901935389598</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -4267,10 +4267,10 @@
         </is>
       </c>
       <c r="E100">
-        <v>0.2091536779585342</v>
+        <v>0.2025899954528112</v>
       </c>
       <c r="F100">
-        <v>0.7645347053249966</v>
+        <v>0.7647723477624265</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.02453450999274235</v>
+        <v>0.0238200780736581</v>
       </c>
       <c r="C101">
-        <v>0.02758542547839167</v>
+        <v>0.02728854259993618</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="E101">
-        <v>0.002708489944995829</v>
+        <v>0.00252230360319896</v>
       </c>
       <c r="F101">
-        <v>0.2222427229963008</v>
+        <v>0.224951555679323</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.2755638955333911</v>
+        <v>0.2399137870809855</v>
       </c>
       <c r="C119">
-        <v>0.1125098096160225</v>
+        <v>0.1061067056493954</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="E119">
-        <v>0.1237900598111527</v>
+        <v>0.1008310234528371</v>
       </c>
       <c r="F119">
-        <v>0.6134213089272326</v>
+        <v>0.5708424179435508</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.1525474106172603</v>
+        <v>0.1488716504952723</v>
       </c>
       <c r="C120">
-        <v>0.09321829838172978</v>
+        <v>0.10150597323412</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="E120">
-        <v>0.04605265618867013</v>
+        <v>0.03912303973523568</v>
       </c>
       <c r="F120">
-        <v>0.5053066296696272</v>
+        <v>0.5664889147462098</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>3.005895413861683</v>
+        <v>3.050830052910358</v>
       </c>
       <c r="C129">
-        <v>2.069684272765772</v>
+        <v>2.079534405327655</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="E129">
-        <v>0.7796256636683349</v>
+        <v>0.8020737673230141</v>
       </c>
       <c r="F129">
-        <v>11.58941740906891</v>
+        <v>11.60437405004002</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>15.84619863669137</v>
+        <v>16.00037016915394</v>
       </c>
       <c r="C130">
-        <v>16.36021278452448</v>
+        <v>16.39898528751336</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="E130">
-        <v>2.094655164878319</v>
+        <v>2.146459086518233</v>
       </c>
       <c r="F130">
-        <v>119.8774936532649</v>
+        <v>119.2717099328585</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>2.171875021927268</v>
+        <v>2.421052631263999</v>
       </c>
       <c r="C135">
-        <v>0.4328264265517706</v>
+        <v>0.3959703569990478</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="E135">
-        <v>1.469607774623598</v>
+        <v>1.757064430787797</v>
       </c>
       <c r="F135">
-        <v>3.2097279235473</v>
+        <v>3.335959536055416</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5671,10 +5671,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>0.8529411840284921</v>
+        <v>0.8529411764782949</v>
       </c>
       <c r="C136">
-        <v>0.2638593587792704</v>
+        <v>0.2444351371304624</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="E136">
-        <v>0.4651552081095467</v>
+        <v>0.4863875908605457</v>
       </c>
       <c r="F136">
-        <v>1.56401272248164</v>
+        <v>1.495738510197241</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -5910,10 +5910,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>5.117256912087408</v>
+        <v>4.84059440167619</v>
       </c>
       <c r="C142">
-        <v>1.182016862889419</v>
+        <v>1.307304578701699</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="E142">
-        <v>3.254027528745679</v>
+        <v>2.851108668032045</v>
       </c>
       <c r="F142">
-        <v>8.047356106541706</v>
+        <v>8.218330793302304</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>4.260480537499163</v>
+        <v>4.256962556498384</v>
       </c>
       <c r="C143">
-        <v>2.538049027625775</v>
+        <v>3.020499931084274</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="E143">
-        <v>1.325505973035738</v>
+        <v>1.059583883966395</v>
       </c>
       <c r="F143">
-        <v>13.69416266668136</v>
+        <v>17.10268576338973</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>1.194730037020427</v>
+        <v>1.215208091128732</v>
       </c>
       <c r="C158">
-        <v>0.2194036530078327</v>
+        <v>0.2148816925485773</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="E158">
-        <v>0.8335903686112511</v>
+        <v>0.8592809291390611</v>
       </c>
       <c r="F158">
-        <v>1.712327679285479</v>
+        <v>1.718565668883534</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>1.443782267964201</v>
+        <v>1.443910139390572</v>
       </c>
       <c r="C159">
-        <v>0.3606872414371426</v>
+        <v>0.356358682309031</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="E159">
-        <v>0.8848173240669273</v>
+        <v>0.8901488737680818</v>
       </c>
       <c r="F159">
-        <v>2.35586169098355</v>
+        <v>2.342166071400427</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="B168">
-        <v>1.867478357921862</v>
+        <v>2.043337857025457</v>
       </c>
       <c r="C168">
-        <v>0.1893193365181137</v>
+        <v>0.1661706654959868</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -6935,10 +6935,10 @@
         </is>
       </c>
       <c r="E168">
-        <v>1.530958175852966</v>
+        <v>1.742279364190738</v>
       </c>
       <c r="F168">
-        <v>2.277969099556559</v>
+        <v>2.396417981965088</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -6963,10 +6963,10 @@
         </is>
       </c>
       <c r="B169">
-        <v>2.379171867789107</v>
+        <v>2.379173243469807</v>
       </c>
       <c r="C169">
-        <v>0.3148525762541546</v>
+        <v>0.3148527420883831</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="E169">
-        <v>1.835609591849261</v>
+        <v>1.835610677758746</v>
       </c>
       <c r="F169">
-        <v>3.083694267895251</v>
+        <v>3.083696009741013</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>1.227397510184339</v>
+        <v>1.161279401387074</v>
       </c>
       <c r="C174">
-        <v>0.1384849555300378</v>
+        <v>0.1398823062387273</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -7169,10 +7169,10 @@
         </is>
       </c>
       <c r="E174">
-        <v>0.9838882333884059</v>
+        <v>0.9170752028357867</v>
       </c>
       <c r="F174">
-        <v>1.531174575407283</v>
+        <v>1.470511735478032</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>0.9395817166639281</v>
+        <v>0.930783839096531</v>
       </c>
       <c r="C175">
-        <v>0.1662360055356704</v>
+        <v>0.1912220550988395</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -7208,10 +7208,10 @@
         </is>
       </c>
       <c r="E175">
-        <v>0.6642556573337101</v>
+        <v>0.6222663576366618</v>
       </c>
       <c r="F175">
-        <v>1.329027148722686</v>
+        <v>1.392263207693994</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>1.455940381128768</v>
+        <v>1.36718287786625</v>
       </c>
       <c r="C181">
-        <v>0.2167160058219382</v>
+        <v>0.2046844851097469</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="E181">
-        <v>1.087533547673891</v>
+        <v>1.019508910754709</v>
       </c>
       <c r="F181">
-        <v>1.949146670404154</v>
+        <v>1.833420975346789</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>1.623168676388054</v>
+        <v>1.605106417236052</v>
       </c>
       <c r="C182">
-        <v>0.5201232479748265</v>
+        <v>0.5831152302286878</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="E182">
-        <v>0.8661781261292163</v>
+        <v>0.787540469245164</v>
       </c>
       <c r="F182">
-        <v>3.04172602901116</v>
+        <v>3.27140853234086</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -9676,10 +9676,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>54.39554894921703</v>
+        <v>53.8050957844205</v>
       </c>
       <c r="D10">
-        <v>26.40290950679339</v>
+        <v>26.58793991623825</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -9687,10 +9687,10 @@
         </is>
       </c>
       <c r="F10">
-        <v>21.00878475285498</v>
+        <v>20.42677307462774</v>
       </c>
       <c r="G10">
-        <v>140.839928643877</v>
+        <v>141.7251918251616</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="C11">
-        <v>36.97318639561054</v>
+        <v>37.10402538438835</v>
       </c>
       <c r="D11">
-        <v>25.09747163264186</v>
+        <v>25.64527010365702</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="F11">
-        <v>9.774388544938466</v>
+        <v>9.574017177620778</v>
       </c>
       <c r="G11">
-        <v>139.8569850133952</v>
+        <v>143.7963473622531</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="C28">
-        <v>65.16972616560392</v>
+        <v>90.02605602904687</v>
       </c>
       <c r="D28">
-        <v>6.680869051694412</v>
+        <v>16.30031517602278</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -10479,10 +10479,10 @@
         </is>
       </c>
       <c r="F28">
-        <v>53.30709804087025</v>
+        <v>63.13174678573355</v>
       </c>
       <c r="G28">
-        <v>79.67218934415783</v>
+        <v>128.3774198685181</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="C29">
-        <v>113.2837345455801</v>
+        <v>114.1643162661077</v>
       </c>
       <c r="D29">
-        <v>17.34297694018339</v>
+        <v>32.85757371868844</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -10523,10 +10523,10 @@
         </is>
       </c>
       <c r="F29">
-        <v>83.91784701623297</v>
+        <v>64.9451160805832</v>
       </c>
       <c r="G29">
-        <v>152.9258074281984</v>
+        <v>200.6846995597953</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -10820,10 +10820,10 @@
         </is>
       </c>
       <c r="C36">
-        <v>43.90952843525387</v>
+        <v>44.46152625565278</v>
       </c>
       <c r="D36">
-        <v>14.81369812229629</v>
+        <v>15.07955361426927</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="F36">
-        <v>22.66679211418147</v>
+        <v>22.87131782678436</v>
       </c>
       <c r="G36">
-        <v>85.06041250539754</v>
+        <v>86.43259351969039</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -10864,10 +10864,10 @@
         </is>
       </c>
       <c r="C37">
-        <v>56.22079263758614</v>
+        <v>55.87001406754705</v>
       </c>
       <c r="D37">
-        <v>26.59422633498228</v>
+        <v>27.3014564884895</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -10875,10 +10875,10 @@
         </is>
       </c>
       <c r="F37">
-        <v>22.24597842474823</v>
+        <v>21.44027738458317</v>
       </c>
       <c r="G37">
-        <v>142.0830976479844</v>
+        <v>145.588530218943</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -11309,10 +11309,10 @@
         </is>
       </c>
       <c r="C47">
-        <v>47.95717740569766</v>
+        <v>51.09039141395343</v>
       </c>
       <c r="D47">
-        <v>9.775897052735727</v>
+        <v>11.19940934960214</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         </is>
       </c>
       <c r="F47">
-        <v>32.16171951461919</v>
+        <v>33.24675488005372</v>
       </c>
       <c r="G47">
-        <v>71.51019595442148</v>
+        <v>78.51076305786955</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -11353,10 +11353,10 @@
         </is>
       </c>
       <c r="C48">
-        <v>28.88867698075944</v>
+        <v>28.71110335920381</v>
       </c>
       <c r="D48">
-        <v>13.98144042524336</v>
+        <v>12.49958015561968</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -11364,10 +11364,10 @@
         </is>
       </c>
       <c r="F48">
-        <v>11.18835195072431</v>
+        <v>12.23131983374387</v>
       </c>
       <c r="G48">
-        <v>74.59147346939093</v>
+        <v>67.39480835328355</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -12541,10 +12541,10 @@
         </is>
       </c>
       <c r="C75">
-        <v>6.594673063748478</v>
+        <v>6.545049038694915</v>
       </c>
       <c r="D75">
-        <v>0.6832713081755707</v>
+        <v>0.6732661075647761</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -12552,10 +12552,10 @@
         </is>
       </c>
       <c r="F75">
-        <v>5.382705699093748</v>
+        <v>5.349987959668783</v>
       </c>
       <c r="G75">
-        <v>8.079526403431609</v>
+        <v>8.007058565711855</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -12585,10 +12585,10 @@
         </is>
       </c>
       <c r="C76">
-        <v>6.372641538497676</v>
+        <v>6.372430455808225</v>
       </c>
       <c r="D76">
-        <v>0.936541579069879</v>
+        <v>0.9487036926196882</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -12596,10 +12596,10 @@
         </is>
       </c>
       <c r="F76">
-        <v>4.777761683086264</v>
+        <v>4.75971985209074</v>
       </c>
       <c r="G76">
-        <v>8.499913321744643</v>
+        <v>8.531567230007234</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="C93">
-        <v>12.34205353363573</v>
+        <v>14.6875302541931</v>
       </c>
       <c r="D93">
-        <v>1.201469832151453</v>
+        <v>2.186339239028763</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -13344,10 +13344,10 @@
         </is>
       </c>
       <c r="F93">
-        <v>10.19823372846994</v>
+        <v>10.97088362340551</v>
       </c>
       <c r="G93">
-        <v>14.93653602014316</v>
+        <v>19.66327894570031</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="C94">
-        <v>21.01366087843392</v>
+        <v>21.07176065924943</v>
       </c>
       <c r="D94">
-        <v>2.999514037109731</v>
+        <v>4.943306492668542</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -13388,10 +13388,10 @@
         </is>
       </c>
       <c r="F94">
-        <v>15.88547609805879</v>
+        <v>13.30497723731398</v>
       </c>
       <c r="G94">
-        <v>27.79733769312617</v>
+        <v>33.37240563143805</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -13685,10 +13685,10 @@
         </is>
       </c>
       <c r="C101">
-        <v>7.251172817222687</v>
+        <v>7.422014673448216</v>
       </c>
       <c r="D101">
-        <v>0.8122109911180107</v>
+        <v>0.8658004066776671</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -13696,10 +13696,10 @@
         </is>
       </c>
       <c r="F101">
-        <v>5.821894546443334</v>
+        <v>5.90509080341915</v>
       </c>
       <c r="G101">
-        <v>9.031339679168642</v>
+        <v>9.328612149534552</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -13729,10 +13729,10 @@
         </is>
       </c>
       <c r="C102">
-        <v>4.4240851541318</v>
+        <v>4.421188814099455</v>
       </c>
       <c r="D102">
-        <v>0.8758185067377169</v>
+        <v>0.9459209006530866</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -13740,10 +13740,10 @@
         </is>
       </c>
       <c r="F102">
-        <v>3.001335190766546</v>
+        <v>2.906852786276614</v>
       </c>
       <c r="G102">
-        <v>6.521274102014089</v>
+        <v>6.724423961956384</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -14174,10 +14174,10 @@
         </is>
       </c>
       <c r="C112">
-        <v>8.49675602835925</v>
+        <v>8.237373818308416</v>
       </c>
       <c r="D112">
-        <v>0.9486239869286902</v>
+        <v>1.066070985291034</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -14185,10 +14185,10 @@
         </is>
       </c>
       <c r="F112">
-        <v>6.826850388935858</v>
+        <v>6.39186064393784</v>
       </c>
       <c r="G112">
-        <v>10.57513478286621</v>
+        <v>10.61573948532612</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -14218,10 +14218,10 @@
         </is>
       </c>
       <c r="C113">
-        <v>8.44294113934108</v>
+        <v>8.433995358585774</v>
       </c>
       <c r="D113">
-        <v>2.362031935298869</v>
+        <v>2.835391858903747</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -14229,10 +14229,10 @@
         </is>
       </c>
       <c r="F113">
-        <v>4.879306696253529</v>
+        <v>4.363864383603863</v>
       </c>
       <c r="G113">
-        <v>14.60929995179671</v>
+        <v>16.30029520988513</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -15406,10 +15406,10 @@
         </is>
       </c>
       <c r="C140">
-        <v>0.2710968672491423</v>
+        <v>0.2597860392987643</v>
       </c>
       <c r="D140">
-        <v>0.07862912914724053</v>
+        <v>0.07329549183118837</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -15417,10 +15417,10 @@
         </is>
       </c>
       <c r="F140">
-        <v>0.153547020984009</v>
+        <v>0.1494374949885568</v>
       </c>
       <c r="G140">
-        <v>0.4786384715334396</v>
+        <v>0.4516188271203762</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -15450,10 +15450,10 @@
         </is>
       </c>
       <c r="C141">
-        <v>0.1827599871041677</v>
+        <v>0.1807035838828483</v>
       </c>
       <c r="D141">
-        <v>0.08210069439319335</v>
+        <v>0.08453010028360566</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -15461,10 +15461,10 @@
         </is>
       </c>
       <c r="F141">
-        <v>0.07577021607482355</v>
+        <v>0.07224187116924073</v>
       </c>
       <c r="G141">
-        <v>0.4408224579078887</v>
+        <v>0.4520063600181078</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -16202,10 +16202,10 @@
         </is>
       </c>
       <c r="C158">
-        <v>0.6603773781752778</v>
+        <v>0.8157894779587422</v>
       </c>
       <c r="D158">
-        <v>0.1116241406355907</v>
+        <v>0.1036053781392519</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -16213,10 +16213,10 @@
         </is>
       </c>
       <c r="F158">
-        <v>0.4741468599948633</v>
+        <v>0.6360267536872662</v>
       </c>
       <c r="G158">
-        <v>0.9197536004148128</v>
+        <v>1.04635924273624</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -16246,10 +16246,10 @@
         </is>
       </c>
       <c r="C159">
-        <v>1.083333327275095</v>
+        <v>1.083333325258372</v>
       </c>
       <c r="D159">
-        <v>0.2124591327549221</v>
+        <v>0.2124591686765684</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -16257,10 +16257,10 @@
         </is>
       </c>
       <c r="F159">
-        <v>0.7376116318221362</v>
+        <v>0.7376115819842988</v>
       </c>
       <c r="G159">
-        <v>1.591096245439804</v>
+        <v>1.591096347020678</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -16554,10 +16554,10 @@
         </is>
       </c>
       <c r="C166">
-        <v>0.3998815393909391</v>
+        <v>0.3936181226209304</v>
       </c>
       <c r="D166">
-        <v>0.1322283752779291</v>
+        <v>0.1333901935389598</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -16565,10 +16565,10 @@
         </is>
       </c>
       <c r="F166">
-        <v>0.2091536779585342</v>
+        <v>0.2025899954528112</v>
       </c>
       <c r="G166">
-        <v>0.7645347053249966</v>
+        <v>0.7647723477624265</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -16598,10 +16598,10 @@
         </is>
       </c>
       <c r="C167">
-        <v>0.02453450999274235</v>
+        <v>0.0238200780736581</v>
       </c>
       <c r="D167">
-        <v>0.02758542547839167</v>
+        <v>0.02728854259993618</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -16609,10 +16609,10 @@
         </is>
       </c>
       <c r="F167">
-        <v>0.002708489944995829</v>
+        <v>0.00252230360319896</v>
       </c>
       <c r="G167">
-        <v>0.2222427229963008</v>
+        <v>0.224951555679323</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -18017,10 +18017,10 @@
         </is>
       </c>
       <c r="C199">
-        <v>0.2755638955333911</v>
+        <v>0.2399137870809855</v>
       </c>
       <c r="D199">
-        <v>0.1125098096160225</v>
+        <v>0.1061067056493954</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -18028,10 +18028,10 @@
         </is>
       </c>
       <c r="F199">
-        <v>0.1237900598111527</v>
+        <v>0.1008310234528371</v>
       </c>
       <c r="G199">
-        <v>0.6134213089272326</v>
+        <v>0.5708424179435508</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -18061,10 +18061,10 @@
         </is>
       </c>
       <c r="C200">
-        <v>0.1525474106172603</v>
+        <v>0.1488716504952723</v>
       </c>
       <c r="D200">
-        <v>0.09321829838172978</v>
+        <v>0.10150597323412</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -18072,10 +18072,10 @@
         </is>
       </c>
       <c r="F200">
-        <v>0.04605265618867013</v>
+        <v>0.03912303973523568</v>
       </c>
       <c r="G200">
-        <v>0.5053066296696272</v>
+        <v>0.5664889147462098</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -18811,10 +18811,10 @@
         </is>
       </c>
       <c r="C217">
-        <v>3.005895413861683</v>
+        <v>3.050830052910358</v>
       </c>
       <c r="D217">
-        <v>2.069684272765772</v>
+        <v>2.079534405327655</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -18822,10 +18822,10 @@
         </is>
       </c>
       <c r="F217">
-        <v>0.7796256636683349</v>
+        <v>0.8020737673230141</v>
       </c>
       <c r="G217">
-        <v>11.58941740906891</v>
+        <v>11.60437405004002</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -18855,10 +18855,10 @@
         </is>
       </c>
       <c r="C218">
-        <v>15.84619863669137</v>
+        <v>16.00037016915394</v>
       </c>
       <c r="D218">
-        <v>16.36021278452448</v>
+        <v>16.39898528751336</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -18866,10 +18866,10 @@
         </is>
       </c>
       <c r="F218">
-        <v>2.094655164878319</v>
+        <v>2.146459086518233</v>
       </c>
       <c r="G218">
-        <v>119.8774936532649</v>
+        <v>119.2717099328585</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -19163,10 +19163,10 @@
         </is>
       </c>
       <c r="C225">
-        <v>2.171875021927268</v>
+        <v>2.421052631263999</v>
       </c>
       <c r="D225">
-        <v>0.4328264265517706</v>
+        <v>0.3959703569990478</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -19174,10 +19174,10 @@
         </is>
       </c>
       <c r="F225">
-        <v>1.469607774623598</v>
+        <v>1.757064430787797</v>
       </c>
       <c r="G225">
-        <v>3.2097279235473</v>
+        <v>3.335959536055416</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -19207,10 +19207,10 @@
         </is>
       </c>
       <c r="C226">
-        <v>0.8529411840284921</v>
+        <v>0.8529411764782949</v>
       </c>
       <c r="D226">
-        <v>0.2638593587792704</v>
+        <v>0.2444351371304624</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -19218,10 +19218,10 @@
         </is>
       </c>
       <c r="F226">
-        <v>0.4651552081095467</v>
+        <v>0.4863875908605457</v>
       </c>
       <c r="G226">
-        <v>1.56401272248164</v>
+        <v>1.495738510197241</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -19652,10 +19652,10 @@
         </is>
       </c>
       <c r="C236">
-        <v>5.117256912087408</v>
+        <v>4.84059440167619</v>
       </c>
       <c r="D236">
-        <v>1.182016862889419</v>
+        <v>1.307304578701699</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -19663,10 +19663,10 @@
         </is>
       </c>
       <c r="F236">
-        <v>3.254027528745679</v>
+        <v>2.851108668032045</v>
       </c>
       <c r="G236">
-        <v>8.047356106541706</v>
+        <v>8.218330793302304</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -19696,10 +19696,10 @@
         </is>
       </c>
       <c r="C237">
-        <v>4.260480537499163</v>
+        <v>4.256962556498384</v>
       </c>
       <c r="D237">
-        <v>2.538049027625775</v>
+        <v>3.020499931084274</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -19707,10 +19707,10 @@
         </is>
       </c>
       <c r="F237">
-        <v>1.325505973035738</v>
+        <v>1.059583883966395</v>
       </c>
       <c r="G237">
-        <v>13.69416266668136</v>
+        <v>17.10268576338973</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -20884,10 +20884,10 @@
         </is>
       </c>
       <c r="C264">
-        <v>1.194730037020427</v>
+        <v>1.215208091128732</v>
       </c>
       <c r="D264">
-        <v>0.2194036530078327</v>
+        <v>0.2148816925485773</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -20895,10 +20895,10 @@
         </is>
       </c>
       <c r="F264">
-        <v>0.8335903686112511</v>
+        <v>0.8592809291390611</v>
       </c>
       <c r="G264">
-        <v>1.712327679285479</v>
+        <v>1.718565668883534</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -20928,10 +20928,10 @@
         </is>
       </c>
       <c r="C265">
-        <v>1.443782267964201</v>
+        <v>1.443910139390572</v>
       </c>
       <c r="D265">
-        <v>0.3606872414371426</v>
+        <v>0.356358682309031</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -20939,10 +20939,10 @@
         </is>
       </c>
       <c r="F265">
-        <v>0.8848173240669273</v>
+        <v>0.8901488737680818</v>
       </c>
       <c r="G265">
-        <v>2.35586169098355</v>
+        <v>2.342166071400427</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -21676,10 +21676,10 @@
         </is>
       </c>
       <c r="C282">
-        <v>1.867478357921862</v>
+        <v>2.043337857025457</v>
       </c>
       <c r="D282">
-        <v>0.1893193365181137</v>
+        <v>0.1661706654959868</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -21687,10 +21687,10 @@
         </is>
       </c>
       <c r="F282">
-        <v>1.530958175852966</v>
+        <v>1.742279364190738</v>
       </c>
       <c r="G282">
-        <v>2.277969099556559</v>
+        <v>2.396417981965088</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -21720,10 +21720,10 @@
         </is>
       </c>
       <c r="C283">
-        <v>2.379171867789107</v>
+        <v>2.379173243469807</v>
       </c>
       <c r="D283">
-        <v>0.3148525762541546</v>
+        <v>0.3148527420883831</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -21731,10 +21731,10 @@
         </is>
       </c>
       <c r="F283">
-        <v>1.835609591849261</v>
+        <v>1.835610677758746</v>
       </c>
       <c r="G283">
-        <v>3.083694267895251</v>
+        <v>3.083696009741013</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -22028,10 +22028,10 @@
         </is>
       </c>
       <c r="C290">
-        <v>1.227397510184339</v>
+        <v>1.161279401387074</v>
       </c>
       <c r="D290">
-        <v>0.1384849555300378</v>
+        <v>0.1398823062387273</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -22039,10 +22039,10 @@
         </is>
       </c>
       <c r="F290">
-        <v>0.9838882333884059</v>
+        <v>0.9170752028357867</v>
       </c>
       <c r="G290">
-        <v>1.531174575407283</v>
+        <v>1.470511735478032</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -22072,10 +22072,10 @@
         </is>
       </c>
       <c r="C291">
-        <v>0.9395817166639281</v>
+        <v>0.930783839096531</v>
       </c>
       <c r="D291">
-        <v>0.1662360055356704</v>
+        <v>0.1912220550988395</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -22083,10 +22083,10 @@
         </is>
       </c>
       <c r="F291">
-        <v>0.6642556573337101</v>
+        <v>0.6222663576366618</v>
       </c>
       <c r="G291">
-        <v>1.329027148722686</v>
+        <v>1.392263207693994</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -22517,10 +22517,10 @@
         </is>
       </c>
       <c r="C301">
-        <v>1.455940381128768</v>
+        <v>1.36718287786625</v>
       </c>
       <c r="D301">
-        <v>0.2167160058219382</v>
+        <v>0.2046844851097469</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -22528,10 +22528,10 @@
         </is>
       </c>
       <c r="F301">
-        <v>1.087533547673891</v>
+        <v>1.019508910754709</v>
       </c>
       <c r="G301">
-        <v>1.949146670404154</v>
+        <v>1.833420975346789</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -22561,10 +22561,10 @@
         </is>
       </c>
       <c r="C302">
-        <v>1.623168676388054</v>
+        <v>1.605106417236052</v>
       </c>
       <c r="D302">
-        <v>0.5201232479748265</v>
+        <v>0.5831152302286878</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -22572,10 +22572,10 @@
         </is>
       </c>
       <c r="F302">
-        <v>0.8661781261292163</v>
+        <v>0.787540469245164</v>
       </c>
       <c r="G302">
-        <v>3.04172602901116</v>
+        <v>3.27140853234086</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -26642,10 +26642,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>30.01034049272654</v>
+        <v>30.23235118661874</v>
       </c>
       <c r="C15">
-        <v>4.654023981342773</v>
+        <v>4.014266621010267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -26653,10 +26653,10 @@
         </is>
       </c>
       <c r="E15">
-        <v>22.14450666813065</v>
+        <v>23.30499208214039</v>
       </c>
       <c r="F15">
-        <v>40.67015580823544</v>
+        <v>39.21885298435614</v>
       </c>
       <c r="G15" s="2">
         <v>44480</v>
@@ -26689,10 +26689,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>12.47060788231319</v>
+        <v>12.1009973584268</v>
       </c>
       <c r="C16">
-        <v>2.022918043980451</v>
+        <v>1.664001161934485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -26700,10 +26700,10 @@
         </is>
       </c>
       <c r="E16">
-        <v>9.074236114912571</v>
+        <v>9.242148306378354</v>
       </c>
       <c r="F16">
-        <v>17.13819863016758</v>
+        <v>15.84416655244459</v>
       </c>
       <c r="G16" s="2">
         <v>44691</v>
@@ -26736,10 +26736,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>238.6139996396264</v>
+        <v>239.623449032107</v>
       </c>
       <c r="C17">
-        <v>36.4504590483795</v>
+        <v>38.44001878467662</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -26747,10 +26747,10 @@
         </is>
       </c>
       <c r="E17">
-        <v>176.8752804834931</v>
+        <v>174.9769713498176</v>
       </c>
       <c r="F17">
-        <v>321.9027592119253</v>
+        <v>328.154024401581</v>
       </c>
       <c r="G17" s="2">
         <v>45376</v>
@@ -26783,10 +26783,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>94.81998810326705</v>
+        <v>95.18387400913079</v>
       </c>
       <c r="C18">
-        <v>14.37603151690825</v>
+        <v>15.15496023013078</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -26794,10 +26794,10 @@
         </is>
       </c>
       <c r="E18">
-        <v>70.44430374385782</v>
+        <v>69.66858667219746</v>
       </c>
       <c r="F18">
-        <v>127.6303358266584</v>
+        <v>130.0438304284079</v>
       </c>
       <c r="G18" s="2">
         <v>45610</v>
@@ -26830,10 +26830,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>24.99697789905527</v>
+        <v>24.88675833430699</v>
       </c>
       <c r="C19">
-        <v>3.906221239741933</v>
+        <v>4.064230660864057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -26841,10 +26841,10 @@
         </is>
       </c>
       <c r="E19">
-        <v>18.40230247767273</v>
+        <v>18.07005566555643</v>
       </c>
       <c r="F19">
-        <v>33.95493063131521</v>
+        <v>34.27497689289086</v>
       </c>
       <c r="G19" s="2">
         <v>45799</v>
@@ -26877,10 +26877,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>54.27545784153744</v>
+        <v>54.72133329094129</v>
       </c>
       <c r="C20">
-        <v>8.566213652785782</v>
+        <v>9.041383102304323</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -26888,10 +26888,10 @@
         </is>
       </c>
       <c r="E20">
-        <v>39.83452472450735</v>
+        <v>39.58367435614128</v>
       </c>
       <c r="F20">
-        <v>73.95156197498574</v>
+        <v>75.64796259682507</v>
       </c>
       <c r="G20" s="2">
         <v>45972</v>
@@ -27456,10 +27456,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>72.66666650987288</v>
+        <v>72.6666677747171</v>
       </c>
       <c r="C32">
-        <v>16.95952259657449</v>
+        <v>19.0795035683906</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -27467,10 +27467,10 @@
         </is>
       </c>
       <c r="E32">
-        <v>45.99123534210118</v>
+        <v>43.43522644460637</v>
       </c>
       <c r="F32">
-        <v>114.8141462689364</v>
+        <v>121.5705554618288</v>
       </c>
       <c r="G32" s="2">
         <v>42388</v>
@@ -27503,10 +27503,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>81.58333365354626</v>
+        <v>140.416667078881</v>
       </c>
       <c r="C33">
-        <v>13.4326962038166</v>
+        <v>25.85957988848263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -27514,10 +27514,10 @@
         </is>
       </c>
       <c r="E33">
-        <v>59.08144519221874</v>
+        <v>97.872048348226</v>
       </c>
       <c r="F33">
-        <v>112.655340578948</v>
+        <v>201.4552747827382</v>
       </c>
       <c r="G33" s="2">
         <v>42791</v>
@@ -27550,10 +27550,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>54.36363633912688</v>
+        <v>94.90909100838824</v>
       </c>
       <c r="C34">
-        <v>9.436761026501172</v>
+        <v>12.96296072375452</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -27561,10 +27561,10 @@
         </is>
       </c>
       <c r="E34">
-        <v>38.68582903578757</v>
+        <v>72.61865856520571</v>
       </c>
       <c r="F34">
-        <v>76.3950270596203</v>
+        <v>124.0416131888515</v>
       </c>
       <c r="G34" s="2">
         <v>43512</v>
@@ -27597,10 +27597,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>42.00000000738343</v>
+        <v>42.04166676041796</v>
       </c>
       <c r="C35">
-        <v>7.037012066925351</v>
+        <v>5.585751396784186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -27608,10 +27608,10 @@
         </is>
       </c>
       <c r="E35">
-        <v>30.24351424531661</v>
+        <v>32.40315915096202</v>
       </c>
       <c r="F35">
-        <v>58.32655511894998</v>
+        <v>54.54720435620108</v>
       </c>
       <c r="G35" s="2">
         <v>43931</v>
@@ -27644,10 +27644,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>81.58333322764392</v>
+        <v>140.4166671208178</v>
       </c>
       <c r="C36">
-        <v>13.43269610125514</v>
+        <v>25.85957989994495</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -27655,10 +27655,10 @@
         </is>
       </c>
       <c r="E36">
-        <v>59.08144492982637</v>
+        <v>97.8720483723483</v>
       </c>
       <c r="F36">
-        <v>112.6553399030478</v>
+        <v>201.4552748534192</v>
       </c>
       <c r="G36" s="2">
         <v>44636</v>
@@ -27691,10 +27691,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>119.9999998706312</v>
+        <v>120.0000001615971</v>
       </c>
       <c r="C37">
-        <v>19.63847472628805</v>
+        <v>22.13245383657021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -27702,10 +27702,10 @@
         </is>
       </c>
       <c r="E37">
-        <v>87.072045187518</v>
+        <v>83.59649899852822</v>
       </c>
       <c r="F37">
-        <v>165.3802886786421</v>
+        <v>172.2560180305736</v>
       </c>
       <c r="G37" s="2">
         <v>45971</v>
@@ -27738,10 +27738,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>105.6666666816414</v>
+        <v>105.6666666154595</v>
       </c>
       <c r="C38">
-        <v>17.32315220965586</v>
+        <v>19.51582050139671</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -27749,10 +27749,10 @@
         </is>
       </c>
       <c r="E38">
-        <v>76.62857453145409</v>
+        <v>73.57455261702012</v>
       </c>
       <c r="F38">
-        <v>145.7086278308098</v>
+        <v>151.7568783835152</v>
       </c>
       <c r="G38" s="2">
         <v>46120</v>
@@ -28302,10 +28302,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>121.5000075294275</v>
+        <v>121.8333333837448</v>
       </c>
       <c r="C50">
-        <v>38.25398733758571</v>
+        <v>25.69884009337505</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -28313,10 +28313,10 @@
         </is>
       </c>
       <c r="E50">
-        <v>65.55072974896251</v>
+        <v>80.57836423457621</v>
       </c>
       <c r="F50">
-        <v>225.2034704447296</v>
+        <v>184.2102562442613</v>
       </c>
       <c r="G50" s="2">
         <v>42122</v>
@@ -28349,10 +28349,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>300.1666667897181</v>
+        <v>300.166666792912</v>
       </c>
       <c r="C51">
-        <v>94.11673913264148</v>
+        <v>63.02567014171443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -28360,10 +28360,10 @@
         </is>
       </c>
       <c r="E51">
-        <v>162.3565040131411</v>
+        <v>198.90083021785</v>
       </c>
       <c r="F51">
-        <v>554.9517612448526</v>
+        <v>452.9897022294136</v>
       </c>
       <c r="G51" s="2">
         <v>42286</v>
@@ -28396,10 +28396,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>31.45454569673344</v>
+        <v>31.45454545058989</v>
       </c>
       <c r="C52">
-        <v>7.457601626412768</v>
+        <v>7.081267128438556</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -28407,10 +28407,10 @@
         </is>
       </c>
       <c r="E52">
-        <v>19.76381904921291</v>
+        <v>20.23275266631001</v>
       </c>
       <c r="F52">
-        <v>50.06059013818459</v>
+        <v>48.90033728088205</v>
       </c>
       <c r="G52" s="2">
         <v>44481</v>
@@ -28443,10 +28443,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>51.24999652887922</v>
+        <v>51.24999994481257</v>
       </c>
       <c r="C53">
-        <v>11.51753434796849</v>
+        <v>10.92422786485304</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -28454,10 +28454,10 @@
         </is>
       </c>
       <c r="E53">
-        <v>32.99144067554241</v>
+        <v>33.74857481442027</v>
       </c>
       <c r="F53">
-        <v>79.61344186334011</v>
+        <v>77.82736037851873</v>
       </c>
       <c r="G53" s="2">
         <v>44896</v>
@@ -28490,10 +28490,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>21.25000085726048</v>
+        <v>21.25000006124278</v>
       </c>
       <c r="C54">
-        <v>4.882888036922294</v>
+        <v>4.642572678647519</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -28501,10 +28501,10 @@
         </is>
       </c>
       <c r="E54">
-        <v>13.54463618420475</v>
+        <v>13.84820624778886</v>
       </c>
       <c r="F54">
-        <v>33.33884574619777</v>
+        <v>32.60801395667536</v>
       </c>
       <c r="G54" s="2">
         <v>45261</v>
@@ -28537,10 +28537,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>33.00000106682587</v>
+        <v>32.99999997977276</v>
       </c>
       <c r="C55">
-        <v>7.481900806471854</v>
+        <v>7.103404242176628</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -28548,10 +28548,10 @@
         </is>
       </c>
       <c r="E55">
-        <v>21.16049946013993</v>
+        <v>21.64157324325238</v>
       </c>
       <c r="F55">
-        <v>51.46381693219765</v>
+        <v>50.31981669837896</v>
       </c>
       <c r="G55" s="2">
         <v>45645</v>
@@ -28584,10 +28584,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>19.39999817667932</v>
+        <v>19.40000002445211</v>
       </c>
       <c r="C56">
-        <v>6.9303896224266</v>
+        <v>6.591766439311127</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -28595,10 +28595,10 @@
         </is>
       </c>
       <c r="E56">
-        <v>9.632107782092971</v>
+        <v>9.967332805132667</v>
       </c>
       <c r="F56">
-        <v>39.07347568876365</v>
+        <v>37.75934929702915</v>
       </c>
       <c r="G56" s="2">
         <v>45692</v>
@@ -28631,10 +28631,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>117.6470614023404</v>
+        <v>117.6470585095441</v>
       </c>
       <c r="C57">
-        <v>22.01055681675339</v>
+        <v>20.85515265968233</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -28642,10 +28642,10 @@
         </is>
       </c>
       <c r="E57">
-        <v>81.53236084330871</v>
+        <v>83.11695006777632</v>
       </c>
       <c r="F57">
-        <v>169.7587425832765</v>
+        <v>166.5223563263789</v>
       </c>
       <c r="G57" s="2">
         <v>45974</v>
@@ -28678,10 +28678,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>27.58823565639795</v>
+        <v>27.58823533339308</v>
       </c>
       <c r="C58">
-        <v>5.280446199463094</v>
+        <v>5.015934499281956</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -28689,10 +28689,10 @@
         </is>
       </c>
       <c r="E58">
-        <v>18.95842109598947</v>
+        <v>19.31805268328901</v>
       </c>
       <c r="F58">
-        <v>40.14631507441067</v>
+        <v>39.39893638809016</v>
       </c>
       <c r="G58" s="2">
         <v>46087</v>
@@ -29017,10 +29017,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>72.2000008454764</v>
+        <v>65.6363638575984</v>
       </c>
       <c r="C65">
-        <v>21.95830078576601</v>
+        <v>15.19733584067892</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -29028,10 +29028,10 @@
         </is>
       </c>
       <c r="E65">
-        <v>39.77955560159095</v>
+        <v>41.69257389509855</v>
       </c>
       <c r="F65">
-        <v>131.0431965177185</v>
+        <v>103.3309258211454</v>
       </c>
       <c r="G65" s="2">
         <v>42122</v>
@@ -29064,10 +29064,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>61.83333371381011</v>
+        <v>61.91666708856197</v>
       </c>
       <c r="C66">
-        <v>17.21001005986812</v>
+        <v>13.73640254412281</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -29075,10 +29075,10 @@
         </is>
       </c>
       <c r="E66">
-        <v>35.83509712766735</v>
+        <v>40.08352407420551</v>
       </c>
       <c r="F66">
-        <v>106.6931992549697</v>
+        <v>95.64213107257329</v>
       </c>
       <c r="G66" s="2">
         <v>42286</v>
@@ -29111,10 +29111,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>25.25000033987898</v>
+        <v>25.24999924267759</v>
       </c>
       <c r="C67">
-        <v>8.821557247163714</v>
+        <v>9.893349710224271</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -29122,10 +29122,10 @@
         </is>
       </c>
       <c r="E67">
-        <v>12.73146256953327</v>
+        <v>11.71513021472424</v>
       </c>
       <c r="F67">
-        <v>50.07771209959748</v>
+        <v>54.42214043458896</v>
       </c>
       <c r="G67" s="2">
         <v>44481</v>
@@ -29158,10 +29158,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>46.25000038816111</v>
+        <v>46.25000000998332</v>
       </c>
       <c r="C68">
-        <v>15.85793948225595</v>
+        <v>17.85418157751537</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -29169,10 +29169,10 @@
         </is>
       </c>
       <c r="E68">
-        <v>23.61873060837816</v>
+        <v>21.70286121513126</v>
       </c>
       <c r="F68">
-        <v>90.5663632551922</v>
+        <v>98.56131317063851</v>
       </c>
       <c r="G68" s="2">
         <v>44896</v>
@@ -29205,10 +29205,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>106.7500006755762</v>
+        <v>106.7499989018991</v>
       </c>
       <c r="C69">
-        <v>36.12179986862454</v>
+        <v>40.78361055270997</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -29216,10 +29216,10 @@
         </is>
       </c>
       <c r="E69">
-        <v>54.9971803438188</v>
+        <v>50.48567136379341</v>
       </c>
       <c r="F69">
-        <v>207.202670627755</v>
+        <v>225.7187427189087</v>
       </c>
       <c r="G69" s="2">
         <v>45261</v>
@@ -29252,10 +29252,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>27.00000023968958</v>
+        <v>27.00000089371809</v>
       </c>
       <c r="C70">
-        <v>9.408122336812447</v>
+        <v>10.55689438918133</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -29263,10 +29263,10 @@
         </is>
       </c>
       <c r="E70">
-        <v>13.6384012977624</v>
+        <v>12.54721430158938</v>
       </c>
       <c r="F70">
-        <v>53.45201369480465</v>
+        <v>58.10054971073808</v>
       </c>
       <c r="G70" s="2">
         <v>45645</v>
@@ -29299,10 +29299,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>19.75000030878898</v>
+        <v>19.75000017740724</v>
       </c>
       <c r="C71">
-        <v>6.977528864120881</v>
+        <v>7.807544999995432</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -29310,10 +29310,10 @@
         </is>
       </c>
       <c r="E71">
-        <v>9.881978496582255</v>
+        <v>9.100624393950632</v>
       </c>
       <c r="F71">
-        <v>39.47210696036935</v>
+        <v>42.86107085870597</v>
       </c>
       <c r="G71" s="2">
         <v>45692</v>
@@ -29346,10 +29346,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>28.16666698450187</v>
+        <v>28.16666675711908</v>
       </c>
       <c r="C72">
-        <v>8.000958692479559</v>
+        <v>8.980836391165729</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -29357,10 +29357,10 @@
         </is>
       </c>
       <c r="E72">
-        <v>16.1415451395963</v>
+        <v>15.07762806347348</v>
       </c>
       <c r="F72">
-        <v>49.15025929392966</v>
+        <v>52.61842995905737</v>
       </c>
       <c r="G72" s="2">
         <v>45974</v>
@@ -31649,10 +31649,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>8.62500210862402</v>
+        <v>8.437499710853457</v>
       </c>
       <c r="C121">
-        <v>0.5994789981941818</v>
+        <v>0.4192627721791152</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -31660,10 +31660,10 @@
         </is>
       </c>
       <c r="E121">
-        <v>7.526561622079332</v>
+        <v>7.654506956967564</v>
       </c>
       <c r="F121">
-        <v>9.883751055135477</v>
+        <v>9.300586147596317</v>
       </c>
       <c r="G121" s="2">
         <v>44480</v>
@@ -31696,10 +31696,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>4.62499974348065</v>
+        <v>4.66666665716849</v>
       </c>
       <c r="C122">
-        <v>0.4389855378094189</v>
+        <v>0.3118047956966244</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -31707,10 +31707,10 @@
         </is>
       </c>
       <c r="E122">
-        <v>3.839894035816452</v>
+        <v>4.093864669326385</v>
       </c>
       <c r="F122">
-        <v>5.570628363094381</v>
+        <v>5.319613482170015</v>
       </c>
       <c r="G122" s="2">
         <v>44691</v>
@@ -31743,10 +31743,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>5.91304343244065</v>
+        <v>5.913043536255042</v>
       </c>
       <c r="C123">
-        <v>0.5070392709661709</v>
+        <v>0.5070393261760689</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -31754,10 +31754,10 @@
         </is>
       </c>
       <c r="E123">
-        <v>4.998286449772372</v>
+        <v>4.998286460805716</v>
       </c>
       <c r="F123">
-        <v>6.995213856845241</v>
+        <v>6.995214087031616</v>
       </c>
       <c r="G123" s="2">
         <v>45376</v>
@@ -31790,10 +31790,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>7.833333184725589</v>
+        <v>7.833333317404297</v>
       </c>
       <c r="C124">
-        <v>0.5713045268289471</v>
+        <v>0.571304591878986</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -31801,10 +31801,10 @@
         </is>
       </c>
       <c r="E124">
-        <v>6.789946427544199</v>
+        <v>6.789946448476369</v>
       </c>
       <c r="F124">
-        <v>9.037053449200238</v>
+        <v>9.037053727474587</v>
       </c>
       <c r="G124" s="2">
         <v>45610</v>
@@ -31837,10 +31837,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>5.749999681932471</v>
+        <v>5.750000043157792</v>
       </c>
       <c r="C125">
-        <v>0.4894724696146333</v>
+        <v>0.4894725337729151</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -31848,10 +31848,10 @@
         </is>
       </c>
       <c r="E125">
-        <v>4.866410434427307</v>
+        <v>4.866410684726183</v>
       </c>
       <c r="F125">
-        <v>6.794021340313523</v>
+        <v>6.794021844495218</v>
       </c>
       <c r="G125" s="2">
         <v>45799</v>
@@ -31884,10 +31884,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>7.090908830885652</v>
+        <v>7.090909167977973</v>
       </c>
       <c r="C126">
-        <v>0.5677270598709199</v>
+        <v>0.5677271322000909</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -31895,10 +31895,10 @@
         </is>
       </c>
       <c r="E126">
-        <v>6.061097036490862</v>
+        <v>6.061097248668049</v>
       </c>
       <c r="F126">
-        <v>8.295690985512229</v>
+        <v>8.295691483842061</v>
       </c>
       <c r="G126" s="2">
         <v>45972</v>
@@ -32463,10 +32463,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>12.00009987628843</v>
+        <v>11.99992680727669</v>
       </c>
       <c r="C138">
-        <v>2.275457828648887</v>
+        <v>2.5425192439862</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -32474,10 +32474,10 @@
         </is>
       </c>
       <c r="E138">
-        <v>8.275230561621575</v>
+        <v>7.921871711467497</v>
       </c>
       <c r="F138">
-        <v>17.40161751006</v>
+        <v>18.17730059571017</v>
       </c>
       <c r="G138" s="2">
         <v>42388</v>
@@ -32510,10 +32510,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>15.50007919959341</v>
+        <v>21.00000360778737</v>
       </c>
       <c r="C139">
-        <v>1.985568542282049</v>
+        <v>2.930233075740083</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -32521,10 +32521,10 @@
         </is>
       </c>
       <c r="E139">
-        <v>12.05853472761369</v>
+        <v>15.97522782517282</v>
       </c>
       <c r="F139">
-        <v>19.92385149776922</v>
+        <v>27.60524959976976</v>
       </c>
       <c r="G139" s="2">
         <v>42791</v>
@@ -32557,10 +32557,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>11.81820355049037</v>
+        <v>16.18182154038975</v>
       </c>
       <c r="C140">
-        <v>1.659972859253448</v>
+        <v>1.71744543170389</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -32568,10 +32568,10 @@
         </is>
       </c>
       <c r="E140">
-        <v>8.974134249649335</v>
+        <v>13.1427356630544</v>
       </c>
       <c r="F140">
-        <v>15.56361107103793</v>
+        <v>19.92365631313069</v>
       </c>
       <c r="G140" s="2">
         <v>43512</v>
@@ -32604,10 +32604,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>7.749981221509349</v>
+        <v>7.74999727301975</v>
       </c>
       <c r="C141">
-        <v>1.143905215186859</v>
+        <v>0.8879484179052353</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -32615,10 +32615,10 @@
         </is>
       </c>
       <c r="E141">
-        <v>5.803131678098926</v>
+        <v>6.191216039585557</v>
       </c>
       <c r="F141">
-        <v>10.34996485784096</v>
+        <v>9.701237583664453</v>
       </c>
       <c r="G141" s="2">
         <v>43931</v>
@@ -32651,10 +32651,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>15.50004076660232</v>
+        <v>21.00000362806055</v>
       </c>
       <c r="C142">
-        <v>1.985562770332504</v>
+        <v>2.930233079407215</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -32662,10 +32662,10 @@
         </is>
       </c>
       <c r="E142">
-        <v>12.05850612208139</v>
+        <v>15.97522783934521</v>
       </c>
       <c r="F142">
-        <v>19.92379995780643</v>
+        <v>27.60524962857944</v>
       </c>
       <c r="G142" s="2">
         <v>44636</v>
@@ -32698,10 +32698,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>21.08347122984614</v>
+        <v>21.08331447885612</v>
       </c>
       <c r="C143">
-        <v>2.580981232981866</v>
+        <v>2.940671715193388</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -32709,10 +32709,10 @@
         </is>
       </c>
       <c r="E143">
-        <v>16.58594942221317</v>
+        <v>16.04037310257978</v>
       </c>
       <c r="F143">
-        <v>26.80056159488974</v>
+        <v>27.71170885936898</v>
       </c>
       <c r="G143" s="2">
         <v>45971</v>
@@ -32745,10 +32745,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>20.83332040718475</v>
+        <v>20.83335968326145</v>
       </c>
       <c r="C144">
-        <v>2.554386913562448</v>
+        <v>2.909350340596081</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -32756,10 +32756,10 @@
         </is>
       </c>
       <c r="E144">
-        <v>16.38295055168979</v>
+        <v>15.84492450482307</v>
       </c>
       <c r="F144">
-        <v>26.49261729863755</v>
+        <v>27.3922968556921</v>
       </c>
       <c r="G144" s="2">
         <v>46120</v>
@@ -33309,10 +33309,10 @@
         </is>
       </c>
       <c r="B156">
-        <v>10.9999959283739</v>
+        <v>11.00001014756803</v>
       </c>
       <c r="C156">
-        <v>1.849703690566376</v>
+        <v>1.26862198658435</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -33320,10 +33320,10 @@
         </is>
       </c>
       <c r="E156">
-        <v>7.911498995032065</v>
+        <v>8.774547361707405</v>
       </c>
       <c r="F156">
-        <v>15.29418261952922</v>
+        <v>13.78991055135803</v>
       </c>
       <c r="G156" s="2">
         <v>42122</v>
@@ -33356,10 +33356,10 @@
         </is>
       </c>
       <c r="B157">
-        <v>11.8333286670464</v>
+        <v>11.83335400731299</v>
       </c>
       <c r="C157">
-        <v>1.951928148328592</v>
+        <v>1.337080598661965</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -33367,10 +33367,10 @@
         </is>
       </c>
       <c r="E157">
-        <v>8.564455394594953</v>
+        <v>9.482622064247474</v>
       </c>
       <c r="F157">
-        <v>16.34986241281774</v>
+        <v>14.76682990354975</v>
       </c>
       <c r="G157" s="2">
         <v>42286</v>
@@ -33403,10 +33403,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>6.181822641407582</v>
+        <v>6.18182698250498</v>
       </c>
       <c r="C158">
-        <v>0.9140893025480996</v>
+        <v>0.8947944304099023</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -33414,10 +33414,10 @@
         </is>
       </c>
       <c r="E158">
-        <v>4.62649059337902</v>
+        <v>4.654884058723727</v>
       </c>
       <c r="F158">
-        <v>8.260025693018566</v>
+        <v>8.209653421981121</v>
       </c>
       <c r="G158" s="2">
         <v>44481</v>
@@ -33450,10 +33450,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>6.416664194591469</v>
+        <v>6.416678155083366</v>
       </c>
       <c r="C159">
-        <v>0.8971703583853815</v>
+        <v>0.8777504490386993</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -33461,10 +33461,10 @@
         </is>
       </c>
       <c r="E159">
-        <v>4.878601265470995</v>
+        <v>4.907639657274669</v>
       </c>
       <c r="F159">
-        <v>8.439627906786345</v>
+        <v>8.38972732745192</v>
       </c>
       <c r="G159" s="2">
         <v>44896</v>
@@ -33497,10 +33497,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>5.666666913379977</v>
+        <v>5.666659995380935</v>
       </c>
       <c r="C160">
-        <v>0.8264045692073851</v>
+        <v>0.8099747273381898</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -33508,10 +33508,10 @@
         </is>
       </c>
       <c r="E160">
-        <v>4.257863918088864</v>
+        <v>4.282122216589415</v>
       </c>
       <c r="F160">
-        <v>7.541601733859166</v>
+        <v>7.49886011633413</v>
       </c>
       <c r="G160" s="2">
         <v>45261</v>
@@ -33544,10 +33544,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>4.416666663933992</v>
+        <v>4.4166658680699</v>
       </c>
       <c r="C161">
-        <v>0.7043192913327696</v>
+        <v>0.6926282192323081</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -33555,10 +33555,10 @@
         </is>
       </c>
       <c r="E161">
-        <v>3.23113254676757</v>
+        <v>3.247938760241204</v>
       </c>
       <c r="F161">
-        <v>6.037184837811926</v>
+        <v>6.005943716969894</v>
       </c>
       <c r="G161" s="2">
         <v>45645</v>
@@ -33591,10 +33591,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>9.200001069720079</v>
+        <v>9.199979440565379</v>
       </c>
       <c r="C162">
-        <v>1.781302027693751</v>
+        <v>1.7329033361921</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -33602,10 +33602,10 @@
         </is>
       </c>
       <c r="E162">
-        <v>6.294749277974262</v>
+        <v>6.359968687098996</v>
       </c>
       <c r="F162">
-        <v>13.44613040888087</v>
+        <v>13.30818214223516</v>
       </c>
       <c r="G162" s="2">
         <v>45692</v>
@@ -33638,10 +33638,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>4.705880456231193</v>
+        <v>4.70588860095635</v>
       </c>
       <c r="C163">
-        <v>0.6159529015848002</v>
+        <v>0.6052366889753519</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -33649,10 +33649,10 @@
         </is>
       </c>
       <c r="E163">
-        <v>3.641053688863347</v>
+        <v>3.657348766163481</v>
       </c>
       <c r="F163">
-        <v>6.082115991882548</v>
+        <v>6.055038482928493</v>
       </c>
       <c r="G163" s="2">
         <v>45974</v>
@@ -33685,10 +33685,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>4.176471726400814</v>
+        <v>4.176472747272545</v>
       </c>
       <c r="C164">
-        <v>0.5713789565013353</v>
+        <v>0.5622860251288423</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -33696,10 +33696,10 @@
         </is>
       </c>
       <c r="E164">
-        <v>3.19416617541771</v>
+        <v>3.20782641800504</v>
       </c>
       <c r="F164">
-        <v>5.460866818910679</v>
+        <v>5.437614863075447</v>
       </c>
       <c r="G164" s="2">
         <v>46087</v>
@@ -34024,10 +34024,10 @@
         </is>
       </c>
       <c r="B171">
-        <v>4.399999957576934</v>
+        <v>4.000000028089968</v>
       </c>
       <c r="C171">
-        <v>0.9380831057245846</v>
+        <v>0.6187550265170024</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -34035,10 +34035,10 @@
         </is>
       </c>
       <c r="E171">
-        <v>2.897182816691203</v>
+        <v>2.953851696249587</v>
       </c>
       <c r="F171">
-        <v>6.682353462522457</v>
+        <v>5.416656579284072</v>
       </c>
       <c r="G171" s="2">
         <v>42122</v>
@@ -34071,10 +34071,10 @@
         </is>
       </c>
       <c r="B172">
-        <v>10.33333310768889</v>
+        <v>10.41666608014946</v>
       </c>
       <c r="C172">
-        <v>1.312334641753935</v>
+        <v>0.931694965487031</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -34082,10 +34082,10 @@
         </is>
       </c>
       <c r="E172">
-        <v>8.056338833775975</v>
+        <v>8.741681110869258</v>
       </c>
       <c r="F172">
-        <v>13.25388309970237</v>
+        <v>12.41259328144797</v>
       </c>
       <c r="G172" s="2">
         <v>42286</v>
@@ -34118,10 +34118,10 @@
         </is>
       </c>
       <c r="B173">
-        <v>8.249999960614474</v>
+        <v>8.249999873747434</v>
       </c>
       <c r="C173">
-        <v>1.436140643175713</v>
+        <v>1.436140651956228</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -34129,10 +34129,10 @@
         </is>
       </c>
       <c r="E173">
-        <v>5.865145336719389</v>
+        <v>5.86514524165829</v>
       </c>
       <c r="F173">
-        <v>11.60457165895379</v>
+        <v>11.60457160266144</v>
       </c>
       <c r="G173" s="2">
         <v>44481</v>
@@ -34165,10 +34165,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>13.50000015811472</v>
+        <v>13.49999924469896</v>
       </c>
       <c r="C174">
-        <v>1.837117383805917</v>
+        <v>1.837117258238941</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -34176,10 +34176,10 @@
         </is>
       </c>
       <c r="E174">
-        <v>10.33950891035221</v>
+        <v>10.33950821267829</v>
       </c>
       <c r="F174">
-        <v>17.62656291021944</v>
+        <v>17.62656171435677</v>
       </c>
       <c r="G174" s="2">
         <v>44896</v>
@@ -34212,10 +34212,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>8.749999969498605</v>
+        <v>8.749999631489169</v>
       </c>
       <c r="C175">
-        <v>1.479019934249903</v>
+        <v>1.47901991614637</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -34223,10 +34223,10 @@
         </is>
       </c>
       <c r="E175">
-        <v>6.282445516794241</v>
+        <v>6.28244521918023</v>
       </c>
       <c r="F175">
-        <v>12.1867351275166</v>
+        <v>12.18673476329188</v>
       </c>
       <c r="G175" s="2">
         <v>45261</v>
@@ -34259,10 +34259,10 @@
         </is>
       </c>
       <c r="B176">
-        <v>9.499999924187223</v>
+        <v>9.499999444344411</v>
       </c>
       <c r="C176">
-        <v>1.541103495478997</v>
+        <v>1.54110345727279</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -34270,10 +34270,10 @@
         </is>
       </c>
       <c r="E176">
-        <v>6.912584881798315</v>
+        <v>6.912584476120423</v>
       </c>
       <c r="F176">
-        <v>13.05589733837433</v>
+        <v>13.05589678568318</v>
       </c>
       <c r="G176" s="2">
         <v>45645</v>
@@ -34306,10 +34306,10 @@
         </is>
       </c>
       <c r="B177">
-        <v>6.749999778123152</v>
+        <v>6.749999483427059</v>
       </c>
       <c r="C177">
-        <v>1.299038053520224</v>
+        <v>1.299038057156434</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -34317,10 +34317,10 @@
         </is>
       </c>
       <c r="E177">
-        <v>4.629029477650832</v>
+        <v>4.629029194435899</v>
       </c>
       <c r="F177">
-        <v>9.842775299798896</v>
+        <v>9.842775042557902</v>
       </c>
       <c r="G177" s="2">
         <v>45692</v>
@@ -34353,10 +34353,10 @@
         </is>
       </c>
       <c r="B178">
-        <v>8.499999802133473</v>
+        <v>8.499999562602548</v>
       </c>
       <c r="C178">
-        <v>1.190238047741953</v>
+        <v>1.190238041947796</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -34364,10 +34364,10 @@
         </is>
       </c>
       <c r="E178">
-        <v>6.459915815113322</v>
+        <v>6.459915591741732</v>
       </c>
       <c r="F178">
-        <v>11.18435575696456</v>
+        <v>11.18435551334555</v>
       </c>
       <c r="G178" s="2">
         <v>45974</v>
@@ -36562,10 +36562,10 @@
         </is>
       </c>
       <c r="B225">
-        <v>0.3333329371880054</v>
+        <v>0.3333333216632092</v>
       </c>
       <c r="C225">
-        <v>0.1178510610279026</v>
+        <v>0.08333332503641391</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -36573,10 +36573,10 @@
         </is>
       </c>
       <c r="E225">
-        <v>0.1666989469806874</v>
+        <v>0.204210636047934</v>
       </c>
       <c r="F225">
-        <v>0.6665359861406644</v>
+        <v>0.5441004713630468</v>
       </c>
       <c r="G225" s="2">
         <v>44480</v>
@@ -36609,10 +36609,10 @@
         </is>
       </c>
       <c r="B226">
-        <v>0.1250001559644689</v>
+        <v>0.1249999947550696</v>
       </c>
       <c r="C226">
-        <v>0.0721688288669648</v>
+        <v>0.05103103100919624</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -36620,10 +36620,10 @@
         </is>
       </c>
       <c r="E226">
-        <v>0.04031525582735532</v>
+        <v>0.05615758736631075</v>
       </c>
       <c r="F226">
-        <v>0.3875713714444401</v>
+        <v>0.27823486409498</v>
       </c>
       <c r="G226" s="2">
         <v>44691</v>
@@ -36656,10 +36656,10 @@
         </is>
       </c>
       <c r="B227">
-        <v>0.1739131031107939</v>
+        <v>0.1739130385848418</v>
       </c>
       <c r="C227">
-        <v>0.08695653697710468</v>
+        <v>0.08695651332728262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -36667,10 +36667,10 @@
         </is>
       </c>
       <c r="E227">
-        <v>0.06527270395955094</v>
+        <v>0.06527267340589037</v>
       </c>
       <c r="F227">
-        <v>0.4633754325907615</v>
+        <v>0.4633753056464088</v>
       </c>
       <c r="G227" s="2">
         <v>45376</v>
@@ -36703,10 +36703,10 @@
         </is>
       </c>
       <c r="B228">
-        <v>0.5416668008668513</v>
+        <v>0.5416666366924994</v>
       </c>
       <c r="C228">
-        <v>0.1502313235246018</v>
+        <v>0.1502312867796152</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -36714,10 +36714,10 @@
         </is>
       </c>
       <c r="E228">
-        <v>0.3145222784702506</v>
+        <v>0.3145221731391585</v>
       </c>
       <c r="F228">
-        <v>0.9328525934263218</v>
+        <v>0.9328523403529637</v>
       </c>
       <c r="G228" s="2">
         <v>45610</v>
@@ -36750,10 +36750,10 @@
         </is>
       </c>
       <c r="B229">
-        <v>0.3181817837905367</v>
+        <v>0.3181818054922859</v>
       </c>
       <c r="C229">
-        <v>0.1202614177217613</v>
+        <v>0.1202614109567476</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -36761,10 +36761,10 @@
         </is>
       </c>
       <c r="E229">
-        <v>0.1516880434112292</v>
+        <v>0.1516880677425453</v>
       </c>
       <c r="F229">
-        <v>0.6674200896748678</v>
+        <v>0.6674200736617021</v>
       </c>
       <c r="G229" s="2">
         <v>45972</v>
@@ -37321,10 +37321,10 @@
         </is>
       </c>
       <c r="B241">
-        <v>0.6666670905744827</v>
+        <v>0.6667124910611517</v>
       </c>
       <c r="C241">
-        <v>0.3333332844782937</v>
+        <v>0.3333447622008374</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -37332,10 +37332,10 @@
         </is>
       </c>
       <c r="E241">
-        <v>0.2502122558958997</v>
+        <v>0.2502375510445113</v>
       </c>
       <c r="F241">
-        <v>1.776271941850665</v>
+        <v>1.776334302671862</v>
       </c>
       <c r="G241" s="2">
         <v>42388</v>
@@ -37368,10 +37368,10 @@
         </is>
       </c>
       <c r="B242">
-        <v>0.7500034436971542</v>
+        <v>1.08333189365325</v>
       </c>
       <c r="C242">
-        <v>0.2500005562633066</v>
+        <v>0.3004629958796055</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -37379,10 +37379,10 @@
         </is>
       </c>
       <c r="E242">
-        <v>0.3902384708765489</v>
+        <v>0.6290426289986388</v>
       </c>
       <c r="F242">
-        <v>1.441439549243052</v>
+        <v>1.865705021732121</v>
       </c>
       <c r="G242" s="2">
         <v>42791</v>
@@ -37415,10 +37415,10 @@
         </is>
       </c>
       <c r="B243">
-        <v>0.3636356570916776</v>
+        <v>0.6363626714988994</v>
       </c>
       <c r="C243">
-        <v>0.1818179198032628</v>
+        <v>0.1700751930165019</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -37426,10 +37426,10 @@
         </is>
       </c>
       <c r="E243">
-        <v>0.136478888568871</v>
+        <v>0.3768871764059735</v>
       </c>
       <c r="F243">
-        <v>0.9688743255098299</v>
+        <v>1.074479247447268</v>
       </c>
       <c r="G243" s="2">
         <v>43512</v>
@@ -37462,10 +37462,10 @@
         </is>
       </c>
       <c r="B244">
-        <v>0.7499948309802358</v>
+        <v>0.7499994211992251</v>
       </c>
       <c r="C244">
-        <v>0.2499991208097065</v>
+        <v>0.1767766127970354</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -37473,10 +37473,10 @@
         </is>
       </c>
       <c r="E244">
-        <v>0.390232525681816</v>
+        <v>0.4725314721422891</v>
       </c>
       <c r="F244">
-        <v>1.44142840352501</v>
+        <v>1.190395063526674</v>
       </c>
       <c r="G244" s="2">
         <v>43931</v>
@@ -37509,10 +37509,10 @@
         </is>
       </c>
       <c r="B245">
-        <v>0.7499993429903296</v>
+        <v>1.083331124688278</v>
       </c>
       <c r="C245">
-        <v>0.2499998728128276</v>
+        <v>0.3004628892434991</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -37520,10 +37520,10 @@
         </is>
       </c>
       <c r="E245">
-        <v>0.3902356402348605</v>
+        <v>0.6290420611352285</v>
       </c>
       <c r="F245">
-        <v>1.441434242519187</v>
+        <v>1.865704057373156</v>
       </c>
       <c r="G245" s="2">
         <v>44636</v>
@@ -37556,10 +37556,10 @@
         </is>
       </c>
       <c r="B246">
-        <v>0.9166655856667779</v>
+        <v>0.9166645331959563</v>
       </c>
       <c r="C246">
-        <v>0.2763852174503518</v>
+        <v>0.2763850553801586</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -37567,10 +37567,10 @@
         </is>
       </c>
       <c r="E246">
-        <v>0.5076493930412729</v>
+        <v>0.5076486416573881</v>
       </c>
       <c r="F246">
-        <v>1.655228603567937</v>
+        <v>1.65522725260528</v>
       </c>
       <c r="G246" s="2">
         <v>45971</v>
@@ -37603,10 +37603,10 @@
         </is>
       </c>
       <c r="B247">
-        <v>1.249998582185245</v>
+        <v>1.249998403325595</v>
       </c>
       <c r="C247">
-        <v>0.3227479953576356</v>
+        <v>0.3227483805101925</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -37614,10 +37614,10 @@
         </is>
       </c>
       <c r="E247">
-        <v>0.7535817941447367</v>
+        <v>0.7535811766541454</v>
       </c>
       <c r="F247">
-        <v>2.073426491464602</v>
+        <v>2.073427597082405</v>
       </c>
       <c r="G247" s="2">
         <v>46120</v>
@@ -38120,10 +38120,10 @@
         </is>
       </c>
       <c r="B258">
-        <v>0.1666682844639585</v>
+        <v>0.1666651878949803</v>
       </c>
       <c r="C258">
-        <v>0.1666674620742061</v>
+        <v>0.1178505976044347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -38131,10 +38131,10 @@
         </is>
       </c>
       <c r="E258">
-        <v>0.02347770395664154</v>
+        <v>0.04168232088231637</v>
       </c>
       <c r="F258">
-        <v>1.183178606283638</v>
+        <v>0.6664044676037588</v>
       </c>
       <c r="G258" s="2">
         <v>42122</v>
@@ -38167,10 +38167,10 @@
         </is>
       </c>
       <c r="B259">
-        <v>1.000005185408058</v>
+        <v>1.000001497472312</v>
       </c>
       <c r="C259">
-        <v>0.4082493207839021</v>
+        <v>0.2886753274654309</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -38178,10 +38178,10 @@
         </is>
       </c>
       <c r="E259">
-        <v>0.4492639819409491</v>
+        <v>0.5679108082455103</v>
       </c>
       <c r="F259">
-        <v>2.225885917946666</v>
+        <v>1.760845154604914</v>
       </c>
       <c r="G259" s="2">
         <v>42286</v>
@@ -38214,10 +38214,10 @@
         </is>
       </c>
       <c r="B260">
-        <v>0.5454557986066015</v>
+        <v>0.5454555445650008</v>
       </c>
       <c r="C260">
-        <v>0.2226811246973657</v>
+        <v>0.2226810714237922</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -38225,10 +38225,10 @@
         </is>
       </c>
       <c r="E260">
-        <v>0.2450520915079263</v>
+        <v>0.2450519329641483</v>
       </c>
       <c r="F260">
-        <v>1.214117481727113</v>
+        <v>1.214117136306082</v>
       </c>
       <c r="G260" s="2">
         <v>44481</v>
@@ -38261,10 +38261,10 @@
         </is>
       </c>
       <c r="B261">
-        <v>0.4166675893020094</v>
+        <v>0.4166673114907453</v>
       </c>
       <c r="C261">
-        <v>0.1863391900215774</v>
+        <v>0.186339126994993</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -38272,10 +38272,10 @@
         </is>
       </c>
       <c r="E261">
-        <v>0.1734288196133977</v>
+        <v>0.1734286540423976</v>
       </c>
       <c r="F261">
-        <v>1.001055535993143</v>
+        <v>1.00105515679366</v>
       </c>
       <c r="G261" s="2">
         <v>44896</v>
@@ -38308,10 +38308,10 @@
         </is>
       </c>
       <c r="B262">
-        <v>0.3333325173820389</v>
+        <v>0.3333338330975462</v>
       </c>
       <c r="C262">
-        <v>0.166666449589279</v>
+        <v>0.1666667778699799</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -38319,10 +38319,10 @@
         </is>
       </c>
       <c r="E262">
-        <v>0.125105505803476</v>
+        <v>0.1251062420549695</v>
       </c>
       <c r="F262">
-        <v>0.8881349100557338</v>
+        <v>0.8881366945598317</v>
       </c>
       <c r="G262" s="2">
         <v>45645</v>
@@ -38355,10 +38355,10 @@
         </is>
       </c>
       <c r="B263">
-        <v>1.199999492045763</v>
+        <v>1.200001780130069</v>
       </c>
       <c r="C263">
-        <v>0.4898978125067141</v>
+        <v>0.4898982726983084</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -38366,10 +38366,10 @@
         </is>
       </c>
       <c r="E263">
-        <v>0.5391125436412845</v>
+        <v>0.5391139888863087</v>
       </c>
       <c r="F263">
-        <v>2.671054120136069</v>
+        <v>2.671057145614174</v>
       </c>
       <c r="G263" s="2">
         <v>45692</v>
@@ -40294,10 +40294,10 @@
         </is>
       </c>
       <c r="B304">
-        <v>0.2083333519260731</v>
+        <v>0.1874999531583771</v>
       </c>
       <c r="C304">
-        <v>0.09316949619811285</v>
+        <v>0.06249998698638666</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -40305,10 +40305,10 @@
         </is>
       </c>
       <c r="E304">
-        <v>0.08671414462207409</v>
+        <v>0.09755899190600231</v>
       </c>
       <c r="F304">
-        <v>0.5005271713618951</v>
+        <v>0.3603587096130155</v>
       </c>
       <c r="G304" s="2">
         <v>44480</v>
@@ -40341,10 +40341,10 @@
         </is>
       </c>
       <c r="B305">
-        <v>0.7391304744588201</v>
+        <v>0.7391308854805023</v>
       </c>
       <c r="C305">
-        <v>0.1792654569230143</v>
+        <v>0.179265501718282</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -40352,10 +40352,10 @@
         </is>
       </c>
       <c r="E305">
-        <v>0.4594882681451065</v>
+        <v>0.4594885905434212</v>
       </c>
       <c r="F305">
-        <v>1.188961495097834</v>
+        <v>1.188961983201986</v>
       </c>
       <c r="G305" s="2">
         <v>45376</v>
@@ -40388,10 +40388,10 @@
         </is>
       </c>
       <c r="B306">
-        <v>0.416666676749007</v>
+        <v>0.4166664480171317</v>
       </c>
       <c r="C306">
-        <v>0.1317615618870781</v>
+        <v>0.1317615236296038</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -40399,10 +40399,10 @@
         </is>
       </c>
       <c r="E306">
-        <v>0.2241894790243193</v>
+        <v>0.2241893200208225</v>
       </c>
       <c r="F306">
-        <v>0.7743945892047361</v>
+        <v>0.7743942882162642</v>
       </c>
       <c r="G306" s="2">
         <v>45610</v>
@@ -40435,10 +40435,10 @@
         </is>
       </c>
       <c r="B307">
-        <v>0.2727273266075524</v>
+        <v>0.2727268964920495</v>
       </c>
       <c r="C307">
-        <v>0.1113404457349146</v>
+        <v>0.1113403567809682</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -40446,10 +40446,10 @@
         </is>
       </c>
       <c r="E307">
-        <v>0.122525685275848</v>
+        <v>0.1225254157523621</v>
       </c>
       <c r="F307">
-        <v>0.6070579773624347</v>
+        <v>0.6070573979566455</v>
       </c>
       <c r="G307" s="2">
         <v>45972</v>
@@ -41014,10 +41014,10 @@
         </is>
       </c>
       <c r="B319">
-        <v>7.166646780819126</v>
+        <v>7.166708483647556</v>
       </c>
       <c r="C319">
-        <v>2.581187166784422</v>
+        <v>2.975519924372275</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -41025,10 +41025,10 @@
         </is>
       </c>
       <c r="E319">
-        <v>3.537867725240518</v>
+        <v>3.176233568882223</v>
       </c>
       <c r="F319">
-        <v>14.51745233847979</v>
+        <v>16.17063398384175</v>
       </c>
       <c r="G319" s="2">
         <v>42388</v>
@@ -41061,10 +41061,10 @@
         </is>
       </c>
       <c r="B320">
-        <v>6.000029050740634</v>
+        <v>6.000056853513934</v>
       </c>
       <c r="C320">
-        <v>1.623595367929028</v>
+        <v>1.317911306051661</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -41072,10 +41072,10 @@
         </is>
       </c>
       <c r="E320">
-        <v>3.530368081213267</v>
+        <v>3.901118245359604</v>
       </c>
       <c r="F320">
-        <v>10.19733573994909</v>
+        <v>9.228298139443091</v>
       </c>
       <c r="G320" s="2">
         <v>43512</v>
@@ -41108,10 +41108,10 @@
         </is>
       </c>
       <c r="B321">
-        <v>4.999996299297663</v>
+        <v>5.041714308109698</v>
       </c>
       <c r="C321">
-        <v>1.3219186339887</v>
+        <v>1.075972457167668</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -41119,10 +41119,10 @@
         </is>
       </c>
       <c r="E321">
-        <v>2.978006765670232</v>
+        <v>3.318332492544584</v>
       </c>
       <c r="F321">
-        <v>8.394864404333825</v>
+        <v>7.660137500297987</v>
       </c>
       <c r="G321" s="2">
         <v>43931</v>
@@ -41155,10 +41155,10 @@
         </is>
       </c>
       <c r="B322">
-        <v>10.08334929961487</v>
+        <v>10.08334169272473</v>
       </c>
       <c r="C322">
-        <v>2.500523208622099</v>
+        <v>2.901938030108442</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -41166,10 +41166,10 @@
         </is>
       </c>
       <c r="E322">
-        <v>6.201821663419778</v>
+        <v>5.736311245567516</v>
       </c>
       <c r="F322">
-        <v>16.39420457665647</v>
+        <v>17.72459257171667</v>
       </c>
       <c r="G322" s="2">
         <v>44636</v>
@@ -41202,10 +41202,10 @@
         </is>
       </c>
       <c r="B323">
-        <v>15.58330856725544</v>
+        <v>15.58335866566931</v>
       </c>
       <c r="C323">
-        <v>3.771667109584622</v>
+        <v>4.405140226520501</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -41213,10 +41213,10 @@
         </is>
       </c>
       <c r="E323">
-        <v>9.697085703013149</v>
+        <v>8.954501757763582</v>
       </c>
       <c r="F323">
-        <v>25.04252445936825</v>
+        <v>27.11943934706884</v>
       </c>
       <c r="G323" s="2">
         <v>45971</v>
@@ -41249,10 +41249,10 @@
         </is>
       </c>
       <c r="B324">
-        <v>15.25004250866398</v>
+        <v>15.25035684249721</v>
       </c>
       <c r="C324">
-        <v>3.694693077188547</v>
+        <v>4.314198853514867</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -41260,10 +41260,10 @@
         </is>
       </c>
       <c r="E324">
-        <v>9.485206992007793</v>
+        <v>8.75955781117616</v>
       </c>
       <c r="F324">
-        <v>24.51857895268031</v>
+        <v>26.55081327584427</v>
       </c>
       <c r="G324" s="2">
         <v>46120</v>
@@ -41766,10 +41766,10 @@
         </is>
       </c>
       <c r="B335">
-        <v>3.833342244397123</v>
+        <v>3.833344517984286</v>
       </c>
       <c r="C335">
-        <v>2.255560196175116</v>
+        <v>1.401974566189374</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -41777,10 +41777,10 @@
         </is>
       </c>
       <c r="E335">
-        <v>1.209834058983658</v>
+        <v>1.871831263013666</v>
       </c>
       <c r="F335">
-        <v>12.14589112743607</v>
+        <v>7.850349806585583</v>
       </c>
       <c r="G335" s="2">
         <v>42122</v>
@@ -41813,10 +41813,10 @@
         </is>
       </c>
       <c r="B336">
-        <v>3.666675670459964</v>
+        <v>3.666657009301774</v>
       </c>
       <c r="C336">
-        <v>2.163641628159251</v>
+        <v>1.345953436144311</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -41824,10 +41824,10 @@
         </is>
       </c>
       <c r="E336">
-        <v>1.153435331533746</v>
+        <v>1.785714087997599</v>
       </c>
       <c r="F336">
-        <v>11.65605916932125</v>
+        <v>7.528850062967027</v>
       </c>
       <c r="G336" s="2">
         <v>42286</v>
@@ -41860,10 +41860,10 @@
         </is>
       </c>
       <c r="B337">
-        <v>1.363641209949282</v>
+        <v>1.363635814239609</v>
       </c>
       <c r="C337">
-        <v>0.6565323051124272</v>
+        <v>0.5926255010263267</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -41871,10 +41871,10 @@
         </is>
       </c>
       <c r="E337">
-        <v>0.5307434121866257</v>
+        <v>0.5817988249867524</v>
       </c>
       <c r="F337">
-        <v>3.503608913035511</v>
+        <v>3.196126485678726</v>
       </c>
       <c r="G337" s="2">
         <v>44481</v>
@@ -41907,10 +41907,10 @@
         </is>
       </c>
       <c r="B338">
-        <v>1.583335823862045</v>
+        <v>1.583336528915794</v>
       </c>
       <c r="C338">
-        <v>0.715140255863819</v>
+        <v>0.6424753452680491</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -41918,10 +41918,10 @@
         </is>
       </c>
       <c r="E338">
-        <v>0.6533013328137458</v>
+        <v>0.7147901459330426</v>
       </c>
       <c r="F338">
-        <v>3.837359890768238</v>
+        <v>3.507259547523131</v>
       </c>
       <c r="G338" s="2">
         <v>44896</v>
@@ -41954,10 +41954,10 @@
         </is>
       </c>
       <c r="B339">
-        <v>1.83334204328385</v>
+        <v>1.833329508038056</v>
       </c>
       <c r="C339">
-        <v>0.8133640671796978</v>
+        <v>0.727521192139984</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -41965,10 +41965,10 @@
         </is>
       </c>
       <c r="E339">
-        <v>0.7684348723042577</v>
+        <v>0.8422824190056797</v>
       </c>
       <c r="F339">
-        <v>4.374011603082707</v>
+        <v>3.990463304470797</v>
       </c>
       <c r="G339" s="2">
         <v>45261</v>
@@ -42001,10 +42001,10 @@
         </is>
       </c>
       <c r="B340">
-        <v>1.416668774734561</v>
+        <v>1.416665385008594</v>
       </c>
       <c r="C340">
-        <v>0.6495003033130121</v>
+        <v>0.5855535432846692</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -42012,10 +42012,10 @@
         </is>
       </c>
       <c r="E340">
-        <v>0.5767901667495631</v>
+        <v>0.6301416735024814</v>
       </c>
       <c r="F340">
-        <v>3.479515659252427</v>
+        <v>3.184904121523148</v>
       </c>
       <c r="G340" s="2">
         <v>45645</v>
@@ -42048,10 +42048,10 @@
         </is>
       </c>
       <c r="B341">
-        <v>4.200014098387568</v>
+        <v>4.199947151231427</v>
       </c>
       <c r="C341">
-        <v>2.692307007203703</v>
+        <v>2.362687587367094</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -42059,10 +42059,10 @@
         </is>
       </c>
       <c r="E341">
-        <v>1.195668268462438</v>
+        <v>1.394437053405109</v>
       </c>
       <c r="F341">
-        <v>14.75335499982661</v>
+        <v>12.64994789837414</v>
       </c>
       <c r="G341" s="2">
         <v>45692</v>
@@ -42095,10 +42095,10 @@
         </is>
       </c>
       <c r="B342">
-        <v>0.8823559175295516</v>
+        <v>0.8823605009004264</v>
       </c>
       <c r="C342">
-        <v>0.3675486980556258</v>
+        <v>0.3368488937810574</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -42106,10 +42106,10 @@
         </is>
       </c>
       <c r="E342">
-        <v>0.3900071573046061</v>
+        <v>0.417534505004751</v>
       </c>
       <c r="F342">
-        <v>1.996250454940617</v>
+        <v>1.864660391457689</v>
       </c>
       <c r="G342" s="2">
         <v>45974</v>
@@ -42142,10 +42142,10 @@
         </is>
       </c>
       <c r="B343">
-        <v>0.8235327030471373</v>
+        <v>0.8235329849884613</v>
       </c>
       <c r="C343">
-        <v>0.3477209889763361</v>
+        <v>0.3194858194072979</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -42153,10 +42153,10 @@
         </is>
       </c>
       <c r="E343">
-        <v>0.3599790450673627</v>
+        <v>0.3850004967249528</v>
       </c>
       <c r="F343">
-        <v>1.884015534463158</v>
+        <v>1.761573252848349</v>
       </c>
       <c r="G343" s="2">
         <v>46087</v>
@@ -42483,10 +42483,10 @@
         </is>
       </c>
       <c r="B350">
-        <v>0.799999746882683</v>
+        <v>0.7272727141114353</v>
       </c>
       <c r="C350">
-        <v>0.3999999040507734</v>
+        <v>0.2571297149529692</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -42494,10 +42494,10 @@
         </is>
       </c>
       <c r="E350">
-        <v>0.3002541684145047</v>
+        <v>0.3637073893033126</v>
       </c>
       <c r="F350">
-        <v>2.131526094681321</v>
+        <v>1.454261354723034</v>
       </c>
       <c r="G350" s="2">
         <v>42122</v>
@@ -42530,10 +42530,10 @@
         </is>
       </c>
       <c r="B351">
-        <v>6.999999870896147</v>
+        <v>7.083333392101308</v>
       </c>
       <c r="C351">
-        <v>1.080123365444299</v>
+        <v>0.7682953133303558</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -42541,10 +42541,10 @@
         </is>
       </c>
       <c r="E351">
-        <v>5.173146651424606</v>
+        <v>5.726798740681464</v>
       </c>
       <c r="F351">
-        <v>9.471990935933009</v>
+        <v>8.761196999510236</v>
       </c>
       <c r="G351" s="2">
         <v>42286</v>
@@ -42577,10 +42577,10 @@
         </is>
       </c>
       <c r="B352">
-        <v>6.249999895466288</v>
+        <v>6.249999938620112</v>
       </c>
       <c r="C352">
-        <v>1.249999901582415</v>
+        <v>1.249999893608732</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -42588,10 +42588,10 @@
         </is>
       </c>
       <c r="E352">
-        <v>4.223181164124837</v>
+        <v>4.223181215274619</v>
       </c>
       <c r="F352">
-        <v>9.249543691177044</v>
+        <v>9.249543706878633</v>
       </c>
       <c r="G352" s="2">
         <v>44481</v>
@@ -42624,10 +42624,10 @@
         </is>
       </c>
       <c r="B353">
-        <v>9.749999904719788</v>
+        <v>9.750000243968081</v>
       </c>
       <c r="C353">
-        <v>1.56124939343613</v>
+        <v>1.56124939665557</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -42635,10 +42635,10 @@
         </is>
       </c>
       <c r="E353">
-        <v>7.123661715740052</v>
+        <v>7.123662036786921</v>
       </c>
       <c r="F353">
-        <v>13.34461151236182</v>
+        <v>13.34461183959464</v>
       </c>
       <c r="G353" s="2">
         <v>44896</v>
@@ -42671,10 +42671,10 @@
         </is>
       </c>
       <c r="B354">
-        <v>6.75000026456459</v>
+        <v>6.749999890772609</v>
       </c>
       <c r="C354">
-        <v>1.299038041066337</v>
+        <v>1.299037991306498</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -42682,10 +42682,10 @@
         </is>
       </c>
       <c r="E354">
-        <v>4.629029953812713</v>
+        <v>4.629029667665272</v>
       </c>
       <c r="F354">
-        <v>9.842775705975797</v>
+        <v>9.842775224296727</v>
       </c>
       <c r="G354" s="2">
         <v>45261</v>
@@ -42718,10 +42718,10 @@
         </is>
       </c>
       <c r="B355">
-        <v>7.250000183338481</v>
+        <v>7.250000386528751</v>
       </c>
       <c r="C355">
-        <v>1.346291126857861</v>
+        <v>1.346291130371531</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -42729,10 +42729,10 @@
         </is>
       </c>
       <c r="E355">
-        <v>5.038182231581522</v>
+        <v>5.038182419388239</v>
       </c>
       <c r="F355">
-        <v>10.43283077950681</v>
+        <v>10.43283097539161</v>
       </c>
       <c r="G355" s="2">
         <v>45645</v>
@@ -42765,10 +42765,10 @@
         </is>
       </c>
       <c r="B356">
-        <v>3.499999993521308</v>
+        <v>3.499999808285787</v>
       </c>
       <c r="C356">
-        <v>0.9354142746665616</v>
+        <v>0.9354142447631232</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -42776,10 +42776,10 @@
         </is>
       </c>
       <c r="E356">
-        <v>2.072883425932914</v>
+        <v>2.072883293471891</v>
       </c>
       <c r="F356">
-        <v>5.909642482251972</v>
+        <v>5.909642234359904</v>
       </c>
       <c r="G356" s="2">
         <v>45692</v>
@@ -42812,10 +42812,10 @@
         </is>
       </c>
       <c r="B357">
-        <v>4.333333362034923</v>
+        <v>4.333333083772111</v>
       </c>
       <c r="C357">
-        <v>0.8498365252302161</v>
+        <v>0.8498364921520839</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42823,10 +42823,10 @@
         </is>
       </c>
       <c r="E357">
-        <v>2.950446584909887</v>
+        <v>2.950446366765439</v>
       </c>
       <c r="F357">
-        <v>6.364385012955047</v>
+        <v>6.364384666141176</v>
       </c>
       <c r="G357" s="2">
         <v>45974</v>
@@ -45115,10 +45115,10 @@
         </is>
       </c>
       <c r="B406">
-        <v>1.72851192977073</v>
+        <v>1.702537194707176</v>
       </c>
       <c r="C406">
-        <v>0.2683678791427884</v>
+        <v>0.1883335509126759</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -45126,10 +45126,10 @@
         </is>
       </c>
       <c r="E406">
-        <v>1.275014913290784</v>
+        <v>1.370683707447186</v>
       </c>
       <c r="F406">
-        <v>2.343308662679412</v>
+        <v>2.114735065144901</v>
       </c>
       <c r="G406" s="2">
         <v>44480</v>
@@ -45162,10 +45162,10 @@
         </is>
       </c>
       <c r="B407">
-        <v>1.295548437268859</v>
+        <v>1.314453749567091</v>
       </c>
       <c r="C407">
-        <v>0.23233849438837</v>
+        <v>0.1654824885451146</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -45173,10 +45173,10 @@
         </is>
       </c>
       <c r="E407">
-        <v>0.9115963168174707</v>
+        <v>1.027031402468279</v>
       </c>
       <c r="F407">
-        <v>1.841216032080415</v>
+        <v>1.682313369969571</v>
       </c>
       <c r="G407" s="2">
         <v>44691</v>
@@ -45209,10 +45209,10 @@
         </is>
       </c>
       <c r="B408">
-        <v>0.4595123065097884</v>
+        <v>0.459512794974865</v>
       </c>
       <c r="C408">
-        <v>0.1413463569273271</v>
+        <v>0.1413464446050043</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -45220,10 +45220,10 @@
         </is>
       </c>
       <c r="E408">
-        <v>0.2514588147943693</v>
+        <v>0.2514591492114118</v>
       </c>
       <c r="F408">
-        <v>0.8397063352367073</v>
+        <v>0.8397070037331923</v>
       </c>
       <c r="G408" s="2">
         <v>45376</v>
@@ -45256,10 +45256,10 @@
         </is>
       </c>
       <c r="B409">
-        <v>1.575301837450851</v>
+        <v>1.575302158451272</v>
       </c>
       <c r="C409">
-        <v>0.2561991223362214</v>
+        <v>0.256198346152994</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -45267,10 +45267,10 @@
         </is>
       </c>
       <c r="E409">
-        <v>1.145324804210561</v>
+        <v>1.145326218044208</v>
       </c>
       <c r="F409">
-        <v>2.166700546389116</v>
+        <v>2.166698754752029</v>
       </c>
       <c r="G409" s="2">
         <v>45610</v>
@@ -45303,10 +45303,10 @@
         </is>
       </c>
       <c r="B410">
-        <v>1.473586548008222</v>
+        <v>1.473586418653894</v>
       </c>
       <c r="C410">
-        <v>0.2477890824423105</v>
+        <v>0.247789096493951</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -45314,10 +45314,10 @@
         </is>
       </c>
       <c r="E410">
-        <v>1.059846400697915</v>
+        <v>1.059846257192264</v>
       </c>
       <c r="F410">
-        <v>2.048841523678216</v>
+        <v>2.048841441393411</v>
       </c>
       <c r="G410" s="2">
         <v>45799</v>
@@ -45350,10 +45350,10 @@
         </is>
       </c>
       <c r="B411">
-        <v>1.446739012418593</v>
+        <v>1.446739648575672</v>
       </c>
       <c r="C411">
-        <v>0.2564387906631546</v>
+        <v>0.2564388729745114</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -45361,10 +45361,10 @@
         </is>
       </c>
       <c r="E411">
-        <v>1.022144247455022</v>
+        <v>1.022144739074821</v>
       </c>
       <c r="F411">
-        <v>2.047708799678029</v>
+        <v>2.047709615621908</v>
       </c>
       <c r="G411" s="2">
         <v>45972</v>
@@ -45929,10 +45929,10 @@
         </is>
       </c>
       <c r="B423">
-        <v>1.835060985039405</v>
+        <v>1.835061057229653</v>
       </c>
       <c r="C423">
-        <v>0.5530311469963143</v>
+        <v>0.5530306713607175</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -45940,10 +45940,10 @@
         </is>
       </c>
       <c r="E423">
-        <v>1.016539926589614</v>
+        <v>1.016540506612995</v>
       </c>
       <c r="F423">
-        <v>3.31265770358006</v>
+        <v>3.312656074061223</v>
       </c>
       <c r="G423" s="2">
         <v>42388</v>
@@ -45976,10 +45976,10 @@
         </is>
       </c>
       <c r="B424">
-        <v>2.03413389207243</v>
+        <v>2.443331537302116</v>
       </c>
       <c r="C424">
-        <v>0.4117172953294526</v>
+        <v>0.4512326783878044</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -45987,10 +45987,10 @@
         </is>
       </c>
       <c r="E424">
-        <v>1.368020945074262</v>
+        <v>1.701308701497783</v>
       </c>
       <c r="F424">
-        <v>3.024588699300302</v>
+        <v>3.508986344406176</v>
       </c>
       <c r="G424" s="2">
         <v>42791</v>
@@ -46023,10 +46023,10 @@
         </is>
       </c>
       <c r="B425">
-        <v>1.77665744351763</v>
+        <v>2.100371866770162</v>
       </c>
       <c r="C425">
-        <v>0.4018884020091453</v>
+        <v>0.3089845200015919</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -46034,10 +46034,10 @@
         </is>
       </c>
       <c r="E425">
-        <v>1.140401668186413</v>
+        <v>1.574259830271313</v>
       </c>
       <c r="F425">
-        <v>2.767894645950861</v>
+        <v>2.80230867477529</v>
       </c>
       <c r="G425" s="2">
         <v>43512</v>
@@ -46070,10 +46070,10 @@
         </is>
       </c>
       <c r="B426">
-        <v>1.612370451404255</v>
+        <v>1.606750489186629</v>
       </c>
       <c r="C426">
-        <v>0.3828565120064966</v>
+        <v>0.2702482221426457</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -46081,10 +46081,10 @@
         </is>
       </c>
       <c r="E426">
-        <v>1.012389130640253</v>
+        <v>1.15552716837147</v>
       </c>
       <c r="F426">
-        <v>2.567924125101423</v>
+        <v>2.234172596858877</v>
       </c>
       <c r="G426" s="2">
         <v>43931</v>
@@ -46117,10 +46117,10 @@
         </is>
       </c>
       <c r="B427">
-        <v>2.0341338972575</v>
+        <v>2.443331524543493</v>
       </c>
       <c r="C427">
-        <v>0.4117174517673044</v>
+        <v>0.4512326772092866</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -46128,10 +46128,10 @@
         </is>
       </c>
       <c r="E427">
-        <v>1.368020743737889</v>
+        <v>1.701308691006567</v>
       </c>
       <c r="F427">
-        <v>3.024589159859088</v>
+        <v>3.508986329397989</v>
       </c>
       <c r="G427" s="2">
         <v>44636</v>
@@ -46164,10 +46164,10 @@
         </is>
       </c>
       <c r="B428">
-        <v>2.45768246680554</v>
+        <v>2.457682543990867</v>
       </c>
       <c r="C428">
-        <v>0.4525558979875388</v>
+        <v>0.4525559049439877</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -46175,10 +46175,10 @@
         </is>
       </c>
       <c r="E428">
-        <v>1.713113453240069</v>
+        <v>1.713113516955222</v>
       </c>
       <c r="F428">
-        <v>3.525862864610235</v>
+        <v>3.525862954938847</v>
       </c>
       <c r="G428" s="2">
         <v>45971</v>
@@ -46211,10 +46211,10 @@
         </is>
       </c>
       <c r="B429">
-        <v>2.300662163717895</v>
+        <v>2.300662206454732</v>
       </c>
       <c r="C429">
-        <v>0.4378606465272758</v>
+        <v>0.4378605038530862</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -46222,10 +46222,10 @@
         </is>
       </c>
       <c r="E429">
-        <v>1.584355667682215</v>
+        <v>1.584355900663381</v>
       </c>
       <c r="F429">
-        <v>3.340819551778046</v>
+        <v>3.340819184624439</v>
       </c>
       <c r="G429" s="2">
         <v>46120</v>
@@ -46775,10 +46775,10 @@
         </is>
       </c>
       <c r="B441">
-        <v>1.304647119621589</v>
+        <v>1.300400869132253</v>
       </c>
       <c r="C441">
-        <v>0.4663058555208302</v>
+        <v>0.3291910172425693</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -46786,10 +46786,10 @@
         </is>
       </c>
       <c r="E441">
-        <v>0.6475261824305387</v>
+        <v>0.791770207444372</v>
       </c>
       <c r="F441">
-        <v>2.628625919569663</v>
+        <v>2.135774249321863</v>
       </c>
       <c r="G441" s="2">
         <v>42122</v>
@@ -46822,10 +46822,10 @@
         </is>
       </c>
       <c r="B442">
-        <v>0.3762386759516569</v>
+        <v>0.3762387337630132</v>
       </c>
       <c r="C442">
-        <v>0.2504125308065578</v>
+        <v>0.177068413303501</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -46833,10 +46833,10 @@
         </is>
       </c>
       <c r="E442">
-        <v>0.1020776550864304</v>
+        <v>0.1495768494664819</v>
       </c>
       <c r="F442">
-        <v>1.386743662577271</v>
+        <v>0.9463736219107634</v>
       </c>
       <c r="G442" s="2">
         <v>42286</v>
@@ -46869,10 +46869,10 @@
         </is>
       </c>
       <c r="B443">
-        <v>1.364754499060681</v>
+        <v>1.364754612890914</v>
       </c>
       <c r="C443">
-        <v>0.3522336872897324</v>
+        <v>0.3522337097173175</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -46880,10 +46880,10 @@
         </is>
       </c>
       <c r="E443">
-        <v>0.8229345757932219</v>
+        <v>0.822934652647041</v>
       </c>
       <c r="F443">
-        <v>2.263308527182812</v>
+        <v>2.263308693364604</v>
       </c>
       <c r="G443" s="2">
         <v>44481</v>
@@ -46916,10 +46916,10 @@
         </is>
       </c>
       <c r="B444">
-        <v>1.317421105347096</v>
+        <v>1.317421194985015</v>
       </c>
       <c r="C444">
-        <v>0.3313383076022951</v>
+        <v>0.3313383259011964</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -46927,10 +46927,10 @@
         </is>
       </c>
       <c r="E444">
-        <v>0.8047166192635672</v>
+        <v>0.8047166790995604</v>
       </c>
       <c r="F444">
-        <v>2.15678206124572</v>
+        <v>2.156782194371562</v>
       </c>
       <c r="G444" s="2">
         <v>44896</v>
@@ -46963,10 +46963,10 @@
         </is>
       </c>
       <c r="B445">
-        <v>1.341132244450209</v>
+        <v>1.34113234449351</v>
       </c>
       <c r="C445">
-        <v>0.3343067483970907</v>
+        <v>0.3343067680833415</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -46974,10 +46974,10 @@
         </is>
       </c>
       <c r="E445">
-        <v>0.8227935397781954</v>
+        <v>0.8227936074703905</v>
       </c>
       <c r="F445">
-        <v>2.186010961618541</v>
+        <v>2.186011107908838</v>
       </c>
       <c r="G445" s="2">
         <v>45261</v>
@@ -47010,10 +47010,10 @@
         </is>
       </c>
       <c r="B446">
-        <v>0.9983383169350354</v>
+        <v>0.9983383975171339</v>
       </c>
       <c r="C446">
-        <v>0.28843566756168</v>
+        <v>0.2884351840936168</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -47021,10 +47021,10 @@
         </is>
       </c>
       <c r="E446">
-        <v>0.5666986842676742</v>
+        <v>0.5666992937978065</v>
       </c>
       <c r="F446">
-        <v>1.75874661919968</v>
+        <v>1.758745011446381</v>
       </c>
       <c r="G446" s="2">
         <v>45645</v>
@@ -47057,10 +47057,10 @@
         </is>
       </c>
       <c r="B447">
-        <v>1.914628663005218</v>
+        <v>1.914629220509521</v>
       </c>
       <c r="C447">
-        <v>0.6188098820704762</v>
+        <v>0.6188099912367954</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -47068,10 +47068,10 @@
         </is>
       </c>
       <c r="E447">
-        <v>1.016191068716193</v>
+        <v>1.016191438490525</v>
       </c>
       <c r="F447">
-        <v>3.607395331502322</v>
+        <v>3.60739611964668</v>
       </c>
       <c r="G447" s="2">
         <v>45692</v>
@@ -47104,10 +47104,10 @@
         </is>
       </c>
       <c r="B448">
-        <v>0.7268102440565761</v>
+        <v>0.7268102971826599</v>
       </c>
       <c r="C448">
-        <v>0.2067692837451183</v>
+        <v>0.2067692937212426</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -47115,10 +47115,10 @@
         </is>
       </c>
       <c r="E448">
-        <v>0.4161633589548004</v>
+        <v>0.4161633951399366</v>
       </c>
       <c r="F448">
-        <v>1.269340799709744</v>
+        <v>1.269340874905923</v>
       </c>
       <c r="G448" s="2">
         <v>45974</v>
@@ -47151,10 +47151,10 @@
         </is>
       </c>
       <c r="B449">
-        <v>1.152353685821571</v>
+        <v>1.152353748981535</v>
       </c>
       <c r="C449">
-        <v>0.2603564859551816</v>
+        <v>0.2603564979199823</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -47162,10 +47162,10 @@
         </is>
       </c>
       <c r="E449">
-        <v>0.7400651890074325</v>
+        <v>0.7400652324717004</v>
       </c>
       <c r="F449">
-        <v>1.794327090303423</v>
+        <v>1.794327181614463</v>
       </c>
       <c r="G449" s="2">
         <v>46087</v>
@@ -47490,10 +47490,10 @@
         </is>
       </c>
       <c r="B456">
-        <v>0.5090474242132167</v>
+        <v>0.5090537647273115</v>
       </c>
       <c r="C456">
-        <v>0.3190759611077935</v>
+        <v>0.2256222002087969</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -47501,10 +47501,10 @@
         </is>
       </c>
       <c r="E456">
-        <v>0.1490104398563445</v>
+        <v>0.2135478113155919</v>
       </c>
       <c r="F456">
-        <v>1.739000840128569</v>
+        <v>1.213478769867067</v>
       </c>
       <c r="G456" s="2">
         <v>42122</v>
@@ -47537,10 +47537,10 @@
         </is>
       </c>
       <c r="B457">
-        <v>1.609347873018546</v>
+        <v>1.614931167184502</v>
       </c>
       <c r="C457">
-        <v>0.5179040546422152</v>
+        <v>0.366848202328339</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -47548,10 +47548,10 @@
         </is>
       </c>
       <c r="E457">
-        <v>0.8564950537463927</v>
+        <v>1.034653288920103</v>
       </c>
       <c r="F457">
-        <v>3.023952753796306</v>
+        <v>2.520653732677876</v>
       </c>
       <c r="G457" s="2">
         <v>42286</v>
@@ -47584,10 +47584,10 @@
         </is>
       </c>
       <c r="B458">
-        <v>1.625869522081584</v>
+        <v>1.625866774825172</v>
       </c>
       <c r="C458">
-        <v>0.6375475136093861</v>
+        <v>0.6375474200128176</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -47595,10 +47595,10 @@
         </is>
       </c>
       <c r="E458">
-        <v>0.7538874099678528</v>
+        <v>0.7538852421464146</v>
       </c>
       <c r="F458">
-        <v>3.506427707748191</v>
+        <v>3.506425940842353</v>
       </c>
       <c r="G458" s="2">
         <v>44481</v>
@@ -47631,10 +47631,10 @@
         </is>
       </c>
       <c r="B459">
-        <v>1.908019835156834</v>
+        <v>1.90801663096774</v>
       </c>
       <c r="C459">
-        <v>0.6906550541537662</v>
+        <v>0.6906548950521657</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -47642,10 +47642,10 @@
         </is>
       </c>
       <c r="E459">
-        <v>0.9385758955037363</v>
+        <v>0.938573354492961</v>
       </c>
       <c r="F459">
-        <v>3.878790952113705</v>
+        <v>3.878788425669916</v>
       </c>
       <c r="G459" s="2">
         <v>44896</v>
@@ -47678,10 +47678,10 @@
         </is>
       </c>
       <c r="B460">
-        <v>1.271700716514305</v>
+        <v>1.271704217732224</v>
       </c>
       <c r="C460">
-        <v>0.5638485032212387</v>
+        <v>0.5638493292513272</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -47689,10 +47689,10 @@
         </is>
       </c>
       <c r="E460">
-        <v>0.5333078109125666</v>
+        <v>0.5333098762173869</v>
       </c>
       <c r="F460">
-        <v>3.032437701626185</v>
+        <v>3.032442655794201</v>
       </c>
       <c r="G460" s="2">
         <v>45261</v>
@@ -47725,10 +47725,10 @@
         </is>
       </c>
       <c r="B461">
-        <v>1.882563733419157</v>
+        <v>1.882562697106324</v>
       </c>
       <c r="C461">
-        <v>0.6860327057945818</v>
+        <v>0.6860325793222845</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -47736,10 +47736,10 @@
         </is>
       </c>
       <c r="E461">
-        <v>0.9216369373891615</v>
+        <v>0.9216361890374286</v>
       </c>
       <c r="F461">
-        <v>3.845382131085962</v>
+        <v>3.845381019855234</v>
       </c>
       <c r="G461" s="2">
         <v>45645</v>
@@ -47772,10 +47772,10 @@
         </is>
       </c>
       <c r="B462">
-        <v>1.54504755656838</v>
+        <v>1.545047631090591</v>
       </c>
       <c r="C462">
-        <v>0.6214996679241245</v>
+        <v>0.6214997385606005</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -47783,10 +47783,10 @@
         </is>
       </c>
       <c r="E462">
-        <v>0.7023339598094299</v>
+        <v>0.702333957459591</v>
       </c>
       <c r="F462">
-        <v>3.398912894238593</v>
+        <v>3.398913233489771</v>
       </c>
       <c r="G462" s="2">
         <v>45692</v>
@@ -47819,10 +47819,10 @@
         </is>
       </c>
       <c r="B463">
-        <v>1.623169211046457</v>
+        <v>1.623168284064862</v>
       </c>
       <c r="C463">
-        <v>0.520123221866157</v>
+        <v>0.5201231200878845</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -47830,10 +47830,10 @@
         </is>
       </c>
       <c r="E463">
-        <v>0.8661786179370543</v>
+        <v>0.8661779190439842</v>
       </c>
       <c r="F463">
-        <v>3.041726305786784</v>
+        <v>3.041725285841973</v>
       </c>
       <c r="G463" s="2">
         <v>45974</v>
@@ -53657,10 +53657,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>30.01034049272654</v>
+        <v>30.23235118661874</v>
       </c>
       <c r="C19">
-        <v>4.654023981342773</v>
+        <v>4.014266621010267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -53668,10 +53668,10 @@
         </is>
       </c>
       <c r="E19">
-        <v>22.14450666813065</v>
+        <v>23.30499208214039</v>
       </c>
       <c r="F19">
-        <v>40.67015580823544</v>
+        <v>39.21885298435614</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -53709,10 +53709,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>12.47060788231319</v>
+        <v>12.1009973584268</v>
       </c>
       <c r="C20">
-        <v>2.022918043980451</v>
+        <v>1.664001161934485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -53720,10 +53720,10 @@
         </is>
       </c>
       <c r="E20">
-        <v>9.074236114912571</v>
+        <v>9.242148306378354</v>
       </c>
       <c r="F20">
-        <v>17.13819863016758</v>
+        <v>15.84416655244459</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -53761,10 +53761,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>238.6139996396264</v>
+        <v>239.623449032107</v>
       </c>
       <c r="C21">
-        <v>36.4504590483795</v>
+        <v>38.44001878467662</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -53772,10 +53772,10 @@
         </is>
       </c>
       <c r="E21">
-        <v>176.8752804834931</v>
+        <v>174.9769713498176</v>
       </c>
       <c r="F21">
-        <v>321.9027592119253</v>
+        <v>328.154024401581</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -53813,10 +53813,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>94.81998810326705</v>
+        <v>95.18387400913079</v>
       </c>
       <c r="C22">
-        <v>14.37603151690825</v>
+        <v>15.15496023013078</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -53824,10 +53824,10 @@
         </is>
       </c>
       <c r="E22">
-        <v>70.44430374385782</v>
+        <v>69.66858667219746</v>
       </c>
       <c r="F22">
-        <v>127.6303358266584</v>
+        <v>130.0438304284079</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -53865,10 +53865,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>24.99697789905527</v>
+        <v>24.88675833430699</v>
       </c>
       <c r="C23">
-        <v>3.906221239741933</v>
+        <v>4.064230660864057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -53876,10 +53876,10 @@
         </is>
       </c>
       <c r="E23">
-        <v>18.40230247767273</v>
+        <v>18.07005566555643</v>
       </c>
       <c r="F23">
-        <v>33.95493063131521</v>
+        <v>34.27497689289086</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -53917,10 +53917,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>54.27545784153744</v>
+        <v>54.72133329094129</v>
       </c>
       <c r="C24">
-        <v>8.566213652785782</v>
+        <v>9.041383102304323</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -53928,10 +53928,10 @@
         </is>
       </c>
       <c r="E24">
-        <v>39.83452472450735</v>
+        <v>39.58367435614128</v>
       </c>
       <c r="F24">
-        <v>73.95156197498574</v>
+        <v>75.64796259682507</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -54697,10 +54697,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>72.66666650987288</v>
+        <v>72.6666677747171</v>
       </c>
       <c r="C39">
-        <v>16.95952259657449</v>
+        <v>19.0795035683906</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -54708,10 +54708,10 @@
         </is>
       </c>
       <c r="E39">
-        <v>45.99123534210118</v>
+        <v>43.43522644460637</v>
       </c>
       <c r="F39">
-        <v>114.8141462689364</v>
+        <v>121.5705554618288</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -54749,10 +54749,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>81.58333365354626</v>
+        <v>140.416667078881</v>
       </c>
       <c r="C40">
-        <v>13.4326962038166</v>
+        <v>25.85957988848263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -54760,10 +54760,10 @@
         </is>
       </c>
       <c r="E40">
-        <v>59.08144519221874</v>
+        <v>97.872048348226</v>
       </c>
       <c r="F40">
-        <v>112.655340578948</v>
+        <v>201.4552747827382</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -54801,10 +54801,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>54.36363633912688</v>
+        <v>94.90909100838824</v>
       </c>
       <c r="C41">
-        <v>9.436761026501172</v>
+        <v>12.96296072375452</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -54812,10 +54812,10 @@
         </is>
       </c>
       <c r="E41">
-        <v>38.68582903578757</v>
+        <v>72.61865856520571</v>
       </c>
       <c r="F41">
-        <v>76.3950270596203</v>
+        <v>124.0416131888515</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -54853,10 +54853,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>42.00000000738343</v>
+        <v>42.04166676041796</v>
       </c>
       <c r="C42">
-        <v>7.037012066925351</v>
+        <v>5.585751396784186</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -54864,10 +54864,10 @@
         </is>
       </c>
       <c r="E42">
-        <v>30.24351424531661</v>
+        <v>32.40315915096202</v>
       </c>
       <c r="F42">
-        <v>58.32655511894998</v>
+        <v>54.54720435620108</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -54905,10 +54905,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>81.58333322764392</v>
+        <v>140.4166671208178</v>
       </c>
       <c r="C43">
-        <v>13.43269610125514</v>
+        <v>25.85957989994495</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -54916,10 +54916,10 @@
         </is>
       </c>
       <c r="E43">
-        <v>59.08144492982637</v>
+        <v>97.8720483723483</v>
       </c>
       <c r="F43">
-        <v>112.6553399030478</v>
+        <v>201.4552748534192</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -54957,10 +54957,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>119.9999998706312</v>
+        <v>120.0000001615971</v>
       </c>
       <c r="C44">
-        <v>19.63847472628805</v>
+        <v>22.13245383657021</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -54968,10 +54968,10 @@
         </is>
       </c>
       <c r="E44">
-        <v>87.072045187518</v>
+        <v>83.59649899852822</v>
       </c>
       <c r="F44">
-        <v>165.3802886786421</v>
+        <v>172.2560180305736</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -55009,10 +55009,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>105.6666666816414</v>
+        <v>105.6666666154595</v>
       </c>
       <c r="C45">
-        <v>17.32315220965586</v>
+        <v>19.51582050139671</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -55020,10 +55020,10 @@
         </is>
       </c>
       <c r="E45">
-        <v>76.62857453145409</v>
+        <v>73.57455261702012</v>
       </c>
       <c r="F45">
-        <v>145.7086278308098</v>
+        <v>151.7568783835152</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -55633,10 +55633,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>121.5000075294275</v>
+        <v>121.8333333837448</v>
       </c>
       <c r="C57">
-        <v>38.25398733758571</v>
+        <v>25.69884009337505</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -55644,10 +55644,10 @@
         </is>
       </c>
       <c r="E57">
-        <v>65.55072974896251</v>
+        <v>80.57836423457621</v>
       </c>
       <c r="F57">
-        <v>225.2034704447296</v>
+        <v>184.2102562442613</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -55685,10 +55685,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>300.1666667897181</v>
+        <v>300.166666792912</v>
       </c>
       <c r="C58">
-        <v>94.11673913264148</v>
+        <v>63.02567014171443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -55696,10 +55696,10 @@
         </is>
       </c>
       <c r="E58">
-        <v>162.3565040131411</v>
+        <v>198.90083021785</v>
       </c>
       <c r="F58">
-        <v>554.9517612448526</v>
+        <v>452.9897022294136</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -55737,10 +55737,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>31.45454569673344</v>
+        <v>31.45454545058989</v>
       </c>
       <c r="C59">
-        <v>7.457601626412768</v>
+        <v>7.081267128438556</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -55748,10 +55748,10 @@
         </is>
       </c>
       <c r="E59">
-        <v>19.76381904921291</v>
+        <v>20.23275266631001</v>
       </c>
       <c r="F59">
-        <v>50.06059013818459</v>
+        <v>48.90033728088205</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -55789,10 +55789,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>51.24999652887922</v>
+        <v>51.24999994481257</v>
       </c>
       <c r="C60">
-        <v>11.51753434796849</v>
+        <v>10.92422786485304</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -55800,10 +55800,10 @@
         </is>
       </c>
       <c r="E60">
-        <v>32.99144067554241</v>
+        <v>33.74857481442027</v>
       </c>
       <c r="F60">
-        <v>79.61344186334011</v>
+        <v>77.82736037851873</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -55841,10 +55841,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>21.25000085726048</v>
+        <v>21.25000006124278</v>
       </c>
       <c r="C61">
-        <v>4.882888036922294</v>
+        <v>4.642572678647519</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -55852,10 +55852,10 @@
         </is>
       </c>
       <c r="E61">
-        <v>13.54463618420475</v>
+        <v>13.84820624778886</v>
       </c>
       <c r="F61">
-        <v>33.33884574619777</v>
+        <v>32.60801395667536</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -55893,10 +55893,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>33.00000106682587</v>
+        <v>32.99999997977276</v>
       </c>
       <c r="C62">
-        <v>7.481900806471854</v>
+        <v>7.103404242176628</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -55904,10 +55904,10 @@
         </is>
       </c>
       <c r="E62">
-        <v>21.16049946013993</v>
+        <v>21.64157324325238</v>
       </c>
       <c r="F62">
-        <v>51.46381693219765</v>
+        <v>50.31981669837896</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -55945,10 +55945,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>19.39999817667932</v>
+        <v>19.40000002445211</v>
       </c>
       <c r="C63">
-        <v>6.9303896224266</v>
+        <v>6.591766439311127</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -55956,10 +55956,10 @@
         </is>
       </c>
       <c r="E63">
-        <v>9.632107782092971</v>
+        <v>9.967332805132667</v>
       </c>
       <c r="F63">
-        <v>39.07347568876365</v>
+        <v>37.75934929702915</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -55997,10 +55997,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>117.6470614023404</v>
+        <v>117.6470585095441</v>
       </c>
       <c r="C64">
-        <v>22.01055681675339</v>
+        <v>20.85515265968233</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -56008,10 +56008,10 @@
         </is>
       </c>
       <c r="E64">
-        <v>81.53236084330871</v>
+        <v>83.11695006777632</v>
       </c>
       <c r="F64">
-        <v>169.7587425832765</v>
+        <v>166.5223563263789</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -56049,10 +56049,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>27.58823565639795</v>
+        <v>27.58823533339308</v>
       </c>
       <c r="C65">
-        <v>5.280446199463094</v>
+        <v>5.015934499281956</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -56060,10 +56060,10 @@
         </is>
       </c>
       <c r="E65">
-        <v>18.95842109598947</v>
+        <v>19.31805268328901</v>
       </c>
       <c r="F65">
-        <v>40.14631507441067</v>
+        <v>39.39893638809016</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -56678,10 +56678,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>72.2000008454764</v>
+        <v>65.6363638575984</v>
       </c>
       <c r="C77">
-        <v>21.95830078576601</v>
+        <v>15.19733584067892</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -56689,10 +56689,10 @@
         </is>
       </c>
       <c r="E77">
-        <v>39.77955560159095</v>
+        <v>41.69257389509855</v>
       </c>
       <c r="F77">
-        <v>131.0431965177185</v>
+        <v>103.3309258211454</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -56730,10 +56730,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>61.83333371381011</v>
+        <v>61.91666708856197</v>
       </c>
       <c r="C78">
-        <v>17.21001005986812</v>
+        <v>13.73640254412281</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -56741,10 +56741,10 @@
         </is>
       </c>
       <c r="E78">
-        <v>35.83509712766735</v>
+        <v>40.08352407420551</v>
       </c>
       <c r="F78">
-        <v>106.6931992549697</v>
+        <v>95.64213107257329</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -56782,10 +56782,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>25.25000033987898</v>
+        <v>25.24999924267759</v>
       </c>
       <c r="C79">
-        <v>8.821557247163714</v>
+        <v>9.893349710224271</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -56793,10 +56793,10 @@
         </is>
       </c>
       <c r="E79">
-        <v>12.73146256953327</v>
+        <v>11.71513021472424</v>
       </c>
       <c r="F79">
-        <v>50.07771209959748</v>
+        <v>54.42214043458896</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -56834,10 +56834,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>46.25000038816111</v>
+        <v>46.25000000998332</v>
       </c>
       <c r="C80">
-        <v>15.85793948225595</v>
+        <v>17.85418157751537</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -56845,10 +56845,10 @@
         </is>
       </c>
       <c r="E80">
-        <v>23.61873060837816</v>
+        <v>21.70286121513126</v>
       </c>
       <c r="F80">
-        <v>90.5663632551922</v>
+        <v>98.56131317063851</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -56886,10 +56886,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>106.7500006755762</v>
+        <v>106.7499989018991</v>
       </c>
       <c r="C81">
-        <v>36.12179986862454</v>
+        <v>40.78361055270997</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -56897,10 +56897,10 @@
         </is>
       </c>
       <c r="E81">
-        <v>54.9971803438188</v>
+        <v>50.48567136379341</v>
       </c>
       <c r="F81">
-        <v>207.202670627755</v>
+        <v>225.7187427189087</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -56938,10 +56938,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>27.00000023968958</v>
+        <v>27.00000089371809</v>
       </c>
       <c r="C82">
-        <v>9.408122336812447</v>
+        <v>10.55689438918133</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -56949,10 +56949,10 @@
         </is>
       </c>
       <c r="E82">
-        <v>13.6384012977624</v>
+        <v>12.54721430158938</v>
       </c>
       <c r="F82">
-        <v>53.45201369480465</v>
+        <v>58.10054971073808</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -56990,10 +56990,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>19.75000030878898</v>
+        <v>19.75000017740724</v>
       </c>
       <c r="C83">
-        <v>6.977528864120881</v>
+        <v>7.807544999995432</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -57001,10 +57001,10 @@
         </is>
       </c>
       <c r="E83">
-        <v>9.881978496582255</v>
+        <v>9.100624393950632</v>
       </c>
       <c r="F83">
-        <v>39.47210696036935</v>
+        <v>42.86107085870597</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -57042,10 +57042,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>28.16666698450187</v>
+        <v>28.16666675711908</v>
       </c>
       <c r="C84">
-        <v>8.000958692479559</v>
+        <v>8.980836391165729</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -57053,10 +57053,10 @@
         </is>
       </c>
       <c r="E84">
-        <v>16.1415451395963</v>
+        <v>15.07762806347348</v>
       </c>
       <c r="F84">
-        <v>49.15025929392966</v>
+        <v>52.61842995905737</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -60994,10 +60994,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>8.62500210862402</v>
+        <v>8.437499710853457</v>
       </c>
       <c r="C160">
-        <v>0.5994789981941818</v>
+        <v>0.4192627721791152</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -61005,10 +61005,10 @@
         </is>
       </c>
       <c r="E160">
-        <v>7.526561622079332</v>
+        <v>7.654506956967564</v>
       </c>
       <c r="F160">
-        <v>9.883751055135477</v>
+        <v>9.300586147596317</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -61046,10 +61046,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>4.62499974348065</v>
+        <v>4.66666665716849</v>
       </c>
       <c r="C161">
-        <v>0.4389855378094189</v>
+        <v>0.3118047956966244</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -61057,10 +61057,10 @@
         </is>
       </c>
       <c r="E161">
-        <v>3.839894035816452</v>
+        <v>4.093864669326385</v>
       </c>
       <c r="F161">
-        <v>5.570628363094381</v>
+        <v>5.319613482170015</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -61098,10 +61098,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>5.91304343244065</v>
+        <v>5.913043536255042</v>
       </c>
       <c r="C162">
-        <v>0.5070392709661709</v>
+        <v>0.5070393261760689</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -61109,10 +61109,10 @@
         </is>
       </c>
       <c r="E162">
-        <v>4.998286449772372</v>
+        <v>4.998286460805716</v>
       </c>
       <c r="F162">
-        <v>6.995213856845241</v>
+        <v>6.995214087031616</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -61150,10 +61150,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>7.833333184725589</v>
+        <v>7.833333317404297</v>
       </c>
       <c r="C163">
-        <v>0.5713045268289471</v>
+        <v>0.571304591878986</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -61161,10 +61161,10 @@
         </is>
       </c>
       <c r="E163">
-        <v>6.789946427544199</v>
+        <v>6.789946448476369</v>
       </c>
       <c r="F163">
-        <v>9.037053449200238</v>
+        <v>9.037053727474587</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -61202,10 +61202,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>5.749999681932471</v>
+        <v>5.750000043157792</v>
       </c>
       <c r="C164">
-        <v>0.4894724696146333</v>
+        <v>0.4894725337729151</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -61213,10 +61213,10 @@
         </is>
       </c>
       <c r="E164">
-        <v>4.866410434427307</v>
+        <v>4.866410684726183</v>
       </c>
       <c r="F164">
-        <v>6.794021340313523</v>
+        <v>6.794021844495218</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -61254,10 +61254,10 @@
         </is>
       </c>
       <c r="B165">
-        <v>7.090908830885652</v>
+        <v>7.090909167977973</v>
       </c>
       <c r="C165">
-        <v>0.5677270598709199</v>
+        <v>0.5677271322000909</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -61265,10 +61265,10 @@
         </is>
       </c>
       <c r="E165">
-        <v>6.061097036490862</v>
+        <v>6.061097248668049</v>
       </c>
       <c r="F165">
-        <v>8.295690985512229</v>
+        <v>8.295691483842061</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -62034,10 +62034,10 @@
         </is>
       </c>
       <c r="B180">
-        <v>12.00009987628843</v>
+        <v>11.99992680727669</v>
       </c>
       <c r="C180">
-        <v>2.275457828648887</v>
+        <v>2.5425192439862</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -62045,10 +62045,10 @@
         </is>
       </c>
       <c r="E180">
-        <v>8.275230561621575</v>
+        <v>7.921871711467497</v>
       </c>
       <c r="F180">
-        <v>17.40161751006</v>
+        <v>18.17730059571017</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -62086,10 +62086,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>15.50007919959341</v>
+        <v>21.00000360778737</v>
       </c>
       <c r="C181">
-        <v>1.985568542282049</v>
+        <v>2.930233075740083</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -62097,10 +62097,10 @@
         </is>
       </c>
       <c r="E181">
-        <v>12.05853472761369</v>
+        <v>15.97522782517282</v>
       </c>
       <c r="F181">
-        <v>19.92385149776922</v>
+        <v>27.60524959976976</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -62138,10 +62138,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>11.81820355049037</v>
+        <v>16.18182154038975</v>
       </c>
       <c r="C182">
-        <v>1.659972859253448</v>
+        <v>1.71744543170389</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -62149,10 +62149,10 @@
         </is>
       </c>
       <c r="E182">
-        <v>8.974134249649335</v>
+        <v>13.1427356630544</v>
       </c>
       <c r="F182">
-        <v>15.56361107103793</v>
+        <v>19.92365631313069</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -62190,10 +62190,10 @@
         </is>
       </c>
       <c r="B183">
-        <v>7.749981221509349</v>
+        <v>7.74999727301975</v>
       </c>
       <c r="C183">
-        <v>1.143905215186859</v>
+        <v>0.8879484179052353</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -62201,10 +62201,10 @@
         </is>
       </c>
       <c r="E183">
-        <v>5.803131678098926</v>
+        <v>6.191216039585557</v>
       </c>
       <c r="F183">
-        <v>10.34996485784096</v>
+        <v>9.701237583664453</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -62242,10 +62242,10 @@
         </is>
       </c>
       <c r="B184">
-        <v>15.50004076660232</v>
+        <v>21.00000362806055</v>
       </c>
       <c r="C184">
-        <v>1.985562770332504</v>
+        <v>2.930233079407215</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -62253,10 +62253,10 @@
         </is>
       </c>
       <c r="E184">
-        <v>12.05850612208139</v>
+        <v>15.97522783934521</v>
       </c>
       <c r="F184">
-        <v>19.92379995780643</v>
+        <v>27.60524962857944</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -62294,10 +62294,10 @@
         </is>
       </c>
       <c r="B185">
-        <v>21.08347122984614</v>
+        <v>21.08331447885612</v>
       </c>
       <c r="C185">
-        <v>2.580981232981866</v>
+        <v>2.940671715193388</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -62305,10 +62305,10 @@
         </is>
       </c>
       <c r="E185">
-        <v>16.58594942221317</v>
+        <v>16.04037310257978</v>
       </c>
       <c r="F185">
-        <v>26.80056159488974</v>
+        <v>27.71170885936898</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -62346,10 +62346,10 @@
         </is>
       </c>
       <c r="B186">
-        <v>20.83332040718475</v>
+        <v>20.83335968326145</v>
       </c>
       <c r="C186">
-        <v>2.554386913562448</v>
+        <v>2.909350340596081</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -62357,10 +62357,10 @@
         </is>
       </c>
       <c r="E186">
-        <v>16.38295055168979</v>
+        <v>15.84492450482307</v>
       </c>
       <c r="F186">
-        <v>26.49261729863755</v>
+        <v>27.3922968556921</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -62970,10 +62970,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>10.9999959283739</v>
+        <v>11.00001014756803</v>
       </c>
       <c r="C198">
-        <v>1.849703690566376</v>
+        <v>1.26862198658435</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -62981,10 +62981,10 @@
         </is>
       </c>
       <c r="E198">
-        <v>7.911498995032065</v>
+        <v>8.774547361707405</v>
       </c>
       <c r="F198">
-        <v>15.29418261952922</v>
+        <v>13.78991055135803</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -63022,10 +63022,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>11.8333286670464</v>
+        <v>11.83335400731299</v>
       </c>
       <c r="C199">
-        <v>1.951928148328592</v>
+        <v>1.337080598661965</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -63033,10 +63033,10 @@
         </is>
       </c>
       <c r="E199">
-        <v>8.564455394594953</v>
+        <v>9.482622064247474</v>
       </c>
       <c r="F199">
-        <v>16.34986241281774</v>
+        <v>14.76682990354975</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -63074,10 +63074,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>6.181822641407582</v>
+        <v>6.18182698250498</v>
       </c>
       <c r="C200">
-        <v>0.9140893025480996</v>
+        <v>0.8947944304099023</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -63085,10 +63085,10 @@
         </is>
       </c>
       <c r="E200">
-        <v>4.62649059337902</v>
+        <v>4.654884058723727</v>
       </c>
       <c r="F200">
-        <v>8.260025693018566</v>
+        <v>8.209653421981121</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -63126,10 +63126,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>6.416664194591469</v>
+        <v>6.416678155083366</v>
       </c>
       <c r="C201">
-        <v>0.8971703583853815</v>
+        <v>0.8777504490386993</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -63137,10 +63137,10 @@
         </is>
       </c>
       <c r="E201">
-        <v>4.878601265470995</v>
+        <v>4.907639657274669</v>
       </c>
       <c r="F201">
-        <v>8.439627906786345</v>
+        <v>8.38972732745192</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -63178,10 +63178,10 @@
         </is>
       </c>
       <c r="B202">
-        <v>5.666666913379977</v>
+        <v>5.666659995380935</v>
       </c>
       <c r="C202">
-        <v>0.8264045692073851</v>
+        <v>0.8099747273381898</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -63189,10 +63189,10 @@
         </is>
       </c>
       <c r="E202">
-        <v>4.257863918088864</v>
+        <v>4.282122216589415</v>
       </c>
       <c r="F202">
-        <v>7.541601733859166</v>
+        <v>7.49886011633413</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -63230,10 +63230,10 @@
         </is>
       </c>
       <c r="B203">
-        <v>4.416666663933992</v>
+        <v>4.4166658680699</v>
       </c>
       <c r="C203">
-        <v>0.7043192913327696</v>
+        <v>0.6926282192323081</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -63241,10 +63241,10 @@
         </is>
       </c>
       <c r="E203">
-        <v>3.23113254676757</v>
+        <v>3.247938760241204</v>
       </c>
       <c r="F203">
-        <v>6.037184837811926</v>
+        <v>6.005943716969894</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -63282,10 +63282,10 @@
         </is>
       </c>
       <c r="B204">
-        <v>9.200001069720079</v>
+        <v>9.199979440565379</v>
       </c>
       <c r="C204">
-        <v>1.781302027693751</v>
+        <v>1.7329033361921</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -63293,10 +63293,10 @@
         </is>
       </c>
       <c r="E204">
-        <v>6.294749277974262</v>
+        <v>6.359968687098996</v>
       </c>
       <c r="F204">
-        <v>13.44613040888087</v>
+        <v>13.30818214223516</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -63334,10 +63334,10 @@
         </is>
       </c>
       <c r="B205">
-        <v>4.705880456231193</v>
+        <v>4.70588860095635</v>
       </c>
       <c r="C205">
-        <v>0.6159529015848002</v>
+        <v>0.6052366889753519</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -63345,10 +63345,10 @@
         </is>
       </c>
       <c r="E205">
-        <v>3.641053688863347</v>
+        <v>3.657348766163481</v>
       </c>
       <c r="F205">
-        <v>6.082115991882548</v>
+        <v>6.055038482928493</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -63386,10 +63386,10 @@
         </is>
       </c>
       <c r="B206">
-        <v>4.176471726400814</v>
+        <v>4.176472747272545</v>
       </c>
       <c r="C206">
-        <v>0.5713789565013353</v>
+        <v>0.5622860251288423</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -63397,10 +63397,10 @@
         </is>
       </c>
       <c r="E206">
-        <v>3.19416617541771</v>
+        <v>3.20782641800504</v>
       </c>
       <c r="F206">
-        <v>5.460866818910679</v>
+        <v>5.437614863075447</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -64015,10 +64015,10 @@
         </is>
       </c>
       <c r="B218">
-        <v>4.399999957576934</v>
+        <v>4.000000028089968</v>
       </c>
       <c r="C218">
-        <v>0.9380831057245846</v>
+        <v>0.6187550265170024</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -64026,10 +64026,10 @@
         </is>
       </c>
       <c r="E218">
-        <v>2.897182816691203</v>
+        <v>2.953851696249587</v>
       </c>
       <c r="F218">
-        <v>6.682353462522457</v>
+        <v>5.416656579284072</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -64067,10 +64067,10 @@
         </is>
       </c>
       <c r="B219">
-        <v>10.33333310768889</v>
+        <v>10.41666608014946</v>
       </c>
       <c r="C219">
-        <v>1.312334641753935</v>
+        <v>0.931694965487031</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -64078,10 +64078,10 @@
         </is>
       </c>
       <c r="E219">
-        <v>8.056338833775975</v>
+        <v>8.741681110869258</v>
       </c>
       <c r="F219">
-        <v>13.25388309970237</v>
+        <v>12.41259328144797</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -64119,10 +64119,10 @@
         </is>
       </c>
       <c r="B220">
-        <v>8.249999960614474</v>
+        <v>8.249999873747434</v>
       </c>
       <c r="C220">
-        <v>1.436140643175713</v>
+        <v>1.436140651956228</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -64130,10 +64130,10 @@
         </is>
       </c>
       <c r="E220">
-        <v>5.865145336719389</v>
+        <v>5.86514524165829</v>
       </c>
       <c r="F220">
-        <v>11.60457165895379</v>
+        <v>11.60457160266144</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -64171,10 +64171,10 @@
         </is>
       </c>
       <c r="B221">
-        <v>13.50000015811472</v>
+        <v>13.49999924469896</v>
       </c>
       <c r="C221">
-        <v>1.837117383805917</v>
+        <v>1.837117258238941</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -64182,10 +64182,10 @@
         </is>
       </c>
       <c r="E221">
-        <v>10.33950891035221</v>
+        <v>10.33950821267829</v>
       </c>
       <c r="F221">
-        <v>17.62656291021944</v>
+        <v>17.62656171435677</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -64223,10 +64223,10 @@
         </is>
       </c>
       <c r="B222">
-        <v>8.749999969498605</v>
+        <v>8.749999631489169</v>
       </c>
       <c r="C222">
-        <v>1.479019934249903</v>
+        <v>1.47901991614637</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -64234,10 +64234,10 @@
         </is>
       </c>
       <c r="E222">
-        <v>6.282445516794241</v>
+        <v>6.28244521918023</v>
       </c>
       <c r="F222">
-        <v>12.1867351275166</v>
+        <v>12.18673476329188</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -64275,10 +64275,10 @@
         </is>
       </c>
       <c r="B223">
-        <v>9.499999924187223</v>
+        <v>9.499999444344411</v>
       </c>
       <c r="C223">
-        <v>1.541103495478997</v>
+        <v>1.54110345727279</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -64286,10 +64286,10 @@
         </is>
       </c>
       <c r="E223">
-        <v>6.912584881798315</v>
+        <v>6.912584476120423</v>
       </c>
       <c r="F223">
-        <v>13.05589733837433</v>
+        <v>13.05589678568318</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -64327,10 +64327,10 @@
         </is>
       </c>
       <c r="B224">
-        <v>6.749999778123152</v>
+        <v>6.749999483427059</v>
       </c>
       <c r="C224">
-        <v>1.299038053520224</v>
+        <v>1.299038057156434</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -64338,10 +64338,10 @@
         </is>
       </c>
       <c r="E224">
-        <v>4.629029477650832</v>
+        <v>4.629029194435899</v>
       </c>
       <c r="F224">
-        <v>9.842775299798896</v>
+        <v>9.842775042557902</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -64379,10 +64379,10 @@
         </is>
       </c>
       <c r="B225">
-        <v>8.499999802133473</v>
+        <v>8.499999562602548</v>
       </c>
       <c r="C225">
-        <v>1.190238047741953</v>
+        <v>1.190238041947796</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -64390,10 +64390,10 @@
         </is>
       </c>
       <c r="E225">
-        <v>6.459915815113322</v>
+        <v>6.459915591741732</v>
       </c>
       <c r="F225">
-        <v>11.18435575696456</v>
+        <v>11.18435551334555</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -68175,10 +68175,10 @@
         </is>
       </c>
       <c r="B298">
-        <v>0.3333329371880054</v>
+        <v>0.3333333216632092</v>
       </c>
       <c r="C298">
-        <v>0.1178510610279026</v>
+        <v>0.08333332503641391</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -68186,10 +68186,10 @@
         </is>
       </c>
       <c r="E298">
-        <v>0.1666989469806874</v>
+        <v>0.204210636047934</v>
       </c>
       <c r="F298">
-        <v>0.6665359861406644</v>
+        <v>0.5441004713630468</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -68227,10 +68227,10 @@
         </is>
       </c>
       <c r="B299">
-        <v>0.1250001559644689</v>
+        <v>0.1249999947550696</v>
       </c>
       <c r="C299">
-        <v>0.0721688288669648</v>
+        <v>0.05103103100919624</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -68238,10 +68238,10 @@
         </is>
       </c>
       <c r="E299">
-        <v>0.04031525582735532</v>
+        <v>0.05615758736631075</v>
       </c>
       <c r="F299">
-        <v>0.3875713714444401</v>
+        <v>0.27823486409498</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -68279,10 +68279,10 @@
         </is>
       </c>
       <c r="B300">
-        <v>0.1739131031107939</v>
+        <v>0.1739130385848418</v>
       </c>
       <c r="C300">
-        <v>0.08695653697710468</v>
+        <v>0.08695651332728262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -68290,10 +68290,10 @@
         </is>
       </c>
       <c r="E300">
-        <v>0.06527270395955094</v>
+        <v>0.06527267340589037</v>
       </c>
       <c r="F300">
-        <v>0.4633754325907615</v>
+        <v>0.4633753056464088</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -68331,10 +68331,10 @@
         </is>
       </c>
       <c r="B301">
-        <v>0.5416668008668513</v>
+        <v>0.5416666366924994</v>
       </c>
       <c r="C301">
-        <v>0.1502313235246018</v>
+        <v>0.1502312867796152</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -68342,10 +68342,10 @@
         </is>
       </c>
       <c r="E301">
-        <v>0.3145222784702506</v>
+        <v>0.3145221731391585</v>
       </c>
       <c r="F301">
-        <v>0.9328525934263218</v>
+        <v>0.9328523403529637</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -68383,10 +68383,10 @@
         </is>
       </c>
       <c r="B302">
-        <v>0.3181817837905367</v>
+        <v>0.3181818054922859</v>
       </c>
       <c r="C302">
-        <v>0.1202614177217613</v>
+        <v>0.1202614109567476</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -68394,10 +68394,10 @@
         </is>
       </c>
       <c r="E302">
-        <v>0.1516880434112292</v>
+        <v>0.1516880677425453</v>
       </c>
       <c r="F302">
-        <v>0.6674200896748678</v>
+        <v>0.6674200736617021</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -69147,10 +69147,10 @@
         </is>
       </c>
       <c r="B317">
-        <v>0.6666670905744827</v>
+        <v>0.6667124910611517</v>
       </c>
       <c r="C317">
-        <v>0.3333332844782937</v>
+        <v>0.3333447622008374</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -69158,10 +69158,10 @@
         </is>
       </c>
       <c r="E317">
-        <v>0.2502122558958997</v>
+        <v>0.2502375510445113</v>
       </c>
       <c r="F317">
-        <v>1.776271941850665</v>
+        <v>1.776334302671862</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -69199,10 +69199,10 @@
         </is>
       </c>
       <c r="B318">
-        <v>0.7500034436971542</v>
+        <v>1.08333189365325</v>
       </c>
       <c r="C318">
-        <v>0.2500005562633066</v>
+        <v>0.3004629958796055</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -69210,10 +69210,10 @@
         </is>
       </c>
       <c r="E318">
-        <v>0.3902384708765489</v>
+        <v>0.6290426289986388</v>
       </c>
       <c r="F318">
-        <v>1.441439549243052</v>
+        <v>1.865705021732121</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
@@ -69251,10 +69251,10 @@
         </is>
       </c>
       <c r="B319">
-        <v>0.3636356570916776</v>
+        <v>0.6363626714988994</v>
       </c>
       <c r="C319">
-        <v>0.1818179198032628</v>
+        <v>0.1700751930165019</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -69262,10 +69262,10 @@
         </is>
       </c>
       <c r="E319">
-        <v>0.136478888568871</v>
+        <v>0.3768871764059735</v>
       </c>
       <c r="F319">
-        <v>0.9688743255098299</v>
+        <v>1.074479247447268</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -69303,10 +69303,10 @@
         </is>
       </c>
       <c r="B320">
-        <v>0.7499948309802358</v>
+        <v>0.7499994211992251</v>
       </c>
       <c r="C320">
-        <v>0.2499991208097065</v>
+        <v>0.1767766127970354</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -69314,10 +69314,10 @@
         </is>
       </c>
       <c r="E320">
-        <v>0.390232525681816</v>
+        <v>0.4725314721422891</v>
       </c>
       <c r="F320">
-        <v>1.44142840352501</v>
+        <v>1.190395063526674</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -69355,10 +69355,10 @@
         </is>
       </c>
       <c r="B321">
-        <v>0.7499993429903296</v>
+        <v>1.083331124688278</v>
       </c>
       <c r="C321">
-        <v>0.2499998728128276</v>
+        <v>0.3004628892434991</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -69366,10 +69366,10 @@
         </is>
       </c>
       <c r="E321">
-        <v>0.3902356402348605</v>
+        <v>0.6290420611352285</v>
       </c>
       <c r="F321">
-        <v>1.441434242519187</v>
+        <v>1.865704057373156</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -69407,10 +69407,10 @@
         </is>
       </c>
       <c r="B322">
-        <v>0.9166655856667779</v>
+        <v>0.9166645331959563</v>
       </c>
       <c r="C322">
-        <v>0.2763852174503518</v>
+        <v>0.2763850553801586</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -69418,10 +69418,10 @@
         </is>
       </c>
       <c r="E322">
-        <v>0.5076493930412729</v>
+        <v>0.5076486416573881</v>
       </c>
       <c r="F322">
-        <v>1.655228603567937</v>
+        <v>1.65522725260528</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -69459,10 +69459,10 @@
         </is>
       </c>
       <c r="B323">
-        <v>1.249998582185245</v>
+        <v>1.249998403325595</v>
       </c>
       <c r="C323">
-        <v>0.3227479953576356</v>
+        <v>0.3227483805101925</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -69470,10 +69470,10 @@
         </is>
       </c>
       <c r="E323">
-        <v>0.7535817941447367</v>
+        <v>0.7535811766541454</v>
       </c>
       <c r="F323">
-        <v>2.073426491464602</v>
+        <v>2.073427597082405</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -70031,10 +70031,10 @@
         </is>
       </c>
       <c r="B334">
-        <v>0.1666682844639585</v>
+        <v>0.1666651878949803</v>
       </c>
       <c r="C334">
-        <v>0.1666674620742061</v>
+        <v>0.1178505976044347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -70042,10 +70042,10 @@
         </is>
       </c>
       <c r="E334">
-        <v>0.02347770395664154</v>
+        <v>0.04168232088231637</v>
       </c>
       <c r="F334">
-        <v>1.183178606283638</v>
+        <v>0.6664044676037588</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -70083,10 +70083,10 @@
         </is>
       </c>
       <c r="B335">
-        <v>1.000005185408058</v>
+        <v>1.000001497472312</v>
       </c>
       <c r="C335">
-        <v>0.4082493207839021</v>
+        <v>0.2886753274654309</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -70094,10 +70094,10 @@
         </is>
       </c>
       <c r="E335">
-        <v>0.4492639819409491</v>
+        <v>0.5679108082455103</v>
       </c>
       <c r="F335">
-        <v>2.225885917946666</v>
+        <v>1.760845154604914</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -70135,10 +70135,10 @@
         </is>
       </c>
       <c r="B336">
-        <v>0.5454557986066015</v>
+        <v>0.5454555445650008</v>
       </c>
       <c r="C336">
-        <v>0.2226811246973657</v>
+        <v>0.2226810714237922</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -70146,10 +70146,10 @@
         </is>
       </c>
       <c r="E336">
-        <v>0.2450520915079263</v>
+        <v>0.2450519329641483</v>
       </c>
       <c r="F336">
-        <v>1.214117481727113</v>
+        <v>1.214117136306082</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -70187,10 +70187,10 @@
         </is>
       </c>
       <c r="B337">
-        <v>0.4166675893020094</v>
+        <v>0.4166673114907453</v>
       </c>
       <c r="C337">
-        <v>0.1863391900215774</v>
+        <v>0.186339126994993</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -70198,10 +70198,10 @@
         </is>
       </c>
       <c r="E337">
-        <v>0.1734288196133977</v>
+        <v>0.1734286540423976</v>
       </c>
       <c r="F337">
-        <v>1.001055535993143</v>
+        <v>1.00105515679366</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -70239,10 +70239,10 @@
         </is>
       </c>
       <c r="B338">
-        <v>0.3333325173820389</v>
+        <v>0.3333338330975462</v>
       </c>
       <c r="C338">
-        <v>0.166666449589279</v>
+        <v>0.1666667778699799</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -70250,10 +70250,10 @@
         </is>
       </c>
       <c r="E338">
-        <v>0.125105505803476</v>
+        <v>0.1251062420549695</v>
       </c>
       <c r="F338">
-        <v>0.8881349100557338</v>
+        <v>0.8881366945598317</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -70291,10 +70291,10 @@
         </is>
       </c>
       <c r="B339">
-        <v>1.199999492045763</v>
+        <v>1.200001780130069</v>
       </c>
       <c r="C339">
-        <v>0.4898978125067141</v>
+        <v>0.4898982726983084</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -70302,10 +70302,10 @@
         </is>
       </c>
       <c r="E339">
-        <v>0.5391125436412845</v>
+        <v>0.5391139888863087</v>
       </c>
       <c r="F339">
-        <v>2.671054120136069</v>
+        <v>2.671057145614174</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -73470,10 +73470,10 @@
         </is>
       </c>
       <c r="B400">
-        <v>0.2083333519260731</v>
+        <v>0.1874999531583771</v>
       </c>
       <c r="C400">
-        <v>0.09316949619811285</v>
+        <v>0.06249998698638666</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -73481,10 +73481,10 @@
         </is>
       </c>
       <c r="E400">
-        <v>0.08671414462207409</v>
+        <v>0.09755899190600231</v>
       </c>
       <c r="F400">
-        <v>0.5005271713618951</v>
+        <v>0.3603587096130155</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -73522,10 +73522,10 @@
         </is>
       </c>
       <c r="B401">
-        <v>0.7391304744588201</v>
+        <v>0.7391308854805023</v>
       </c>
       <c r="C401">
-        <v>0.1792654569230143</v>
+        <v>0.179265501718282</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -73533,10 +73533,10 @@
         </is>
       </c>
       <c r="E401">
-        <v>0.4594882681451065</v>
+        <v>0.4594885905434212</v>
       </c>
       <c r="F401">
-        <v>1.188961495097834</v>
+        <v>1.188961983201986</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
@@ -73574,10 +73574,10 @@
         </is>
       </c>
       <c r="B402">
-        <v>0.416666676749007</v>
+        <v>0.4166664480171317</v>
       </c>
       <c r="C402">
-        <v>0.1317615618870781</v>
+        <v>0.1317615236296038</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -73585,10 +73585,10 @@
         </is>
       </c>
       <c r="E402">
-        <v>0.2241894790243193</v>
+        <v>0.2241893200208225</v>
       </c>
       <c r="F402">
-        <v>0.7743945892047361</v>
+        <v>0.7743942882162642</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -73626,10 +73626,10 @@
         </is>
       </c>
       <c r="B403">
-        <v>0.2727273266075524</v>
+        <v>0.2727268964920495</v>
       </c>
       <c r="C403">
-        <v>0.1113404457349146</v>
+        <v>0.1113403567809682</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -73637,10 +73637,10 @@
         </is>
       </c>
       <c r="E403">
-        <v>0.122525685275848</v>
+        <v>0.1225254157523621</v>
       </c>
       <c r="F403">
-        <v>0.6070579773624347</v>
+        <v>0.6070573979566455</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
@@ -74406,10 +74406,10 @@
         </is>
       </c>
       <c r="B418">
-        <v>7.166646780819126</v>
+        <v>7.166708483647556</v>
       </c>
       <c r="C418">
-        <v>2.581187166784422</v>
+        <v>2.975519924372275</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -74417,10 +74417,10 @@
         </is>
       </c>
       <c r="E418">
-        <v>3.537867725240518</v>
+        <v>3.176233568882223</v>
       </c>
       <c r="F418">
-        <v>14.51745233847979</v>
+        <v>16.17063398384175</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
@@ -74458,10 +74458,10 @@
         </is>
       </c>
       <c r="B419">
-        <v>6.000029050740634</v>
+        <v>6.000056853513934</v>
       </c>
       <c r="C419">
-        <v>1.623595367929028</v>
+        <v>1.317911306051661</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -74469,10 +74469,10 @@
         </is>
       </c>
       <c r="E419">
-        <v>3.530368081213267</v>
+        <v>3.901118245359604</v>
       </c>
       <c r="F419">
-        <v>10.19733573994909</v>
+        <v>9.228298139443091</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -74510,10 +74510,10 @@
         </is>
       </c>
       <c r="B420">
-        <v>4.999996299297663</v>
+        <v>5.041714308109698</v>
       </c>
       <c r="C420">
-        <v>1.3219186339887</v>
+        <v>1.075972457167668</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -74521,10 +74521,10 @@
         </is>
       </c>
       <c r="E420">
-        <v>2.978006765670232</v>
+        <v>3.318332492544584</v>
       </c>
       <c r="F420">
-        <v>8.394864404333825</v>
+        <v>7.660137500297987</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
@@ -74562,10 +74562,10 @@
         </is>
       </c>
       <c r="B421">
-        <v>10.08334929961487</v>
+        <v>10.08334169272473</v>
       </c>
       <c r="C421">
-        <v>2.500523208622099</v>
+        <v>2.901938030108442</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -74573,10 +74573,10 @@
         </is>
       </c>
       <c r="E421">
-        <v>6.201821663419778</v>
+        <v>5.736311245567516</v>
       </c>
       <c r="F421">
-        <v>16.39420457665647</v>
+        <v>17.72459257171667</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
@@ -74614,10 +74614,10 @@
         </is>
       </c>
       <c r="B422">
-        <v>15.58330856725544</v>
+        <v>15.58335866566931</v>
       </c>
       <c r="C422">
-        <v>3.771667109584622</v>
+        <v>4.405140226520501</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -74625,10 +74625,10 @@
         </is>
       </c>
       <c r="E422">
-        <v>9.697085703013149</v>
+        <v>8.954501757763582</v>
       </c>
       <c r="F422">
-        <v>25.04252445936825</v>
+        <v>27.11943934706884</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>
@@ -74666,10 +74666,10 @@
         </is>
       </c>
       <c r="B423">
-        <v>15.25004250866398</v>
+        <v>15.25035684249721</v>
       </c>
       <c r="C423">
-        <v>3.694693077188547</v>
+        <v>4.314198853514867</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -74677,10 +74677,10 @@
         </is>
       </c>
       <c r="E423">
-        <v>9.485206992007793</v>
+        <v>8.75955781117616</v>
       </c>
       <c r="F423">
-        <v>24.51857895268031</v>
+        <v>26.55081327584427</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
@@ -75238,10 +75238,10 @@
         </is>
       </c>
       <c r="B434">
-        <v>3.833342244397123</v>
+        <v>3.833344517984286</v>
       </c>
       <c r="C434">
-        <v>2.255560196175116</v>
+        <v>1.401974566189374</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -75249,10 +75249,10 @@
         </is>
       </c>
       <c r="E434">
-        <v>1.209834058983658</v>
+        <v>1.871831263013666</v>
       </c>
       <c r="F434">
-        <v>12.14589112743607</v>
+        <v>7.850349806585583</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
@@ -75290,10 +75290,10 @@
         </is>
       </c>
       <c r="B435">
-        <v>3.666675670459964</v>
+        <v>3.666657009301774</v>
       </c>
       <c r="C435">
-        <v>2.163641628159251</v>
+        <v>1.345953436144311</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -75301,10 +75301,10 @@
         </is>
       </c>
       <c r="E435">
-        <v>1.153435331533746</v>
+        <v>1.785714087997599</v>
       </c>
       <c r="F435">
-        <v>11.65605916932125</v>
+        <v>7.528850062967027</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
@@ -75342,10 +75342,10 @@
         </is>
       </c>
       <c r="B436">
-        <v>1.363641209949282</v>
+        <v>1.363635814239609</v>
       </c>
       <c r="C436">
-        <v>0.6565323051124272</v>
+        <v>0.5926255010263267</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -75353,10 +75353,10 @@
         </is>
       </c>
       <c r="E436">
-        <v>0.5307434121866257</v>
+        <v>0.5817988249867524</v>
       </c>
       <c r="F436">
-        <v>3.503608913035511</v>
+        <v>3.196126485678726</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
@@ -75394,10 +75394,10 @@
         </is>
       </c>
       <c r="B437">
-        <v>1.583335823862045</v>
+        <v>1.583336528915794</v>
       </c>
       <c r="C437">
-        <v>0.715140255863819</v>
+        <v>0.6424753452680491</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -75405,10 +75405,10 @@
         </is>
       </c>
       <c r="E437">
-        <v>0.6533013328137458</v>
+        <v>0.7147901459330426</v>
       </c>
       <c r="F437">
-        <v>3.837359890768238</v>
+        <v>3.507259547523131</v>
       </c>
       <c r="G437" t="inlineStr">
         <is>
@@ -75446,10 +75446,10 @@
         </is>
       </c>
       <c r="B438">
-        <v>1.83334204328385</v>
+        <v>1.833329508038056</v>
       </c>
       <c r="C438">
-        <v>0.8133640671796978</v>
+        <v>0.727521192139984</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -75457,10 +75457,10 @@
         </is>
       </c>
       <c r="E438">
-        <v>0.7684348723042577</v>
+        <v>0.8422824190056797</v>
       </c>
       <c r="F438">
-        <v>4.374011603082707</v>
+        <v>3.990463304470797</v>
       </c>
       <c r="G438" t="inlineStr">
         <is>
@@ -75498,10 +75498,10 @@
         </is>
       </c>
       <c r="B439">
-        <v>1.416668774734561</v>
+        <v>1.416665385008594</v>
       </c>
       <c r="C439">
-        <v>0.6495003033130121</v>
+        <v>0.5855535432846692</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -75509,10 +75509,10 @@
         </is>
       </c>
       <c r="E439">
-        <v>0.5767901667495631</v>
+        <v>0.6301416735024814</v>
       </c>
       <c r="F439">
-        <v>3.479515659252427</v>
+        <v>3.184904121523148</v>
       </c>
       <c r="G439" t="inlineStr">
         <is>
@@ -75550,10 +75550,10 @@
         </is>
       </c>
       <c r="B440">
-        <v>4.200014098387568</v>
+        <v>4.199947151231427</v>
       </c>
       <c r="C440">
-        <v>2.692307007203703</v>
+        <v>2.362687587367094</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -75561,10 +75561,10 @@
         </is>
       </c>
       <c r="E440">
-        <v>1.195668268462438</v>
+        <v>1.394437053405109</v>
       </c>
       <c r="F440">
-        <v>14.75335499982661</v>
+        <v>12.64994789837414</v>
       </c>
       <c r="G440" t="inlineStr">
         <is>
@@ -75602,10 +75602,10 @@
         </is>
       </c>
       <c r="B441">
-        <v>0.8823559175295516</v>
+        <v>0.8823605009004264</v>
       </c>
       <c r="C441">
-        <v>0.3675486980556258</v>
+        <v>0.3368488937810574</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -75613,10 +75613,10 @@
         </is>
       </c>
       <c r="E441">
-        <v>0.3900071573046061</v>
+        <v>0.417534505004751</v>
       </c>
       <c r="F441">
-        <v>1.996250454940617</v>
+        <v>1.864660391457689</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
@@ -75654,10 +75654,10 @@
         </is>
       </c>
       <c r="B442">
-        <v>0.8235327030471373</v>
+        <v>0.8235329849884613</v>
       </c>
       <c r="C442">
-        <v>0.3477209889763361</v>
+        <v>0.3194858194072979</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -75665,10 +75665,10 @@
         </is>
       </c>
       <c r="E442">
-        <v>0.3599790450673627</v>
+        <v>0.3850004967249528</v>
       </c>
       <c r="F442">
-        <v>1.884015534463158</v>
+        <v>1.761573252848349</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -76285,10 +76285,10 @@
         </is>
       </c>
       <c r="B454">
-        <v>0.799999746882683</v>
+        <v>0.7272727141114353</v>
       </c>
       <c r="C454">
-        <v>0.3999999040507734</v>
+        <v>0.2571297149529692</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -76296,10 +76296,10 @@
         </is>
       </c>
       <c r="E454">
-        <v>0.3002541684145047</v>
+        <v>0.3637073893033126</v>
       </c>
       <c r="F454">
-        <v>2.131526094681321</v>
+        <v>1.454261354723034</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
@@ -76337,10 +76337,10 @@
         </is>
       </c>
       <c r="B455">
-        <v>6.999999870896147</v>
+        <v>7.083333392101308</v>
       </c>
       <c r="C455">
-        <v>1.080123365444299</v>
+        <v>0.7682953133303558</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -76348,10 +76348,10 @@
         </is>
       </c>
       <c r="E455">
-        <v>5.173146651424606</v>
+        <v>5.726798740681464</v>
       </c>
       <c r="F455">
-        <v>9.471990935933009</v>
+        <v>8.761196999510236</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -76389,10 +76389,10 @@
         </is>
       </c>
       <c r="B456">
-        <v>6.249999895466288</v>
+        <v>6.249999938620112</v>
       </c>
       <c r="C456">
-        <v>1.249999901582415</v>
+        <v>1.249999893608732</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -76400,10 +76400,10 @@
         </is>
       </c>
       <c r="E456">
-        <v>4.223181164124837</v>
+        <v>4.223181215274619</v>
       </c>
       <c r="F456">
-        <v>9.249543691177044</v>
+        <v>9.249543706878633</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -76441,10 +76441,10 @@
         </is>
       </c>
       <c r="B457">
-        <v>9.749999904719788</v>
+        <v>9.750000243968081</v>
       </c>
       <c r="C457">
-        <v>1.56124939343613</v>
+        <v>1.56124939665557</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -76452,10 +76452,10 @@
         </is>
       </c>
       <c r="E457">
-        <v>7.123661715740052</v>
+        <v>7.123662036786921</v>
       </c>
       <c r="F457">
-        <v>13.34461151236182</v>
+        <v>13.34461183959464</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
@@ -76493,10 +76493,10 @@
         </is>
       </c>
       <c r="B458">
-        <v>6.75000026456459</v>
+        <v>6.749999890772609</v>
       </c>
       <c r="C458">
-        <v>1.299038041066337</v>
+        <v>1.299037991306498</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -76504,10 +76504,10 @@
         </is>
       </c>
       <c r="E458">
-        <v>4.629029953812713</v>
+        <v>4.629029667665272</v>
       </c>
       <c r="F458">
-        <v>9.842775705975797</v>
+        <v>9.842775224296727</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
@@ -76545,10 +76545,10 @@
         </is>
       </c>
       <c r="B459">
-        <v>7.250000183338481</v>
+        <v>7.250000386528751</v>
       </c>
       <c r="C459">
-        <v>1.346291126857861</v>
+        <v>1.346291130371531</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -76556,10 +76556,10 @@
         </is>
       </c>
       <c r="E459">
-        <v>5.038182231581522</v>
+        <v>5.038182419388239</v>
       </c>
       <c r="F459">
-        <v>10.43283077950681</v>
+        <v>10.43283097539161</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -76597,10 +76597,10 @@
         </is>
       </c>
       <c r="B460">
-        <v>3.499999993521308</v>
+        <v>3.499999808285787</v>
       </c>
       <c r="C460">
-        <v>0.9354142746665616</v>
+        <v>0.9354142447631232</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -76608,10 +76608,10 @@
         </is>
       </c>
       <c r="E460">
-        <v>2.072883425932914</v>
+        <v>2.072883293471891</v>
       </c>
       <c r="F460">
-        <v>5.909642482251972</v>
+        <v>5.909642234359904</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -76649,10 +76649,10 @@
         </is>
       </c>
       <c r="B461">
-        <v>4.333333362034923</v>
+        <v>4.333333083772111</v>
       </c>
       <c r="C461">
-        <v>0.8498365252302161</v>
+        <v>0.8498364921520839</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -76660,10 +76660,10 @@
         </is>
       </c>
       <c r="E461">
-        <v>2.950446584909887</v>
+        <v>2.950446366765439</v>
       </c>
       <c r="F461">
-        <v>6.364385012955047</v>
+        <v>6.364384666141176</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -80601,10 +80601,10 @@
         </is>
       </c>
       <c r="B537">
-        <v>1.72851192977073</v>
+        <v>1.702537194707176</v>
       </c>
       <c r="C537">
-        <v>0.2683678791427884</v>
+        <v>0.1883335509126759</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -80612,10 +80612,10 @@
         </is>
       </c>
       <c r="E537">
-        <v>1.275014913290784</v>
+        <v>1.370683707447186</v>
       </c>
       <c r="F537">
-        <v>2.343308662679412</v>
+        <v>2.114735065144901</v>
       </c>
       <c r="G537" t="inlineStr">
         <is>
@@ -80653,10 +80653,10 @@
         </is>
       </c>
       <c r="B538">
-        <v>1.295548437268859</v>
+        <v>1.314453749567091</v>
       </c>
       <c r="C538">
-        <v>0.23233849438837</v>
+        <v>0.1654824885451146</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -80664,10 +80664,10 @@
         </is>
       </c>
       <c r="E538">
-        <v>0.9115963168174707</v>
+        <v>1.027031402468279</v>
       </c>
       <c r="F538">
-        <v>1.841216032080415</v>
+        <v>1.682313369969571</v>
       </c>
       <c r="G538" t="inlineStr">
         <is>
@@ -80705,10 +80705,10 @@
         </is>
       </c>
       <c r="B539">
-        <v>0.4595123065097884</v>
+        <v>0.459512794974865</v>
       </c>
       <c r="C539">
-        <v>0.1413463569273271</v>
+        <v>0.1413464446050043</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -80716,10 +80716,10 @@
         </is>
       </c>
       <c r="E539">
-        <v>0.2514588147943693</v>
+        <v>0.2514591492114118</v>
       </c>
       <c r="F539">
-        <v>0.8397063352367073</v>
+        <v>0.8397070037331923</v>
       </c>
       <c r="G539" t="inlineStr">
         <is>
@@ -80757,10 +80757,10 @@
         </is>
       </c>
       <c r="B540">
-        <v>1.575301837450851</v>
+        <v>1.575302158451272</v>
       </c>
       <c r="C540">
-        <v>0.2561991223362214</v>
+        <v>0.256198346152994</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -80768,10 +80768,10 @@
         </is>
       </c>
       <c r="E540">
-        <v>1.145324804210561</v>
+        <v>1.145326218044208</v>
       </c>
       <c r="F540">
-        <v>2.166700546389116</v>
+        <v>2.166698754752029</v>
       </c>
       <c r="G540" t="inlineStr">
         <is>
@@ -80809,10 +80809,10 @@
         </is>
       </c>
       <c r="B541">
-        <v>1.473586548008222</v>
+        <v>1.473586418653894</v>
       </c>
       <c r="C541">
-        <v>0.2477890824423105</v>
+        <v>0.247789096493951</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -80820,10 +80820,10 @@
         </is>
       </c>
       <c r="E541">
-        <v>1.059846400697915</v>
+        <v>1.059846257192264</v>
       </c>
       <c r="F541">
-        <v>2.048841523678216</v>
+        <v>2.048841441393411</v>
       </c>
       <c r="G541" t="inlineStr">
         <is>
@@ -80861,10 +80861,10 @@
         </is>
       </c>
       <c r="B542">
-        <v>1.446739012418593</v>
+        <v>1.446739648575672</v>
       </c>
       <c r="C542">
-        <v>0.2564387906631546</v>
+        <v>0.2564388729745114</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -80872,10 +80872,10 @@
         </is>
       </c>
       <c r="E542">
-        <v>1.022144247455022</v>
+        <v>1.022144739074821</v>
       </c>
       <c r="F542">
-        <v>2.047708799678029</v>
+        <v>2.047709615621908</v>
       </c>
       <c r="G542" t="inlineStr">
         <is>
@@ -81641,10 +81641,10 @@
         </is>
       </c>
       <c r="B557">
-        <v>1.835060985039405</v>
+        <v>1.835061057229653</v>
       </c>
       <c r="C557">
-        <v>0.5530311469963143</v>
+        <v>0.5530306713607175</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -81652,10 +81652,10 @@
         </is>
       </c>
       <c r="E557">
-        <v>1.016539926589614</v>
+        <v>1.016540506612995</v>
       </c>
       <c r="F557">
-        <v>3.31265770358006</v>
+        <v>3.312656074061223</v>
       </c>
       <c r="G557" t="inlineStr">
         <is>
@@ -81693,10 +81693,10 @@
         </is>
       </c>
       <c r="B558">
-        <v>2.03413389207243</v>
+        <v>2.443331537302116</v>
       </c>
       <c r="C558">
-        <v>0.4117172953294526</v>
+        <v>0.4512326783878044</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -81704,10 +81704,10 @@
         </is>
       </c>
       <c r="E558">
-        <v>1.368020945074262</v>
+        <v>1.701308701497783</v>
       </c>
       <c r="F558">
-        <v>3.024588699300302</v>
+        <v>3.508986344406176</v>
       </c>
       <c r="G558" t="inlineStr">
         <is>
@@ -81745,10 +81745,10 @@
         </is>
       </c>
       <c r="B559">
-        <v>1.77665744351763</v>
+        <v>2.100371866770162</v>
       </c>
       <c r="C559">
-        <v>0.4018884020091453</v>
+        <v>0.3089845200015919</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -81756,10 +81756,10 @@
         </is>
       </c>
       <c r="E559">
-        <v>1.140401668186413</v>
+        <v>1.574259830271313</v>
       </c>
       <c r="F559">
-        <v>2.767894645950861</v>
+        <v>2.80230867477529</v>
       </c>
       <c r="G559" t="inlineStr">
         <is>
@@ -81797,10 +81797,10 @@
         </is>
       </c>
       <c r="B560">
-        <v>1.612370451404255</v>
+        <v>1.606750489186629</v>
       </c>
       <c r="C560">
-        <v>0.3828565120064966</v>
+        <v>0.2702482221426457</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -81808,10 +81808,10 @@
         </is>
       </c>
       <c r="E560">
-        <v>1.012389130640253</v>
+        <v>1.15552716837147</v>
       </c>
       <c r="F560">
-        <v>2.567924125101423</v>
+        <v>2.234172596858877</v>
       </c>
       <c r="G560" t="inlineStr">
         <is>
@@ -81849,10 +81849,10 @@
         </is>
       </c>
       <c r="B561">
-        <v>2.0341338972575</v>
+        <v>2.443331524543493</v>
       </c>
       <c r="C561">
-        <v>0.4117174517673044</v>
+        <v>0.4512326772092866</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -81860,10 +81860,10 @@
         </is>
       </c>
       <c r="E561">
-        <v>1.368020743737889</v>
+        <v>1.701308691006567</v>
       </c>
       <c r="F561">
-        <v>3.024589159859088</v>
+        <v>3.508986329397989</v>
       </c>
       <c r="G561" t="inlineStr">
         <is>
@@ -81901,10 +81901,10 @@
         </is>
       </c>
       <c r="B562">
-        <v>2.45768246680554</v>
+        <v>2.457682543990867</v>
       </c>
       <c r="C562">
-        <v>0.4525558979875388</v>
+        <v>0.4525559049439877</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -81912,10 +81912,10 @@
         </is>
       </c>
       <c r="E562">
-        <v>1.713113453240069</v>
+        <v>1.713113516955222</v>
       </c>
       <c r="F562">
-        <v>3.525862864610235</v>
+        <v>3.525862954938847</v>
       </c>
       <c r="G562" t="inlineStr">
         <is>
@@ -81953,10 +81953,10 @@
         </is>
       </c>
       <c r="B563">
-        <v>2.300662163717895</v>
+        <v>2.300662206454732</v>
       </c>
       <c r="C563">
-        <v>0.4378606465272758</v>
+        <v>0.4378605038530862</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -81964,10 +81964,10 @@
         </is>
       </c>
       <c r="E563">
-        <v>1.584355667682215</v>
+        <v>1.584355900663381</v>
       </c>
       <c r="F563">
-        <v>3.340819551778046</v>
+        <v>3.340819184624439</v>
       </c>
       <c r="G563" t="inlineStr">
         <is>
@@ -82577,10 +82577,10 @@
         </is>
       </c>
       <c r="B575">
-        <v>1.304647119621589</v>
+        <v>1.300400869132253</v>
       </c>
       <c r="C575">
-        <v>0.4663058555208302</v>
+        <v>0.3291910172425693</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -82588,10 +82588,10 @@
         </is>
       </c>
       <c r="E575">
-        <v>0.6475261824305387</v>
+        <v>0.791770207444372</v>
       </c>
       <c r="F575">
-        <v>2.628625919569663</v>
+        <v>2.135774249321863</v>
       </c>
       <c r="G575" t="inlineStr">
         <is>
@@ -82629,10 +82629,10 @@
         </is>
       </c>
       <c r="B576">
-        <v>0.3762386759516569</v>
+        <v>0.3762387337630132</v>
       </c>
       <c r="C576">
-        <v>0.2504125308065578</v>
+        <v>0.177068413303501</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -82640,10 +82640,10 @@
         </is>
       </c>
       <c r="E576">
-        <v>0.1020776550864304</v>
+        <v>0.1495768494664819</v>
       </c>
       <c r="F576">
-        <v>1.386743662577271</v>
+        <v>0.9463736219107634</v>
       </c>
       <c r="G576" t="inlineStr">
         <is>
@@ -82681,10 +82681,10 @@
         </is>
       </c>
       <c r="B577">
-        <v>1.364754499060681</v>
+        <v>1.364754612890914</v>
       </c>
       <c r="C577">
-        <v>0.3522336872897324</v>
+        <v>0.3522337097173175</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -82692,10 +82692,10 @@
         </is>
       </c>
       <c r="E577">
-        <v>0.8229345757932219</v>
+        <v>0.822934652647041</v>
       </c>
       <c r="F577">
-        <v>2.263308527182812</v>
+        <v>2.263308693364604</v>
       </c>
       <c r="G577" t="inlineStr">
         <is>
@@ -82733,10 +82733,10 @@
         </is>
       </c>
       <c r="B578">
-        <v>1.317421105347096</v>
+        <v>1.317421194985015</v>
       </c>
       <c r="C578">
-        <v>0.3313383076022951</v>
+        <v>0.3313383259011964</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -82744,10 +82744,10 @@
         </is>
       </c>
       <c r="E578">
-        <v>0.8047166192635672</v>
+        <v>0.8047166790995604</v>
       </c>
       <c r="F578">
-        <v>2.15678206124572</v>
+        <v>2.156782194371562</v>
       </c>
       <c r="G578" t="inlineStr">
         <is>
@@ -82785,10 +82785,10 @@
         </is>
       </c>
       <c r="B579">
-        <v>1.341132244450209</v>
+        <v>1.34113234449351</v>
       </c>
       <c r="C579">
-        <v>0.3343067483970907</v>
+        <v>0.3343067680833415</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -82796,10 +82796,10 @@
         </is>
       </c>
       <c r="E579">
-        <v>0.8227935397781954</v>
+        <v>0.8227936074703905</v>
       </c>
       <c r="F579">
-        <v>2.186010961618541</v>
+        <v>2.186011107908838</v>
       </c>
       <c r="G579" t="inlineStr">
         <is>
@@ -82837,10 +82837,10 @@
         </is>
       </c>
       <c r="B580">
-        <v>0.9983383169350354</v>
+        <v>0.9983383975171339</v>
       </c>
       <c r="C580">
-        <v>0.28843566756168</v>
+        <v>0.2884351840936168</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -82848,10 +82848,10 @@
         </is>
       </c>
       <c r="E580">
-        <v>0.5666986842676742</v>
+        <v>0.5666992937978065</v>
       </c>
       <c r="F580">
-        <v>1.75874661919968</v>
+        <v>1.758745011446381</v>
       </c>
       <c r="G580" t="inlineStr">
         <is>
@@ -82889,10 +82889,10 @@
         </is>
       </c>
       <c r="B581">
-        <v>1.914628663005218</v>
+        <v>1.914629220509521</v>
       </c>
       <c r="C581">
-        <v>0.6188098820704762</v>
+        <v>0.6188099912367954</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -82900,10 +82900,10 @@
         </is>
       </c>
       <c r="E581">
-        <v>1.016191068716193</v>
+        <v>1.016191438490525</v>
       </c>
       <c r="F581">
-        <v>3.607395331502322</v>
+        <v>3.60739611964668</v>
       </c>
       <c r="G581" t="inlineStr">
         <is>
@@ -82941,10 +82941,10 @@
         </is>
       </c>
       <c r="B582">
-        <v>0.7268102440565761</v>
+        <v>0.7268102971826599</v>
       </c>
       <c r="C582">
-        <v>0.2067692837451183</v>
+        <v>0.2067692937212426</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -82952,10 +82952,10 @@
         </is>
       </c>
       <c r="E582">
-        <v>0.4161633589548004</v>
+        <v>0.4161633951399366</v>
       </c>
       <c r="F582">
-        <v>1.269340799709744</v>
+        <v>1.269340874905923</v>
       </c>
       <c r="G582" t="inlineStr">
         <is>
@@ -82993,10 +82993,10 @@
         </is>
       </c>
       <c r="B583">
-        <v>1.152353685821571</v>
+        <v>1.152353748981535</v>
       </c>
       <c r="C583">
-        <v>0.2603564859551816</v>
+        <v>0.2603564979199823</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -83004,10 +83004,10 @@
         </is>
       </c>
       <c r="E583">
-        <v>0.7400651890074325</v>
+        <v>0.7400652324717004</v>
       </c>
       <c r="F583">
-        <v>1.794327090303423</v>
+        <v>1.794327181614463</v>
       </c>
       <c r="G583" t="inlineStr">
         <is>
@@ -83622,10 +83622,10 @@
         </is>
       </c>
       <c r="B595">
-        <v>0.5090474242132167</v>
+        <v>0.5090537647273115</v>
       </c>
       <c r="C595">
-        <v>0.3190759611077935</v>
+        <v>0.2256222002087969</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -83633,10 +83633,10 @@
         </is>
       </c>
       <c r="E595">
-        <v>0.1490104398563445</v>
+        <v>0.2135478113155919</v>
       </c>
       <c r="F595">
-        <v>1.739000840128569</v>
+        <v>1.213478769867067</v>
       </c>
       <c r="G595" t="inlineStr">
         <is>
@@ -83674,10 +83674,10 @@
         </is>
       </c>
       <c r="B596">
-        <v>1.609347873018546</v>
+        <v>1.614931167184502</v>
       </c>
       <c r="C596">
-        <v>0.5179040546422152</v>
+        <v>0.366848202328339</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -83685,10 +83685,10 @@
         </is>
       </c>
       <c r="E596">
-        <v>0.8564950537463927</v>
+        <v>1.034653288920103</v>
       </c>
       <c r="F596">
-        <v>3.023952753796306</v>
+        <v>2.520653732677876</v>
       </c>
       <c r="G596" t="inlineStr">
         <is>
@@ -83726,10 +83726,10 @@
         </is>
       </c>
       <c r="B597">
-        <v>1.625869522081584</v>
+        <v>1.625866774825172</v>
       </c>
       <c r="C597">
-        <v>0.6375475136093861</v>
+        <v>0.6375474200128176</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -83737,10 +83737,10 @@
         </is>
       </c>
       <c r="E597">
-        <v>0.7538874099678528</v>
+        <v>0.7538852421464146</v>
       </c>
       <c r="F597">
-        <v>3.506427707748191</v>
+        <v>3.506425940842353</v>
       </c>
       <c r="G597" t="inlineStr">
         <is>
@@ -83778,10 +83778,10 @@
         </is>
       </c>
       <c r="B598">
-        <v>1.908019835156834</v>
+        <v>1.90801663096774</v>
       </c>
       <c r="C598">
-        <v>0.6906550541537662</v>
+        <v>0.6906548950521657</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -83789,10 +83789,10 @@
         </is>
       </c>
       <c r="E598">
-        <v>0.9385758955037363</v>
+        <v>0.938573354492961</v>
       </c>
       <c r="F598">
-        <v>3.878790952113705</v>
+        <v>3.878788425669916</v>
       </c>
       <c r="G598" t="inlineStr">
         <is>
@@ -83830,10 +83830,10 @@
         </is>
       </c>
       <c r="B599">
-        <v>1.271700716514305</v>
+        <v>1.271704217732224</v>
       </c>
       <c r="C599">
-        <v>0.5638485032212387</v>
+        <v>0.5638493292513272</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -83841,10 +83841,10 @@
         </is>
       </c>
       <c r="E599">
-        <v>0.5333078109125666</v>
+        <v>0.5333098762173869</v>
       </c>
       <c r="F599">
-        <v>3.032437701626185</v>
+        <v>3.032442655794201</v>
       </c>
       <c r="G599" t="inlineStr">
         <is>
@@ -83882,10 +83882,10 @@
         </is>
       </c>
       <c r="B600">
-        <v>1.882563733419157</v>
+        <v>1.882562697106324</v>
       </c>
       <c r="C600">
-        <v>0.6860327057945818</v>
+        <v>0.6860325793222845</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -83893,10 +83893,10 @@
         </is>
       </c>
       <c r="E600">
-        <v>0.9216369373891615</v>
+        <v>0.9216361890374286</v>
       </c>
       <c r="F600">
-        <v>3.845382131085962</v>
+        <v>3.845381019855234</v>
       </c>
       <c r="G600" t="inlineStr">
         <is>
@@ -83934,10 +83934,10 @@
         </is>
       </c>
       <c r="B601">
-        <v>1.54504755656838</v>
+        <v>1.545047631090591</v>
       </c>
       <c r="C601">
-        <v>0.6214996679241245</v>
+        <v>0.6214997385606005</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -83945,10 +83945,10 @@
         </is>
       </c>
       <c r="E601">
-        <v>0.7023339598094299</v>
+        <v>0.702333957459591</v>
       </c>
       <c r="F601">
-        <v>3.398912894238593</v>
+        <v>3.398913233489771</v>
       </c>
       <c r="G601" t="inlineStr">
         <is>
@@ -83986,10 +83986,10 @@
         </is>
       </c>
       <c r="B602">
-        <v>1.623169211046457</v>
+        <v>1.623168284064862</v>
       </c>
       <c r="C602">
-        <v>0.520123221866157</v>
+        <v>0.5201231200878845</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -83997,10 +83997,10 @@
         </is>
       </c>
       <c r="E602">
-        <v>0.8661786179370543</v>
+        <v>0.8661779190439842</v>
       </c>
       <c r="F602">
-        <v>3.041726305786784</v>
+        <v>3.041725285841973</v>
       </c>
       <c r="G602" t="inlineStr">
         <is>
